--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
@@ -3777,13 +3777,13 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
         <v>3</v>
-      </c>
-      <c r="C8" t="n">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3867,127 +3867,127 @@
         <v>2</v>
       </c>
       <c r="AF8" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>115</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>53.33</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BK8" t="n">
         <v>0.5</v>
       </c>
-      <c r="AG8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>118.5</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL8" t="n">
+      <c r="BL8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BQ8" t="n">
         <v>5.5</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>66.5</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>13</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>7.33</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BT8" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -3999,7 +3999,7 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
         <v>2.05</v>
@@ -4008,73 +4008,73 @@
         <v>1.99</v>
       </c>
       <c r="CA8" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.99</v>
+        <v>3.1</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.54</v>
+        <v>4.35</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="CX8" t="n">
         <v>1.71</v>
@@ -4089,55 +4089,55 @@
         <v>1.65</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.39</v>
+        <v>2.34</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.53</v>
+        <v>4.39</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="DH8" t="n">
-        <v>118.67</v>
+        <v>116</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.67</v>
+        <v>4.5</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DM8" t="n">
-        <v>62.33</v>
+        <v>53.5</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DO8" t="n">
-        <v>3.33</v>
+        <v>2.75</v>
       </c>
       <c r="DP8" t="n">
-        <v>10</v>
+        <v>7.25</v>
       </c>
       <c r="DQ8" t="n">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="DR8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4149,28 +4149,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.67</v>
+        <v>52.25</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>13</v>
+        <v>11.25</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.33</v>
+        <v>7.25</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.67</v>
+        <v>4</v>
       </c>
       <c r="EA8" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="EC8" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="9">
@@ -6973,91 +6973,91 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F16" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="G16" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" t="n">
+        <v>116</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>59</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2</v>
+      </c>
+      <c r="R16" t="n">
         <v>4</v>
       </c>
-      <c r="H16" t="n">
-        <v>128</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4</v>
-      </c>
-      <c r="K16" t="n">
-        <v>9</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>90</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>52</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA16" t="n">
         <v>5</v>
       </c>
-      <c r="P16" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>5</v>
-      </c>
-      <c r="R16" t="n">
-        <v>9</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>58</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>8</v>
-      </c>
       <c r="AB16" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.82</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
@@ -7144,49 +7144,49 @@
         <v>3</v>
       </c>
       <c r="BG16" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.67</v>
+        <v>6.75</v>
       </c>
       <c r="BI16" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="BJ16" t="n">
         <v>1</v>
       </c>
       <c r="BK16" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BM16" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="BN16" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BO16" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="BP16" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.67</v>
+        <v>4.25</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BT16" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BU16" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BV16" t="n">
         <v>0</v>
@@ -7195,19 +7195,19 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.5</v>
+        <v>1.87</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.62</v>
+        <v>3.54</v>
       </c>
       <c r="CC16" t="n">
         <v>3.28</v>
@@ -7219,7 +7219,7 @@
         <v>1.42</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="CG16" t="n">
         <v>2.56</v>
@@ -7228,49 +7228,49 @@
         <v>1.33</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS16" t="n">
-        <v>3</v>
+        <v>3.07</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CW16" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="CX16" t="n">
         <v>1.56</v>
@@ -7285,88 +7285,88 @@
         <v>1.82</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.82</v>
+        <v>3.86</v>
       </c>
       <c r="DE16" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DF16" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="DH16" t="n">
-        <v>107.67</v>
+        <v>106.75</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.33</v>
+        <v>4</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.67</v>
+        <v>3.5</v>
       </c>
       <c r="DL16" t="n">
         <v>0</v>
       </c>
       <c r="DM16" t="n">
-        <v>50.33</v>
+        <v>44.75</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="DP16" t="n">
-        <v>10</v>
+        <v>7.25</v>
       </c>
       <c r="DQ16" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="DR16" t="n">
-        <v>3.67</v>
+        <v>2.5</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>52.33</v>
+        <v>50.75</v>
       </c>
       <c r="DW16" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.33</v>
+        <v>8.75</v>
       </c>
       <c r="DY16" t="n">
-        <v>5.33</v>
+        <v>4.5</v>
       </c>
       <c r="DZ16" t="n">
-        <v>5</v>
+        <v>4.25</v>
       </c>
       <c r="EA16" t="n">
-        <v>22.67</v>
+        <v>16.75</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.37</v>
+        <v>1.18</v>
       </c>
       <c r="EC16" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="17">

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
@@ -1379,61 +1379,61 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" t="n">
         <v>3</v>
       </c>
-      <c r="C2" t="n">
-        <v>2</v>
-      </c>
       <c r="D2" t="n">
         <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="H2" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>61</v>
+        <v>54.33</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>16.5</v>
+        <v>10.67</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="R2" t="n">
-        <v>9</v>
+        <v>5.67</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>60.5</v>
+        <v>60</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.5</v>
+        <v>9.67</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.5</v>
+        <v>5.33</v>
       </c>
       <c r="AB2" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>15</v>
+        <v>9.67</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="AE2" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,49 +1550,49 @@
         <v>1</v>
       </c>
       <c r="BG2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.67</v>
+        <v>9</v>
       </c>
       <c r="BI2" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BL2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="BM2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="BO2" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="BP2" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="BR2" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BS2" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BT2" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BU2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BV2" t="n">
         <v>0</v>
@@ -1601,16 +1601,16 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CB2" t="n">
         <v>3.11</v>
@@ -1625,54 +1625,54 @@
         <v>1.52</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.44</v>
+        <v>3.39</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CJ2" t="n">
         <v>2.01</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.44</v>
+        <v>2.28</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.58</v>
+        <v>4.51</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CS2" t="inlineStr"/>
       <c r="CT2" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="CU2" t="inlineStr"/>
       <c r="CV2" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="CX2" t="n">
         <v>1.62</v>
@@ -1687,56 +1687,56 @@
         <v>1.74</v>
       </c>
       <c r="DB2" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>96.25</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>5</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>56.75</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DO2" t="n">
         <v>1.5</v>
       </c>
-      <c r="DC2" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>3</v>
-      </c>
-      <c r="DG2" t="n">
+      <c r="DP2" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DR2" t="n">
         <v>4</v>
       </c>
-      <c r="DH2" t="n">
-        <v>98</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>62</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>5.67</v>
-      </c>
       <c r="DS2" t="n">
         <v>0</v>
       </c>
@@ -1747,28 +1747,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>59.33</v>
+        <v>59.25</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>9.67</v>
+        <v>9.25</v>
       </c>
       <c r="DY2" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="EA2" t="n">
-        <v>9.67</v>
+        <v>7</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="EC2" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="3">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1874,46 +1874,46 @@
         <v>2</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>104</v>
+        <v>118.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>52</v>
+        <v>39.5</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AR3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AT3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1925,70 +1925,70 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>0.79</v>
       </c>
       <c r="BF3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.67</v>
+        <v>7.75</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BL3" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="BO3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BR3" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BS3" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BT3" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
         <v>3.35</v>
@@ -2009,55 +2009,55 @@
         <v>4.11</v>
       </c>
       <c r="CA3" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="CB3" t="n">
         <v>3.13</v>
       </c>
-      <c r="CB3" t="n">
-        <v>3.19</v>
-      </c>
       <c r="CC3" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.19</v>
+        <v>2.74</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.02</v>
+        <v>1.16</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.26</v>
+        <v>2.56</v>
       </c>
       <c r="CG3" t="n">
-        <v>1.51</v>
+        <v>1.68</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="CL3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CM3" t="n">
         <v>1.59</v>
       </c>
-      <c r="CM3" t="n">
-        <v>1.45</v>
-      </c>
       <c r="CN3" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="CO3" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.33</v>
+        <v>2.41</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="CR3" t="n">
         <v>1.54</v>
@@ -2068,73 +2068,73 @@
       </c>
       <c r="CU3" t="inlineStr"/>
       <c r="CV3" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="CY3" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="CZ3" t="n">
+        <v>2</v>
+      </c>
+      <c r="DA3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DB3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="DC3" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="DD3" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="DE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF3" t="n">
         <v>2.25</v>
       </c>
-      <c r="DA3" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="DB3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="DC3" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="DD3" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="DE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF3" t="n">
-        <v>2.33</v>
-      </c>
       <c r="DG3" t="n">
         <v>2</v>
       </c>
       <c r="DH3" t="n">
-        <v>88.33</v>
+        <v>99.5</v>
       </c>
       <c r="DI3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="DK3" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>41</v>
+        <v>37.5</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="DP3" t="n">
-        <v>7.33</v>
+        <v>5.25</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.33</v>
+        <v>4.5</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2146,28 +2146,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>41.33</v>
+        <v>46.5</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DX3" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="DY3" t="n">
         <v>3</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="EA3" t="n">
-        <v>14.67</v>
+        <v>10.75</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.9</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
@@ -2189,49 +2189,49 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P4" t="n">
-        <v>14</v>
+        <v>6.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="R4" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2243,25 +2243,25 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA4" t="n">
         <v>5</v>
       </c>
       <c r="AB4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.04</v>
+        <v>0.88</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -2348,46 +2348,46 @@
         <v>0.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="BH4" t="n">
-        <v>7.67</v>
+        <v>8</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="BJ4" t="n">
         <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BM4" t="n">
         <v>1</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2.67</v>
+        <v>3.25</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BT4" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BU4" t="n">
         <v>0</v>
@@ -2399,19 +2399,19 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BY4" t="n">
-        <v>6</v>
+        <v>4.42</v>
       </c>
       <c r="BZ4" t="n">
-        <v>7.07</v>
+        <v>4.9</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.56</v>
+        <v>3.42</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.51</v>
+        <v>3.34</v>
       </c>
       <c r="CC4" t="n">
         <v>3.12</v>
@@ -2423,58 +2423,58 @@
         <v>1.49</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.06</v>
+        <v>3.17</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.51</v>
+        <v>2.41</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="CI4" t="n">
         <v>1.65</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CK4" t="n">
         <v>1.64</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="CN4" t="n">
         <v>1.7</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.27</v>
+        <v>4.58</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="CS4" t="n">
         <v>2.91</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="CU4" t="n">
         <v>1.4</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="CX4" t="n">
         <v>1.67</v>
@@ -2489,88 +2489,88 @@
         <v>1.7</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.37</v>
+        <v>2.46</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.47</v>
+        <v>4.7</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="DH4" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="DK4" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="DL4" t="n">
         <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.67</v>
+        <v>37.75</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DO4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="DP4" t="n">
-        <v>7.67</v>
+        <v>5.5</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0.33</v>
+        <v>-0.5</v>
       </c>
       <c r="DR4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>35.67</v>
+        <v>37.75</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.67</v>
+        <v>9.75</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.33</v>
+        <v>6</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="EA4" t="n">
-        <v>14.67</v>
+        <v>10.75</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="EC4" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="5">
@@ -2580,61 +2580,61 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
         <v>3</v>
       </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="H5" t="n">
-        <v>92.5</v>
+        <v>96.67</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5</v>
+        <v>3.67</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="M5" t="n">
-        <v>58.5</v>
+        <v>48.33</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="P5" t="n">
-        <v>19.5</v>
+        <v>12.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>2.33</v>
       </c>
       <c r="R5" t="n">
-        <v>6</v>
+        <v>3.67</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2646,28 +2646,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>35.5</v>
+        <v>36.33</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.5</v>
+        <v>9.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>7</v>
+        <v>7.33</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AC5" t="n">
-        <v>33</v>
+        <v>21.67</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AE5" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2754,43 +2754,43 @@
         <v>2</v>
       </c>
       <c r="BH5" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BI5" t="n">
         <v>2</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BL5" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="BP5" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BT5" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BU5" t="n">
         <v>0</v>
@@ -2802,19 +2802,19 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.38</v>
+        <v>3.15</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="CA5" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="CC5" t="n">
         <v>3.5</v>
@@ -2823,43 +2823,43 @@
         <v>3.87</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.56</v>
+        <v>3.53</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CO5" t="n">
         <v>1.55</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CQ5" t="n">
-        <v>5.08</v>
+        <v>5.06</v>
       </c>
       <c r="CR5" t="n">
         <v>1.58</v>
@@ -2870,73 +2870,73 @@
       </c>
       <c r="CU5" t="inlineStr"/>
       <c r="CV5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CW5" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CY5" t="n">
         <v>2.28</v>
       </c>
-      <c r="CX5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CY5" t="n">
-        <v>2.06</v>
-      </c>
       <c r="CZ5" t="n">
-        <v>2.17</v>
+        <v>1.96</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="DD5" t="n">
         <v>5.44</v>
       </c>
       <c r="DE5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DH5" t="n">
-        <v>96.33</v>
+        <v>98.5</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>4.67</v>
+        <v>4</v>
       </c>
       <c r="DK5" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DL5" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DM5" t="n">
-        <v>56.33</v>
+        <v>49.25</v>
       </c>
       <c r="DN5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="DP5" t="n">
-        <v>18</v>
+        <v>13.25</v>
       </c>
       <c r="DQ5" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.67</v>
+        <v>4.75</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -2951,25 +2951,25 @@
         <v>38</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DX5" t="n">
-        <v>12</v>
+        <v>11.75</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.67</v>
+        <v>9.25</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="EA5" t="n">
-        <v>30.67</v>
+        <v>22.75</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="EC5" t="n">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="6">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
@@ -3390,46 +3390,46 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M7" t="n">
-        <v>59</v>
+        <v>70.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="P7" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="R7" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>2</v>
@@ -3444,28 +3444,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>62</v>
+        <v>61.5</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AB7" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AE7" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3549,49 +3549,49 @@
         <v>1</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="BH7" t="n">
-        <v>6</v>
+        <v>7.25</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BN7" t="n">
         <v>2</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.67</v>
+        <v>4.5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BT7" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3600,19 +3600,19 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.52</v>
+        <v>2.36</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="CB7" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="CC7" t="n">
         <v>2.44</v>
@@ -3621,153 +3621,157 @@
         <v>2.58</v>
       </c>
       <c r="CE7" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="CR7" t="n">
         <v>1.54</v>
       </c>
-      <c r="CF7" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="CH7" t="n">
+      <c r="CS7" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>5</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>5</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>60.25</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>8</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>17</v>
+      </c>
+      <c r="EB7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="EC7" t="n">
         <v>1.25</v>
-      </c>
-      <c r="CI7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CP7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="CQ7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="CS7" t="inlineStr"/>
-      <c r="CT7" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="CU7" t="inlineStr"/>
-      <c r="CV7" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CW7" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="CX7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CY7" t="n">
-        <v>2</v>
-      </c>
-      <c r="CZ7" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="DA7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="DB7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="DC7" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="DD7" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="DE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DG7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DH7" t="n">
-        <v>94.33</v>
-      </c>
-      <c r="DI7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ7" t="n">
-        <v>2</v>
-      </c>
-      <c r="DK7" t="n">
-        <v>2</v>
-      </c>
-      <c r="DL7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DM7" t="n">
-        <v>45.67</v>
-      </c>
-      <c r="DN7" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="DO7" t="n">
-        <v>1</v>
-      </c>
-      <c r="DP7" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="DQ7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DR7" t="n">
-        <v>7</v>
-      </c>
-      <c r="DS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV7" t="n">
-        <v>60</v>
-      </c>
-      <c r="DW7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DX7" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="DY7" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="DZ7" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="EA7" t="n">
-        <v>23</v>
-      </c>
-      <c r="EB7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="EC7" t="n">
-        <v>1.33</v>
       </c>
     </row>
     <row r="8">
@@ -3870,7 +3874,7 @@
         <v>0.33</v>
       </c>
       <c r="AG8" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="n">
         <v>1.67</v>
@@ -3882,7 +3886,7 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AL8" t="n">
         <v>4</v>
@@ -3945,7 +3949,7 @@
         <v>1.26</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="BG8" t="n">
         <v>1.75</v>
@@ -4011,13 +4015,13 @@
         <v>3</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CC8" t="n">
         <v>2.75</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.1</v>
+        <v>2.83</v>
       </c>
       <c r="CE8" t="n">
         <v>1.46</v>
@@ -4059,16 +4063,16 @@
         <v>4.35</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CV8" t="n">
         <v>1.81</v>
@@ -4077,16 +4081,16 @@
         <v>2.01</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.07</v>
+        <v>2.12</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="DB8" t="n">
         <v>1.42</v>
@@ -4095,13 +4099,13 @@
         <v>2.34</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.39</v>
+        <v>4.4</v>
       </c>
       <c r="DE8" t="n">
         <v>0.25</v>
       </c>
       <c r="DF8" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DG8" t="n">
         <v>1.75</v>
@@ -4113,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DK8" t="n">
         <v>4.5</v>
@@ -4170,7 +4174,7 @@
         <v>1.38</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6179,13 +6183,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
         <v>2</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -6272,49 +6276,49 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>88.5</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
         <v>3</v>
       </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>86</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>4</v>
-      </c>
       <c r="AL14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM14" t="n">
         <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>35</v>
+        <v>47.5</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP14" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AT14" t="n">
         <v>2</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6326,73 +6330,73 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>42</v>
+        <v>40.5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="BF14" t="n">
         <v>2</v>
       </c>
       <c r="BG14" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>7.67</v>
+        <v>8.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BK14" t="n">
         <v>1</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.67</v>
+        <v>5.25</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BT14" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6401,7 +6405,7 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BY14" t="n">
         <v>4.24</v>
@@ -6410,132 +6414,136 @@
         <v>4.36</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.45</v>
+        <v>3.36</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.55</v>
+        <v>3.38</v>
       </c>
       <c r="CC14" t="n">
-        <v>2.75</v>
+        <v>3.18</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.12</v>
+        <v>3.58</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="CH14" t="n">
         <v>1.3</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.99</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CN14" t="n">
         <v>1.68</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.93</v>
+        <v>3.94</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CS14" t="inlineStr"/>
+        <v>1.52</v>
+      </c>
+      <c r="CS14" t="n">
+        <v>3.36</v>
+      </c>
       <c r="CT14" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="CU14" t="inlineStr"/>
+        <v>2.53</v>
+      </c>
+      <c r="CU14" t="n">
+        <v>1.31</v>
+      </c>
       <c r="CV14" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY14" t="n">
         <v>2.08</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DB14" t="n">
         <v>1.4</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="DD14" t="n">
-        <v>4.2</v>
+        <v>4.22</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DO14" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="DQ14" t="n">
         <v>3</v>
       </c>
-      <c r="DG14" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="DH14" t="n">
-        <v>94.67</v>
-      </c>
-      <c r="DI14" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DJ14" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="DK14" t="n">
-        <v>3</v>
-      </c>
-      <c r="DL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM14" t="n">
-        <v>39</v>
-      </c>
-      <c r="DN14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DO14" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="DP14" t="n">
-        <v>14.33</v>
-      </c>
-      <c r="DQ14" t="n">
-        <v>4.33</v>
-      </c>
       <c r="DR14" t="n">
-        <v>12.33</v>
+        <v>9</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6547,28 +6555,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>45</v>
+        <v>43.5</v>
       </c>
       <c r="DW14" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DX14" t="n">
-        <v>6.33</v>
+        <v>5.75</v>
       </c>
       <c r="DY14" t="n">
-        <v>4.67</v>
+        <v>3.75</v>
       </c>
       <c r="DZ14" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="EA14" t="n">
-        <v>21.67</v>
+        <v>16</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.83</v>
       </c>
       <c r="EC14" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="15">
@@ -6578,13 +6586,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6671,88 +6679,88 @@
         <v>1</v>
       </c>
       <c r="AG15" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="AH15" t="n">
         <v>3</v>
       </c>
       <c r="AI15" t="n">
-        <v>110</v>
+        <v>96.5</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AL15" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AM15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AN15" t="n">
-        <v>77</v>
+        <v>57.5</v>
       </c>
       <c r="AO15" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BF15" t="n">
         <v>4</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>34</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>6</v>
       </c>
       <c r="BG15" t="n">
         <v>4</v>
       </c>
       <c r="BH15" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BI15" t="n">
         <v>4</v>
@@ -6764,10 +6772,10 @@
         <v>1</v>
       </c>
       <c r="BL15" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="BN15" t="n">
         <v>2</v>
@@ -6776,10 +6784,10 @@
         <v>2</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.67</v>
+        <v>4</v>
       </c>
       <c r="BQ15" t="n">
-        <v>8.33</v>
+        <v>7.5</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
@@ -6788,19 +6796,19 @@
         <v>100</v>
       </c>
       <c r="BT15" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BU15" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BV15" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BW15" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BX15" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BY15" t="n">
         <v>2.3</v>
@@ -6809,65 +6817,69 @@
         <v>2.49</v>
       </c>
       <c r="CA15" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="CB15" t="n">
         <v>3.28</v>
       </c>
-      <c r="CB15" t="n">
-        <v>3.34</v>
-      </c>
       <c r="CC15" t="n">
-        <v>6.67</v>
+        <v>4.58</v>
       </c>
       <c r="CD15" t="n">
-        <v>6.87</v>
+        <v>4.89</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.03</v>
+        <v>1.15</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="CG15" t="n">
-        <v>1.59</v>
+        <v>1.8</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.82</v>
+        <v>0.93</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.35</v>
+        <v>1.51</v>
       </c>
       <c r="CK15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CO15" t="n">
         <v>1.09</v>
       </c>
-      <c r="CL15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="CM15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="CN15" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="CO15" t="n">
-        <v>0.98</v>
-      </c>
       <c r="CP15" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="CR15" t="inlineStr"/>
+        <v>3.46</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>1.51</v>
+      </c>
       <c r="CS15" t="inlineStr"/>
-      <c r="CT15" t="inlineStr"/>
+      <c r="CT15" t="n">
+        <v>2.54</v>
+      </c>
       <c r="CU15" t="inlineStr"/>
       <c r="CV15" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CX15" t="n">
         <v>1.65</v>
@@ -6882,55 +6894,55 @@
         <v>1.7</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="DD15" t="n">
-        <v>5.06</v>
+        <v>4.93</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DF15" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="DH15" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="DK15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="DL15" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DM15" t="n">
-        <v>67.33</v>
+        <v>60</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="DO15" t="n">
-        <v>3.67</v>
+        <v>2.75</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.67</v>
+        <v>9.25</v>
       </c>
       <c r="DQ15" t="n">
-        <v>2.33</v>
+        <v>1.5</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.33</v>
+        <v>5.25</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6942,28 +6954,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>44.33</v>
+        <v>43.5</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>16</v>
+        <v>13.75</v>
       </c>
       <c r="DY15" t="n">
-        <v>10</v>
+        <v>8.25</v>
       </c>
       <c r="DZ15" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="EA15" t="n">
-        <v>24</v>
+        <v>17.75</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -7201,13 +7213,13 @@
         <v>1.88</v>
       </c>
       <c r="BZ16" t="n">
-        <v>1.87</v>
+        <v>2.21</v>
       </c>
       <c r="CA16" t="n">
         <v>3.34</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CC16" t="n">
         <v>3.28</v>
@@ -7255,16 +7267,16 @@
         <v>3.72</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CV16" t="n">
         <v>1.83</v>
@@ -7273,16 +7285,16 @@
         <v>1.98</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="DB16" t="n">
         <v>1.36</v>
@@ -7291,7 +7303,7 @@
         <v>2.14</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="DE16" t="n">
         <v>0.25</v>
@@ -7376,13 +7388,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C17" t="n">
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7466,31 +7478,31 @@
         <v>1</v>
       </c>
       <c r="AF17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AM17" t="n">
         <v>1</v>
       </c>
       <c r="AN17" t="n">
-        <v>46</v>
+        <v>37.5</v>
       </c>
       <c r="AO17" t="n">
         <v>1</v>
@@ -7499,97 +7511,97 @@
         <v>1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12</v>
+        <v>5.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS17" t="n">
-        <v>14</v>
+        <v>6.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AU17" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>45</v>
+        <v>50.5</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC17" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>20</v>
+        <v>9.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="BF17" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.33</v>
+        <v>10</v>
       </c>
       <c r="BI17" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BN17" t="n">
         <v>1</v>
       </c>
       <c r="BO17" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BR17" t="n">
         <v>100</v>
       </c>
       <c r="BS17" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BT17" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BU17" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7598,7 +7610,7 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
         <v>2.86</v>
@@ -7607,66 +7619,66 @@
         <v>3.24</v>
       </c>
       <c r="CA17" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.03</v>
+        <v>2.97</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.07</v>
+        <v>2.84</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.36</v>
+        <v>3.22</v>
       </c>
       <c r="CE17" t="n">
         <v>1.51</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.33</v>
+        <v>3.37</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="CK17" t="n">
         <v>1.63</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="CN17" t="n">
         <v>1.7</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.66</v>
+        <v>4.87</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="CS17" t="inlineStr"/>
       <c r="CT17" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="CU17" t="inlineStr"/>
       <c r="CV17" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CW17" t="n">
         <v>2.03</v>
@@ -7684,88 +7696,88 @@
         <v>1.71</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.46</v>
+        <v>2.53</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.71</v>
+        <v>4.89</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="DG17" t="n">
-        <v>4.67</v>
+        <v>4.25</v>
       </c>
       <c r="DH17" t="n">
-        <v>97.67</v>
+        <v>97.5</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DK17" t="n">
-        <v>6.33</v>
+        <v>5.75</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DM17" t="n">
-        <v>68.67</v>
+        <v>58.75</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="DP17" t="n">
-        <v>6.67</v>
+        <v>4.75</v>
       </c>
       <c r="DQ17" t="n">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.67</v>
+        <v>5.5</v>
       </c>
       <c r="DS17" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DT17" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>49</v>
+        <v>50.75</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>10.67</v>
+        <v>10.25</v>
       </c>
       <c r="DY17" t="n">
-        <v>5.67</v>
+        <v>5.75</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="EA17" t="n">
-        <v>17.33</v>
+        <v>12.75</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1421,13 +1421,13 @@
         <v>1.33</v>
       </c>
       <c r="P2" t="n">
-        <v>10.67</v>
+        <v>14.67</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.67</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>5.67</v>
+        <v>8.33</v>
       </c>
       <c r="S2" t="n">
         <v>1.67</v>
@@ -1445,25 +1445,25 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>60</v>
+        <v>61.67</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.67</v>
+        <v>10</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.33</v>
+        <v>5.67</v>
       </c>
       <c r="AB2" t="n">
         <v>4.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.67</v>
+        <v>14</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AE2" t="n">
         <v>4.33</v>
@@ -1729,13 +1729,13 @@
         <v>1.5</v>
       </c>
       <c r="DP2" t="n">
-        <v>7.75</v>
+        <v>10.75</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="DR2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
@@ -1747,25 +1747,25 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>59.25</v>
+        <v>60.5</v>
       </c>
       <c r="DW2" t="n">
         <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>9.25</v>
+        <v>9.5</v>
       </c>
       <c r="DY2" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="DZ2" t="n">
         <v>4</v>
       </c>
       <c r="EA2" t="n">
-        <v>7</v>
+        <v>10.25</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="EC2" t="n">
         <v>3.5</v>
@@ -2210,7 +2210,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>22</v>
+        <v>35.5</v>
       </c>
       <c r="N4" t="n">
         <v>0.5</v>
@@ -2243,7 +2243,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>37</v>
+        <v>35.5</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
@@ -2261,7 +2261,7 @@
         <v>10</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.88</v>
+        <v>0.98</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>37.75</v>
+        <v>44.5</v>
       </c>
       <c r="DN4" t="n">
         <v>0.25</v>
@@ -2549,7 +2549,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>37.75</v>
+        <v>37</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
@@ -2567,7 +2567,7 @@
         <v>10.75</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="EC4" t="n">
         <v>1.25</v>
@@ -2979,13 +2979,13 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
         <v>3</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3072,124 +3072,124 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>83</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
         <v>3</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AL6" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>56.33</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>43.67</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="BF6" t="n">
         <v>3</v>
       </c>
-      <c r="AI6" t="n">
-        <v>91</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4</v>
-      </c>
       <c r="BG6" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BH6" t="n">
         <v>11</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BK6" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BM6" t="n">
         <v>0</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BO6" t="n">
         <v>1</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.67</v>
+        <v>6</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="BT6" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BU6" t="n">
         <v>0</v>
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BY6" t="n">
         <v>2.4</v>
@@ -3210,108 +3210,112 @@
         <v>2.49</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.02</v>
+        <v>3.12</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="CC6" t="n">
-        <v>2.95</v>
+        <v>3.44</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.42</v>
+        <v>3.77</v>
       </c>
       <c r="CE6" t="n">
         <v>1.5</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="CK6" t="n">
         <v>1.64</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.17</v>
+        <v>2.24</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.58</v>
+        <v>4.56</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CS6" t="inlineStr"/>
+        <v>1.48</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>3.27</v>
+      </c>
       <c r="CT6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="CU6" t="inlineStr"/>
+        <v>2.61</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>1.33</v>
+      </c>
       <c r="CV6" t="n">
         <v>1.77</v>
       </c>
       <c r="CW6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CY6" t="n">
         <v>2.05</v>
       </c>
-      <c r="CX6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CY6" t="n">
-        <v>2.09</v>
-      </c>
       <c r="CZ6" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>84.25</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ6" t="n">
         <v>3</v>
-      </c>
-      <c r="DG6" t="n">
-        <v>3</v>
-      </c>
-      <c r="DH6" t="n">
-        <v>90</v>
-      </c>
-      <c r="DI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ6" t="n">
-        <v>3.67</v>
       </c>
       <c r="DK6" t="n">
         <v>6</v>
@@ -3320,55 +3324,55 @@
         <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>59</v>
+        <v>56.25</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="DO6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="EB6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="EC6" t="n">
         <v>3</v>
-      </c>
-      <c r="DP6" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="DQ6" t="n">
-        <v>1</v>
-      </c>
-      <c r="DR6" t="n">
-        <v>5</v>
-      </c>
-      <c r="DS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV6" t="n">
-        <v>47.33</v>
-      </c>
-      <c r="DW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX6" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="DY6" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="DZ6" t="n">
-        <v>2</v>
-      </c>
-      <c r="EA6" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="EB6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="EC6" t="n">
-        <v>3.67</v>
       </c>
     </row>
     <row r="7">
@@ -4184,10 +4188,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
@@ -4196,13 +4200,13 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -4211,64 +4215,64 @@
         <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>49</v>
+        <v>45.5</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P9" t="n">
-        <v>16</v>
+        <v>7.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="T9" t="n">
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA9" t="n">
         <v>11</v>
       </c>
       <c r="AB9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC9" t="n">
-        <v>18</v>
+        <v>8.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.98</v>
+        <v>1.82</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -4355,37 +4359,37 @@
         <v>2.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>12</v>
+        <v>10.75</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="BK9" t="n">
         <v>1</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="BP9" t="n">
-        <v>6.33</v>
+        <v>5.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.67</v>
+        <v>5.25</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
@@ -4394,31 +4398,31 @@
         <v>100</v>
       </c>
       <c r="BT9" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BU9" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BV9" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BW9" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BX9" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.41</v>
+        <v>2.01</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.39</v>
+        <v>3.47</v>
       </c>
       <c r="CC9" t="n">
         <v>5.68</v>
@@ -4427,53 +4431,61 @@
         <v>5.15</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.22</v>
+        <v>3.25</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.97</v>
+        <v>2.11</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="CR9" t="inlineStr"/>
-      <c r="CS9" t="inlineStr"/>
-      <c r="CT9" t="inlineStr"/>
-      <c r="CU9" t="inlineStr"/>
+        <v>4.08</v>
+      </c>
+      <c r="CR9" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CS9" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="CT9" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>1.32</v>
+      </c>
       <c r="CV9" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="CX9" t="n">
         <v>1.77</v>
@@ -4491,85 +4503,85 @@
         <v>1.41</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DG9" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="DH9" t="n">
-        <v>96.67</v>
+        <v>101</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="DK9" t="n">
-        <v>7.33</v>
+        <v>6.5</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.33</v>
+        <v>37</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DO9" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="DP9" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>10</v>
+        <v>7.25</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>50.33</v>
+        <v>54.25</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.67</v>
+        <v>14.25</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.33</v>
+        <v>9</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.33</v>
+        <v>5.25</v>
       </c>
       <c r="EA9" t="n">
-        <v>22.33</v>
+        <v>16.5</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="10">
@@ -4579,13 +4591,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4672,19 +4684,19 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="n">
         <v>2</v>
       </c>
       <c r="AI10" t="n">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AL10" t="n">
         <v>3</v>
@@ -4693,28 +4705,28 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>55</v>
+        <v>35.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP10" t="n">
         <v>1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AR10" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>16</v>
+        <v>7.5</v>
       </c>
       <c r="AT10" t="n">
         <v>2</v>
       </c>
       <c r="AU10" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AV10" t="n">
         <v>0</v>
@@ -4726,73 +4738,73 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB10" t="n">
         <v>5</v>
       </c>
       <c r="BC10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BD10" t="n">
-        <v>24</v>
+        <v>11.5</v>
       </c>
       <c r="BE10" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO10" t="n">
         <v>1.25</v>
       </c>
-      <c r="BF10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>0.67</v>
-      </c>
       <c r="BP10" t="n">
-        <v>6.67</v>
+        <v>5.75</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="BT10" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="BU10" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4801,7 +4813,7 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="BY10" t="n">
         <v>2.89</v>
@@ -4810,73 +4822,73 @@
         <v>3.28</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.29</v>
+        <v>3.34</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.44</v>
+        <v>3.51</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.5</v>
+        <v>5.92</v>
       </c>
       <c r="CD10" t="n">
-        <v>7.12</v>
+        <v>6.63</v>
       </c>
       <c r="CE10" t="n">
         <v>1.45</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CP10" t="n">
         <v>2.23</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="CR10" t="n">
         <v>1.46</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.9</v>
+        <v>3.14</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="CX10" t="n">
         <v>1.56</v>
@@ -4894,53 +4906,53 @@
         <v>1.41</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DD10" t="n">
-        <v>4.3</v>
+        <v>4.28</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="DG10" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="DH10" t="n">
-        <v>105.33</v>
+        <v>103.25</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="DK10" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>1</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DR10" t="n">
         <v>6</v>
       </c>
-      <c r="DL10" t="n">
-        <v>1</v>
-      </c>
-      <c r="DM10" t="n">
-        <v>67.33</v>
-      </c>
-      <c r="DN10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="DO10" t="n">
-        <v>3</v>
-      </c>
-      <c r="DP10" t="n">
-        <v>9</v>
-      </c>
-      <c r="DQ10" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="DR10" t="n">
-        <v>8.33</v>
-      </c>
       <c r="DS10" t="n">
         <v>0</v>
       </c>
@@ -4951,28 +4963,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>54.33</v>
+        <v>49.25</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>12</v>
+        <v>10.75</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="DZ10" t="n">
-        <v>6.33</v>
+        <v>5.25</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.67</v>
+        <v>15.25</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="EC10" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="11">
@@ -4982,40 +4994,40 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G11" t="n">
         <v>3</v>
       </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4</v>
-      </c>
       <c r="H11" t="n">
-        <v>122</v>
+        <v>103.5</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -5024,49 +5036,49 @@
         <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="Q11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>55</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA11" t="n">
         <v>6</v>
       </c>
-      <c r="R11" t="n">
-        <v>5</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>54</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>8</v>
-      </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC11" t="n">
-        <v>28</v>
+        <v>13.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -5153,37 +5165,37 @@
         <v>1.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.67</v>
+        <v>10.75</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BP11" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.67</v>
+        <v>6</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
@@ -5192,7 +5204,7 @@
         <v>100</v>
       </c>
       <c r="BT11" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
         <v>0</v>
@@ -5204,19 +5216,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.27</v>
+        <v>2.04</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.08</v>
+        <v>3.16</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="CC11" t="n">
         <v>2.1</v>
@@ -5231,22 +5243,22 @@
         <v>3.33</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="CH11" t="n">
         <v>1.27</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="CK11" t="n">
         <v>1.66</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="CM11" t="n">
         <v>2.1</v>
@@ -5255,94 +5267,94 @@
         <v>1.66</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.31</v>
+        <v>4.36</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="CU11" t="n">
         <v>1.34</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CW11" t="n">
         <v>2.04</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.55</v>
+        <v>4.44</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="DG11" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="DH11" t="n">
-        <v>108.33</v>
+        <v>102.5</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="DK11" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="DM11" t="n">
-        <v>62.33</v>
+        <v>61.5</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DO11" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="DP11" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="DQ11" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="DR11" t="n">
-        <v>8</v>
+        <v>5.75</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5354,28 +5366,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>51.67</v>
+        <v>52.75</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.67</v>
+        <v>10.75</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.67</v>
+        <v>7.5</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="EA11" t="n">
-        <v>22</v>
+        <v>16.25</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="12">
@@ -5385,94 +5397,94 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q12" t="n">
         <v>3</v>
       </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" t="n">
-        <v>7</v>
-      </c>
-      <c r="H12" t="n">
-        <v>120</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>90</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>62</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA12" t="n">
         <v>8</v>
       </c>
-      <c r="Q12" t="n">
-        <v>5</v>
-      </c>
-      <c r="R12" t="n">
-        <v>8</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>66</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>9</v>
-      </c>
       <c r="AB12" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.75</v>
+        <v>1.32</v>
       </c>
       <c r="AE12" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5556,46 +5568,46 @@
         <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="BH12" t="n">
-        <v>11.33</v>
+        <v>9.75</v>
       </c>
       <c r="BI12" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BN12" t="n">
         <v>1</v>
       </c>
       <c r="BO12" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="BP12" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.33</v>
+        <v>5.25</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BT12" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BU12" t="n">
         <v>0</v>
@@ -5607,19 +5619,19 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>66.67</v>
+        <v>50</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.48</v>
+        <v>2.06</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1.51</v>
+        <v>1.94</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.83</v>
+        <v>3.59</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.96</v>
+        <v>3.73</v>
       </c>
       <c r="CC12" t="n">
         <v>1.57</v>
@@ -5628,116 +5640,124 @@
         <v>1.59</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.44</v>
+        <v>0.71</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.87</v>
+        <v>1.48</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.97</v>
+        <v>1.36</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.47</v>
+        <v>0.67</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.64</v>
+        <v>0.96</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.52</v>
+        <v>0.82</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.75</v>
+        <v>1.17</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.74</v>
+        <v>1.07</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.59</v>
+        <v>0.86</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.42</v>
+        <v>0.68</v>
       </c>
       <c r="CP12" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CQ12" t="n">
         <v>1.9</v>
       </c>
-      <c r="CQ12" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR12" t="inlineStr"/>
-      <c r="CS12" t="inlineStr"/>
-      <c r="CT12" t="inlineStr"/>
-      <c r="CU12" t="inlineStr"/>
+      <c r="CR12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>1.29</v>
+      </c>
       <c r="CV12" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.88</v>
+        <v>1.99</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.34</v>
+        <v>2.23</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.11</v>
+        <v>3.94</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="DG12" t="n">
-        <v>4.67</v>
+        <v>3.75</v>
       </c>
       <c r="DH12" t="n">
-        <v>98.67</v>
+        <v>97.25</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="DK12" t="n">
-        <v>7.67</v>
+        <v>6.5</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DM12" t="n">
-        <v>40</v>
+        <v>40.25</v>
       </c>
       <c r="DN12" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="DO12" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="DP12" t="n">
-        <v>11.67</v>
+        <v>12.5</v>
       </c>
       <c r="DQ12" t="n">
-        <v>3.33</v>
+        <v>2.75</v>
       </c>
       <c r="DR12" t="n">
-        <v>6</v>
+        <v>7.25</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5749,28 +5769,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>63.33</v>
+        <v>62</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.67</v>
+        <v>11.5</v>
       </c>
       <c r="DY12" t="n">
         <v>7</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5.67</v>
+        <v>4.5</v>
       </c>
       <c r="EA12" t="n">
         <v>23</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.49</v>
+        <v>1.34</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="13">
@@ -5780,13 +5800,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C13" t="n">
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -5873,46 +5893,46 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>92</v>
+        <v>91.5</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AL13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AR13" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AS13" t="n">
         <v>8</v>
       </c>
       <c r="AT13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU13" t="n">
         <v>1</v>
@@ -5927,73 +5947,73 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BB13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BC13" t="n">
         <v>3</v>
       </c>
       <c r="BD13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="BF13" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.33</v>
+        <v>2.75</v>
       </c>
       <c r="BH13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.33</v>
+        <v>2.75</v>
       </c>
       <c r="BJ13" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BN13" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="BP13" t="n">
-        <v>5.67</v>
+        <v>5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BT13" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BU13" t="n">
-        <v>33.33</v>
+        <v>25</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6002,7 +6022,7 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BY13" t="n">
         <v>1.66</v>
@@ -6011,136 +6031,136 @@
         <v>1.68</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.95</v>
+        <v>3.67</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.95</v>
+        <v>3.72</v>
       </c>
       <c r="CC13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="CE13" t="n">
         <v>1.42</v>
       </c>
-      <c r="CD13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CE13" t="n">
-        <v>1.39</v>
-      </c>
       <c r="CF13" t="n">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="CH13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DB13" t="n">
         <v>1.37</v>
       </c>
-      <c r="CI13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CJ13" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="CK13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CL13" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="CM13" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="CN13" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="CO13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="CP13" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="CQ13" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="CS13" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="CT13" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="CU13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="CV13" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="CW13" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="CX13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CY13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="CZ13" t="n">
+      <c r="DC13" t="n">
         <v>2.14</v>
       </c>
-      <c r="DA13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DB13" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="DC13" t="n">
-        <v>2.04</v>
-      </c>
       <c r="DD13" t="n">
-        <v>3.57</v>
+        <v>3.87</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="DH13" t="n">
-        <v>100.67</v>
+        <v>98.25</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.67</v>
+        <v>4</v>
       </c>
       <c r="DL13" t="n">
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>15</v>
+        <v>18.25</v>
       </c>
       <c r="DN13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="DP13" t="n">
-        <v>8.33</v>
+        <v>10.5</v>
       </c>
       <c r="DQ13" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.67</v>
+        <v>7.75</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6152,28 +6172,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>56.33</v>
+        <v>52.75</v>
       </c>
       <c r="DW13" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="DX13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="DY13" t="n">
-        <v>7.67</v>
+        <v>8.25</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="EA13" t="n">
-        <v>23.33</v>
+        <v>23.75</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6709,13 +6729,13 @@
         <v>2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AR15" t="n">
-        <v>-0.5</v>
+        <v>1.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="AT15" t="n">
         <v>1</v>
@@ -6733,25 +6753,25 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>37.5</v>
+        <v>35</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="BB15" t="n">
         <v>5</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="BD15" t="n">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="BF15" t="n">
         <v>4</v>
@@ -6936,13 +6956,13 @@
         <v>2.75</v>
       </c>
       <c r="DP15" t="n">
-        <v>9.25</v>
+        <v>11.75</v>
       </c>
       <c r="DQ15" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="DR15" t="n">
-        <v>5.25</v>
+        <v>6.75</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6954,25 +6974,25 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>43.5</v>
+        <v>42.25</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>13.75</v>
+        <v>14</v>
       </c>
       <c r="DY15" t="n">
         <v>8.25</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="EA15" t="n">
-        <v>17.75</v>
+        <v>21.5</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="EC15" t="n">
         <v>3</v>
@@ -7481,7 +7501,7 @@
         <v>0.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="AH17" t="n">
         <v>2.5</v>
@@ -7493,7 +7513,7 @@
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="AL17" t="n">
         <v>3.5</v>
@@ -7502,7 +7522,7 @@
         <v>1</v>
       </c>
       <c r="AN17" t="n">
-        <v>37.5</v>
+        <v>49.5</v>
       </c>
       <c r="AO17" t="n">
         <v>1</v>
@@ -7535,7 +7555,7 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>50.5</v>
+        <v>52</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
@@ -7553,10 +7573,10 @@
         <v>9.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.93</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="BG17" t="n">
         <v>2.5</v>
@@ -7708,7 +7728,7 @@
         <v>0.25</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="DG17" t="n">
         <v>4.25</v>
@@ -7720,7 +7740,7 @@
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="DK17" t="n">
         <v>5.75</v>
@@ -7729,7 +7749,7 @@
         <v>0.5</v>
       </c>
       <c r="DM17" t="n">
-        <v>58.75</v>
+        <v>64.75</v>
       </c>
       <c r="DN17" t="n">
         <v>0.5</v>
@@ -7756,7 +7776,7 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.75</v>
+        <v>51.5</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
@@ -7774,10 +7794,10 @@
         <v>12.75</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
@@ -3102,13 +3102,13 @@
         <v>2.67</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4</v>
+        <v>8.67</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.67</v>
+        <v>6.33</v>
       </c>
       <c r="AT6" t="n">
         <v>1</v>
@@ -3126,25 +3126,25 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>43.67</v>
+        <v>44.33</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.33</v>
+        <v>6.33</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.67</v>
+        <v>2.67</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.33</v>
+        <v>12</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.97</v>
+        <v>1.16</v>
       </c>
       <c r="BF6" t="n">
         <v>3</v>
@@ -3333,13 +3333,13 @@
         <v>2.5</v>
       </c>
       <c r="DP6" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="DR6" t="n">
-        <v>3.5</v>
+        <v>6.25</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3351,25 +3351,25 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.5</v>
+        <v>47</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="DZ6" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="EA6" t="n">
-        <v>9.75</v>
+        <v>15.5</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.07</v>
+        <v>1.21</v>
       </c>
       <c r="EC6" t="n">
         <v>3</v>
@@ -4230,13 +4230,13 @@
         <v>2.5</v>
       </c>
       <c r="P9" t="n">
-        <v>7.5</v>
+        <v>12</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R9" t="n">
-        <v>3.5</v>
+        <v>9</v>
       </c>
       <c r="S9" t="n">
         <v>0.5</v>
@@ -4254,25 +4254,25 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.5</v>
+        <v>25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -4542,13 +4542,13 @@
         <v>3</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.5</v>
+        <v>14.75</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.25</v>
+        <v>10</v>
       </c>
       <c r="DS9" t="n">
         <v>0.5</v>
@@ -4560,25 +4560,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>54.25</v>
+        <v>53.75</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.25</v>
+        <v>13.75</v>
       </c>
       <c r="DY9" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="DZ9" t="n">
-        <v>5.25</v>
+        <v>4.5</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.5</v>
+        <v>24.75</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.54</v>
+        <v>1.46</v>
       </c>
       <c r="EC9" t="n">
         <v>2.25</v>
@@ -4684,7 +4684,7 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH10" t="n">
         <v>2</v>
@@ -4696,7 +4696,7 @@
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="AL10" t="n">
         <v>3</v>
@@ -4714,13 +4714,13 @@
         <v>1</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7</v>
+        <v>16.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT10" t="n">
         <v>2</v>
@@ -4738,28 +4738,28 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC10" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.98</v>
+        <v>1.11</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="BG10" t="n">
         <v>2.25</v>
@@ -4915,7 +4915,7 @@
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="DG10" t="n">
         <v>2.75</v>
@@ -4927,7 +4927,7 @@
         <v>0.5</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="DK10" t="n">
         <v>5.25</v>
@@ -4945,46 +4945,46 @@
         <v>2.5</v>
       </c>
       <c r="DP10" t="n">
-        <v>6.5</v>
+        <v>11.25</v>
       </c>
       <c r="DQ10" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="DR10" t="n">
+        <v>10</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="DY10" t="n">
         <v>6</v>
       </c>
-      <c r="DS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV10" t="n">
-        <v>49.25</v>
-      </c>
-      <c r="DW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX10" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="DY10" t="n">
+      <c r="DZ10" t="n">
         <v>5.5</v>
       </c>
-      <c r="DZ10" t="n">
-        <v>5.25</v>
-      </c>
       <c r="EA10" t="n">
-        <v>15.25</v>
+        <v>21</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="EC10" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="11">
@@ -5036,13 +5036,13 @@
         <v>3</v>
       </c>
       <c r="P11" t="n">
-        <v>4.5</v>
+        <v>11</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>6.5</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -5060,25 +5060,25 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="Y11" t="n">
         <v>0.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AB11" t="n">
         <v>3</v>
       </c>
       <c r="AC11" t="n">
-        <v>13.5</v>
+        <v>28.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -5348,13 +5348,13 @@
         <v>3.5</v>
       </c>
       <c r="DP11" t="n">
-        <v>6.5</v>
+        <v>9.75</v>
       </c>
       <c r="DQ11" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="DR11" t="n">
-        <v>5.75</v>
+        <v>8</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5366,25 +5366,25 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>52.75</v>
+        <v>52.25</v>
       </c>
       <c r="DW11" t="n">
         <v>0.25</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.75</v>
+        <v>11.5</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.5</v>
+        <v>8.25</v>
       </c>
       <c r="DZ11" t="n">
         <v>3.25</v>
       </c>
       <c r="EA11" t="n">
-        <v>16.25</v>
+        <v>23.75</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="EC11" t="n">
         <v>1.25</v>
@@ -5430,7 +5430,7 @@
         <v>0.5</v>
       </c>
       <c r="M12" t="n">
-        <v>65.5</v>
+        <v>83</v>
       </c>
       <c r="N12" t="n">
         <v>1.5</v>
@@ -5481,7 +5481,7 @@
         <v>21</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AE12" t="n">
         <v>3.5</v>
@@ -5742,7 +5742,7 @@
         <v>0.5</v>
       </c>
       <c r="DM12" t="n">
-        <v>40.25</v>
+        <v>49</v>
       </c>
       <c r="DN12" t="n">
         <v>1</v>
@@ -5787,7 +5787,7 @@
         <v>23</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="EC12" t="n">
         <v>2.75</v>
@@ -5914,7 +5914,7 @@
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>24</v>
+        <v>33.5</v>
       </c>
       <c r="AO13" t="n">
         <v>1</v>
@@ -5965,7 +5965,7 @@
         <v>24</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="BF13" t="n">
         <v>2.5</v>
@@ -6145,7 +6145,7 @@
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>18.25</v>
+        <v>23</v>
       </c>
       <c r="DN13" t="n">
         <v>0.5</v>
@@ -6190,7 +6190,7 @@
         <v>23.75</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="EC13" t="n">
         <v>2</v>

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
@@ -4188,13 +4188,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4278,52 +4278,52 @@
         <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="AI9" t="n">
-        <v>100</v>
+        <v>100.67</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AL9" t="n">
-        <v>8</v>
+        <v>7.33</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AN9" t="n">
-        <v>28.5</v>
+        <v>28.67</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="AQ9" t="n">
-        <v>17.5</v>
+        <v>11.33</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0.33</v>
       </c>
       <c r="AS9" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AT9" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AU9" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="AV9" t="n">
         <v>0</v>
@@ -4335,82 +4335,82 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>46.5</v>
+        <v>48</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>11.5</v>
+        <v>10.67</v>
       </c>
       <c r="BB9" t="n">
-        <v>7</v>
+        <v>6.67</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BD9" t="n">
-        <v>24.5</v>
+        <v>16</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.75</v>
+        <v>11.2</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BK9" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BL9" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="BO9" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="BR9" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BS9" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BT9" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BU9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BV9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BW9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BX9" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BY9" t="n">
         <v>2.2</v>
@@ -4419,55 +4419,55 @@
         <v>2.01</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.41</v>
+        <v>3.36</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.47</v>
+        <v>3.42</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.68</v>
+        <v>4.69</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.15</v>
+        <v>4.29</v>
       </c>
       <c r="CE9" t="n">
         <v>1.45</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.25</v>
+        <v>3.27</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CJ9" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.06</v>
+        <v>2.11</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="CP9" t="n">
         <v>2.22</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
       <c r="CR9" t="n">
         <v>1.47</v>
@@ -4482,10 +4482,10 @@
         <v>1.32</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="CX9" t="n">
         <v>1.77</v>
@@ -4506,82 +4506,82 @@
         <v>2.31</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.34</v>
+        <v>4.37</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="DH9" t="n">
-        <v>101</v>
+        <v>101.2</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="DK9" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DM9" t="n">
-        <v>37</v>
+        <v>35.4</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="DO9" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="DP9" t="n">
-        <v>14.75</v>
+        <v>11.6</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="DR9" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>53.75</v>
+        <v>53.2</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.75</v>
+        <v>12.8</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.25</v>
+        <v>8.6</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="EA9" t="n">
-        <v>24.75</v>
+        <v>19.6</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="10">
@@ -7408,10 +7408,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
@@ -7420,49 +7420,49 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>4.67</v>
       </c>
       <c r="H17" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>2.67</v>
       </c>
       <c r="K17" t="n">
-        <v>8</v>
+        <v>7.67</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="M17" t="n">
-        <v>80</v>
+        <v>64.67</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>4</v>
+        <v>2.33</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4.5</v>
+        <v>2.67</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7474,28 +7474,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>51</v>
+        <v>50.33</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>13</v>
+        <v>9.67</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.5</v>
+        <v>4.67</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="AC17" t="n">
-        <v>16</v>
+        <v>10.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.86</v>
+        <v>1.43</v>
       </c>
       <c r="AE17" t="n">
-        <v>1</v>
+        <v>2.67</v>
       </c>
       <c r="AF17" t="n">
         <v>0.5</v>
@@ -7579,49 +7579,49 @@
         <v>4.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="BH17" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BK17" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BN17" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="BP17" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BQ17" t="n">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="BR17" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BS17" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BT17" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BU17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7630,19 +7630,19 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="CA17" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="CB17" t="n">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="CC17" t="n">
         <v>2.84</v>
@@ -7651,43 +7651,43 @@
         <v>3.22</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="CF17" t="n">
         <v>3.37</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.26</v>
+        <v>2.35</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="CK17" t="n">
         <v>1.63</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.87</v>
+        <v>4.68</v>
       </c>
       <c r="CR17" t="n">
         <v>1.55</v>
@@ -7698,10 +7698,10 @@
       </c>
       <c r="CU17" t="inlineStr"/>
       <c r="CV17" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CX17" t="n">
         <v>1.65</v>
@@ -7716,88 +7716,88 @@
         <v>1.71</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.89</v>
+        <v>4.8</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DF17" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="DG17" t="n">
-        <v>4.25</v>
+        <v>3.8</v>
       </c>
       <c r="DH17" t="n">
-        <v>97.5</v>
+        <v>96.8</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="DM17" t="n">
-        <v>64.75</v>
+        <v>58.6</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="DO17" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="DP17" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="DR17" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>51.5</v>
+        <v>51</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>10.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DY17" t="n">
-        <v>5.75</v>
+        <v>4.8</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="EA17" t="n">
-        <v>12.75</v>
+        <v>10</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.44</v>
+        <v>1.26</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" t="n">
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>0.33</v>
@@ -1472,50 +1472,50 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>98</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>51</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT2" t="n">
         <v>1</v>
       </c>
-      <c r="AH2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>94</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
+      <c r="AU2" t="n">
         <v>1</v>
       </c>
-      <c r="AL2" t="n">
-        <v>6</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>64</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
       <c r="AV2" t="n">
         <v>0</v>
       </c>
@@ -1526,73 +1526,73 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB2" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="BF2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="BH2" t="n">
         <v>9</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BR2" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BS2" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BT2" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BU2" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BV2" t="n">
         <v>0</v>
@@ -1601,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BY2" t="n">
         <v>2.82</v>
@@ -1610,55 +1610,55 @@
         <v>2.8</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="CB2" t="n">
         <v>3.11</v>
       </c>
       <c r="CC2" t="n">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.01</v>
+        <v>2.78</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="CF2" t="n">
         <v>3.39</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="CH2" t="n">
         <v>1.24</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.51</v>
+        <v>4.45</v>
       </c>
       <c r="CR2" t="n">
         <v>1.55</v>
@@ -1669,49 +1669,49 @@
       </c>
       <c r="CU2" t="inlineStr"/>
       <c r="CV2" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="CZ2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DF2" t="n">
         <v>2.2</v>
       </c>
-      <c r="DA2" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>2.75</v>
-      </c>
       <c r="DG2" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="DH2" t="n">
-        <v>96.25</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="DK2" t="n">
         <v>5</v>
@@ -1720,22 +1720,22 @@
         <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>56.75</v>
+        <v>53</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.75</v>
+        <v>10.2</v>
       </c>
       <c r="DQ2" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="DR2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
@@ -1747,28 +1747,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>60.5</v>
+        <v>57.8</v>
       </c>
       <c r="DW2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="DX2" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="DY2" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="EA2" t="n">
-        <v>10.25</v>
+        <v>11.2</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="EC2" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="3">
@@ -2177,13 +2177,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
         <v>2</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2267,127 +2267,127 @@
         <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.5</v>
+        <v>1.67</v>
       </c>
       <c r="AI4" t="n">
-        <v>88</v>
+        <v>92.67</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AL4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>53.5</v>
+        <v>40.67</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.5</v>
+        <v>2.67</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.5</v>
+        <v>-0.67</v>
       </c>
       <c r="AS4" t="n">
-        <v>4</v>
+        <v>2.33</v>
       </c>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>38.5</v>
+        <v>38</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BB4" t="n">
-        <v>7</v>
+        <v>6.33</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="BD4" t="n">
-        <v>11.5</v>
+        <v>7.33</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="BG4" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="BH4" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="BJ4" t="n">
         <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BM4" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="BR4" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BS4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BT4" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BU4" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BY4" t="n">
         <v>4.42</v>
@@ -2408,55 +2408,55 @@
         <v>4.9</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.34</v>
+        <v>3.29</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.32</v>
+        <v>3.69</v>
       </c>
       <c r="CE4" t="n">
         <v>1.49</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CH4" t="n">
         <v>1.28</v>
       </c>
       <c r="CI4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CK4" t="n">
         <v>1.65</v>
       </c>
-      <c r="CJ4" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="CK4" t="n">
-        <v>1.64</v>
-      </c>
       <c r="CL4" t="n">
-        <v>2.24</v>
+        <v>2.31</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CO4" t="n">
         <v>1.41</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.58</v>
+        <v>4.47</v>
       </c>
       <c r="CR4" t="n">
         <v>1.51</v>
@@ -2471,10 +2471,10 @@
         <v>1.4</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="CX4" t="n">
         <v>1.67</v>
@@ -2489,61 +2489,61 @@
         <v>1.7</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.7</v>
+        <v>4.65</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DF4" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.75</v>
+        <v>1.4</v>
       </c>
       <c r="DH4" t="n">
-        <v>80</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="DK4" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="DL4" t="n">
         <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.5</v>
+        <v>38.6</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="DP4" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="DR4" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
@@ -2555,22 +2555,22 @@
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DY4" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="EA4" t="n">
-        <v>10.75</v>
+        <v>8.4</v>
       </c>
       <c r="EB4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="EC4" t="n">
         <v>1.2</v>
-      </c>
-      <c r="EC4" t="n">
-        <v>1.25</v>
       </c>
     </row>
     <row r="5">
@@ -2580,13 +2580,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
         <v>3</v>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>0.33</v>
@@ -2673,46 +2673,46 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>104</v>
+        <v>103.5</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN5" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AO5" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AP5" t="n">
         <v>3</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AS5" t="n">
-        <v>8</v>
+        <v>3.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="n">
         <v>0</v>
@@ -2727,70 +2727,70 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>19</v>
+        <v>12.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BC5" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>26</v>
+        <v>12.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="BF5" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="BH5" t="n">
-        <v>6.25</v>
+        <v>7.4</v>
       </c>
       <c r="BI5" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BP5" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BT5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BU5" t="n">
         <v>0</v>
@@ -2802,7 +2802,7 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BY5" t="n">
         <v>3.15</v>
@@ -2811,55 +2811,55 @@
         <v>3.74</v>
       </c>
       <c r="CA5" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="CB5" t="n">
         <v>3.03</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.87</v>
+        <v>4.14</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CF5" t="n">
         <v>3.53</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CH5" t="n">
         <v>1.23</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CN5" t="n">
         <v>1.64</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CQ5" t="n">
-        <v>5.06</v>
+        <v>5.03</v>
       </c>
       <c r="CR5" t="n">
         <v>1.58</v>
@@ -2870,43 +2870,43 @@
       </c>
       <c r="CU5" t="inlineStr"/>
       <c r="CV5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="CZ5" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="DB5" t="n">
         <v>1.55</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="DD5" t="n">
-        <v>5.44</v>
+        <v>5.43</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="DH5" t="n">
-        <v>98.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
@@ -2915,28 +2915,28 @@
         <v>4</v>
       </c>
       <c r="DK5" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="DM5" t="n">
-        <v>49.25</v>
+        <v>51</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.25</v>
+        <v>10.4</v>
       </c>
       <c r="DQ5" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="DR5" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -2948,28 +2948,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>38</v>
+        <v>39.8</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.75</v>
+        <v>10.6</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.25</v>
+        <v>8.4</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="EA5" t="n">
-        <v>22.75</v>
+        <v>18</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="EC5" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="6">
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>3</v>
@@ -2991,49 +2991,49 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>99</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K6" t="n">
         <v>3</v>
       </c>
-      <c r="G6" t="n">
-        <v>3</v>
-      </c>
-      <c r="H6" t="n">
-        <v>88</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>5</v>
-      </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>10</v>
+        <v>4.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="R6" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3045,28 +3045,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>55</v>
+        <v>46.5</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>13</v>
+        <v>9.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AB6" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>26</v>
+        <v>12.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AE6" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3150,46 +3150,46 @@
         <v>3</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="BH6" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="BO6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BP6" t="n">
         <v>5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BT6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BU6" t="n">
         <v>0</v>
@@ -3201,19 +3201,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.4</v>
+        <v>2.69</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.49</v>
+        <v>3.09</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.12</v>
+        <v>3.07</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.23</v>
+        <v>3.13</v>
       </c>
       <c r="CC6" t="n">
         <v>3.44</v>
@@ -3225,25 +3225,25 @@
         <v>1.5</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="CM6" t="n">
         <v>2.12</v>
@@ -3252,94 +3252,94 @@
         <v>1.68</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.56</v>
+        <v>4.49</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.27</v>
+        <v>3.22</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="CU6" t="n">
         <v>1.33</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CW6" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CY6" t="n">
         <v>2.06</v>
       </c>
-      <c r="CX6" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CY6" t="n">
-        <v>2.05</v>
-      </c>
       <c r="CZ6" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DB6" t="n">
         <v>1.43</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="DG6" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="DH6" t="n">
-        <v>84.25</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="DK6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="DL6" t="n">
         <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>56.25</v>
+        <v>58.6</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="DP6" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="DQ6" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.25</v>
+        <v>4.8</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3351,28 +3351,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>47</v>
+        <v>45.2</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.5</v>
+        <v>6.6</v>
       </c>
       <c r="DZ6" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="EA6" t="n">
-        <v>15.5</v>
+        <v>12.2</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="EC6" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="7">
@@ -3382,13 +3382,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3472,52 +3472,52 @@
         <v>1.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.5</v>
+        <v>1.33</v>
       </c>
       <c r="AH7" t="n">
         <v>1</v>
       </c>
       <c r="AI7" t="n">
-        <v>75</v>
+        <v>83.67</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AL7" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>39</v>
+        <v>43.67</v>
       </c>
       <c r="AO7" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AQ7" t="n">
-        <v>13</v>
+        <v>14.33</v>
       </c>
       <c r="AR7" t="n">
         <v>2</v>
       </c>
       <c r="AS7" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AT7" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3529,73 +3529,73 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>59</v>
+        <v>53.67</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.5</v>
+        <v>5.33</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="BC7" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="BD7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BE7" t="n">
         <v>0.78</v>
       </c>
       <c r="BF7" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.25</v>
+        <v>8.4</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BN7" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BU7" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -3604,7 +3604,7 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BY7" t="n">
         <v>2.28</v>
@@ -3613,55 +3613,55 @@
         <v>2.36</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.95</v>
+        <v>3.11</v>
       </c>
       <c r="CB7" t="n">
-        <v>2.92</v>
+        <v>3.09</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.44</v>
+        <v>3.69</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.58</v>
+        <v>4.09</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="CM7" t="n">
         <v>2.2</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="CR7" t="n">
         <v>1.54</v>
@@ -3676,73 +3676,73 @@
         <v>1.31</v>
       </c>
       <c r="CV7" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DA7" t="n">
         <v>1.76</v>
       </c>
-      <c r="CW7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="CX7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="CY7" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="CZ7" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="DA7" t="n">
-        <v>1.74</v>
-      </c>
       <c r="DB7" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="DD7" t="n">
-        <v>5</v>
+        <v>4.84</v>
       </c>
       <c r="DE7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="DH7" t="n">
-        <v>100.5</v>
+        <v>100.6</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="DM7" t="n">
-        <v>54.75</v>
+        <v>54.4</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="DP7" t="n">
-        <v>8.25</v>
+        <v>10</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DR7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3754,28 +3754,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>60.25</v>
+        <v>56.8</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DX7" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="DY7" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="EA7" t="n">
-        <v>17</v>
+        <v>19.2</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="8">
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
         <v>3</v>
@@ -3797,13 +3797,13 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>119</v>
+        <v>113.5</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -3812,16 +3812,16 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M8" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O8" t="n">
         <v>4</v>
@@ -3839,7 +3839,7 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3851,7 +3851,7 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -3869,7 +3869,7 @@
         <v>-1</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AE8" t="n">
         <v>2</v>
@@ -3956,46 +3956,46 @@
         <v>2</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="BH8" t="n">
-        <v>10</v>
+        <v>10.4</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BR8" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BS8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BT8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -4007,19 +4007,19 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="BZ8" t="n">
         <v>1.99</v>
       </c>
       <c r="CA8" t="n">
-        <v>3</v>
+        <v>3.03</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CC8" t="n">
         <v>2.75</v>
@@ -4028,34 +4028,34 @@
         <v>2.83</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CO8" t="n">
         <v>1.4</v>
@@ -4064,7 +4064,7 @@
         <v>2.28</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.35</v>
+        <v>4.29</v>
       </c>
       <c r="CR8" t="n">
         <v>1.45</v>
@@ -4100,82 +4100,82 @@
         <v>1.42</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DD8" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>114.4</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>3</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>12</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="DZ8" t="n">
         <v>4.4</v>
       </c>
-      <c r="DE8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DF8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DG8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DH8" t="n">
-        <v>116</v>
-      </c>
-      <c r="DI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ8" t="n">
-        <v>2</v>
-      </c>
-      <c r="DK8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="DL8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DM8" t="n">
-        <v>53.5</v>
-      </c>
-      <c r="DN8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DO8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="DP8" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="DQ8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="DR8" t="n">
-        <v>5</v>
-      </c>
-      <c r="DS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV8" t="n">
-        <v>52.25</v>
-      </c>
-      <c r="DW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX8" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="DY8" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="DZ8" t="n">
-        <v>4</v>
-      </c>
       <c r="EA8" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="EC8" t="n">
         <v>2</v>
@@ -4302,7 +4302,7 @@
         <v>0.33</v>
       </c>
       <c r="AN9" t="n">
-        <v>28.67</v>
+        <v>43.67</v>
       </c>
       <c r="AO9" t="n">
         <v>1</v>
@@ -4311,13 +4311,13 @@
         <v>2.67</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11.33</v>
+        <v>17</v>
       </c>
       <c r="AR9" t="n">
-        <v>-0.33</v>
+        <v>1</v>
       </c>
       <c r="AS9" t="n">
-        <v>7</v>
+        <v>9.33</v>
       </c>
       <c r="AT9" t="n">
         <v>1.33</v>
@@ -4335,25 +4335,25 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>48</v>
+        <v>49.67</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>10.67</v>
+        <v>12.67</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.67</v>
+        <v>8.33</v>
       </c>
       <c r="BC9" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="BD9" t="n">
-        <v>16</v>
+        <v>22.67</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.17</v>
+        <v>1.42</v>
       </c>
       <c r="BF9" t="n">
         <v>2.67</v>
@@ -4533,7 +4533,7 @@
         <v>0.2</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.4</v>
+        <v>44.4</v>
       </c>
       <c r="DN9" t="n">
         <v>0.8</v>
@@ -4542,13 +4542,13 @@
         <v>2.6</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.6</v>
+        <v>15</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DS9" t="n">
         <v>0.4</v>
@@ -4560,25 +4560,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>53.2</v>
+        <v>54.2</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.8</v>
+        <v>14</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.6</v>
+        <v>23.6</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="EC9" t="n">
         <v>2.4</v>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
@@ -4603,49 +4603,49 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="H10" t="n">
-        <v>108</v>
+        <v>101.33</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="K10" t="n">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>73.5</v>
+        <v>69.67</v>
       </c>
       <c r="N10" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="O10" t="n">
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>6</v>
+        <v>3.67</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="R10" t="n">
-        <v>4.5</v>
+        <v>2.67</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4657,28 +4657,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>60.5</v>
+        <v>56.33</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>13.5</v>
+        <v>11.33</v>
       </c>
       <c r="AA10" t="n">
-        <v>6</v>
+        <v>4.67</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.5</v>
+        <v>6.67</v>
       </c>
       <c r="AC10" t="n">
-        <v>19</v>
+        <v>12.33</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.9</v>
+        <v>1.68</v>
       </c>
       <c r="AE10" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4762,49 +4762,49 @@
         <v>4.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="BH10" t="n">
-        <v>10.25</v>
+        <v>10.2</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BN10" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="BP10" t="n">
-        <v>5.75</v>
+        <v>5.8</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BT10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BU10" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BV10" t="n">
         <v>0</v>
@@ -4813,19 +4813,19 @@
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.89</v>
+        <v>3.93</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.28</v>
+        <v>5</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.34</v>
+        <v>3.47</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.51</v>
+        <v>3.77</v>
       </c>
       <c r="CC10" t="n">
         <v>5.92</v>
@@ -4834,43 +4834,43 @@
         <v>6.63</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.16</v>
+        <v>3.11</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="CH10" t="n">
         <v>1.3</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.08</v>
+        <v>3.95</v>
       </c>
       <c r="CR10" t="n">
         <v>1.46</v>
@@ -4885,73 +4885,73 @@
         <v>1.36</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.29</v>
+        <v>2.23</v>
       </c>
       <c r="DD10" t="n">
-        <v>4.28</v>
+        <v>4.1</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="DH10" t="n">
-        <v>103.25</v>
+        <v>100.2</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="DL10" t="n">
         <v>1</v>
       </c>
       <c r="DM10" t="n">
-        <v>54.5</v>
+        <v>56</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DQ10" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="DR10" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4963,28 +4963,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>49.75</v>
+        <v>49.4</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.5</v>
+        <v>10.6</v>
       </c>
       <c r="DY10" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="EA10" t="n">
-        <v>21</v>
+        <v>16.6</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="EC10" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -5397,13 +5397,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5490,127 +5490,127 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="AI12" t="n">
-        <v>88</v>
+        <v>98.33</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AL12" t="n">
-        <v>7</v>
+        <v>6.33</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>37.33</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AP12" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.5</v>
+        <v>8.67</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.5</v>
+        <v>1.33</v>
       </c>
       <c r="AS12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>58.67</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="BC12" t="n">
         <v>5</v>
       </c>
-      <c r="AT12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>62</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>6.5</v>
-      </c>
       <c r="BD12" t="n">
-        <v>25</v>
+        <v>16.33</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="BF12" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.75</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="BN12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BO12" t="n">
         <v>1</v>
       </c>
-      <c r="BO12" t="n">
-        <v>0.75</v>
-      </c>
       <c r="BP12" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BT12" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5619,7 +5619,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BY12" t="n">
         <v>2.06</v>
@@ -5628,55 +5628,55 @@
         <v>1.94</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.59</v>
+        <v>3.66</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.73</v>
+        <v>3.94</v>
       </c>
       <c r="CC12" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CD12" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.71</v>
+        <v>0.85</v>
       </c>
       <c r="CF12" t="n">
-        <v>1.48</v>
+        <v>1.77</v>
       </c>
       <c r="CG12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CM12" t="n">
         <v>1.36</v>
       </c>
-      <c r="CH12" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="CI12" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="CJ12" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="CK12" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="CL12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="CM12" t="n">
-        <v>1.07</v>
-      </c>
       <c r="CN12" t="n">
-        <v>0.86</v>
+        <v>1.08</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.68</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="CP12" t="n">
         <v>1.99</v>
       </c>
       <c r="CQ12" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="CR12" t="n">
         <v>1.52</v>
@@ -5691,73 +5691,73 @@
         <v>1.29</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="CW12" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="CX12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF12" t="n">
         <v>1.6</v>
       </c>
-      <c r="CY12" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="CZ12" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="DA12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="DB12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="DC12" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="DD12" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="DE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF12" t="n">
-        <v>1.75</v>
-      </c>
       <c r="DG12" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="DH12" t="n">
-        <v>97.25</v>
+        <v>101.6</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="DK12" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DM12" t="n">
-        <v>49</v>
+        <v>55.6</v>
       </c>
       <c r="DN12" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DQ12" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.25</v>
+        <v>5.6</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5769,28 +5769,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="DY12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="EA12" t="n">
-        <v>23</v>
+        <v>18.2</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="13">
@@ -5800,61 +5800,61 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F13" t="n">
         <v>1</v>
       </c>
-      <c r="F13" t="n">
-        <v>1.5</v>
-      </c>
       <c r="G13" t="n">
-        <v>1.5</v>
+        <v>2.33</v>
       </c>
       <c r="H13" t="n">
-        <v>105</v>
+        <v>111.33</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>12.5</v>
+        <v>36</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="O13" t="n">
-        <v>2.5</v>
+        <v>3.67</v>
       </c>
       <c r="P13" t="n">
-        <v>10</v>
+        <v>9.33</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>4.67</v>
       </c>
       <c r="R13" t="n">
-        <v>7.5</v>
+        <v>7.33</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -5866,28 +5866,28 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>49.5</v>
+        <v>52</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>8</v>
+        <v>10.33</v>
       </c>
       <c r="AA13" t="n">
-        <v>4.5</v>
+        <v>5.33</v>
       </c>
       <c r="AB13" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AC13" t="n">
-        <v>23.5</v>
+        <v>25</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.86</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5971,49 +5971,49 @@
         <v>2.5</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="BH13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="BL13" t="n">
         <v>1</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="BO13" t="n">
         <v>1</v>
       </c>
       <c r="BP13" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BQ13" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BT13" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BU13" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6022,16 +6022,16 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.67</v>
+        <v>3.69</v>
       </c>
       <c r="CB13" t="n">
         <v>3.72</v>
@@ -6046,40 +6046,40 @@
         <v>1.42</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.01</v>
+        <v>2.05</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="CR13" t="n">
         <v>1.44</v>
@@ -6094,73 +6094,73 @@
         <v>1.35</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="DB13" t="n">
         <v>1.37</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="DG13" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DH13" t="n">
-        <v>98.25</v>
+        <v>103.4</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="DK13" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="DL13" t="n">
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="DQ13" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.75</v>
+        <v>7.6</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6172,28 +6172,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>52.75</v>
+        <v>53.6</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DX13" t="n">
-        <v>11.5</v>
+        <v>12.2</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="DZ13" t="n">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="EA13" t="n">
-        <v>23.75</v>
+        <v>24.6</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="EC13" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="14">
@@ -6203,34 +6203,34 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="F14" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="G14" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" t="n">
+        <v>103</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5</v>
+      </c>
+      <c r="K14" t="n">
         <v>3</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>99</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J14" t="n">
-        <v>6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>2.5</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -6239,25 +6239,25 @@
         <v>41</v>
       </c>
       <c r="N14" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="O14" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>15.5</v>
+        <v>15.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="R14" t="n">
-        <v>11</v>
+        <v>8.67</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6269,28 +6269,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>46.5</v>
+        <v>48.67</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.5</v>
+        <v>8.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>5</v>
+        <v>5.67</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>2.67</v>
       </c>
       <c r="AC14" t="n">
-        <v>22</v>
+        <v>21.67</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.82</v>
+        <v>1.02</v>
       </c>
       <c r="AE14" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6374,49 +6374,49 @@
         <v>2</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BK14" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="BN14" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BT14" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BU14" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6425,19 +6425,19 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="BY14" t="n">
-        <v>4.24</v>
+        <v>3.73</v>
       </c>
       <c r="BZ14" t="n">
-        <v>4.36</v>
+        <v>3.91</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="CC14" t="n">
         <v>3.18</v>
@@ -6449,40 +6449,40 @@
         <v>1.45</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.01</v>
+        <v>3.09</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="CN14" t="n">
         <v>1.68</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="CQ14" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="CR14" t="n">
         <v>1.52</v>
@@ -6500,70 +6500,70 @@
         <v>1.79</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="DB14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DG14" t="n">
         <v>1.4</v>
       </c>
-      <c r="DC14" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="DD14" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="DE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DG14" t="n">
-        <v>0.75</v>
-      </c>
       <c r="DH14" t="n">
-        <v>93.75</v>
+        <v>97.2</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DJ14" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="DK14" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="DL14" t="n">
         <v>0</v>
       </c>
       <c r="DM14" t="n">
-        <v>44.25</v>
+        <v>43.6</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="DO14" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="DP14" t="n">
-        <v>10.5</v>
+        <v>11.6</v>
       </c>
       <c r="DQ14" t="n">
         <v>3</v>
       </c>
       <c r="DR14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6575,28 +6575,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>43.5</v>
+        <v>45.4</v>
       </c>
       <c r="DW14" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="DX14" t="n">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="DY14" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="EA14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.83</v>
+        <v>0.95</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="15">
@@ -6606,94 +6606,94 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="H15" t="n">
+        <v>89</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="K15" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M15" t="n">
+        <v>65</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" t="n">
         <v>4</v>
       </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H15" t="n">
-        <v>93.5</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2</v>
-      </c>
-      <c r="K15" t="n">
-        <v>7</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>62.5</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.5</v>
-      </c>
       <c r="P15" t="n">
-        <v>10.5</v>
+        <v>6.67</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>50.67</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="AB15" t="n">
         <v>6</v>
       </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>7.5</v>
-      </c>
       <c r="AC15" t="n">
-        <v>25.5</v>
+        <v>16.67</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AE15" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="AF15" t="n">
         <v>1</v>
@@ -6777,70 +6777,70 @@
         <v>4</v>
       </c>
       <c r="BG15" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="BI15" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BK15" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BL15" t="n">
         <v>1</v>
       </c>
       <c r="BM15" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BN15" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="BO15" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="BP15" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BQ15" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BT15" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BU15" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BV15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BW15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BX15" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.49</v>
+        <v>2.34</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="CC15" t="n">
         <v>4.58</v>
@@ -6849,43 +6849,43 @@
         <v>4.89</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.54</v>
+        <v>2.73</v>
       </c>
       <c r="CG15" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.48</v>
+        <v>1.61</v>
       </c>
       <c r="CM15" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.46</v>
+        <v>3.75</v>
       </c>
       <c r="CR15" t="n">
         <v>1.51</v>
@@ -6896,73 +6896,73 @@
       </c>
       <c r="CU15" t="inlineStr"/>
       <c r="CV15" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="DD15" t="n">
-        <v>4.93</v>
+        <v>5.05</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="DH15" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="DK15" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="DM15" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.75</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DQ15" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.75</v>
+        <v>5.2</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6974,28 +6974,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>42.25</v>
+        <v>44.4</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>14</v>
+        <v>12.8</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.25</v>
+        <v>7.6</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.5</v>
+        <v>17</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="EC15" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="16">
@@ -7005,13 +7005,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
         <v>0.5</v>
@@ -7098,127 +7098,127 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AI16" t="n">
-        <v>97.5</v>
+        <v>110.67</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.5</v>
+        <v>4.33</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN16" t="n">
-        <v>30.5</v>
+        <v>55</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AP16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AT16" t="n">
         <v>1</v>
       </c>
-      <c r="AQ16" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AU16" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>49.5</v>
+        <v>53.67</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>9</v>
+        <v>8.67</v>
       </c>
       <c r="BB16" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="BC16" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="BD16" t="n">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="BF16" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="BH16" t="n">
-        <v>6.75</v>
+        <v>7.2</v>
       </c>
       <c r="BI16" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="BJ16" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BM16" t="n">
         <v>1</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="BP16" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="BR16" t="n">
         <v>100</v>
       </c>
       <c r="BS16" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BT16" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BU16" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BV16" t="n">
         <v>0</v>
@@ -7227,7 +7227,7 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BY16" t="n">
         <v>1.88</v>
@@ -7236,25 +7236,25 @@
         <v>2.21</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.53</v>
+        <v>3.37</v>
       </c>
       <c r="CC16" t="n">
-        <v>3.28</v>
+        <v>2.95</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.37</v>
+        <v>3.05</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="CF16" t="n">
         <v>3.11</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="CH16" t="n">
         <v>1.33</v>
@@ -7263,142 +7263,142 @@
         <v>1.86</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CP16" t="n">
         <v>2.18</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.72</v>
+        <v>3.82</v>
       </c>
       <c r="CR16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CS16" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="CT16" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="CU16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CV16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CW16" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CY16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DA16" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DB16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="DC16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DD16" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="DE16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DF16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="DG16" t="n">
+        <v>2</v>
+      </c>
+      <c r="DH16" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="DI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="DK16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="DL16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DM16" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="DN16" t="n">
         <v>1.4</v>
       </c>
-      <c r="CS16" t="n">
-        <v>3</v>
-      </c>
-      <c r="CT16" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="CU16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="CV16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="CW16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="CX16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CY16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="CZ16" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="DA16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="DB16" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="DC16" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DD16" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="DE16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DF16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DG16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DH16" t="n">
-        <v>106.75</v>
-      </c>
-      <c r="DI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ16" t="n">
+      <c r="DO16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DP16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>53</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="DZ16" t="n">
         <v>4</v>
       </c>
-      <c r="DK16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="DL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM16" t="n">
-        <v>44.75</v>
-      </c>
-      <c r="DN16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="DO16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DP16" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="DQ16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="DR16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DS16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DT16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV16" t="n">
-        <v>50.75</v>
-      </c>
-      <c r="DW16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DX16" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="DY16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="DZ16" t="n">
-        <v>4.25</v>
-      </c>
       <c r="EA16" t="n">
-        <v>16.75</v>
+        <v>13.2</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="EC16" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="17">
@@ -7420,7 +7420,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
         <v>4.67</v>
@@ -7432,7 +7432,7 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.67</v>
+        <v>3.33</v>
       </c>
       <c r="K17" t="n">
         <v>7.67</v>
@@ -7441,7 +7441,7 @@
         <v>0.33</v>
       </c>
       <c r="M17" t="n">
-        <v>64.67</v>
+        <v>73</v>
       </c>
       <c r="N17" t="n">
         <v>1.33</v>
@@ -7450,13 +7450,13 @@
         <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>2.33</v>
+        <v>8.33</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R17" t="n">
-        <v>2.67</v>
+        <v>5.67</v>
       </c>
       <c r="S17" t="n">
         <v>1.67</v>
@@ -7474,28 +7474,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>50.33</v>
+        <v>48.67</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>9.67</v>
+        <v>11.67</v>
       </c>
       <c r="AA17" t="n">
-        <v>4.67</v>
+        <v>6.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>5</v>
+        <v>5.33</v>
       </c>
       <c r="AC17" t="n">
-        <v>10.33</v>
+        <v>16.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.67</v>
+        <v>3.33</v>
       </c>
       <c r="AF17" t="n">
         <v>0.5</v>
@@ -7728,7 +7728,7 @@
         <v>0.2</v>
       </c>
       <c r="DF17" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="DG17" t="n">
         <v>3.8</v>
@@ -7740,7 +7740,7 @@
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="DK17" t="n">
         <v>6</v>
@@ -7749,7 +7749,7 @@
         <v>0.6</v>
       </c>
       <c r="DM17" t="n">
-        <v>58.6</v>
+        <v>63.6</v>
       </c>
       <c r="DN17" t="n">
         <v>1.2</v>
@@ -7758,13 +7758,13 @@
         <v>2.2</v>
       </c>
       <c r="DP17" t="n">
-        <v>3.6</v>
+        <v>7.2</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="DR17" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="DS17" t="n">
         <v>0.2</v>
@@ -7776,28 +7776,28 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="DW17" t="n">
         <v>0</v>
       </c>
       <c r="DX17" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="DY17" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="EA17" t="n">
-        <v>10</v>
+        <v>13.6</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="EC17" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -1790,49 +1790,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>80.5</v>
+        <v>79.67</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>35.5</v>
+        <v>35.33</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>5.5</v>
+        <v>3.33</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.33</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1844,28 +1844,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>5</v>
+        <v>6.67</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.5</v>
+        <v>2.33</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.5</v>
+        <v>4.67</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.83</v>
+        <v>0.99</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.5</v>
+        <v>3.33</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1949,46 +1949,46 @@
         <v>3</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.75</v>
+        <v>7</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="BR3" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BS3" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BT3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
@@ -2000,19 +2000,19 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.35</v>
+        <v>3.27</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.11</v>
+        <v>4.07</v>
       </c>
       <c r="CA3" t="n">
         <v>3.02</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="CC3" t="n">
         <v>2.62</v>
@@ -2021,50 +2021,50 @@
         <v>2.74</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="CG3" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.5</v>
+        <v>3.66</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CS3" t="inlineStr"/>
       <c r="CT3" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="CU3" t="inlineStr"/>
       <c r="CV3" t="n">
@@ -2074,67 +2074,67 @@
         <v>2.11</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.63</v>
+        <v>2.58</v>
       </c>
       <c r="DD3" t="n">
-        <v>5.21</v>
+        <v>5.06</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="DG3" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="DH3" t="n">
-        <v>99.5</v>
+        <v>95.2</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="DK3" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="DP3" t="n">
-        <v>5.25</v>
+        <v>4</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="DR3" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2146,28 +2146,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>46.5</v>
+        <v>47</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DX3" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="DY3" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="EA3" t="n">
-        <v>10.75</v>
+        <v>8.4</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.91</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="4">
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>40.67</v>
+        <v>53</v>
       </c>
       <c r="AO4" t="n">
         <v>0.33</v>
@@ -2300,13 +2300,13 @@
         <v>0.33</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.67</v>
+        <v>8.33</v>
       </c>
       <c r="AR4" t="n">
-        <v>-0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.33</v>
+        <v>7</v>
       </c>
       <c r="AT4" t="n">
         <v>0</v>
@@ -2324,25 +2324,25 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>38</v>
+        <v>37.33</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>11</v>
+        <v>11.33</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.33</v>
+        <v>7</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.67</v>
+        <v>4.33</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.33</v>
+        <v>17.33</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="BF4" t="n">
         <v>0.67</v>
@@ -2522,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="DM4" t="n">
-        <v>38.6</v>
+        <v>46</v>
       </c>
       <c r="DN4" t="n">
         <v>0.4</v>
@@ -2531,13 +2531,13 @@
         <v>1.2</v>
       </c>
       <c r="DP4" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0.6</v>
+        <v>-0</v>
       </c>
       <c r="DR4" t="n">
-        <v>6.2</v>
+        <v>9</v>
       </c>
       <c r="DS4" t="n">
         <v>0.2</v>
@@ -2549,25 +2549,25 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>37</v>
+        <v>36.6</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="DY4" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="EA4" t="n">
-        <v>8.4</v>
+        <v>14.4</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="EC4" t="n">
         <v>1.2</v>
@@ -2703,13 +2703,13 @@
         <v>3</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AR5" t="n">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="AT5" t="n">
         <v>2</v>
@@ -2727,25 +2727,25 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>45</v>
+        <v>44.5</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BB5" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BC5" t="n">
         <v>2.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>12.5</v>
+        <v>20.5</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="BF5" t="n">
         <v>3.5</v>
@@ -2930,13 +2930,13 @@
         <v>1.6</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="DQ5" t="n">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="DR5" t="n">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -2948,25 +2948,25 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>39.8</v>
+        <v>39.6</v>
       </c>
       <c r="DW5" t="n">
         <v>0.4</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="DZ5" t="n">
         <v>2.2</v>
       </c>
       <c r="EA5" t="n">
-        <v>18</v>
+        <v>21.2</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="EC5" t="n">
         <v>3.4</v>
@@ -3207,13 +3207,13 @@
         <v>2.69</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.09</v>
+        <v>3.28</v>
       </c>
       <c r="CA6" t="n">
         <v>3.07</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="CC6" t="n">
         <v>3.44</v>
@@ -3261,13 +3261,13 @@
         <v>4.49</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.22</v>
+        <v>3.27</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CU6" t="n">
         <v>1.33</v>
@@ -3279,10 +3279,10 @@
         <v>2.03</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.16</v>
@@ -3294,10 +3294,10 @@
         <v>1.43</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.52</v>
+        <v>4.48</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
@@ -3818,7 +3818,7 @@
         <v>0.5</v>
       </c>
       <c r="M8" t="n">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="N8" t="n">
         <v>0.5</v>
@@ -3827,13 +3827,13 @@
         <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1</v>
+        <v>1.5</v>
       </c>
       <c r="R8" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -3851,25 +3851,25 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA8" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.7</v>
+        <v>1.96</v>
       </c>
       <c r="AE8" t="n">
         <v>2</v>
@@ -4130,7 +4130,7 @@
         <v>0.4</v>
       </c>
       <c r="DM8" t="n">
-        <v>50.4</v>
+        <v>56.4</v>
       </c>
       <c r="DN8" t="n">
         <v>0.4</v>
@@ -4139,13 +4139,13 @@
         <v>3</v>
       </c>
       <c r="DP8" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="DR8" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4157,25 +4157,25 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>54.4</v>
+        <v>54.8</v>
       </c>
       <c r="DW8" t="n">
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>12</v>
+        <v>13.2</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="EA8" t="n">
-        <v>8.6</v>
+        <v>13.8</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="EC8" t="n">
         <v>2</v>
@@ -4633,13 +4633,13 @@
         <v>4</v>
       </c>
       <c r="P10" t="n">
-        <v>3.67</v>
+        <v>9.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
-        <v>2.67</v>
+        <v>5.33</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -4657,25 +4657,25 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>56.33</v>
+        <v>52.33</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>11.33</v>
+        <v>12.33</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.67</v>
+        <v>5</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.67</v>
+        <v>7.33</v>
       </c>
       <c r="AC10" t="n">
-        <v>12.33</v>
+        <v>24.33</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AE10" t="n">
         <v>3.67</v>
@@ -4945,13 +4945,13 @@
         <v>2.8</v>
       </c>
       <c r="DP10" t="n">
-        <v>8.800000000000001</v>
+        <v>12.2</v>
       </c>
       <c r="DQ10" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
@@ -4963,25 +4963,25 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>49.4</v>
+        <v>47</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="EA10" t="n">
-        <v>16.6</v>
+        <v>23.8</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="EC10" t="n">
         <v>4</v>
@@ -4994,13 +4994,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
         <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5087,124 +5087,124 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AH11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>96.33</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP11" t="n">
         <v>3</v>
       </c>
-      <c r="AI11" t="n">
-        <v>101.5</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL11" t="n">
+      <c r="AQ11" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>50.67</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB11" t="n">
         <v>7</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="BC11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BN11" t="n">
         <v>1</v>
       </c>
-      <c r="AN11" t="n">
-        <v>58</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>9</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>19</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BO11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="BQ11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
       </c>
       <c r="BS11" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="BU11" t="n">
         <v>0</v>
@@ -5216,7 +5216,7 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="BY11" t="n">
         <v>2.02</v>
@@ -5225,31 +5225,31 @@
         <v>2.04</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.16</v>
+        <v>3.13</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CD11" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CF11" t="n">
         <v>3.33</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CH11" t="n">
         <v>1.27</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CJ11" t="n">
         <v>2</v>
@@ -5258,22 +5258,22 @@
         <v>1.66</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="CM11" t="n">
         <v>2.1</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CO11" t="n">
         <v>1.43</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="CR11" t="n">
         <v>1.49</v>
@@ -5282,79 +5282,79 @@
         <v>3.26</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="CU11" t="n">
         <v>1.34</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CY11" t="n">
         <v>2.07</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DB11" t="n">
         <v>1.43</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.44</v>
+        <v>4.48</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="DG11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>57</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DO11" t="n">
         <v>3</v>
       </c>
-      <c r="DH11" t="n">
-        <v>102.5</v>
-      </c>
-      <c r="DI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DK11" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="DL11" t="n">
-        <v>1</v>
-      </c>
-      <c r="DM11" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="DN11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DO11" t="n">
-        <v>3.5</v>
-      </c>
       <c r="DP11" t="n">
-        <v>9.75</v>
+        <v>7.6</v>
       </c>
       <c r="DQ11" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="DR11" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5366,28 +5366,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>52.25</v>
+        <v>52</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.5</v>
+        <v>10.2</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.25</v>
+        <v>7.2</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="EA11" t="n">
-        <v>23.75</v>
+        <v>18.8</v>
       </c>
       <c r="EB11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="EC11" t="n">
         <v>1.4</v>
-      </c>
-      <c r="EC11" t="n">
-        <v>1.25</v>
       </c>
     </row>
     <row r="12">
@@ -5520,13 +5520,13 @@
         <v>3</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8.67</v>
+        <v>13</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.33</v>
+        <v>4.33</v>
       </c>
       <c r="AS12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AT12" t="n">
         <v>1.33</v>
@@ -5544,25 +5544,25 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>58.67</v>
+        <v>62.67</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.67</v>
+        <v>12.33</v>
       </c>
       <c r="BB12" t="n">
-        <v>4.67</v>
+        <v>6.67</v>
       </c>
       <c r="BC12" t="n">
-        <v>5</v>
+        <v>5.67</v>
       </c>
       <c r="BD12" t="n">
-        <v>16.33</v>
+        <v>26.67</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.24</v>
+        <v>1.45</v>
       </c>
       <c r="BF12" t="n">
         <v>1.67</v>
@@ -5751,13 +5751,13 @@
         <v>2.6</v>
       </c>
       <c r="DP12" t="n">
-        <v>9.800000000000001</v>
+        <v>12.4</v>
       </c>
       <c r="DQ12" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5769,25 +5769,25 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>60</v>
+        <v>62.4</v>
       </c>
       <c r="DW12" t="n">
         <v>0</v>
       </c>
       <c r="DX12" t="n">
-        <v>10</v>
+        <v>11.6</v>
       </c>
       <c r="DY12" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.2</v>
+        <v>24.4</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="EC12" t="n">
         <v>2.4</v>
@@ -6648,13 +6648,13 @@
         <v>4</v>
       </c>
       <c r="P15" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4</v>
+      </c>
+      <c r="R15" t="n">
         <v>6.67</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>3.67</v>
       </c>
       <c r="S15" t="n">
         <v>1.33</v>
@@ -6672,25 +6672,25 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>50.67</v>
+        <v>51</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>15.33</v>
+        <v>17</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.33</v>
+        <v>11</v>
       </c>
       <c r="AB15" t="n">
         <v>6</v>
       </c>
       <c r="AC15" t="n">
-        <v>16.67</v>
+        <v>27.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AE15" t="n">
         <v>2.67</v>
@@ -6956,13 +6956,13 @@
         <v>3.2</v>
       </c>
       <c r="DP15" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="DQ15" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="DR15" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6974,25 +6974,25 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>44.4</v>
+        <v>44.6</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.8</v>
+        <v>13.8</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="DZ15" t="n">
         <v>5.2</v>
       </c>
       <c r="EA15" t="n">
-        <v>17</v>
+        <v>23.4</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="EC15" t="n">
         <v>3.2</v>
@@ -7239,13 +7239,13 @@
         <v>3.25</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.37</v>
+        <v>3.41</v>
       </c>
       <c r="CC16" t="n">
         <v>2.95</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="CE16" t="n">
         <v>1.44</v>
@@ -7287,16 +7287,16 @@
         <v>3.82</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.82</v>
+        <v>2.95</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="CV16" t="n">
         <v>1.84</v>
@@ -7308,7 +7308,7 @@
         <v>1.59</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.27</v>
@@ -7320,10 +7320,10 @@
         <v>1.37</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.98</v>
+        <v>3.94</v>
       </c>
       <c r="DE16" t="n">
         <v>0.2</v>

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1820,13 +1820,13 @@
         <v>1.33</v>
       </c>
       <c r="P3" t="n">
-        <v>3.33</v>
+        <v>8.33</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.33</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.67</v>
+        <v>5.33</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -1844,25 +1844,25 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>45</v>
+        <v>46.67</v>
       </c>
       <c r="Y3" t="n">
         <v>0.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.67</v>
+        <v>7</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="AB3" t="n">
         <v>4.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.67</v>
+        <v>14.33</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
       <c r="AE3" t="n">
         <v>3.33</v>
@@ -2128,13 +2128,13 @@
         <v>1</v>
       </c>
       <c r="DP3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2146,25 +2146,25 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="DW3" t="n">
         <v>0.2</v>
       </c>
       <c r="DX3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="DY3" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="DZ3" t="n">
         <v>3.2</v>
       </c>
       <c r="EA3" t="n">
-        <v>8.4</v>
+        <v>14.2</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="EC3" t="n">
         <v>3.2</v>
@@ -3021,13 +3021,13 @@
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5</v>
+        <v>9</v>
       </c>
       <c r="S6" t="n">
         <v>1.5</v>
@@ -3045,7 +3045,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>46.5</v>
+        <v>49</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -3054,16 +3054,16 @@
         <v>9.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AC6" t="n">
-        <v>12.5</v>
+        <v>25.5</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AE6" t="n">
         <v>3.5</v>
@@ -3333,13 +3333,13 @@
         <v>2</v>
       </c>
       <c r="DP6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="DQ6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DR6" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3351,7 +3351,7 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.2</v>
+        <v>46.2</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
@@ -3360,16 +3360,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="DZ6" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="EA6" t="n">
-        <v>12.2</v>
+        <v>17.4</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="EC6" t="n">
         <v>3.2</v>
@@ -5117,13 +5117,13 @@
         <v>3</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.33</v>
+        <v>7.67</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.67</v>
+        <v>4</v>
       </c>
       <c r="AS11" t="n">
-        <v>6</v>
+        <v>8.67</v>
       </c>
       <c r="AT11" t="n">
         <v>0.67</v>
@@ -5141,25 +5141,25 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>50.67</v>
+        <v>49</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>10</v>
+        <v>10.67</v>
       </c>
       <c r="BB11" t="n">
-        <v>7</v>
+        <v>7.33</v>
       </c>
       <c r="BC11" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="BD11" t="n">
-        <v>12.33</v>
+        <v>20</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="BF11" t="n">
         <v>1.67</v>
@@ -5348,13 +5348,13 @@
         <v>3</v>
       </c>
       <c r="DP11" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="DQ11" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="DR11" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5366,25 +5366,25 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="DW11" t="n">
         <v>0.2</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.2</v>
+        <v>10.6</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.8</v>
+        <v>23.4</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="EC11" t="n">
         <v>1.4</v>
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
         <v>3</v>
@@ -5409,50 +5409,50 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>106.5</v>
+        <v>114.67</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="K12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M12" t="n">
+        <v>62.67</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2</v>
+      </c>
+      <c r="P12" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R12" t="n">
         <v>6</v>
       </c>
-      <c r="L12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M12" t="n">
-        <v>83</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2</v>
-      </c>
-      <c r="P12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3</v>
-      </c>
-      <c r="R12" t="n">
-        <v>9.5</v>
-      </c>
       <c r="S12" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="T12" t="n">
         <v>1</v>
       </c>
-      <c r="T12" t="n">
-        <v>0.5</v>
-      </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
@@ -5463,28 +5463,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>62</v>
+        <v>57.67</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.5</v>
+        <v>11.33</v>
       </c>
       <c r="AA12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.5</v>
+        <v>4.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>21</v>
+        <v>13.67</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AE12" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5568,49 +5568,49 @@
         <v>1.67</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BO12" t="n">
         <v>1</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.8</v>
+        <v>4.67</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>60</v>
+        <v>66.67</v>
       </c>
       <c r="BT12" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BU12" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5619,19 +5619,19 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.06</v>
+        <v>1.86</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.66</v>
+        <v>3.68</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.94</v>
+        <v>3.92</v>
       </c>
       <c r="CC12" t="n">
         <v>1.56</v>
@@ -5640,43 +5640,43 @@
         <v>1.52</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.85</v>
+        <v>0.71</v>
       </c>
       <c r="CF12" t="n">
-        <v>1.77</v>
+        <v>1.47</v>
       </c>
       <c r="CG12" t="n">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.05</v>
+        <v>0.88</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.19</v>
+        <v>0.99</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.08</v>
+        <v>0.9</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="CR12" t="n">
         <v>1.52</v>
@@ -5721,43 +5721,43 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.6</v>
+        <v>3.17</v>
       </c>
       <c r="DH12" t="n">
-        <v>101.6</v>
+        <v>106.5</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="DK12" t="n">
-        <v>6.2</v>
+        <v>5.66</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="DM12" t="n">
-        <v>55.6</v>
+        <v>50</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.4</v>
+        <v>10.17</v>
       </c>
       <c r="DQ12" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5769,28 +5769,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>62.4</v>
+        <v>60.17</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.6</v>
+        <v>11.83</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.2</v>
+        <v>6.84</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="EA12" t="n">
-        <v>24.4</v>
+        <v>20.17</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="13">
@@ -7128,13 +7128,13 @@
         <v>2.33</v>
       </c>
       <c r="AQ16" t="n">
-        <v>5.67</v>
+        <v>10.67</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.33</v>
+        <v>2.33</v>
       </c>
       <c r="AT16" t="n">
         <v>1</v>
@@ -7152,25 +7152,25 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>53.67</v>
+        <v>52</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.67</v>
+        <v>9.67</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.33</v>
+        <v>5.33</v>
       </c>
       <c r="BC16" t="n">
         <v>4.33</v>
       </c>
       <c r="BD16" t="n">
-        <v>10</v>
+        <v>22.67</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="BF16" t="n">
         <v>3.67</v>
@@ -7359,13 +7359,13 @@
         <v>2.4</v>
       </c>
       <c r="DP16" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="DR16" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="DS16" t="n">
         <v>0.2</v>
@@ -7377,25 +7377,25 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="DW16" t="n">
         <v>0.2</v>
       </c>
       <c r="DX16" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DY16" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="DZ16" t="n">
         <v>4</v>
       </c>
       <c r="EA16" t="n">
-        <v>13.2</v>
+        <v>20.8</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="EC16" t="n">
         <v>3.8</v>
@@ -7408,13 +7408,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
         <v>3</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7498,130 +7498,130 @@
         <v>3.33</v>
       </c>
       <c r="AF17" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>95.33</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>40.67</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>51.67</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BM17" t="n">
         <v>0.5</v>
       </c>
-      <c r="AG17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>89</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ17" t="n">
+      <c r="BN17" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="BQ17" t="n">
         <v>5.5</v>
       </c>
-      <c r="AR17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>52</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BO17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BP17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BQ17" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BR17" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BS17" t="n">
-        <v>60</v>
+        <v>66.67</v>
       </c>
       <c r="BT17" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BU17" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7630,7 +7630,7 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BY17" t="n">
         <v>2.76</v>
@@ -7639,55 +7639,55 @@
         <v>3.12</v>
       </c>
       <c r="CA17" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.02</v>
+        <v>3.15</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.84</v>
+        <v>3.83</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.22</v>
+        <v>4.32</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.49</v>
+        <v>1.24</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.37</v>
+        <v>2.8</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.35</v>
+        <v>1.96</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.76</v>
+        <v>1.47</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.94</v>
+        <v>1.62</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.63</v>
+        <v>1.36</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.29</v>
+        <v>1.91</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.09</v>
+        <v>1.74</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.71</v>
+        <v>1.42</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.68</v>
+        <v>3.9</v>
       </c>
       <c r="CR17" t="n">
         <v>1.55</v>
@@ -7725,79 +7725,79 @@
         <v>4.8</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DF17" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.8</v>
+        <v>3.17</v>
       </c>
       <c r="DH17" t="n">
-        <v>96.8</v>
+        <v>98.66</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.8</v>
+        <v>4.33</v>
       </c>
       <c r="DK17" t="n">
-        <v>6</v>
+        <v>5.34</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DM17" t="n">
-        <v>63.6</v>
+        <v>56.84</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="DP17" t="n">
-        <v>7.2</v>
+        <v>5.83</v>
       </c>
       <c r="DQ17" t="n">
-        <v>1.6</v>
+        <v>1.16</v>
       </c>
       <c r="DR17" t="n">
-        <v>6</v>
+        <v>4.84</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50</v>
+        <v>50.17</v>
       </c>
       <c r="DW17" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="DX17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="DY17" t="n">
-        <v>5.8</v>
+        <v>5.16</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.2</v>
+        <v>3.83</v>
       </c>
       <c r="EA17" t="n">
-        <v>13.6</v>
+        <v>11.16</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.39</v>
+        <v>1.25</v>
       </c>
       <c r="EC17" t="n">
-        <v>3.8</v>
+        <v>3.67</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
@@ -1379,61 +1379,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="F2" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="G2" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>97</v>
+        <v>96.5</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="K2" t="n">
-        <v>4.67</v>
+        <v>4.25</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>54.33</v>
+        <v>41.75</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="O2" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
-        <v>14.67</v>
+        <v>13.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="R2" t="n">
-        <v>8.33</v>
+        <v>8.25</v>
       </c>
       <c r="S2" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>61.67</v>
+        <v>58.75</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="Z2" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AC2" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AE2" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>0.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>9</v>
+        <v>9.33</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BP2" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>66.67</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>33.33</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="BZ2" t="n">
         <v>3.4</v>
       </c>
-      <c r="BQ2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>80</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>80</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>80</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>40</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>2.8</v>
-      </c>
       <c r="CA2" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.11</v>
+        <v>3.19</v>
       </c>
       <c r="CC2" t="n">
         <v>2.68</v>
@@ -1625,117 +1625,117 @@
         <v>1.5</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.39</v>
+        <v>3.32</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.39</v>
+        <v>2.43</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CN2" t="n">
         <v>1.72</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CS2" t="inlineStr"/>
       <c r="CT2" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="CU2" t="inlineStr"/>
       <c r="CV2" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.95</v>
+        <v>2.03</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="DB2" t="n">
         <v>1.48</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.91</v>
+        <v>4.84</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="DH2" t="n">
-        <v>97.40000000000001</v>
+        <v>97</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="DK2" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="DL2" t="n">
         <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>53</v>
+        <v>44.83</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="DP2" t="n">
-        <v>10.2</v>
+        <v>10.17</v>
       </c>
       <c r="DQ2" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
@@ -1747,28 +1747,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>57.8</v>
+        <v>56.5</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="DX2" t="n">
-        <v>9.6</v>
+        <v>9.33</v>
       </c>
       <c r="DY2" t="n">
-        <v>5.2</v>
+        <v>5.17</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.4</v>
+        <v>4.17</v>
       </c>
       <c r="EA2" t="n">
-        <v>11.2</v>
+        <v>12.67</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="3">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -1790,49 +1790,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="H3" t="n">
-        <v>79.67</v>
+        <v>78</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>35.33</v>
+        <v>37.75</v>
       </c>
       <c r="N3" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>8.33</v>
+        <v>6</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="R3" t="n">
-        <v>5.33</v>
+        <v>3.75</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1844,28 +1844,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>46.67</v>
+        <v>45.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.33</v>
+        <v>3.75</v>
       </c>
       <c r="AC3" t="n">
-        <v>14.33</v>
+        <v>10.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.01</v>
+        <v>0.97</v>
       </c>
       <c r="AE3" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1949,46 +1949,46 @@
         <v>3</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="BN3" t="n">
         <v>1</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="BR3" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BS3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BT3" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
@@ -2000,19 +2000,19 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.27</v>
+        <v>3.16</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.07</v>
+        <v>3.79</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.17</v>
+        <v>3.13</v>
       </c>
       <c r="CC3" t="n">
         <v>2.62</v>
@@ -2021,46 +2021,46 @@
         <v>2.74</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.71</v>
+        <v>2.82</v>
       </c>
       <c r="CG3" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.66</v>
+        <v>3.84</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CS3" t="inlineStr"/>
       <c r="CT3" t="n">
@@ -2068,73 +2068,73 @@
       </c>
       <c r="CU3" t="inlineStr"/>
       <c r="CV3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DB3" t="n">
         <v>1.49</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="DD3" t="n">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="DH3" t="n">
-        <v>95.2</v>
+        <v>91.5</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="DK3" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>37</v>
+        <v>38.33</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="DO3" t="n">
         <v>1</v>
       </c>
       <c r="DP3" t="n">
-        <v>7</v>
+        <v>5.67</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="DR3" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2146,28 +2146,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DX3" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="DY3" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="EA3" t="n">
-        <v>14.2</v>
+        <v>11.67</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="EC3" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -2177,10 +2177,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -2189,46 +2189,46 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>2.33</v>
       </c>
       <c r="H4" t="n">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>5.33</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="M4" t="n">
-        <v>35.5</v>
+        <v>56.33</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="O4" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.5</v>
+        <v>-0.67</v>
       </c>
       <c r="R4" t="n">
-        <v>12</v>
+        <v>7.67</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -2243,25 +2243,25 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>35.5</v>
+        <v>39.67</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>8</v>
+        <v>7.33</v>
       </c>
       <c r="AA4" t="n">
-        <v>5</v>
+        <v>3.67</v>
       </c>
       <c r="AB4" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="AC4" t="n">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.98</v>
+        <v>1.13</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -2348,49 +2348,49 @@
         <v>0.67</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="BH4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.33</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="BJ4" t="n">
         <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.2</v>
+        <v>4.67</v>
       </c>
       <c r="BR4" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BS4" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BT4" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BU4" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2399,19 +2399,19 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>20</v>
+        <v>33.33</v>
       </c>
       <c r="BY4" t="n">
-        <v>4.42</v>
+        <v>3.66</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4.9</v>
+        <v>4.04</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.35</v>
+        <v>3.27</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="CC4" t="n">
         <v>3.5</v>
@@ -2423,13 +2423,13 @@
         <v>1.49</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="CG4" t="n">
         <v>2.4</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CI4" t="n">
         <v>1.66</v>
@@ -2438,34 +2438,34 @@
         <v>2.07</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.47</v>
+        <v>4.6</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CS4" t="n">
         <v>2.91</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="CU4" t="n">
         <v>1.4</v>
@@ -2477,100 +2477,100 @@
         <v>2.16</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.13</v>
+        <v>2.07</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="DH4" t="n">
-        <v>84.40000000000001</v>
+        <v>91.34</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="DK4" t="n">
-        <v>2.6</v>
+        <v>3.67</v>
       </c>
       <c r="DL4" t="n">
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="DM4" t="n">
-        <v>46</v>
+        <v>54.66</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.2</v>
+        <v>1.66</v>
       </c>
       <c r="DP4" t="n">
-        <v>7.6</v>
+        <v>6.16</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>-0.17</v>
       </c>
       <c r="DR4" t="n">
-        <v>9</v>
+        <v>7.34</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>36.6</v>
+        <v>38.5</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>10</v>
+        <v>9.33</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.2</v>
+        <v>5.34</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="EA4" t="n">
-        <v>14.4</v>
+        <v>11.83</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="5">
@@ -2580,61 +2580,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="F5" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="H5" t="n">
-        <v>96.67</v>
+        <v>91</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="M5" t="n">
-        <v>48.33</v>
+        <v>50.25</v>
       </c>
       <c r="N5" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="O5" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="P5" t="n">
-        <v>12.67</v>
+        <v>13.75</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="R5" t="n">
-        <v>3.67</v>
+        <v>4.75</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2646,28 +2646,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>36.33</v>
+        <v>39.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.33</v>
+        <v>9.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.33</v>
+        <v>6.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AC5" t="n">
-        <v>21.67</v>
+        <v>23</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2751,46 +2751,46 @@
         <v>3.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="BH5" t="n">
-        <v>7.4</v>
+        <v>7.33</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.6</v>
+        <v>3.83</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BT5" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BU5" t="n">
         <v>0</v>
@@ -2802,19 +2802,19 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.74</v>
+        <v>3.46</v>
       </c>
       <c r="CA5" t="n">
         <v>2.89</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CC5" t="n">
         <v>3.92</v>
@@ -2826,10 +2826,10 @@
         <v>1.55</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CH5" t="n">
         <v>1.23</v>
@@ -2838,54 +2838,54 @@
         <v>1.68</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CL5" t="n">
         <v>2.2</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="CQ5" t="n">
-        <v>5.03</v>
+        <v>4.99</v>
       </c>
       <c r="CR5" t="n">
         <v>1.58</v>
       </c>
       <c r="CS5" t="inlineStr"/>
       <c r="CT5" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CU5" t="inlineStr"/>
       <c r="CV5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CX5" t="n">
         <v>1.78</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CZ5" t="n">
         <v>2</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="DB5" t="n">
         <v>1.55</v>
@@ -2894,19 +2894,19 @@
         <v>2.71</v>
       </c>
       <c r="DD5" t="n">
-        <v>5.43</v>
+        <v>5.41</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF5" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="DH5" t="n">
-        <v>99.40000000000001</v>
+        <v>95.17</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
@@ -2915,28 +2915,28 @@
         <v>4</v>
       </c>
       <c r="DK5" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DM5" t="n">
-        <v>51</v>
+        <v>51.83</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.2</v>
+        <v>13.83</v>
       </c>
       <c r="DQ5" t="n">
-        <v>3.6</v>
+        <v>3.33</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
@@ -2948,28 +2948,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>39.6</v>
+        <v>41</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="DY5" t="n">
-        <v>9</v>
+        <v>8.33</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.2</v>
+        <v>2.67</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.2</v>
+        <v>22.17</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="EC5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="6">
@@ -2979,13 +2979,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3075,10 +3075,10 @@
         <v>2</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
@@ -3087,34 +3087,34 @@
         <v>3</v>
       </c>
       <c r="AL6" t="n">
-        <v>6.33</v>
+        <v>5.5</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>56.33</v>
+        <v>64.25</v>
       </c>
       <c r="AO6" t="n">
         <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.67</v>
+        <v>6.25</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.33</v>
+        <v>4.5</v>
       </c>
       <c r="AT6" t="n">
         <v>1</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3126,7 +3126,7 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>44.33</v>
+        <v>46.25</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -3135,64 +3135,64 @@
         <v>9</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.33</v>
+        <v>5.25</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.67</v>
+        <v>3.75</v>
       </c>
       <c r="BD6" t="n">
-        <v>12</v>
+        <v>8.75</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="BF6" t="n">
         <v>3</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.6</v>
+        <v>10.83</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="BP6" t="n">
         <v>5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.6</v>
+        <v>5.83</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BT6" t="n">
-        <v>20</v>
+        <v>33.33</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3201,7 +3201,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>20</v>
+        <v>33.33</v>
       </c>
       <c r="BY6" t="n">
         <v>2.69</v>
@@ -3210,136 +3210,136 @@
         <v>3.28</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.07</v>
+        <v>3.04</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.44</v>
+        <v>3.29</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.77</v>
+        <v>3.69</v>
       </c>
       <c r="CE6" t="n">
         <v>1.5</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CO6" t="n">
         <v>1.43</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.49</v>
+        <v>4.61</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="CS6" t="n">
         <v>3.27</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="CU6" t="n">
         <v>1.33</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.37</v>
+        <v>2.41</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.48</v>
+        <v>4.61</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="DG6" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="DH6" t="n">
-        <v>89.40000000000001</v>
+        <v>99</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="DK6" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="DL6" t="n">
         <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>58.6</v>
+        <v>63.5</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="DO6" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DP6" t="n">
-        <v>10</v>
+        <v>8.17</v>
       </c>
       <c r="DQ6" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3351,28 +3351,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>46.2</v>
+        <v>47.17</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="DZ6" t="n">
-        <v>2.4</v>
+        <v>3.17</v>
       </c>
       <c r="EA6" t="n">
-        <v>17.4</v>
+        <v>14.33</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="7">
@@ -3785,13 +3785,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
         <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3875,52 +3875,52 @@
         <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AI8" t="n">
-        <v>115</v>
+        <v>108.75</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>53</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" t="n">
         <v>2</v>
       </c>
-      <c r="AL8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>53.33</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>2.33</v>
-      </c>
       <c r="AQ8" t="n">
-        <v>10</v>
+        <v>7.25</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="AS8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
         <v>1</v>
       </c>
       <c r="AU8" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3932,70 +3932,70 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>51.33</v>
+        <v>48.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BA8" t="n">
-        <v>10</v>
+        <v>8.25</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.67</v>
+        <v>5.75</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.33</v>
+        <v>2.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.26</v>
+        <v>1.09</v>
       </c>
       <c r="BF8" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="BH8" t="n">
-        <v>10.4</v>
+        <v>9.67</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.4</v>
+        <v>4.17</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="BR8" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BS8" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BT8" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -4007,7 +4007,7 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BY8" t="n">
         <v>2.01</v>
@@ -4016,55 +4016,55 @@
         <v>1.99</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.83</v>
+        <v>3.04</v>
       </c>
       <c r="CE8" t="n">
         <v>1.47</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="CH8" t="n">
         <v>1.29</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK8" t="n">
         <v>1.65</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="CR8" t="n">
         <v>1.45</v>
@@ -4100,52 +4100,52 @@
         <v>1.42</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.41</v>
+        <v>4.44</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="DH8" t="n">
-        <v>114.4</v>
+        <v>110.33</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.2</v>
+        <v>4.83</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="DM8" t="n">
-        <v>56.4</v>
+        <v>55.67</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.4</v>
+        <v>0.83</v>
       </c>
       <c r="DO8" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="DP8" t="n">
-        <v>7.6</v>
+        <v>6.17</v>
       </c>
       <c r="DQ8" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="DR8" t="n">
-        <v>5.8</v>
+        <v>4.67</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4157,28 +4157,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>54.8</v>
+        <v>52.33</v>
       </c>
       <c r="DW8" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.2</v>
+        <v>11.5</v>
       </c>
       <c r="DY8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="EA8" t="n">
-        <v>13.8</v>
+        <v>11.33</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="EC8" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="9">
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -4200,82 +4200,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>102</v>
+        <v>107.67</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>45.5</v>
+        <v>56.67</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="O9" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="P9" t="n">
-        <v>12</v>
+        <v>7.67</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="R9" t="n">
-        <v>9</v>
+        <v>5.67</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>61</v>
+        <v>60.67</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AA9" t="n">
-        <v>11.5</v>
+        <v>9.67</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.5</v>
+        <v>5.33</v>
       </c>
       <c r="AC9" t="n">
-        <v>25</v>
+        <v>16.33</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AF9" t="n">
         <v>0.33</v>
@@ -4359,70 +4359,70 @@
         <v>2.67</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>11.2</v>
+        <v>10.33</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.6</v>
+        <v>5.17</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.6</v>
+        <v>5.17</v>
       </c>
       <c r="BR9" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BS9" t="n">
-        <v>80</v>
+        <v>66.67</v>
       </c>
       <c r="BT9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BV9" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BW9" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BX9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.42</v>
+        <v>3.37</v>
       </c>
       <c r="CC9" t="n">
         <v>4.69</v>
@@ -4434,40 +4434,40 @@
         <v>1.45</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CH9" t="n">
         <v>1.29</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="CO9" t="n">
         <v>1.38</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.05</v>
+        <v>4.08</v>
       </c>
       <c r="CR9" t="n">
         <v>1.47</v>
@@ -4482,106 +4482,106 @@
         <v>1.32</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.37</v>
+        <v>4.4</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.6</v>
+        <v>1.34</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.8</v>
+        <v>3.33</v>
       </c>
       <c r="DH9" t="n">
-        <v>101.2</v>
+        <v>104.17</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="DK9" t="n">
-        <v>6.4</v>
+        <v>5.83</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DM9" t="n">
-        <v>44.4</v>
+        <v>50.17</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="DP9" t="n">
-        <v>15</v>
+        <v>12.34</v>
       </c>
       <c r="DQ9" t="n">
-        <v>1.2</v>
+        <v>0.84</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>54.2</v>
+        <v>55.17</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>14</v>
+        <v>13.84</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.4</v>
+        <v>4.83</v>
       </c>
       <c r="EA9" t="n">
-        <v>23.6</v>
+        <v>19.5</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="10">
@@ -5439,13 +5439,13 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>7.33</v>
+        <v>10</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.67</v>
+        <v>2.33</v>
       </c>
       <c r="R12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="S12" t="n">
         <v>0.67</v>
@@ -5463,25 +5463,25 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>57.67</v>
+        <v>60</v>
       </c>
       <c r="Y12" t="n">
         <v>0.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>11.33</v>
+        <v>12</v>
       </c>
       <c r="AA12" t="n">
-        <v>7</v>
+        <v>8.67</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.33</v>
+        <v>3.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>13.67</v>
+        <v>19.33</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="AE12" t="n">
         <v>2.67</v>
@@ -5751,13 +5751,13 @@
         <v>2.5</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.17</v>
+        <v>11.5</v>
       </c>
       <c r="DQ12" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="DR12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5769,25 +5769,25 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>60.17</v>
+        <v>61.34</v>
       </c>
       <c r="DW12" t="n">
         <v>0.16</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.83</v>
+        <v>12.16</v>
       </c>
       <c r="DY12" t="n">
-        <v>6.84</v>
+        <v>7.67</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.17</v>
+        <v>23</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="EC12" t="n">
         <v>2.17</v>
@@ -5800,13 +5800,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
         <v>3</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>0.67</v>
@@ -5896,43 +5896,43 @@
         <v>2</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.5</v>
+        <v>2.33</v>
       </c>
       <c r="AI13" t="n">
-        <v>91.5</v>
+        <v>101</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AL13" t="n">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>33.5</v>
+        <v>28.33</v>
       </c>
       <c r="AO13" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP13" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR13" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="AS13" t="n">
-        <v>8</v>
+        <v>8.33</v>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AU13" t="n">
         <v>1</v>
@@ -5947,73 +5947,73 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="BA13" t="n">
         <v>15</v>
       </c>
       <c r="BB13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD13" t="n">
-        <v>24</v>
+        <v>23.67</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="BH13" t="n">
-        <v>9</v>
+        <v>9.33</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="BL13" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="BO13" t="n">
         <v>1</v>
       </c>
       <c r="BP13" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.2</v>
+        <v>3.67</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>80</v>
+        <v>66.67</v>
       </c>
       <c r="BT13" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6022,7 +6022,7 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>80</v>
+        <v>66.67</v>
       </c>
       <c r="BY13" t="n">
         <v>1.59</v>
@@ -6031,19 +6031,19 @@
         <v>1.64</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.69</v>
+        <v>3.64</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.18</v>
+        <v>2.01</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="CF13" t="n">
         <v>3</v>
@@ -6058,13 +6058,13 @@
         <v>1.71</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="CM13" t="n">
         <v>2.09</v>
@@ -6073,64 +6073,64 @@
         <v>1.67</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.73</v>
+        <v>3.87</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="CS13" t="n">
         <v>3.11</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.79</v>
+        <v>2.72</v>
       </c>
       <c r="CU13" t="n">
         <v>1.35</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.17</v>
+        <v>2.13</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="DD13" t="n">
-        <v>3.94</v>
+        <v>4.04</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="DG13" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="DH13" t="n">
-        <v>103.4</v>
+        <v>106.16</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
@@ -6139,28 +6139,28 @@
         <v>2</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.2</v>
+        <v>5.66</v>
       </c>
       <c r="DL13" t="n">
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>35</v>
+        <v>32.16</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DO13" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="DP13" t="n">
-        <v>10</v>
+        <v>9.67</v>
       </c>
       <c r="DQ13" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.6</v>
+        <v>7.83</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
@@ -6172,28 +6172,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.6</v>
+        <v>53</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.2</v>
+        <v>12.66</v>
       </c>
       <c r="DY13" t="n">
-        <v>8</v>
+        <v>8.17</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="EA13" t="n">
-        <v>24.6</v>
+        <v>24.33</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="14">
@@ -6203,13 +6203,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
         <v>3</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
         <v>0.33</v>
@@ -6296,46 +6296,46 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>89.67</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>54</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP14" t="n">
         <v>2</v>
       </c>
-      <c r="AH14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>88.5</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
+      <c r="AQ14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR14" t="n">
         <v>3</v>
       </c>
-      <c r="AL14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>7.33</v>
       </c>
       <c r="AT14" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AU14" t="n">
         <v>1</v>
@@ -6350,73 +6350,73 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>40.5</v>
+        <v>44.33</v>
       </c>
       <c r="AZ14" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ14" t="n">
         <v>0.5</v>
       </c>
-      <c r="BA14" t="n">
-        <v>5</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0.6</v>
-      </c>
       <c r="BK14" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>80</v>
+        <v>66.67</v>
       </c>
       <c r="BT14" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BU14" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6425,7 +6425,7 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BY14" t="n">
         <v>3.73</v>
@@ -6434,133 +6434,133 @@
         <v>3.91</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.31</v>
+        <v>3.24</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.18</v>
+        <v>3.07</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.58</v>
+        <v>3.39</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.09</v>
+        <v>3.16</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CI14" t="n">
         <v>1.75</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CL14" t="n">
         <v>2.2</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4</v>
+        <v>4.13</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CS14" t="n">
         <v>3.36</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="CU14" t="n">
         <v>1.31</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="DD14" t="n">
-        <v>4.31</v>
+        <v>4.48</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DF14" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.4</v>
+        <v>1.84</v>
       </c>
       <c r="DH14" t="n">
-        <v>97.2</v>
+        <v>96.34</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DJ14" t="n">
-        <v>4.2</v>
+        <v>3.67</v>
       </c>
       <c r="DK14" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="DL14" t="n">
         <v>0</v>
       </c>
       <c r="DM14" t="n">
-        <v>43.6</v>
+        <v>47.5</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="DP14" t="n">
-        <v>11.6</v>
+        <v>12.34</v>
       </c>
       <c r="DQ14" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="DR14" t="n">
         <v>8</v>
@@ -6575,28 +6575,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>45.4</v>
+        <v>46.5</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.8</v>
+        <v>0.66</v>
       </c>
       <c r="DX14" t="n">
-        <v>7</v>
+        <v>7.33</v>
       </c>
       <c r="DY14" t="n">
-        <v>4.4</v>
+        <v>4.67</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="EA14" t="n">
-        <v>17</v>
+        <v>17.34</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="15">
@@ -6606,13 +6606,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
         <v>3</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6696,16 +6696,16 @@
         <v>2.67</v>
       </c>
       <c r="AF15" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AH15" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="AI15" t="n">
-        <v>96.5</v>
+        <v>93.67</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
@@ -6714,34 +6714,34 @@
         <v>4</v>
       </c>
       <c r="AL15" t="n">
-        <v>5</v>
+        <v>6.33</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AN15" t="n">
-        <v>57.5</v>
+        <v>56</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP15" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="AQ15" t="n">
-        <v>13</v>
+        <v>8.33</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.5</v>
+        <v>4.67</v>
       </c>
       <c r="AT15" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AU15" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6753,82 +6753,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>35</v>
+        <v>42.67</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BB15" t="n">
-        <v>5</v>
+        <v>5.67</v>
       </c>
       <c r="BC15" t="n">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="BD15" t="n">
-        <v>17.5</v>
+        <v>11.33</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.27</v>
+        <v>1.48</v>
       </c>
       <c r="BF15" t="n">
         <v>4</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.6</v>
+        <v>11.83</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BL15" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.8</v>
+        <v>4.83</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>80</v>
+        <v>66.67</v>
       </c>
       <c r="BT15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BV15" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BW15" t="n">
-        <v>20</v>
+        <v>16.67</v>
       </c>
       <c r="BX15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BY15" t="n">
         <v>2.16</v>
@@ -6837,132 +6837,132 @@
         <v>2.34</v>
       </c>
       <c r="CA15" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="CB15" t="n">
         <v>3.18</v>
       </c>
-      <c r="CB15" t="n">
-        <v>3.23</v>
-      </c>
       <c r="CC15" t="n">
-        <v>4.58</v>
+        <v>3.94</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.89</v>
+        <v>4.17</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.73</v>
+        <v>2.83</v>
       </c>
       <c r="CG15" t="n">
-        <v>1.91</v>
+        <v>2.01</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.99</v>
+        <v>1.04</v>
       </c>
       <c r="CI15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CJ15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="CK15" t="n">
         <v>1.34</v>
       </c>
-      <c r="CJ15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CK15" t="n">
-        <v>1.29</v>
-      </c>
       <c r="CL15" t="n">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="CM15" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CS15" t="inlineStr"/>
       <c r="CT15" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CU15" t="inlineStr"/>
       <c r="CV15" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CW15" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="CX15" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CY15" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CZ15" t="n">
         <v>2.13</v>
-      </c>
-      <c r="CX15" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CY15" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="CZ15" t="n">
-        <v>2.12</v>
       </c>
       <c r="DA15" t="n">
         <v>1.69</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="DD15" t="n">
-        <v>5.05</v>
+        <v>4.99</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.4</v>
+        <v>0.34</v>
       </c>
       <c r="DF15" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="DH15" t="n">
-        <v>92</v>
+        <v>91.34</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="DK15" t="n">
-        <v>6.4</v>
+        <v>6.83</v>
       </c>
       <c r="DL15" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="DM15" t="n">
-        <v>62</v>
+        <v>60.5</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DO15" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="DP15" t="n">
-        <v>12</v>
+        <v>9.83</v>
       </c>
       <c r="DQ15" t="n">
-        <v>3</v>
+        <v>2.34</v>
       </c>
       <c r="DR15" t="n">
-        <v>7</v>
+        <v>5.67</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6974,28 +6974,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>44.6</v>
+        <v>46.84</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>13.8</v>
+        <v>14</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.6</v>
+        <v>8.33</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.2</v>
+        <v>5.66</v>
       </c>
       <c r="EA15" t="n">
-        <v>23.4</v>
+        <v>19.33</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="16">
@@ -7531,13 +7531,13 @@
         <v>1.33</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.33</v>
+        <v>7.67</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AS17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AT17" t="n">
         <v>1</v>
@@ -7555,25 +7555,25 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>51.67</v>
+        <v>49.33</v>
       </c>
       <c r="AZ17" t="n">
         <v>0.67</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.33</v>
+        <v>7.67</v>
       </c>
       <c r="BB17" t="n">
-        <v>4</v>
+        <v>5.33</v>
       </c>
       <c r="BC17" t="n">
         <v>2.33</v>
       </c>
       <c r="BD17" t="n">
-        <v>6</v>
+        <v>13.67</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.87</v>
+        <v>0.95</v>
       </c>
       <c r="BF17" t="n">
         <v>4</v>
@@ -7758,13 +7758,13 @@
         <v>2.16</v>
       </c>
       <c r="DP17" t="n">
-        <v>5.83</v>
+        <v>8</v>
       </c>
       <c r="DQ17" t="n">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="DR17" t="n">
-        <v>4.84</v>
+        <v>6.84</v>
       </c>
       <c r="DS17" t="n">
         <v>0.16</v>
@@ -7776,25 +7776,25 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>50.17</v>
+        <v>49</v>
       </c>
       <c r="DW17" t="n">
         <v>0.34</v>
       </c>
       <c r="DX17" t="n">
-        <v>9</v>
+        <v>9.67</v>
       </c>
       <c r="DY17" t="n">
-        <v>5.16</v>
+        <v>5.83</v>
       </c>
       <c r="DZ17" t="n">
         <v>3.83</v>
       </c>
       <c r="EA17" t="n">
-        <v>11.16</v>
+        <v>15</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="EC17" t="n">
         <v>3.67</v>

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
@@ -1820,13 +1820,13 @@
         <v>1.25</v>
       </c>
       <c r="P3" t="n">
-        <v>6</v>
+        <v>8.75</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.25</v>
+        <v>0.75</v>
       </c>
       <c r="R3" t="n">
-        <v>3.75</v>
+        <v>6.5</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -1844,25 +1844,25 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>45.5</v>
+        <v>47</v>
       </c>
       <c r="Y3" t="n">
         <v>0.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>6.75</v>
+        <v>7.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.5</v>
+        <v>18.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.97</v>
+        <v>1.02</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -2128,13 +2128,13 @@
         <v>1</v>
       </c>
       <c r="DP3" t="n">
-        <v>5.67</v>
+        <v>7.5</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0.17</v>
+        <v>0.5</v>
       </c>
       <c r="DR3" t="n">
-        <v>4.5</v>
+        <v>6.33</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2146,25 +2146,25 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="DW3" t="n">
         <v>0.17</v>
       </c>
       <c r="DX3" t="n">
-        <v>6.5</v>
+        <v>6.83</v>
       </c>
       <c r="DY3" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="EA3" t="n">
-        <v>11.67</v>
+        <v>16.83</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="EC3" t="n">
         <v>3</v>
@@ -2219,13 +2219,13 @@
         <v>3</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.67</v>
+        <v>0.67</v>
       </c>
       <c r="R4" t="n">
-        <v>7.67</v>
+        <v>10.33</v>
       </c>
       <c r="S4" t="n">
         <v>1.67</v>
@@ -2243,25 +2243,25 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>39.67</v>
+        <v>39</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.33</v>
+        <v>9</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.67</v>
+        <v>5.33</v>
       </c>
       <c r="AB4" t="n">
         <v>3.67</v>
       </c>
       <c r="AC4" t="n">
-        <v>6.33</v>
+        <v>16</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -2531,13 +2531,13 @@
         <v>1.66</v>
       </c>
       <c r="DP4" t="n">
-        <v>6.16</v>
+        <v>7.66</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0.17</v>
+        <v>0.5</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.34</v>
+        <v>8.67</v>
       </c>
       <c r="DS4" t="n">
         <v>0.16</v>
@@ -2549,25 +2549,25 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>38.5</v>
+        <v>38.16</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.33</v>
+        <v>10.17</v>
       </c>
       <c r="DY4" t="n">
-        <v>5.34</v>
+        <v>6.16</v>
       </c>
       <c r="DZ4" t="n">
         <v>4</v>
       </c>
       <c r="EA4" t="n">
-        <v>11.83</v>
+        <v>16.66</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="EC4" t="n">
         <v>1.34</v>
@@ -3102,13 +3102,13 @@
         <v>2.25</v>
       </c>
       <c r="AQ6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AS6" t="n">
         <v>6.25</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>4.5</v>
       </c>
       <c r="AT6" t="n">
         <v>1</v>
@@ -3126,25 +3126,25 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>46.25</v>
+        <v>46.75</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>9</v>
+        <v>10.25</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="BC6" t="n">
         <v>3.75</v>
       </c>
       <c r="BD6" t="n">
-        <v>8.75</v>
+        <v>16.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="BF6" t="n">
         <v>3</v>
@@ -3333,13 +3333,13 @@
         <v>1.83</v>
       </c>
       <c r="DP6" t="n">
-        <v>8.17</v>
+        <v>10.33</v>
       </c>
       <c r="DQ6" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="DR6" t="n">
-        <v>6</v>
+        <v>7.17</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3351,25 +3351,25 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>47.17</v>
+        <v>47.5</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>9.17</v>
+        <v>10</v>
       </c>
       <c r="DY6" t="n">
-        <v>6</v>
+        <v>6.83</v>
       </c>
       <c r="DZ6" t="n">
         <v>3.17</v>
       </c>
       <c r="EA6" t="n">
-        <v>14.33</v>
+        <v>19.5</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="EC6" t="n">
         <v>3.17</v>
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D7" t="n">
         <v>3</v>
@@ -3394,49 +3394,49 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H7" t="n">
+        <v>118.67</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="K7" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H7" t="n">
-        <v>126</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="K7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.5</v>
-      </c>
       <c r="M7" t="n">
-        <v>70.5</v>
+        <v>59.67</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="O7" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
-        <v>3.5</v>
+        <v>6.33</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.5</v>
+        <v>0.33</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5</v>
+        <v>4.67</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3448,28 +3448,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>61.5</v>
+        <v>57</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.5</v>
+        <v>11.33</v>
       </c>
       <c r="AA7" t="n">
-        <v>5</v>
+        <v>5.67</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.5</v>
+        <v>5.67</v>
       </c>
       <c r="AC7" t="n">
-        <v>12</v>
+        <v>16.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.5</v>
+        <v>2.67</v>
       </c>
       <c r="AF7" t="n">
         <v>0.33</v>
@@ -3553,70 +3553,70 @@
         <v>1.67</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="BH7" t="n">
-        <v>8.4</v>
+        <v>7.67</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.2</v>
+        <v>4.83</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>80</v>
+        <v>83.33</v>
       </c>
       <c r="BT7" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CC7" t="n">
         <v>3.69</v>
@@ -3628,31 +3628,31 @@
         <v>1.51</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.26</v>
+        <v>3.29</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.12</v>
+        <v>2.07</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CO7" t="n">
         <v>1.46</v>
@@ -3679,22 +3679,22 @@
         <v>1.74</v>
       </c>
       <c r="CW7" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="DC7" t="n">
         <v>2.5</v>
@@ -3703,46 +3703,46 @@
         <v>4.84</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.2</v>
+        <v>1.66</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="DH7" t="n">
-        <v>100.6</v>
+        <v>101.17</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.6</v>
+        <v>3.17</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="DM7" t="n">
-        <v>54.4</v>
+        <v>51.67</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="DP7" t="n">
-        <v>10</v>
+        <v>10.33</v>
       </c>
       <c r="DQ7" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="DR7" t="n">
-        <v>6</v>
+        <v>6.84</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3754,28 +3754,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>56.8</v>
+        <v>55.34</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="DX7" t="n">
-        <v>7.4</v>
+        <v>8.33</v>
       </c>
       <c r="DY7" t="n">
-        <v>4.2</v>
+        <v>4.67</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.2</v>
+        <v>3.67</v>
       </c>
       <c r="EA7" t="n">
-        <v>19.2</v>
+        <v>20.16</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.6</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="8">
@@ -3908,13 +3908,13 @@
         <v>2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.25</v>
+        <v>10.75</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AS8" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="AT8" t="n">
         <v>1</v>
@@ -3938,19 +3938,19 @@
         <v>0.25</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.25</v>
+        <v>9.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="BC8" t="n">
         <v>2.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>11</v>
+        <v>16.25</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="BF8" t="n">
         <v>2.5</v>
@@ -4139,13 +4139,13 @@
         <v>2.67</v>
       </c>
       <c r="DP8" t="n">
-        <v>6.17</v>
+        <v>8.5</v>
       </c>
       <c r="DQ8" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="DR8" t="n">
-        <v>4.67</v>
+        <v>7</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4163,19 +4163,19 @@
         <v>0.17</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.5</v>
+        <v>12.33</v>
       </c>
       <c r="DY8" t="n">
-        <v>8</v>
+        <v>8.83</v>
       </c>
       <c r="DZ8" t="n">
         <v>3.5</v>
       </c>
       <c r="EA8" t="n">
-        <v>11.33</v>
+        <v>14.83</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="EC8" t="n">
         <v>2.33</v>
@@ -4230,13 +4230,13 @@
         <v>2.33</v>
       </c>
       <c r="P9" t="n">
-        <v>7.67</v>
+        <v>11</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.67</v>
+        <v>1.33</v>
       </c>
       <c r="R9" t="n">
-        <v>5.67</v>
+        <v>8.33</v>
       </c>
       <c r="S9" t="n">
         <v>0.33</v>
@@ -4260,19 +4260,19 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA9" t="n">
-        <v>9.67</v>
+        <v>11</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="AC9" t="n">
-        <v>16.33</v>
+        <v>23.33</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AE9" t="n">
         <v>1.67</v>
@@ -4542,13 +4542,13 @@
         <v>2.5</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.34</v>
+        <v>14</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.84</v>
+        <v>1.16</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.5</v>
+        <v>8.83</v>
       </c>
       <c r="DS9" t="n">
         <v>0.34</v>
@@ -4566,19 +4566,19 @@
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.84</v>
+        <v>14.34</v>
       </c>
       <c r="DY9" t="n">
-        <v>9</v>
+        <v>9.67</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.83</v>
+        <v>4.66</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="EC9" t="n">
         <v>2.17</v>
@@ -4591,13 +4591,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4687,133 +4687,133 @@
         <v>3</v>
       </c>
       <c r="AH10" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" t="n">
-        <v>98.5</v>
+        <v>104.67</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AK10" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AL10" t="n">
         <v>3</v>
       </c>
       <c r="AM10" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>42.67</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>43.33</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>23.67</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ10" t="n">
         <v>1</v>
       </c>
-      <c r="AN10" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="AO10" t="n">
+      <c r="BK10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BN10" t="n">
         <v>1.5</v>
       </c>
-      <c r="AP10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU10" t="n">
+      <c r="BO10" t="n">
         <v>1.5</v>
       </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>39</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>1.4</v>
-      </c>
       <c r="BP10" t="n">
-        <v>5.8</v>
+        <v>5.33</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.4</v>
+        <v>3.83</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>60</v>
+        <v>66.67</v>
       </c>
       <c r="BT10" t="n">
-        <v>60</v>
+        <v>66.67</v>
       </c>
       <c r="BU10" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="BV10" t="n">
-        <v>0</v>
+        <v>16.67</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>60</v>
+        <v>66.67</v>
       </c>
       <c r="BY10" t="n">
         <v>3.93</v>
@@ -4822,28 +4822,28 @@
         <v>5</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.47</v>
+        <v>3.39</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.77</v>
+        <v>3.65</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.92</v>
+        <v>5.08</v>
       </c>
       <c r="CD10" t="n">
-        <v>6.63</v>
+        <v>5.81</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.11</v>
+        <v>3.17</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CI10" t="n">
         <v>1.73</v>
@@ -4855,22 +4855,22 @@
         <v>1.52</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.01</v>
+        <v>1.98</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CN10" t="n">
         <v>1.85</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="CQ10" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="CR10" t="n">
         <v>1.46</v>
@@ -4885,10 +4885,10 @@
         <v>1.36</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CX10" t="n">
         <v>1.53</v>
@@ -4903,88 +4903,88 @@
         <v>1.88</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="DD10" t="n">
-        <v>4.1</v>
+        <v>4.23</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="DH10" t="n">
-        <v>100.2</v>
+        <v>103</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="DJ10" t="n">
-        <v>4</v>
+        <v>4.34</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.2</v>
+        <v>4.84</v>
       </c>
       <c r="DL10" t="n">
-        <v>1</v>
+        <v>0.84</v>
       </c>
       <c r="DM10" t="n">
-        <v>56</v>
+        <v>56.17</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.2</v>
+        <v>12</v>
       </c>
       <c r="DQ10" t="n">
-        <v>2.4</v>
+        <v>2.83</v>
       </c>
       <c r="DR10" t="n">
-        <v>9.4</v>
+        <v>8.5</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>47</v>
+        <v>47.83</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.2</v>
+        <v>10.66</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.4</v>
+        <v>5.34</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.8</v>
+        <v>5.33</v>
       </c>
       <c r="EA10" t="n">
-        <v>23.8</v>
+        <v>24</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="EC10" t="n">
-        <v>4</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="11">
@@ -4994,10 +4994,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>3</v>
@@ -5006,13 +5006,13 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="H11" t="n">
-        <v>103.5</v>
+        <v>84</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -5027,29 +5027,29 @@
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>65</v>
+        <v>44.67</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="O11" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="P11" t="n">
-        <v>11</v>
+        <v>10.33</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.5</v>
+        <v>4.67</v>
       </c>
       <c r="R11" t="n">
-        <v>6.5</v>
+        <v>8.67</v>
       </c>
       <c r="S11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="T11" t="n">
         <v>1</v>
       </c>
-      <c r="T11" t="n">
-        <v>1.5</v>
-      </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
@@ -5060,28 +5060,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>54</v>
+        <v>49.33</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.5</v>
+        <v>11.67</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.5</v>
+        <v>7.33</v>
       </c>
       <c r="AB11" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>28.5</v>
+        <v>27</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE11" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5165,46 +5165,46 @@
         <v>1.67</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.4</v>
+        <v>9.67</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="BN11" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BO11" t="n">
         <v>1</v>
       </c>
-      <c r="BO11" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BP11" t="n">
-        <v>4.4</v>
+        <v>4.67</v>
       </c>
       <c r="BQ11" t="n">
         <v>5</v>
       </c>
       <c r="BR11" t="n">
-        <v>100</v>
+        <v>83.33</v>
       </c>
       <c r="BS11" t="n">
-        <v>80</v>
+        <v>66.67</v>
       </c>
       <c r="BT11" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BU11" t="n">
         <v>0</v>
@@ -5216,19 +5216,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CC11" t="n">
         <v>2.12</v>
@@ -5237,43 +5237,43 @@
         <v>2.13</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.33</v>
+        <v>3.27</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CJ11" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="CK11" t="n">
         <v>1.66</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="CM11" t="n">
         <v>2.1</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.34</v>
+        <v>4.24</v>
       </c>
       <c r="CR11" t="n">
         <v>1.49</v>
@@ -5288,73 +5288,73 @@
         <v>1.34</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY11" t="n">
         <v>2.07</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DA11" t="n">
         <v>1.72</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.48</v>
+        <v>4.35</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="DH11" t="n">
-        <v>99.2</v>
+        <v>90.16</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.8</v>
+        <v>0.84</v>
       </c>
       <c r="DM11" t="n">
-        <v>57</v>
+        <v>48.17</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="DO11" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="DP11" t="n">
         <v>9</v>
       </c>
       <c r="DQ11" t="n">
-        <v>4.6</v>
+        <v>4.34</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.8</v>
+        <v>8.67</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5366,28 +5366,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>51</v>
+        <v>49.16</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.6</v>
+        <v>11.17</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.4</v>
+        <v>7.33</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.2</v>
+        <v>3.83</v>
       </c>
       <c r="EA11" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="12">
@@ -6729,13 +6729,13 @@
         <v>2.67</v>
       </c>
       <c r="AQ15" t="n">
-        <v>8.33</v>
+        <v>15.33</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.67</v>
+        <v>1.67</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.67</v>
+        <v>7.33</v>
       </c>
       <c r="AT15" t="n">
         <v>0.67</v>
@@ -6753,7 +6753,7 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>42.67</v>
+        <v>40.67</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
@@ -6762,16 +6762,16 @@
         <v>11</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.67</v>
+        <v>6</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="BD15" t="n">
-        <v>11.33</v>
+        <v>20.67</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="BF15" t="n">
         <v>4</v>
@@ -6956,13 +6956,13 @@
         <v>3.33</v>
       </c>
       <c r="DP15" t="n">
-        <v>9.83</v>
+        <v>13.33</v>
       </c>
       <c r="DQ15" t="n">
-        <v>2.34</v>
+        <v>2.83</v>
       </c>
       <c r="DR15" t="n">
-        <v>5.67</v>
+        <v>7</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>46.84</v>
+        <v>45.84</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
@@ -6983,16 +6983,16 @@
         <v>14</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.33</v>
+        <v>8.5</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.66</v>
+        <v>5.5</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.33</v>
+        <v>24</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="EC15" t="n">
         <v>3.33</v>
@@ -7005,13 +7005,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
         <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
         <v>0.5</v>
@@ -7098,127 +7098,127 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AH16" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AI16" t="n">
-        <v>110.67</v>
+        <v>99</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.67</v>
+        <v>4.75</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AN16" t="n">
-        <v>55</v>
+        <v>42.75</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.67</v>
+        <v>12</v>
       </c>
       <c r="AR16" t="n">
         <v>2</v>
       </c>
       <c r="AS16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>54</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>23.25</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG16" t="n">
         <v>2.33</v>
       </c>
-      <c r="AT16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV16" t="n">
+      <c r="BH16" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL16" t="n">
         <v>0.33</v>
       </c>
-      <c r="AW16" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>52</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="BC16" t="n">
+      <c r="BM16" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BQ16" t="n">
         <v>4.33</v>
       </c>
-      <c r="BD16" t="n">
-        <v>22.67</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>3</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BR16" t="n">
-        <v>100</v>
+        <v>83.33</v>
       </c>
       <c r="BS16" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BT16" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BU16" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BV16" t="n">
         <v>0</v>
@@ -7227,7 +7227,7 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>40</v>
+        <v>33.33</v>
       </c>
       <c r="BY16" t="n">
         <v>1.88</v>
@@ -7236,55 +7236,55 @@
         <v>2.21</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.97</v>
+        <v>2.98</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CI16" t="n">
         <v>1.86</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CR16" t="n">
         <v>1.4</v>
@@ -7299,106 +7299,106 @@
         <v>1.38</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="DB16" t="n">
         <v>1.37</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.94</v>
+        <v>3.9</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="DG16" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="DH16" t="n">
-        <v>112.8</v>
+        <v>104.67</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>4.2</v>
+        <v>4.83</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DM16" t="n">
-        <v>56.6</v>
+        <v>48.17</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="DP16" t="n">
-        <v>8.6</v>
+        <v>9.83</v>
       </c>
       <c r="DQ16" t="n">
         <v>2</v>
       </c>
       <c r="DR16" t="n">
-        <v>3</v>
+        <v>3.83</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>52</v>
+        <v>53.33</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="DX16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.83</v>
       </c>
       <c r="DY16" t="n">
-        <v>5.2</v>
+        <v>6.17</v>
       </c>
       <c r="DZ16" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="EA16" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="EB16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="EC16" t="n">
         <v>4</v>
-      </c>
-      <c r="EA16" t="n">
-        <v>20.8</v>
-      </c>
-      <c r="EB16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="EC16" t="n">
-        <v>3.8</v>
       </c>
     </row>
     <row r="17">

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
@@ -2991,82 +2991,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5</v>
+        <v>2.67</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M6" t="n">
+        <v>61.67</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O6" t="n">
+        <v>2</v>
+      </c>
+      <c r="P6" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R6" t="n">
+        <v>5.67</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>49.33</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB6" t="n">
         <v>3</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>62</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q6" t="n">
+      <c r="AC6" t="n">
+        <v>16.67</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE6" t="n">
         <v>3</v>
-      </c>
-      <c r="R6" t="n">
-        <v>9</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>49</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>3.5</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3150,49 +3150,49 @@
         <v>3</v>
       </c>
       <c r="BG6" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.83</v>
+        <v>10.57</v>
       </c>
       <c r="BI6" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="BP6" t="n">
         <v>5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.83</v>
+        <v>5.57</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BT6" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BU6" t="n">
-        <v>16.67</v>
+        <v>28.57</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3201,19 +3201,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.69</v>
+        <v>2.95</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.28</v>
+        <v>3.33</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CC6" t="n">
         <v>3.29</v>
@@ -3222,34 +3222,34 @@
         <v>3.69</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="CO6" t="n">
         <v>1.43</v>
@@ -3258,37 +3258,37 @@
         <v>2.31</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.61</v>
+        <v>4.56</v>
       </c>
       <c r="CR6" t="n">
         <v>1.51</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CW6" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="DB6" t="n">
         <v>1.44</v>
@@ -3303,43 +3303,43 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="DH6" t="n">
-        <v>99</v>
+        <v>99.43000000000001</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.67</v>
+        <v>4.86</v>
       </c>
       <c r="DL6" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="DM6" t="n">
-        <v>63.5</v>
+        <v>63.14</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.33</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DQ6" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.17</v>
+        <v>6</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3351,28 +3351,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>47.5</v>
+        <v>47.86</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>10</v>
+        <v>10.14</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.83</v>
+        <v>6.71</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.17</v>
+        <v>3.43</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.5</v>
+        <v>16.57</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -3785,10 +3785,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
@@ -3797,49 +3797,49 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="H8" t="n">
-        <v>113.5</v>
+        <v>118.67</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="K8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>61</v>
+        <v>64.33</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>2.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="R8" t="n">
-        <v>4</v>
+        <v>2.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3851,28 +3851,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>60</v>
+        <v>56.33</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>18</v>
+        <v>13.67</v>
       </c>
       <c r="AA8" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.5</v>
+        <v>4.67</v>
       </c>
       <c r="AC8" t="n">
-        <v>12</v>
+        <v>7.67</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.96</v>
+        <v>1.66</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AF8" t="n">
         <v>0.25</v>
@@ -3956,46 +3956,46 @@
         <v>2.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.67</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.17</v>
+        <v>4.29</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.5</v>
+        <v>5.43</v>
       </c>
       <c r="BR8" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BT8" t="n">
-        <v>16.67</v>
+        <v>28.57</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -4007,19 +4007,19 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.01</v>
+        <v>2.57</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1.99</v>
+        <v>2.85</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="CC8" t="n">
         <v>2.86</v>
@@ -4031,19 +4031,19 @@
         <v>1.47</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="CH8" t="n">
         <v>1.29</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CK8" t="n">
         <v>1.65</v>
@@ -4052,19 +4052,19 @@
         <v>2.36</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CN8" t="n">
         <v>1.65</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CP8" t="n">
         <v>2.27</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.28</v>
+        <v>4.22</v>
       </c>
       <c r="CR8" t="n">
         <v>1.45</v>
@@ -4088,7 +4088,7 @@
         <v>1.68</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.12</v>
@@ -4100,52 +4100,52 @@
         <v>1.42</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.44</v>
+        <v>4.37</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DH8" t="n">
-        <v>110.33</v>
+        <v>113</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.83</v>
+        <v>4.71</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="DM8" t="n">
-        <v>55.67</v>
+        <v>57.86</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.67</v>
+        <v>2.72</v>
       </c>
       <c r="DP8" t="n">
-        <v>8.5</v>
+        <v>7.14</v>
       </c>
       <c r="DQ8" t="n">
-        <v>1.17</v>
+        <v>0.86</v>
       </c>
       <c r="DR8" t="n">
-        <v>7</v>
+        <v>5.86</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4157,28 +4157,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>52.33</v>
+        <v>51.86</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.33</v>
+        <v>11.29</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.83</v>
+        <v>7.86</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="EA8" t="n">
-        <v>14.83</v>
+        <v>12.57</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="9">
@@ -4188,13 +4188,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
         <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4278,139 +4278,139 @@
         <v>1.67</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.67</v>
+        <v>4</v>
       </c>
       <c r="AI9" t="n">
-        <v>100.67</v>
+        <v>100</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="AL9" t="n">
-        <v>7.33</v>
+        <v>6.25</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AN9" t="n">
-        <v>43.67</v>
+        <v>46</v>
       </c>
       <c r="AO9" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="AQ9" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.33</v>
+        <v>6.75</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>49.67</v>
+        <v>49.75</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>12.67</v>
+        <v>14</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.33</v>
+        <v>9.75</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="BD9" t="n">
-        <v>22.67</v>
+        <v>16.75</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.33</v>
+        <v>10.14</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.83</v>
+        <v>1.14</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.17</v>
+        <v>5.14</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.17</v>
+        <v>5</v>
       </c>
       <c r="BR9" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BU9" t="n">
-        <v>16.67</v>
+        <v>28.57</v>
       </c>
       <c r="BV9" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BW9" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BY9" t="n">
         <v>2.18</v>
@@ -4419,46 +4419,46 @@
         <v>2.08</v>
       </c>
       <c r="CA9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="CB9" t="n">
         <v>3.33</v>
       </c>
-      <c r="CB9" t="n">
-        <v>3.37</v>
-      </c>
       <c r="CC9" t="n">
-        <v>4.69</v>
+        <v>4.08</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.29</v>
+        <v>3.8</v>
       </c>
       <c r="CE9" t="n">
         <v>1.45</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CH9" t="n">
         <v>1.29</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="CO9" t="n">
         <v>1.38</v>
@@ -4467,16 +4467,16 @@
         <v>2.23</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.08</v>
+        <v>4.1</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.37</v>
+        <v>3.34</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="CU9" t="n">
         <v>1.32</v>
@@ -4485,103 +4485,103 @@
         <v>1.77</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="DB9" t="n">
         <v>1.42</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.4</v>
+        <v>4.44</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="DH9" t="n">
-        <v>104.17</v>
+        <v>103.29</v>
       </c>
       <c r="DI9" t="n">
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.83</v>
+        <v>5.43</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DM9" t="n">
-        <v>50.17</v>
+        <v>50.57</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.84</v>
+        <v>0.72</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.5</v>
+        <v>2.28</v>
       </c>
       <c r="DP9" t="n">
-        <v>14</v>
+        <v>11.86</v>
       </c>
       <c r="DQ9" t="n">
-        <v>1.16</v>
+        <v>0.86</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.83</v>
+        <v>7.43</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.34</v>
+        <v>0.43</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.34</v>
+        <v>0.43</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>55.17</v>
+        <v>54.43</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.34</v>
+        <v>14.86</v>
       </c>
       <c r="DY9" t="n">
-        <v>9.67</v>
+        <v>10.29</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.66</v>
+        <v>4.57</v>
       </c>
       <c r="EA9" t="n">
-        <v>23</v>
+        <v>19.57</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -5397,13 +5397,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" t="n">
         <v>3</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5487,52 +5487,52 @@
         <v>2.67</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>98.33</v>
+        <v>104</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AL12" t="n">
-        <v>6.33</v>
+        <v>6.25</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>37.33</v>
+        <v>49</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AP12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AR12" t="n">
         <v>3</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>4.33</v>
-      </c>
       <c r="AS12" t="n">
-        <v>6</v>
+        <v>4.25</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -5544,73 +5544,73 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>62.67</v>
+        <v>59.75</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>12.33</v>
+        <v>11</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.67</v>
+        <v>6.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.67</v>
+        <v>4.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>26.67</v>
+        <v>19.75</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="BH12" t="n">
-        <v>9</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BO12" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.67</v>
+        <v>4.71</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.33</v>
+        <v>4.43</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BU12" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5619,7 +5619,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BY12" t="n">
         <v>1.86</v>
@@ -5628,55 +5628,55 @@
         <v>1.81</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.68</v>
+        <v>3.61</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.92</v>
+        <v>3.83</v>
       </c>
       <c r="CC12" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CD12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CG12" t="n">
         <v>1.56</v>
       </c>
-      <c r="CD12" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CE12" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="CF12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="CG12" t="n">
-        <v>1.38</v>
-      </c>
       <c r="CH12" t="n">
-        <v>0.67</v>
+        <v>0.76</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.99</v>
+        <v>1.13</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.79</v>
+        <v>0.91</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.11</v>
+        <v>1.29</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.9</v>
+        <v>1.02</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.67</v>
+        <v>0.77</v>
       </c>
       <c r="CP12" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="CQ12" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="CR12" t="n">
         <v>1.52</v>
@@ -5691,73 +5691,73 @@
         <v>1.29</v>
       </c>
       <c r="CV12" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CW12" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.77</v>
+        <v>3.82</v>
       </c>
       <c r="DE12" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.17</v>
+        <v>3.29</v>
       </c>
       <c r="DH12" t="n">
-        <v>106.5</v>
+        <v>108.57</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.66</v>
+        <v>5.71</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DM12" t="n">
-        <v>50</v>
+        <v>54.86</v>
       </c>
       <c r="DN12" t="n">
         <v>1</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="DP12" t="n">
-        <v>11.5</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="DQ12" t="n">
-        <v>3.33</v>
+        <v>2.71</v>
       </c>
       <c r="DR12" t="n">
-        <v>7</v>
+        <v>5.86</v>
       </c>
       <c r="DS12" t="n">
         <v>0</v>
@@ -5769,28 +5769,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>61.34</v>
+        <v>59.86</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.16</v>
+        <v>11.43</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.67</v>
+        <v>7.43</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="EA12" t="n">
-        <v>23</v>
+        <v>19.57</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="13">

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>0.25</v>
@@ -1469,49 +1469,49 @@
         <v>4</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AH2" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AI2" t="n">
-        <v>98</v>
+        <v>94.67</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.5</v>
+        <v>2.33</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.5</v>
+        <v>4.67</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>51</v>
+        <v>48.67</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.5</v>
+        <v>2</v>
       </c>
       <c r="AR2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS2" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="AT2" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AU2" t="n">
         <v>1</v>
@@ -1526,73 +1526,73 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>52</v>
+        <v>48.33</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="BA2" t="n">
-        <v>9</v>
+        <v>7.67</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.5</v>
+        <v>3.67</v>
       </c>
       <c r="BD2" t="n">
-        <v>7</v>
+        <v>4.33</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.5</v>
+        <v>1.67</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.33</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.67</v>
+        <v>6</v>
       </c>
       <c r="BR2" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BT2" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BU2" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BV2" t="n">
         <v>0</v>
@@ -1601,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BY2" t="n">
         <v>3.39</v>
@@ -1610,55 +1610,55 @@
         <v>3.4</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.78</v>
+        <v>2.99</v>
       </c>
       <c r="CE2" t="n">
         <v>1.5</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CK2" t="n">
         <v>1.64</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CN2" t="n">
         <v>1.72</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.48</v>
+        <v>4.56</v>
       </c>
       <c r="CR2" t="n">
         <v>1.54</v>
@@ -1672,7 +1672,7 @@
         <v>1.71</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CX2" t="n">
         <v>1.64</v>
@@ -1681,94 +1681,94 @@
         <v>2.03</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.84</v>
+        <v>4.93</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.17</v>
+        <v>0.28</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="DG2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>95.72</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>54.28</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>10.71</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="EC2" t="n">
         <v>3</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>97</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>44.83</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>10.17</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>12.67</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>2.83</v>
       </c>
     </row>
     <row r="3">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" t="n">
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1871,124 +1871,124 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AI3" t="n">
-        <v>118.5</v>
+        <v>115</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AK3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>44.67</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AQ3" t="n">
         <v>3</v>
       </c>
-      <c r="AL3" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="AO3" t="n">
+      <c r="AR3" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AT3" t="n">
         <v>1</v>
       </c>
-      <c r="AP3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>47.67</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
         <v>5</v>
       </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>6</v>
-      </c>
       <c r="BB3" t="n">
-        <v>4.5</v>
+        <v>3.33</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="BD3" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="BF3" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BH3" t="n">
-        <v>8</v>
+        <v>8.43</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BN3" t="n">
         <v>1</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.5</v>
+        <v>4.57</v>
       </c>
       <c r="BR3" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BT3" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BY3" t="n">
         <v>3.16</v>
@@ -2009,165 +2009,169 @@
         <v>3.79</v>
       </c>
       <c r="CA3" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CG3" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.84</v>
+        <v>3.92</v>
       </c>
       <c r="CR3" t="n">
         <v>1.52</v>
       </c>
-      <c r="CS3" t="inlineStr"/>
+      <c r="CS3" t="n">
+        <v>3.27</v>
+      </c>
       <c r="CT3" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="CU3" t="inlineStr"/>
+        <v>2.51</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>1.32</v>
+      </c>
       <c r="CV3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CW3" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="DD3" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="DG3" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="DH3" t="n">
-        <v>91.5</v>
+        <v>93.86</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="DK3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="DL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM3" t="n">
+        <v>40.72</v>
+      </c>
+      <c r="DN3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DO3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DP3" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="DQ3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DR3" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="DS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV3" t="n">
+        <v>47.29</v>
+      </c>
+      <c r="DW3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DX3" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="DY3" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="DZ3" t="n">
         <v>3</v>
       </c>
-      <c r="DL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM3" t="n">
-        <v>38.33</v>
-      </c>
-      <c r="DN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO3" t="n">
-        <v>1</v>
-      </c>
-      <c r="DP3" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="DQ3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DR3" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="DS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV3" t="n">
-        <v>48</v>
-      </c>
-      <c r="DW3" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="DX3" t="n">
-        <v>6.83</v>
-      </c>
-      <c r="DY3" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="DZ3" t="n">
-        <v>3.17</v>
-      </c>
       <c r="EA3" t="n">
-        <v>16.83</v>
+        <v>14.29</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="EC3" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="4">
@@ -2177,13 +2181,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2267,130 +2271,130 @@
         <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>92.67</v>
+        <v>94.25</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>53</v>
+        <v>52.75</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.33</v>
+        <v>6</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>37.33</v>
+        <v>39.25</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>11.33</v>
+        <v>10.75</v>
       </c>
       <c r="BB4" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="BD4" t="n">
-        <v>17.33</v>
+        <v>12.75</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.33</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BM4" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.5</v>
+        <v>4.29</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.67</v>
+        <v>4.86</v>
       </c>
       <c r="BR4" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BT4" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BU4" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -2399,7 +2403,7 @@
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BY4" t="n">
         <v>3.66</v>
@@ -2408,169 +2412,169 @@
         <v>4.04</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="CB4" t="n">
         <v>3.25</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.69</v>
+        <v>3.94</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CI4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CK4" t="n">
         <v>1.66</v>
       </c>
-      <c r="CJ4" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="CK4" t="n">
-        <v>1.67</v>
-      </c>
       <c r="CL4" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.6</v>
+        <v>4.52</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="DA4" t="n">
         <v>1.66</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.75</v>
+        <v>4.65</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="DG4" t="n">
-        <v>2</v>
+        <v>2.43</v>
       </c>
       <c r="DH4" t="n">
-        <v>91.34</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.34</v>
+        <v>1.71</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.67</v>
+        <v>4.14</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="DM4" t="n">
-        <v>54.66</v>
+        <v>54.28</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="DP4" t="n">
-        <v>7.66</v>
+        <v>6.43</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.5</v>
+        <v>0.29</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.67</v>
+        <v>7.28</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>38.16</v>
+        <v>39.14</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.17</v>
+        <v>10</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.16</v>
+        <v>6</v>
       </c>
       <c r="DZ4" t="n">
         <v>4</v>
       </c>
       <c r="EA4" t="n">
-        <v>16.66</v>
+        <v>14.14</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.34</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="5">
@@ -2580,13 +2584,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
         <v>0.25</v>
@@ -2673,127 +2677,127 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="AI5" t="n">
-        <v>103.5</v>
+        <v>98.33</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>4.5</v>
+        <v>5.67</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AM5" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AN5" t="n">
-        <v>55</v>
+        <v>46.67</v>
       </c>
       <c r="AO5" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AP5" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AQ5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.5</v>
+        <v>3.33</v>
       </c>
       <c r="AS5" t="n">
-        <v>10</v>
+        <v>6.33</v>
       </c>
       <c r="AT5" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>41</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="BC5" t="n">
         <v>2</v>
       </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>14</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2.5</v>
-      </c>
       <c r="BD5" t="n">
-        <v>20.5</v>
+        <v>13.33</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.46</v>
+        <v>1.13</v>
       </c>
       <c r="BF5" t="n">
-        <v>3.5</v>
+        <v>4.67</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="BH5" t="n">
-        <v>7.33</v>
+        <v>7.57</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="BQ5" t="n">
-        <v>3.83</v>
+        <v>4.29</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BT5" t="n">
-        <v>16.67</v>
+        <v>28.57</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="BV5" t="n">
         <v>0</v>
@@ -2802,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BY5" t="n">
         <v>2.99</v>
@@ -2811,165 +2815,169 @@
         <v>3.46</v>
       </c>
       <c r="CA5" t="n">
-        <v>2.89</v>
+        <v>3.09</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.02</v>
+        <v>3.36</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.92</v>
+        <v>5.63</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.14</v>
+        <v>7.25</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="CK5" t="n">
         <v>1.65</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="CQ5" t="n">
-        <v>4.99</v>
+        <v>4.89</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CS5" t="inlineStr"/>
+        <v>1.55</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>3.11</v>
+      </c>
       <c r="CT5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="CU5" t="inlineStr"/>
+        <v>2.47</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>1.36</v>
+      </c>
       <c r="CV5" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="CW5" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="DD5" t="n">
-        <v>5.41</v>
+        <v>5.19</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.83</v>
+        <v>2.43</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DH5" t="n">
-        <v>95.17</v>
+        <v>94.14</v>
       </c>
       <c r="DI5" t="n">
         <v>0</v>
       </c>
       <c r="DJ5" t="n">
-        <v>4</v>
+        <v>4.57</v>
       </c>
       <c r="DK5" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DM5" t="n">
-        <v>51.83</v>
+        <v>48.72</v>
       </c>
       <c r="DN5" t="n">
         <v>2</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.83</v>
+        <v>11.71</v>
       </c>
       <c r="DQ5" t="n">
-        <v>3.33</v>
+        <v>2.71</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.5</v>
+        <v>5.43</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="DX5" t="n">
-        <v>11</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.33</v>
+        <v>7.43</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="EA5" t="n">
-        <v>22.17</v>
+        <v>18.86</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="EC5" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -2991,7 +2999,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
@@ -3003,10 +3011,10 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="L6" t="n">
         <v>0.33</v>
@@ -3021,13 +3029,13 @@
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>7.67</v>
+        <v>11.33</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.67</v>
+        <v>2.67</v>
       </c>
       <c r="R6" t="n">
-        <v>5.67</v>
+        <v>9.33</v>
       </c>
       <c r="S6" t="n">
         <v>1.33</v>
@@ -3045,28 +3053,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>49.33</v>
+        <v>49.67</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>10</v>
+        <v>9.67</v>
       </c>
       <c r="AA6" t="n">
         <v>7</v>
       </c>
       <c r="AB6" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AC6" t="n">
-        <v>16.67</v>
+        <v>28</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3153,7 +3161,7 @@
         <v>2.29</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.57</v>
+        <v>10.43</v>
       </c>
       <c r="BI6" t="n">
         <v>2.29</v>
@@ -3207,13 +3215,13 @@
         <v>2.95</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="CA6" t="n">
         <v>3.05</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CC6" t="n">
         <v>3.29</v>
@@ -3267,7 +3275,7 @@
         <v>3.28</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CU6" t="n">
         <v>1.32</v>
@@ -3297,13 +3305,13 @@
         <v>2.41</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.61</v>
+        <v>4.6</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.29</v>
+        <v>2.43</v>
       </c>
       <c r="DG6" t="n">
         <v>2.71</v>
@@ -3315,10 +3323,10 @@
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.86</v>
+        <v>4.72</v>
       </c>
       <c r="DL6" t="n">
         <v>0.14</v>
@@ -3333,13 +3341,13 @@
         <v>2.14</v>
       </c>
       <c r="DP6" t="n">
-        <v>8.720000000000001</v>
+        <v>10.28</v>
       </c>
       <c r="DQ6" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="DR6" t="n">
-        <v>6</v>
+        <v>7.57</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3351,28 +3359,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>47.86</v>
+        <v>48</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.14</v>
+        <v>10</v>
       </c>
       <c r="DY6" t="n">
         <v>6.71</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.43</v>
+        <v>3.29</v>
       </c>
       <c r="EA6" t="n">
-        <v>16.57</v>
+        <v>21.43</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="EC6" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="7">
@@ -3382,13 +3390,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3472,52 +3480,52 @@
         <v>2.67</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP7" t="n">
         <v>1</v>
       </c>
-      <c r="AI7" t="n">
-        <v>83.67</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>43.67</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0.67</v>
-      </c>
       <c r="AQ7" t="n">
-        <v>14.33</v>
+        <v>10.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AS7" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3529,82 +3537,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>53.67</v>
+        <v>54.25</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.33</v>
+        <v>6.75</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.67</v>
+        <v>4.25</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>24</v>
+        <v>17.75</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.78</v>
+        <v>0.98</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="BG7" t="n">
         <v>3</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.67</v>
+        <v>7.71</v>
       </c>
       <c r="BI7" t="n">
         <v>3</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BN7" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="BO7" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.83</v>
+        <v>4.57</v>
       </c>
       <c r="BQ7" t="n">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BU7" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BV7" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BY7" t="n">
         <v>2.2</v>
@@ -3613,16 +3621,16 @@
         <v>2.27</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CC7" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="CD7" t="n">
         <v>3.69</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>4.09</v>
       </c>
       <c r="CE7" t="n">
         <v>1.51</v>
@@ -3631,7 +3639,7 @@
         <v>3.29</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CH7" t="n">
         <v>1.26</v>
@@ -3640,28 +3648,28 @@
         <v>1.68</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.5</v>
+        <v>4.52</v>
       </c>
       <c r="CR7" t="n">
         <v>1.54</v>
@@ -3670,7 +3678,7 @@
         <v>3.36</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CU7" t="n">
         <v>1.31</v>
@@ -3682,67 +3690,67 @@
         <v>2.11</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="DB7" t="n">
         <v>1.48</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.84</v>
+        <v>4.9</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.34</v>
+        <v>1.57</v>
       </c>
       <c r="DH7" t="n">
-        <v>101.17</v>
+        <v>103.29</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.17</v>
+        <v>3.43</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="DM7" t="n">
-        <v>51.67</v>
+        <v>54.86</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.33</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="DQ7" t="n">
-        <v>1.16</v>
+        <v>0.86</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.84</v>
+        <v>5.72</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3754,28 +3762,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>55.34</v>
+        <v>55.43</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.33</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="DY7" t="n">
-        <v>4.67</v>
+        <v>4.86</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.67</v>
+        <v>3.86</v>
       </c>
       <c r="EA7" t="n">
-        <v>20.16</v>
+        <v>17.14</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -4013,7 +4021,7 @@
         <v>2.57</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.85</v>
+        <v>2.66</v>
       </c>
       <c r="CA8" t="n">
         <v>3.08</v>
@@ -4067,13 +4075,13 @@
         <v>4.22</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CS8" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CU8" t="n">
         <v>1.34</v>
@@ -4085,16 +4093,16 @@
         <v>2.01</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="DB8" t="n">
         <v>1.42</v>
@@ -4103,7 +4111,7 @@
         <v>2.34</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.37</v>
+        <v>4.39</v>
       </c>
       <c r="DE8" t="n">
         <v>0.14</v>
@@ -4281,7 +4289,7 @@
         <v>0.25</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="n">
         <v>4</v>
@@ -4293,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AL9" t="n">
         <v>6.25</v>
@@ -4311,13 +4319,13 @@
         <v>2.25</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.75</v>
+        <v>10.25</v>
       </c>
       <c r="AT9" t="n">
         <v>1.75</v>
@@ -4335,34 +4343,34 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>49.75</v>
+        <v>49.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.75</v>
+        <v>9.25</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>16.75</v>
+        <v>24.5</v>
       </c>
       <c r="BE9" t="n">
         <v>1.52</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="BG9" t="n">
         <v>2.71</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.14</v>
+        <v>10</v>
       </c>
       <c r="BI9" t="n">
         <v>2.71</v>
@@ -4422,7 +4430,7 @@
         <v>3.3</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="CC9" t="n">
         <v>4.08</v>
@@ -4482,10 +4490,10 @@
         <v>1.32</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CX9" t="n">
         <v>1.7</v>
@@ -4503,16 +4511,16 @@
         <v>1.42</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.44</v>
+        <v>4.43</v>
       </c>
       <c r="DE9" t="n">
         <v>0.14</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="DG9" t="n">
         <v>3.14</v>
@@ -4524,7 +4532,7 @@
         <v>0</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="DK9" t="n">
         <v>5.43</v>
@@ -4542,13 +4550,13 @@
         <v>2.28</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.86</v>
+        <v>13.86</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.86</v>
+        <v>1.14</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.43</v>
+        <v>9.43</v>
       </c>
       <c r="DS9" t="n">
         <v>0.43</v>
@@ -4560,28 +4568,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>54.43</v>
+        <v>54.29</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.86</v>
+        <v>14.71</v>
       </c>
       <c r="DY9" t="n">
-        <v>10.29</v>
+        <v>10</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.57</v>
+        <v>4.71</v>
       </c>
       <c r="EA9" t="n">
-        <v>19.57</v>
+        <v>24</v>
       </c>
       <c r="EB9" t="n">
         <v>1.63</v>
       </c>
       <c r="EC9" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="10">
@@ -4591,10 +4599,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
@@ -4603,49 +4611,49 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.67</v>
+        <v>3.5</v>
       </c>
       <c r="H10" t="n">
-        <v>101.33</v>
+        <v>108.5</v>
       </c>
       <c r="I10" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.67</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
-        <v>6.67</v>
+        <v>7.25</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>69.67</v>
+        <v>72.75</v>
       </c>
       <c r="N10" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="O10" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="P10" t="n">
-        <v>9.33</v>
+        <v>6.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="R10" t="n">
-        <v>5.33</v>
+        <v>3.75</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4657,28 +4665,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>52.33</v>
+        <v>54</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.33</v>
+        <v>11.75</v>
       </c>
       <c r="AA10" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.33</v>
+        <v>6.25</v>
       </c>
       <c r="AC10" t="n">
-        <v>24.33</v>
+        <v>18</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="AE10" t="n">
-        <v>3.67</v>
+        <v>3</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4762,70 +4770,70 @@
         <v>4.67</v>
       </c>
       <c r="BG10" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.17</v>
+        <v>9.57</v>
       </c>
       <c r="BI10" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BP10" t="n">
-        <v>5.33</v>
+        <v>5.14</v>
       </c>
       <c r="BQ10" t="n">
-        <v>3.83</v>
+        <v>4.43</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BT10" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BU10" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BV10" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.93</v>
+        <v>3.52</v>
       </c>
       <c r="BZ10" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.39</v>
+        <v>3.32</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="CC10" t="n">
         <v>5.08</v>
@@ -4834,43 +4842,43 @@
         <v>5.81</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.17</v>
+        <v>3.21</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CL10" t="n">
         <v>1.98</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.22</v>
+        <v>2.27</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.05</v>
+        <v>4.19</v>
       </c>
       <c r="CR10" t="n">
         <v>1.46</v>
@@ -4888,103 +4896,103 @@
         <v>1.71</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="DD10" t="n">
-        <v>4.23</v>
+        <v>4.4</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="DG10" t="n">
-        <v>2</v>
+        <v>2.57</v>
       </c>
       <c r="DH10" t="n">
-        <v>103</v>
+        <v>106.86</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="DJ10" t="n">
-        <v>4.34</v>
+        <v>3.86</v>
       </c>
       <c r="DK10" t="n">
-        <v>4.84</v>
+        <v>5.43</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="DM10" t="n">
-        <v>56.17</v>
+        <v>59.86</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="DP10" t="n">
-        <v>12</v>
+        <v>10.14</v>
       </c>
       <c r="DQ10" t="n">
-        <v>2.83</v>
+        <v>2.29</v>
       </c>
       <c r="DR10" t="n">
-        <v>8.5</v>
+        <v>7.14</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>47.83</v>
+        <v>49.43</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.66</v>
+        <v>10.57</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.34</v>
+        <v>5.57</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="EA10" t="n">
-        <v>24</v>
+        <v>20.43</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="EC10" t="n">
-        <v>4.17</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="11">
@@ -4994,13 +5002,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" t="n">
         <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5087,124 +5095,124 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>97.5</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>51.5</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AU11" t="n">
         <v>1</v>
       </c>
-      <c r="AH11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>96.33</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>51.67</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AP11" t="n">
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC11" t="n">
         <v>3</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>49</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>3.33</v>
-      </c>
       <c r="BD11" t="n">
-        <v>20</v>
+        <v>14.75</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.29</v>
+        <v>1.16</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.67</v>
+        <v>9</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="BO11" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.67</v>
+        <v>4.14</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="BR11" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BT11" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BU11" t="n">
         <v>0</v>
@@ -5216,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BY11" t="n">
         <v>2.12</v>
@@ -5225,28 +5233,28 @@
         <v>2.2</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="CD11" t="n">
-        <v>2.13</v>
+        <v>2.37</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="CI11" t="n">
         <v>1.75</v>
@@ -5255,25 +5263,25 @@
         <v>1.96</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO11" t="n">
         <v>1.4</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.24</v>
+        <v>4.28</v>
       </c>
       <c r="CR11" t="n">
         <v>1.49</v>
@@ -5297,97 +5305,97 @@
         <v>1.64</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DA11" t="n">
         <v>1.72</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.35</v>
+        <v>4.42</v>
       </c>
       <c r="DE11" t="n">
         <v>0</v>
       </c>
       <c r="DF11" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>91.70999999999999</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>48.57</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>49.57</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>10.14</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>20</v>
+      </c>
+      <c r="EB11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="EC11" t="n">
         <v>1</v>
-      </c>
-      <c r="DG11" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="DH11" t="n">
-        <v>90.16</v>
-      </c>
-      <c r="DI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ11" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="DK11" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="DL11" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="DM11" t="n">
-        <v>48.17</v>
-      </c>
-      <c r="DN11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DO11" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="DP11" t="n">
-        <v>9</v>
-      </c>
-      <c r="DQ11" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="DR11" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="DS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV11" t="n">
-        <v>49.16</v>
-      </c>
-      <c r="DW11" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="DX11" t="n">
-        <v>11.17</v>
-      </c>
-      <c r="DY11" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="DZ11" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="EA11" t="n">
-        <v>23.5</v>
-      </c>
-      <c r="EB11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="EC11" t="n">
-        <v>1.17</v>
       </c>
     </row>
     <row r="12">
@@ -5637,7 +5645,7 @@
         <v>1.65</v>
       </c>
       <c r="CD12" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="CE12" t="n">
         <v>0.8100000000000001</v>
@@ -5679,16 +5687,16 @@
         <v>2.12</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="CS12" t="n">
         <v>3.3</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="CV12" t="n">
         <v>1.77</v>
@@ -5697,16 +5705,16 @@
         <v>2.07</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="DB12" t="n">
         <v>1.36</v>
@@ -5715,7 +5723,7 @@
         <v>2.13</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="DE12" t="n">
         <v>0.14</v>
@@ -5800,94 +5808,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
         <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="G13" t="n">
-        <v>2.33</v>
+        <v>3.5</v>
       </c>
       <c r="H13" t="n">
-        <v>111.33</v>
+        <v>114.25</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>36</v>
+        <v>36.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="O13" t="n">
-        <v>3.67</v>
+        <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>9.33</v>
+        <v>6.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.67</v>
+        <v>3.25</v>
       </c>
       <c r="R13" t="n">
-        <v>7.33</v>
+        <v>5.25</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>52</v>
+        <v>55.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>10.33</v>
+        <v>11.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.33</v>
+        <v>5.75</v>
       </c>
       <c r="AB13" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5971,49 +5979,49 @@
         <v>2.33</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.33</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BO13" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="BP13" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.67</v>
+        <v>4.14</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT13" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BU13" t="n">
-        <v>16.67</v>
+        <v>28.57</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6022,19 +6030,19 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.64</v>
+        <v>3.74</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.71</v>
+        <v>3.95</v>
       </c>
       <c r="CC13" t="n">
         <v>2.01</v>
@@ -6046,28 +6054,28 @@
         <v>1.44</v>
       </c>
       <c r="CF13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="CK13" t="n">
         <v>1.66</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CN13" t="n">
         <v>1.67</v>
@@ -6076,124 +6084,124 @@
         <v>1.38</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.87</v>
+        <v>3.93</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CS13" t="n">
         <v>3.11</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="CU13" t="n">
         <v>1.35</v>
       </c>
       <c r="CV13" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="DB13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>108.57</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>33</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>54.86</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>8</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="EB13" t="n">
         <v>1.4</v>
       </c>
-      <c r="DC13" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="DD13" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="DE13" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="DF13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DG13" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="DH13" t="n">
-        <v>106.16</v>
-      </c>
-      <c r="DI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ13" t="n">
+      <c r="EC13" t="n">
         <v>2</v>
-      </c>
-      <c r="DK13" t="n">
-        <v>5.66</v>
-      </c>
-      <c r="DL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM13" t="n">
-        <v>32.16</v>
-      </c>
-      <c r="DN13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DO13" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="DP13" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="DQ13" t="n">
-        <v>4</v>
-      </c>
-      <c r="DR13" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="DS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV13" t="n">
-        <v>53</v>
-      </c>
-      <c r="DW13" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="DX13" t="n">
-        <v>12.66</v>
-      </c>
-      <c r="DY13" t="n">
-        <v>8.17</v>
-      </c>
-      <c r="DZ13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="EA13" t="n">
-        <v>24.33</v>
-      </c>
-      <c r="EB13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="EC13" t="n">
-        <v>1.83</v>
       </c>
     </row>
     <row r="14">
@@ -6203,94 +6211,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
         <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="F14" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H14" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="I14" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="J14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>50.75</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA14" t="n">
         <v>5</v>
       </c>
-      <c r="K14" t="n">
-        <v>3</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>41</v>
-      </c>
-      <c r="N14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" t="n">
-        <v>15.67</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="R14" t="n">
-        <v>8.67</v>
-      </c>
-      <c r="S14" t="n">
-        <v>2</v>
-      </c>
-      <c r="T14" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>48.67</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>5.67</v>
-      </c>
       <c r="AB14" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>21.67</v>
+        <v>16</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AE14" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6374,49 +6382,49 @@
         <v>1.67</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.33</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.33</v>
+        <v>4.57</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BT14" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BU14" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6425,19 +6433,19 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>33.33</v>
+        <v>28.57</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.73</v>
+        <v>3.47</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.91</v>
+        <v>3.63</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.27</v>
+        <v>3.23</v>
       </c>
       <c r="CC14" t="n">
         <v>3.07</v>
@@ -6446,13 +6454,13 @@
         <v>3.39</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.16</v>
+        <v>3.13</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CH14" t="n">
         <v>1.28</v>
@@ -6467,7 +6475,7 @@
         <v>1.65</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CM14" t="n">
         <v>2.08</v>
@@ -6479,22 +6487,22 @@
         <v>1.41</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.18</v>
+        <v>2.21</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.13</v>
+        <v>4.17</v>
       </c>
       <c r="CR14" t="n">
         <v>1.53</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.36</v>
+        <v>3.32</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CV14" t="n">
         <v>1.78</v>
@@ -6509,61 +6517,61 @@
         <v>2.07</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DB14" t="n">
         <v>1.43</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DD14" t="n">
-        <v>4.48</v>
+        <v>4.51</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF14" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.84</v>
+        <v>2.14</v>
       </c>
       <c r="DH14" t="n">
-        <v>96.34</v>
+        <v>100.72</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="DK14" t="n">
-        <v>3.33</v>
+        <v>4.29</v>
       </c>
       <c r="DL14" t="n">
         <v>0</v>
       </c>
       <c r="DM14" t="n">
-        <v>47.5</v>
+        <v>52.43</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.5</v>
+        <v>2.14</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.34</v>
+        <v>10.43</v>
       </c>
       <c r="DQ14" t="n">
-        <v>3.17</v>
+        <v>2.57</v>
       </c>
       <c r="DR14" t="n">
-        <v>8</v>
+        <v>6.71</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6575,28 +6583,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>46.5</v>
+        <v>48</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.66</v>
+        <v>0.57</v>
       </c>
       <c r="DX14" t="n">
-        <v>7.33</v>
+        <v>7</v>
       </c>
       <c r="DY14" t="n">
-        <v>4.67</v>
+        <v>4.43</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.34</v>
+        <v>14.71</v>
       </c>
       <c r="EB14" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="15">
@@ -6606,10 +6614,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="n">
         <v>3</v>
@@ -6618,49 +6626,49 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="G15" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="H15" t="n">
-        <v>89</v>
+        <v>89.25</v>
       </c>
       <c r="I15" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="J15" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="K15" t="n">
-        <v>7.33</v>
+        <v>6.75</v>
       </c>
       <c r="L15" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="M15" t="n">
-        <v>65</v>
+        <v>62.5</v>
       </c>
       <c r="N15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P15" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R15" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="S15" t="n">
         <v>1</v>
       </c>
-      <c r="O15" t="n">
-        <v>4</v>
-      </c>
-      <c r="P15" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>4</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.33</v>
-      </c>
       <c r="T15" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -6672,28 +6680,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>51</v>
+        <v>50.25</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AB15" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>27.33</v>
+        <v>20.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.96</v>
+        <v>1.75</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AF15" t="n">
         <v>0.67</v>
@@ -6777,70 +6785,70 @@
         <v>4</v>
       </c>
       <c r="BG15" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="BH15" t="n">
-        <v>11.83</v>
+        <v>10.86</v>
       </c>
       <c r="BI15" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.83</v>
+        <v>4.29</v>
       </c>
       <c r="BQ15" t="n">
-        <v>7</v>
+        <v>6.57</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>66.67</v>
+        <v>57.14</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BU15" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BV15" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BW15" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BX15" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.16</v>
+        <v>2.29</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="CC15" t="n">
         <v>3.94</v>
@@ -6849,43 +6857,43 @@
         <v>4.17</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="CM15" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="CR15" t="n">
         <v>1.52</v>
@@ -6896,73 +6904,73 @@
       </c>
       <c r="CU15" t="inlineStr"/>
       <c r="CV15" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CW15" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CX15" t="n">
         <v>1.65</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DB15" t="n">
         <v>1.49</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="DD15" t="n">
-        <v>4.99</v>
+        <v>4.97</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.34</v>
+        <v>2</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="DH15" t="n">
-        <v>91.34</v>
+        <v>91.14</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="DK15" t="n">
-        <v>6.83</v>
+        <v>6.57</v>
       </c>
       <c r="DL15" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="DM15" t="n">
-        <v>60.5</v>
+        <v>59.71</v>
       </c>
       <c r="DN15" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="DO15" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="DP15" t="n">
-        <v>13.33</v>
+        <v>11.28</v>
       </c>
       <c r="DQ15" t="n">
-        <v>2.83</v>
+        <v>2.29</v>
       </c>
       <c r="DR15" t="n">
-        <v>7</v>
+        <v>5.86</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6974,28 +6982,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.84</v>
+        <v>46.14</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.5</v>
+        <v>7.71</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.5</v>
+        <v>5.29</v>
       </c>
       <c r="EA15" t="n">
-        <v>24</v>
+        <v>20.43</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="16">
@@ -7005,61 +7013,61 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
         <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="F16" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="G16" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="H16" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="K16" t="n">
-        <v>4.5</v>
+        <v>3.67</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="N16" t="n">
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>5.5</v>
+        <v>3.33</v>
       </c>
       <c r="Q16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>4</v>
+        <v>2.33</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -7071,25 +7079,25 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.5</v>
+        <v>0.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.5</v>
+        <v>7.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="AC16" t="n">
-        <v>18</v>
+        <v>11.67</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
@@ -7176,49 +7184,49 @@
         <v>4</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="BH16" t="n">
-        <v>7.83</v>
+        <v>8</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.33</v>
+        <v>4.57</v>
       </c>
       <c r="BR16" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BT16" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BU16" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BV16" t="n">
         <v>0</v>
@@ -7227,19 +7235,19 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.37</v>
+        <v>3.36</v>
       </c>
       <c r="CC16" t="n">
         <v>2.96</v>
@@ -7251,16 +7259,16 @@
         <v>1.42</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="CH16" t="n">
         <v>1.34</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.88</v>
@@ -7269,7 +7277,7 @@
         <v>1.59</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CM16" t="n">
         <v>2.18</v>
@@ -7284,118 +7292,118 @@
         <v>2.16</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.81</v>
+        <v>3.83</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CS16" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.95</v>
+        <v>2.87</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CY16" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DB16" t="n">
         <v>1.37</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.9</v>
+        <v>3.93</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DF16" t="n">
         <v>3</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="DH16" t="n">
-        <v>104.67</v>
+        <v>105.86</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>4.83</v>
+        <v>4.72</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.5</v>
+        <v>4.14</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DM16" t="n">
-        <v>48.17</v>
+        <v>48</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="DP16" t="n">
-        <v>9.83</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DQ16" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="DR16" t="n">
-        <v>3.83</v>
+        <v>3.14</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.33</v>
+        <v>53.57</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DX16" t="n">
-        <v>9.83</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.17</v>
+        <v>5.57</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.67</v>
+        <v>3.57</v>
       </c>
       <c r="EA16" t="n">
-        <v>21.5</v>
+        <v>18.29</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
       <c r="EC16" t="n">
         <v>4</v>
@@ -7408,10 +7416,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" t="n">
         <v>3</v>
@@ -7423,46 +7431,46 @@
         <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>4.67</v>
+        <v>4</v>
       </c>
       <c r="H17" t="n">
-        <v>102</v>
+        <v>101.5</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>7.67</v>
+        <v>6.5</v>
       </c>
       <c r="L17" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="M17" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N17" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="O17" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="P17" t="n">
-        <v>8.33</v>
+        <v>6</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="R17" t="n">
-        <v>5.67</v>
+        <v>4</v>
       </c>
       <c r="S17" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="T17" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -7474,28 +7482,28 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>48.67</v>
+        <v>47.5</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>11.67</v>
+        <v>11.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.33</v>
+        <v>6.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.33</v>
+        <v>5</v>
       </c>
       <c r="AC17" t="n">
-        <v>16.33</v>
+        <v>12</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AE17" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="AF17" t="n">
         <v>0.33</v>
@@ -7579,49 +7587,49 @@
         <v>4</v>
       </c>
       <c r="BG17" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.67</v>
+        <v>9.43</v>
       </c>
       <c r="BI17" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.5</v>
+        <v>5.43</v>
       </c>
       <c r="BR17" t="n">
-        <v>83.33</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>66.67</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT17" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BU17" t="n">
-        <v>16.67</v>
+        <v>14.29</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7630,19 +7638,19 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>33.33</v>
+        <v>42.86</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="BZ17" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="CA17" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="CB17" t="n">
         <v>3.12</v>
-      </c>
-      <c r="CA17" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="CB17" t="n">
-        <v>3.15</v>
       </c>
       <c r="CC17" t="n">
         <v>3.83</v>
@@ -7651,153 +7659,153 @@
         <v>4.32</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="CG17" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="CM17" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="CQ17" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="CR17" t="n">
         <v>1.55</v>
       </c>
       <c r="CS17" t="inlineStr"/>
       <c r="CT17" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CU17" t="inlineStr"/>
       <c r="CV17" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.01</v>
+        <v>2.03</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.8</v>
+        <v>4.88</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DF17" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="DH17" t="n">
-        <v>98.66</v>
+        <v>98.86</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>4.33</v>
+        <v>4.28</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.34</v>
+        <v>5</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DM17" t="n">
-        <v>56.84</v>
+        <v>57.43</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="DP17" t="n">
-        <v>8</v>
+        <v>6.72</v>
       </c>
       <c r="DQ17" t="n">
-        <v>1.34</v>
+        <v>1</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.84</v>
+        <v>5.71</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>49</v>
+        <v>48.28</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.34</v>
+        <v>0.29</v>
       </c>
       <c r="DX17" t="n">
-        <v>9.67</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DY17" t="n">
-        <v>5.83</v>
+        <v>6</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.83</v>
+        <v>3.86</v>
       </c>
       <c r="EA17" t="n">
-        <v>15</v>
+        <v>12.72</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="EC17" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
@@ -2181,13 +2181,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2271,139 +2271,139 @@
         <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AG4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>88</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>49.8</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BK4" t="n">
         <v>0.75</v>
       </c>
-      <c r="AH4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>94.25</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
+      <c r="BL4" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BN4" t="n">
         <v>1.5</v>
       </c>
-      <c r="AL4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>52.75</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
+      <c r="BO4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BQ4" t="n">
         <v>5</v>
       </c>
-      <c r="AT4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>39.25</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>9.289999999999999</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>4.86</v>
-      </c>
       <c r="BR4" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS4" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>14.29</v>
+        <v>25</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BX4" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
         <v>3.66</v>
@@ -2415,28 +2415,28 @@
         <v>3.3</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.7</v>
+        <v>3.76</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.94</v>
+        <v>4.04</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CF4" t="n">
         <v>3.14</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="CH4" t="n">
         <v>1.28</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CJ4" t="n">
         <v>2.05</v>
@@ -2445,136 +2445,136 @@
         <v>1.66</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CN4" t="n">
         <v>1.69</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.52</v>
+        <v>4.43</v>
       </c>
       <c r="CR4" t="n">
         <v>1.51</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.65</v>
+        <v>4.62</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="DF4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>88.75</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>52.25</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="DQ4" t="n">
         <v>1</v>
       </c>
-      <c r="DG4" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="DH4" t="n">
-        <v>92.43000000000001</v>
-      </c>
-      <c r="DI4" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DJ4" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DK4" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="DL4" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="DM4" t="n">
-        <v>54.28</v>
-      </c>
-      <c r="DN4" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="DO4" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DP4" t="n">
-        <v>6.43</v>
-      </c>
-      <c r="DQ4" t="n">
-        <v>0.29</v>
-      </c>
       <c r="DR4" t="n">
-        <v>7.28</v>
+        <v>7.37</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>39.14</v>
+        <v>39.25</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>10</v>
+        <v>10.25</v>
       </c>
       <c r="DY4" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="DZ4" t="n">
         <v>4</v>
       </c>
       <c r="EA4" t="n">
-        <v>14.14</v>
+        <v>15.62</v>
       </c>
       <c r="EB4" t="n">
         <v>1.31</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="5">
@@ -2707,13 +2707,13 @@
         <v>2.67</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9</v>
+        <v>16.33</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.33</v>
+        <v>5</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.33</v>
+        <v>10.67</v>
       </c>
       <c r="AT5" t="n">
         <v>2.33</v>
@@ -2731,25 +2731,25 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>41</v>
+        <v>39.33</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.67</v>
       </c>
       <c r="BA5" t="n">
-        <v>10.33</v>
+        <v>12</v>
       </c>
       <c r="BB5" t="n">
-        <v>8.33</v>
+        <v>9.67</v>
       </c>
       <c r="BC5" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="BD5" t="n">
-        <v>13.33</v>
+        <v>22</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="BF5" t="n">
         <v>4.67</v>
@@ -2938,13 +2938,13 @@
         <v>1.57</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.71</v>
+        <v>14.86</v>
       </c>
       <c r="DQ5" t="n">
-        <v>2.71</v>
+        <v>3.43</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.43</v>
+        <v>7.29</v>
       </c>
       <c r="DS5" t="n">
         <v>0.14</v>
@@ -2956,25 +2956,25 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>40</v>
+        <v>39.28</v>
       </c>
       <c r="DW5" t="n">
         <v>0.43</v>
       </c>
       <c r="DX5" t="n">
-        <v>9.859999999999999</v>
+        <v>10.57</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.43</v>
+        <v>8</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.43</v>
+        <v>2.57</v>
       </c>
       <c r="EA5" t="n">
-        <v>18.86</v>
+        <v>22.57</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="EC5" t="n">
         <v>4</v>
@@ -2987,13 +2987,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
         <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3080,127 +3080,127 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>52</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AP6" t="n">
         <v>2</v>
       </c>
-      <c r="AH6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>99</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>64.25</v>
-      </c>
-      <c r="AO6" t="n">
+      <c r="AQ6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR6" t="n">
         <v>1</v>
       </c>
-      <c r="AP6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AR6" t="n">
+      <c r="AS6" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BN6" t="n">
         <v>1.5</v>
       </c>
-      <c r="AS6" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>46.75</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1.43</v>
-      </c>
       <c r="BO6" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="BP6" t="n">
-        <v>5</v>
+        <v>5.12</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.57</v>
+        <v>5.38</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BU6" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3209,7 +3209,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BY6" t="n">
         <v>2.95</v>
@@ -3218,136 +3218,136 @@
         <v>3.29</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.05</v>
+        <v>3.19</v>
       </c>
       <c r="CB6" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CF6" t="n">
         <v>3.15</v>
       </c>
-      <c r="CC6" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="CE6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CF6" t="n">
-        <v>3.22</v>
-      </c>
       <c r="CG6" t="n">
-        <v>2.39</v>
+        <v>2.44</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CL6" t="n">
         <v>2.15</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CO6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CY6" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="DB6" t="n">
         <v>1.43</v>
       </c>
-      <c r="CP6" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="CQ6" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="CS6" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="CT6" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="CU6" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="CV6" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="CW6" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="CX6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CY6" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="CZ6" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="DA6" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DB6" t="n">
-        <v>1.44</v>
-      </c>
       <c r="DC6" t="n">
-        <v>2.41</v>
+        <v>2.36</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.6</v>
+        <v>4.46</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="DH6" t="n">
-        <v>99.43000000000001</v>
+        <v>103</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.72</v>
+        <v>4.5</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DM6" t="n">
-        <v>63.14</v>
+        <v>55.63</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.28</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DQ6" t="n">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.57</v>
+        <v>6.5</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3359,28 +3359,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>48</v>
+        <v>45.25</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.71</v>
+        <v>6.38</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.29</v>
+        <v>3.13</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.43</v>
+        <v>18.62</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="7">
@@ -3835,13 +3835,13 @@
         <v>3.67</v>
       </c>
       <c r="P8" t="n">
-        <v>2.33</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.67</v>
+        <v>1.67</v>
       </c>
       <c r="R8" t="n">
-        <v>2.33</v>
+        <v>4.67</v>
       </c>
       <c r="S8" t="n">
         <v>0.33</v>
@@ -3859,25 +3859,25 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>56.33</v>
+        <v>58</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>13.67</v>
+        <v>14</v>
       </c>
       <c r="AA8" t="n">
-        <v>9</v>
+        <v>9.33</v>
       </c>
       <c r="AB8" t="n">
         <v>4.67</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.67</v>
+        <v>15.67</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="AE8" t="n">
         <v>1.67</v>
@@ -4147,13 +4147,13 @@
         <v>2.72</v>
       </c>
       <c r="DP8" t="n">
-        <v>7.14</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.86</v>
+        <v>1.29</v>
       </c>
       <c r="DR8" t="n">
-        <v>5.86</v>
+        <v>6.86</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4165,25 +4165,25 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.86</v>
+        <v>52.57</v>
       </c>
       <c r="DW8" t="n">
         <v>0.14</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.29</v>
+        <v>11.43</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.86</v>
+        <v>8</v>
       </c>
       <c r="DZ8" t="n">
         <v>3.43</v>
       </c>
       <c r="EA8" t="n">
-        <v>12.57</v>
+        <v>16</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="EC8" t="n">
         <v>2.14</v>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
         <v>4</v>
@@ -4208,82 +4208,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="H9" t="n">
-        <v>107.67</v>
+        <v>92.75</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="J9" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="K9" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>56.67</v>
+        <v>47</v>
       </c>
       <c r="N9" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="O9" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="P9" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="R9" t="n">
-        <v>8.33</v>
+        <v>6</v>
       </c>
       <c r="S9" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="T9" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="U9" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="V9" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>60.67</v>
+        <v>56.5</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>11</v>
+        <v>8.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AC9" t="n">
-        <v>23.33</v>
+        <v>17.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.77</v>
+        <v>1.53</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AF9" t="n">
         <v>0.25</v>
@@ -4367,70 +4367,70 @@
         <v>2.75</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.14</v>
+        <v>5.12</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BR9" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS9" t="n">
-        <v>71.43000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BV9" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BX9" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.34</v>
+        <v>3.33</v>
       </c>
       <c r="CC9" t="n">
         <v>4.08</v>
@@ -4442,154 +4442,154 @@
         <v>1.45</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CH9" t="n">
         <v>1.29</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CO9" t="n">
         <v>1.38</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.1</v>
+        <v>4.04</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.34</v>
+        <v>3.21</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="CV9" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CW9" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.43</v>
+        <v>4.32</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="DH9" t="n">
-        <v>103.29</v>
+        <v>96.38</v>
       </c>
       <c r="DI9" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.43</v>
+        <v>4.75</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DM9" t="n">
-        <v>50.57</v>
+        <v>46.5</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.72</v>
+        <v>0.75</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.86</v>
+        <v>12</v>
       </c>
       <c r="DQ9" t="n">
-        <v>1.14</v>
+        <v>0.88</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.43</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>54.29</v>
+        <v>53</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>14.71</v>
+        <v>13.62</v>
       </c>
       <c r="DY9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.71</v>
+        <v>4.62</v>
       </c>
       <c r="EA9" t="n">
-        <v>24</v>
+        <v>20.88</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="10">
@@ -5002,31 +5002,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
         <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="G11" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="H11" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="K11" t="n">
         <v>6</v>
@@ -5035,28 +5035,28 @@
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>44.67</v>
+        <v>46.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="O11" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
-        <v>10.33</v>
+        <v>7.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.67</v>
+        <v>3.25</v>
       </c>
       <c r="R11" t="n">
-        <v>8.67</v>
+        <v>6.25</v>
       </c>
       <c r="S11" t="n">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5068,28 +5068,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>49.33</v>
+        <v>51</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>11.67</v>
+        <v>11.75</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.33</v>
+        <v>7</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -5125,13 +5125,13 @@
         <v>2.25</v>
       </c>
       <c r="AQ11" t="n">
-        <v>5.5</v>
+        <v>8.75</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.75</v>
+        <v>4.25</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.25</v>
+        <v>9.25</v>
       </c>
       <c r="AT11" t="n">
         <v>0.75</v>
@@ -5149,94 +5149,94 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>49.75</v>
+        <v>50.75</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB11" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="BC11" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="BD11" t="n">
-        <v>14.75</v>
+        <v>24</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.16</v>
+        <v>1.27</v>
       </c>
       <c r="BF11" t="n">
         <v>1.25</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="BH11" t="n">
-        <v>9</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.29</v>
+        <v>0.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.86</v>
+        <v>1.25</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.14</v>
+        <v>4.38</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.86</v>
+        <v>5</v>
       </c>
       <c r="BR11" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS11" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>28.57</v>
+        <v>37.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BV11" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BX11" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BZ11" t="n">
         <v>2.12</v>
       </c>
-      <c r="BZ11" t="n">
-        <v>2.2</v>
-      </c>
       <c r="CA11" t="n">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CC11" t="n">
         <v>2.24</v>
@@ -5248,28 +5248,28 @@
         <v>1.45</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="CK11" t="n">
         <v>1.65</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN11" t="n">
         <v>1.69</v>
@@ -5278,40 +5278,40 @@
         <v>1.4</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.28</v>
+        <v>4.22</v>
       </c>
       <c r="CR11" t="n">
         <v>1.49</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.26</v>
+        <v>3.3</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CV11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DB11" t="n">
         <v>1.43</v>
@@ -5323,46 +5323,46 @@
         <v>4.42</v>
       </c>
       <c r="DE11" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.86</v>
+        <v>1.25</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="DH11" t="n">
-        <v>91.70999999999999</v>
+        <v>93.25</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.71</v>
+        <v>4.88</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="DM11" t="n">
-        <v>48.57</v>
+        <v>49</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="DP11" t="n">
-        <v>7.57</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DQ11" t="n">
-        <v>3.57</v>
+        <v>3.75</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.29</v>
+        <v>7.75</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.57</v>
+        <v>50.88</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.14</v>
+        <v>10.88</v>
       </c>
       <c r="DY11" t="n">
-        <v>6.57</v>
+        <v>6.62</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.57</v>
+        <v>4.25</v>
       </c>
       <c r="EA11" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="EC11" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="12">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
         <v>4</v>
@@ -5417,49 +5417,49 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="H12" t="n">
-        <v>114.67</v>
+        <v>117.75</v>
       </c>
       <c r="I12" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
-        <v>3.33</v>
+        <v>2.75</v>
       </c>
       <c r="K12" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="L12" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="M12" t="n">
-        <v>62.67</v>
+        <v>56</v>
       </c>
       <c r="N12" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="O12" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="P12" t="n">
-        <v>10</v>
+        <v>7.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.33</v>
+        <v>1.5</v>
       </c>
       <c r="R12" t="n">
-        <v>8</v>
+        <v>5.75</v>
       </c>
       <c r="S12" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5471,28 +5471,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>60</v>
+        <v>63.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="Z12" t="n">
         <v>12</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.67</v>
+        <v>7.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>3.33</v>
+        <v>4.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.33</v>
+        <v>14.25</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="AF12" t="n">
         <v>0.25</v>
@@ -5528,13 +5528,13 @@
         <v>2.75</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.25</v>
+        <v>6.5</v>
       </c>
       <c r="AT12" t="n">
         <v>1.5</v>
@@ -5552,73 +5552,73 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>59.75</v>
+        <v>58.5</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="BC12" t="n">
         <v>4.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>19.75</v>
+        <v>26.75</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="BF12" t="n">
         <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.140000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.71</v>
+        <v>4.88</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT12" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BU12" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5627,19 +5627,19 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.61</v>
+        <v>3.69</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.83</v>
+        <v>3.88</v>
       </c>
       <c r="CC12" t="n">
         <v>1.65</v>
@@ -5648,157 +5648,157 @@
         <v>1.64</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="CF12" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="CG12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="CO12" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="CP12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CQ12" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CR12" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CS12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="CT12" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="CU12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CX12" t="n">
         <v>1.56</v>
       </c>
-      <c r="CH12" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="CI12" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="CK12" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="CL12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="CM12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="CN12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="CO12" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="CP12" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="CQ12" t="n">
+      <c r="CY12" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>110.88</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>61</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="DZ12" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="EA12" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="EB12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="EC12" t="n">
         <v>2.12</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CS12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="CT12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="CU12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="CV12" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="CW12" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="CX12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CY12" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="CZ12" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="DA12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="DB12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="DC12" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="DD12" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="DE12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DF12" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="DG12" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="DH12" t="n">
-        <v>108.57</v>
-      </c>
-      <c r="DI12" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="DJ12" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="DK12" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="DL12" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="DM12" t="n">
-        <v>54.86</v>
-      </c>
-      <c r="DN12" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO12" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="DP12" t="n">
-        <v>9.710000000000001</v>
-      </c>
-      <c r="DQ12" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="DR12" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="DS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV12" t="n">
-        <v>59.86</v>
-      </c>
-      <c r="DW12" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DX12" t="n">
-        <v>11.43</v>
-      </c>
-      <c r="DY12" t="n">
-        <v>7.43</v>
-      </c>
-      <c r="DZ12" t="n">
-        <v>4</v>
-      </c>
-      <c r="EA12" t="n">
-        <v>19.57</v>
-      </c>
-      <c r="EB12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="EC12" t="n">
-        <v>2.29</v>
       </c>
     </row>
     <row r="13">
@@ -5850,13 +5850,13 @@
         <v>2.75</v>
       </c>
       <c r="P13" t="n">
-        <v>6.75</v>
+        <v>9.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="R13" t="n">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -5874,25 +5874,25 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>55.5</v>
+        <v>56.75</v>
       </c>
       <c r="Y13" t="n">
         <v>0.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>11.25</v>
+        <v>13.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>5.75</v>
+        <v>6.75</v>
       </c>
       <c r="AB13" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>18.5</v>
+        <v>21.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.37</v>
+        <v>1.57</v>
       </c>
       <c r="AE13" t="n">
         <v>1.75</v>
@@ -6162,13 +6162,13 @@
         <v>2.72</v>
       </c>
       <c r="DP13" t="n">
-        <v>8.140000000000001</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DQ13" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.57</v>
+        <v>7.28</v>
       </c>
       <c r="DS13" t="n">
         <v>0.14</v>
@@ -6180,25 +6180,25 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>54.86</v>
+        <v>55.57</v>
       </c>
       <c r="DW13" t="n">
         <v>0.28</v>
       </c>
       <c r="DX13" t="n">
-        <v>12.86</v>
+        <v>14</v>
       </c>
       <c r="DY13" t="n">
-        <v>8</v>
+        <v>8.57</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.86</v>
+        <v>5.43</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.72</v>
+        <v>22.57</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="EC13" t="n">
         <v>2</v>
@@ -6656,13 +6656,13 @@
         <v>3.25</v>
       </c>
       <c r="P15" t="n">
-        <v>8.25</v>
+        <v>11.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="R15" t="n">
-        <v>4.75</v>
+        <v>6.75</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -6680,25 +6680,25 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>50.25</v>
+        <v>49.25</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>14.5</v>
+        <v>15.25</v>
       </c>
       <c r="AA15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.25</v>
+        <v>29.25</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AE15" t="n">
         <v>2.5</v>
@@ -6964,13 +6964,13 @@
         <v>3</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.28</v>
+        <v>13</v>
       </c>
       <c r="DQ15" t="n">
-        <v>2.29</v>
+        <v>2.86</v>
       </c>
       <c r="DR15" t="n">
-        <v>5.86</v>
+        <v>7</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6982,25 +6982,25 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>46.14</v>
+        <v>45.57</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>13</v>
+        <v>13.43</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.71</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.29</v>
+        <v>5.14</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.43</v>
+        <v>25.57</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="EC15" t="n">
         <v>3.14</v>
@@ -7013,13 +7013,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E16" t="n">
         <v>0.33</v>
@@ -7055,13 +7055,13 @@
         <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>3.33</v>
+        <v>8.67</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="R16" t="n">
-        <v>2.33</v>
+        <v>3.67</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -7079,25 +7079,25 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>53</v>
+        <v>54.33</v>
       </c>
       <c r="Y16" t="n">
         <v>0.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>7.33</v>
+        <v>9.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>4</v>
+        <v>5.67</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.33</v>
+        <v>3.67</v>
       </c>
       <c r="AC16" t="n">
-        <v>11.67</v>
+        <v>17.33</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AE16" t="n">
         <v>4</v>
@@ -7106,127 +7106,127 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AI16" t="n">
-        <v>99</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AN16" t="n">
-        <v>42.75</v>
+        <v>43.6</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="AT16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BJ16" t="n">
         <v>0.75</v>
       </c>
-      <c r="AU16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>54</v>
-      </c>
-      <c r="AZ16" t="n">
+      <c r="BK16" t="n">
         <v>0.5</v>
       </c>
-      <c r="BA16" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>23.25</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>8</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0.57</v>
-      </c>
       <c r="BL16" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.43</v>
+        <v>3.62</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.57</v>
+        <v>4.12</v>
       </c>
       <c r="BR16" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS16" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BT16" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BU16" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BV16" t="n">
         <v>0</v>
@@ -7235,7 +7235,7 @@
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BY16" t="n">
         <v>1.84</v>
@@ -7244,169 +7244,169 @@
         <v>2.1</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="CD16" t="n">
-        <v>2.98</v>
+        <v>3.04</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CH16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CO16" t="n">
         <v>1.34</v>
       </c>
-      <c r="CI16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="CJ16" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="CK16" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="CL16" t="n">
+      <c r="CP16" t="n">
         <v>2.14</v>
       </c>
-      <c r="CM16" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="CN16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="CO16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="CP16" t="n">
-        <v>2.16</v>
-      </c>
       <c r="CQ16" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="CR16" t="n">
         <v>1.41</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CV16" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="DB16" t="n">
         <v>1.37</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.93</v>
+        <v>3.88</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF16" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="DH16" t="n">
-        <v>105.86</v>
+        <v>100.38</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>4.72</v>
+        <v>4.5</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.14</v>
+        <v>4.38</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DM16" t="n">
-        <v>48</v>
+        <v>47.88</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="DP16" t="n">
-        <v>8.279999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="DQ16" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
       <c r="DR16" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.57</v>
+        <v>54.37</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.43</v>
+        <v>0.37</v>
       </c>
       <c r="DX16" t="n">
-        <v>9.140000000000001</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="DY16" t="n">
-        <v>5.57</v>
+        <v>6.13</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.57</v>
+        <v>3.75</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.29</v>
+        <v>18</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="EC16" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="17">

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,61 +1379,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="G2" t="n">
         <v>3</v>
       </c>
       <c r="H2" t="n">
-        <v>96.5</v>
+        <v>97.8</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.25</v>
+        <v>5.2</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>41.75</v>
+        <v>47.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>2.2</v>
       </c>
       <c r="P2" t="n">
-        <v>13.5</v>
+        <v>10.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="R2" t="n">
-        <v>8.25</v>
+        <v>6.4</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1445,28 +1445,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>58.75</v>
+        <v>57.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.5</v>
+        <v>10.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC2" t="n">
-        <v>15.5</v>
+        <v>12.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="AE2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AF2" t="n">
         <v>0.33</v>
@@ -1550,49 +1550,49 @@
         <v>1.67</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.710000000000001</v>
+        <v>10.12</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.71</v>
+        <v>4.38</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="BR2" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS2" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BV2" t="n">
         <v>0</v>
@@ -1601,19 +1601,19 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.39</v>
+        <v>3.18</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.4</v>
+        <v>3.24</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="CC2" t="n">
         <v>2.78</v>
@@ -1622,34 +1622,34 @@
         <v>2.99</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="CH2" t="n">
         <v>1.25</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CJ2" t="n">
         <v>2.07</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CO2" t="n">
         <v>1.47</v>
@@ -1658,7 +1658,7 @@
         <v>2.48</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.56</v>
+        <v>4.58</v>
       </c>
       <c r="CR2" t="n">
         <v>1.54</v>
@@ -1669,10 +1669,10 @@
       </c>
       <c r="CU2" t="inlineStr"/>
       <c r="CV2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CX2" t="n">
         <v>1.64</v>
@@ -1684,58 +1684,58 @@
         <v>2.2</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.93</v>
+        <v>4.97</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="DH2" t="n">
-        <v>95.72</v>
+        <v>96.63</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.43</v>
+        <v>3.62</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.43</v>
+        <v>5</v>
       </c>
       <c r="DL2" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DM2" t="n">
-        <v>44.72</v>
+        <v>48</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.57</v>
+        <v>2.12</v>
       </c>
       <c r="DP2" t="n">
-        <v>8.57</v>
+        <v>7.38</v>
       </c>
       <c r="DQ2" t="n">
-        <v>1.43</v>
+        <v>1.12</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.43</v>
+        <v>4.63</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
@@ -1747,28 +1747,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54.28</v>
+        <v>54</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DX2" t="n">
-        <v>8.720000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="DY2" t="n">
-        <v>4.86</v>
+        <v>4.75</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.86</v>
+        <v>4.5</v>
       </c>
       <c r="EA2" t="n">
-        <v>10.71</v>
+        <v>9.25</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="EC2" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="3">
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
         <v>3</v>
@@ -1790,49 +1790,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="G3" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>78</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>37.75</v>
+        <v>31.4</v>
       </c>
       <c r="N3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O3" t="n">
         <v>1</v>
       </c>
-      <c r="O3" t="n">
-        <v>1.25</v>
-      </c>
       <c r="P3" t="n">
-        <v>8.75</v>
+        <v>9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="R3" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="T3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1844,28 +1844,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>47</v>
+        <v>48.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.25</v>
+        <v>7.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.25</v>
+        <v>18.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.02</v>
+        <v>0.98</v>
       </c>
       <c r="AE3" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1949,46 +1949,46 @@
         <v>2.33</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.43</v>
+        <v>8.25</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BN3" t="n">
         <v>1</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="BR3" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS3" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BT3" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
@@ -2000,19 +2000,19 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.16</v>
+        <v>3.53</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.79</v>
+        <v>4.43</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.01</v>
+        <v>3.06</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.11</v>
+        <v>3.2</v>
       </c>
       <c r="CC3" t="n">
         <v>2.58</v>
@@ -2021,73 +2021,73 @@
         <v>2.76</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="CG3" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="CJ3" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CN3" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CO3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CP3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="CQ3" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CS3" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CV3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CW3" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="CX3" t="n">
         <v>1.74</v>
       </c>
-      <c r="CK3" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="CL3" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="CM3" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CN3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="CO3" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="CP3" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="CQ3" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CS3" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="CT3" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="CU3" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="CV3" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="CW3" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="CX3" t="n">
-        <v>1.72</v>
-      </c>
       <c r="CY3" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="DB3" t="n">
         <v>1.48</v>
@@ -2105,40 +2105,40 @@
         <v>2</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DH3" t="n">
-        <v>93.86</v>
+        <v>94.75</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="DK3" t="n">
-        <v>2.72</v>
+        <v>2.5</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>40.72</v>
+        <v>36.38</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DP3" t="n">
-        <v>6.29</v>
+        <v>6.75</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="DR3" t="n">
-        <v>5.29</v>
+        <v>5.88</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2150,28 +2150,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>47.29</v>
+        <v>48.25</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX3" t="n">
-        <v>6.29</v>
+        <v>6.62</v>
       </c>
       <c r="DY3" t="n">
-        <v>3.28</v>
+        <v>3.62</v>
       </c>
       <c r="DZ3" t="n">
         <v>3</v>
       </c>
       <c r="EA3" t="n">
-        <v>14.29</v>
+        <v>15</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="4">
@@ -2304,13 +2304,13 @@
         <v>1.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT4" t="n">
         <v>1</v>
@@ -2328,25 +2328,25 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>39.4</v>
+        <v>37</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>11</v>
+        <v>11.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BC4" t="n">
         <v>4.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>15.4</v>
+        <v>18</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="BF4" t="n">
         <v>1.8</v>
@@ -2355,7 +2355,7 @@
         <v>2.62</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.619999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="BI4" t="n">
         <v>2.62</v>
@@ -2535,13 +2535,13 @@
         <v>2</v>
       </c>
       <c r="DP4" t="n">
-        <v>6.88</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DQ4" t="n">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.37</v>
+        <v>8.75</v>
       </c>
       <c r="DS4" t="n">
         <v>0.12</v>
@@ -2553,25 +2553,25 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>39.25</v>
+        <v>37.75</v>
       </c>
       <c r="DW4" t="n">
         <v>0</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.25</v>
+        <v>10.62</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.25</v>
+        <v>6.62</v>
       </c>
       <c r="DZ4" t="n">
         <v>4</v>
       </c>
       <c r="EA4" t="n">
-        <v>15.62</v>
+        <v>17.25</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="EC4" t="n">
         <v>1.88</v>
@@ -2584,61 +2584,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="G5" t="n">
-        <v>0.75</v>
+        <v>1.4</v>
       </c>
       <c r="H5" t="n">
-        <v>91</v>
+        <v>90.8</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="L5" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="M5" t="n">
-        <v>50.25</v>
+        <v>52.2</v>
       </c>
       <c r="N5" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="O5" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>13.75</v>
+        <v>10.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="R5" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2650,28 +2650,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>39.25</v>
+        <v>40</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.75</v>
+        <v>5.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="AC5" t="n">
-        <v>23</v>
+        <v>18.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2755,49 +2755,49 @@
         <v>4.67</v>
       </c>
       <c r="BG5" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="BH5" t="n">
-        <v>7.57</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="BI5" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.29</v>
+        <v>4.88</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BT5" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BU5" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV5" t="n">
         <v>0</v>
@@ -2806,19 +2806,19 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.36</v>
+        <v>3.33</v>
       </c>
       <c r="CC5" t="n">
         <v>5.63</v>
@@ -2830,13 +2830,13 @@
         <v>1.54</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="CG5" t="n">
         <v>2.31</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CI5" t="n">
         <v>1.65</v>
@@ -2845,25 +2845,25 @@
         <v>2.11</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CO5" t="n">
         <v>1.51</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CQ5" t="n">
-        <v>4.89</v>
+        <v>4.88</v>
       </c>
       <c r="CR5" t="n">
         <v>1.55</v>
@@ -2872,28 +2872,28 @@
         <v>3.11</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CU5" t="n">
         <v>1.36</v>
       </c>
       <c r="CV5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CY5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="DA5" t="n">
         <v>1.62</v>
-      </c>
-      <c r="CW5" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="CX5" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CY5" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="CZ5" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="DA5" t="n">
-        <v>1.64</v>
       </c>
       <c r="DB5" t="n">
         <v>1.52</v>
@@ -2902,79 +2902,79 @@
         <v>2.62</v>
       </c>
       <c r="DD5" t="n">
-        <v>5.19</v>
+        <v>5.2</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="DH5" t="n">
-        <v>94.14</v>
+        <v>93.62</v>
       </c>
       <c r="DI5" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DJ5" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="DK5" t="n">
-        <v>2.14</v>
+        <v>2.62</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="DM5" t="n">
-        <v>48.72</v>
+        <v>50.13</v>
       </c>
       <c r="DN5" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="DP5" t="n">
-        <v>14.86</v>
+        <v>12.87</v>
       </c>
       <c r="DQ5" t="n">
-        <v>3.43</v>
+        <v>2.88</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.29</v>
+        <v>6.25</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>39.28</v>
+        <v>39.75</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.57</v>
+        <v>10.62</v>
       </c>
       <c r="DY5" t="n">
-        <v>8</v>
+        <v>7.25</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2.57</v>
+        <v>3.37</v>
       </c>
       <c r="EA5" t="n">
-        <v>22.57</v>
+        <v>19.62</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="EC5" t="n">
         <v>4</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
@@ -3402,50 +3402,50 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>113.25</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M7" t="n">
+        <v>63</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T7" t="n">
         <v>2</v>
       </c>
-      <c r="G7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="H7" t="n">
-        <v>118.67</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="K7" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>59.67</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3</v>
-      </c>
-      <c r="P7" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="R7" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.67</v>
-      </c>
       <c r="U7" t="n">
         <v>0</v>
       </c>
@@ -3456,28 +3456,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>57</v>
+        <v>57.25</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>11.33</v>
+        <v>10</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.67</v>
+        <v>4.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.67</v>
+        <v>5.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>16.33</v>
+        <v>12</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.55</v>
+        <v>1.46</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="AF7" t="n">
         <v>0.25</v>
@@ -3561,70 +3561,70 @@
         <v>1.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.71</v>
+        <v>7.88</v>
       </c>
       <c r="BI7" t="n">
-        <v>3</v>
+        <v>2.62</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.57</v>
+        <v>4.38</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="BR7" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="BS7" t="n">
-        <v>85.70999999999999</v>
+        <v>75</v>
       </c>
       <c r="BT7" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BV7" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CC7" t="n">
         <v>3.36</v>
@@ -3636,7 +3636,7 @@
         <v>1.51</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CG7" t="n">
         <v>2.38</v>
@@ -3651,16 +3651,16 @@
         <v>2.06</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CO7" t="n">
         <v>1.47</v>
@@ -3669,88 +3669,88 @@
         <v>2.42</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.52</v>
+        <v>4.49</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CS7" t="n">
         <v>3.36</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="CU7" t="n">
         <v>1.31</v>
       </c>
       <c r="CV7" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CY7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DA7" t="n">
         <v>1.74</v>
-      </c>
-      <c r="CW7" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="CX7" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="CY7" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="CZ7" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="DA7" t="n">
-        <v>1.76</v>
       </c>
       <c r="DB7" t="n">
         <v>1.48</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.9</v>
+        <v>4.87</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.57</v>
+        <v>2</v>
       </c>
       <c r="DH7" t="n">
-        <v>103.29</v>
+        <v>102.5</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.43</v>
+        <v>3.75</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DM7" t="n">
-        <v>54.86</v>
+        <v>57.12</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DP7" t="n">
-        <v>8.710000000000001</v>
+        <v>7.5</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.86</v>
+        <v>0.62</v>
       </c>
       <c r="DR7" t="n">
-        <v>5.72</v>
+        <v>4.88</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3762,28 +3762,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>55.43</v>
+        <v>55.75</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.710000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DY7" t="n">
-        <v>4.86</v>
+        <v>4.5</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="EA7" t="n">
-        <v>17.14</v>
+        <v>14.88</v>
       </c>
       <c r="EB7" t="n">
         <v>1.22</v>
       </c>
       <c r="EC7" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="8">
@@ -3793,13 +3793,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" t="n">
         <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3883,52 +3883,52 @@
         <v>1.67</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AI8" t="n">
-        <v>108.75</v>
+        <v>103</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AN8" t="n">
-        <v>53</v>
+        <v>50.8</v>
       </c>
       <c r="AO8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AP8" t="n">
         <v>2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10.75</v>
+        <v>8.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.5</v>
+        <v>6.6</v>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3940,70 +3940,70 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>48.5</v>
+        <v>47.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB8" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="BD8" t="n">
-        <v>16.25</v>
+        <v>12.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.17</v>
+        <v>1.09</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.710000000000001</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.29</v>
+        <v>4.12</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.43</v>
+        <v>5.5</v>
       </c>
       <c r="BR8" t="n">
-        <v>85.70999999999999</v>
+        <v>75</v>
       </c>
       <c r="BS8" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -4015,7 +4015,7 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BY8" t="n">
         <v>2.57</v>
@@ -4024,13 +4024,13 @@
         <v>2.66</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="CD8" t="n">
         <v>3.04</v>
@@ -4039,10 +4039,10 @@
         <v>1.47</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CH8" t="n">
         <v>1.29</v>
@@ -4051,37 +4051,37 @@
         <v>1.77</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.22</v>
+        <v>4.23</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CS8" t="n">
         <v>3.28</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
       <c r="CU8" t="n">
         <v>1.34</v>
@@ -4093,67 +4093,67 @@
         <v>2.01</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="DB8" t="n">
         <v>1.42</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="DG8" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="DH8" t="n">
-        <v>113</v>
+        <v>108.88</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.71</v>
+        <v>4.5</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DM8" t="n">
-        <v>57.86</v>
+        <v>55.87</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.71</v>
+        <v>0.87</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
       <c r="DP8" t="n">
-        <v>8.289999999999999</v>
+        <v>7.12</v>
       </c>
       <c r="DQ8" t="n">
-        <v>1.29</v>
+        <v>1</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.86</v>
+        <v>5.88</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4165,28 +4165,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>52.57</v>
+        <v>51.25</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.43</v>
+        <v>10.75</v>
       </c>
       <c r="DY8" t="n">
-        <v>8</v>
+        <v>7.62</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.43</v>
+        <v>3.13</v>
       </c>
       <c r="EA8" t="n">
-        <v>16</v>
+        <v>13.88</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="9">
@@ -4238,13 +4238,13 @@
         <v>1.75</v>
       </c>
       <c r="P9" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.75</v>
+        <v>1.75</v>
       </c>
       <c r="R9" t="n">
-        <v>6</v>
+        <v>10.5</v>
       </c>
       <c r="S9" t="n">
         <v>0.25</v>
@@ -4262,25 +4262,25 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>56.5</v>
+        <v>58.5</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.5</v>
+        <v>13.75</v>
       </c>
       <c r="AA9" t="n">
         <v>8.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AC9" t="n">
-        <v>17.25</v>
+        <v>21.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AE9" t="n">
         <v>1.5</v>
@@ -4550,13 +4550,13 @@
         <v>2</v>
       </c>
       <c r="DP9" t="n">
-        <v>12</v>
+        <v>13.25</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.88</v>
+        <v>1.38</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.119999999999999</v>
+        <v>10.38</v>
       </c>
       <c r="DS9" t="n">
         <v>0.38</v>
@@ -4568,25 +4568,25 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="DW9" t="n">
         <v>0</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.62</v>
+        <v>13.75</v>
       </c>
       <c r="DY9" t="n">
         <v>9</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.62</v>
+        <v>4.75</v>
       </c>
       <c r="EA9" t="n">
-        <v>20.88</v>
+        <v>23.12</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="EC9" t="n">
         <v>2.12</v>
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4692,136 +4692,136 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="AI10" t="n">
-        <v>104.67</v>
+        <v>105</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AK10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>46.75</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="BQ10" t="n">
         <v>5</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>42.67</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>11.67</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>43.33</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>23.67</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>9.57</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>4.43</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BT10" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BU10" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BV10" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BY10" t="n">
         <v>3.52</v>
@@ -4830,25 +4830,25 @@
         <v>4.33</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.32</v>
+        <v>3.26</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.56</v>
+        <v>3.51</v>
       </c>
       <c r="CC10" t="n">
-        <v>5.08</v>
+        <v>4.44</v>
       </c>
       <c r="CD10" t="n">
-        <v>5.81</v>
+        <v>4.94</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.21</v>
+        <v>3.26</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="CH10" t="n">
         <v>1.28</v>
@@ -4857,142 +4857,142 @@
         <v>1.72</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.19</v>
+        <v>4.27</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="CS10" t="n">
         <v>3.14</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="CU10" t="n">
         <v>1.36</v>
       </c>
       <c r="CV10" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CW10" t="n">
         <v>2.16</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="DD10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="DH10" t="n">
-        <v>106.86</v>
+        <v>106.75</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.43</v>
+        <v>5.5</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DM10" t="n">
-        <v>59.86</v>
+        <v>59.38</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.14</v>
+        <v>8.75</v>
       </c>
       <c r="DQ10" t="n">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.14</v>
+        <v>6.12</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>49.43</v>
+        <v>50.38</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.57</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.57</v>
+        <v>5.38</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.43</v>
+        <v>17.75</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="EC10" t="n">
-        <v>3.72</v>
+        <v>3.62</v>
       </c>
     </row>
     <row r="11">
@@ -5029,7 +5029,7 @@
         <v>2.5</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
@@ -5044,13 +5044,13 @@
         <v>2.5</v>
       </c>
       <c r="P11" t="n">
-        <v>7.5</v>
+        <v>11.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="R11" t="n">
-        <v>6.25</v>
+        <v>9.25</v>
       </c>
       <c r="S11" t="n">
         <v>1.25</v>
@@ -5068,25 +5068,25 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Y11" t="n">
         <v>0.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>11.75</v>
+        <v>13.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>7</v>
+        <v>8.25</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.75</v>
+        <v>5.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>20</v>
+        <v>25.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="AE11" t="n">
         <v>1.5</v>
@@ -5176,7 +5176,7 @@
         <v>2.25</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.380000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="BI11" t="n">
         <v>2.25</v>
@@ -5341,7 +5341,7 @@
         <v>1.88</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.88</v>
+        <v>5</v>
       </c>
       <c r="DL11" t="n">
         <v>0.75</v>
@@ -5356,13 +5356,13 @@
         <v>2.38</v>
       </c>
       <c r="DP11" t="n">
-        <v>8.119999999999999</v>
+        <v>10.12</v>
       </c>
       <c r="DQ11" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.75</v>
+        <v>9.25</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,25 +5374,25 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>50.88</v>
+        <v>52.38</v>
       </c>
       <c r="DW11" t="n">
         <v>0.25</v>
       </c>
       <c r="DX11" t="n">
-        <v>10.88</v>
+        <v>11.75</v>
       </c>
       <c r="DY11" t="n">
-        <v>6.62</v>
+        <v>7.25</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="EA11" t="n">
-        <v>22</v>
+        <v>24.62</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="EC11" t="n">
         <v>1.38</v>
@@ -5808,13 +5808,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>0.5</v>
@@ -5898,130 +5898,130 @@
         <v>1.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AG13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>99.75</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>51.75</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>17</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BF13" t="n">
         <v>2</v>
       </c>
-      <c r="AH13" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>101</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>28.33</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>54</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>15</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>23.67</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.33</v>
-      </c>
       <c r="BG13" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.289999999999999</v>
+        <v>9</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BP13" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT13" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6030,7 +6030,7 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>71.43000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="BY13" t="n">
         <v>1.52</v>
@@ -6039,22 +6039,22 @@
         <v>1.54</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.01</v>
+        <v>1.88</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="CE13" t="n">
         <v>1.44</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CG13" t="n">
         <v>2.6</v>
@@ -6063,22 +6063,22 @@
         <v>1.33</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CJ13" t="n">
         <v>2.15</v>
       </c>
       <c r="CK13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CN13" t="n">
         <v>1.66</v>
-      </c>
-      <c r="CL13" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="CM13" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="CN13" t="n">
-        <v>1.67</v>
       </c>
       <c r="CO13" t="n">
         <v>1.38</v>
@@ -6087,16 +6087,16 @@
         <v>2.17</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.93</v>
+        <v>3.88</v>
       </c>
       <c r="CR13" t="n">
         <v>1.45</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CU13" t="n">
         <v>1.35</v>
@@ -6105,19 +6105,19 @@
         <v>1.66</v>
       </c>
       <c r="CW13" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DB13" t="n">
         <v>1.39</v>
@@ -6129,79 +6129,79 @@
         <v>4.01</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DG13" t="n">
         <v>3</v>
       </c>
       <c r="DH13" t="n">
-        <v>108.57</v>
+        <v>107</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.86</v>
+        <v>5.88</v>
       </c>
       <c r="DL13" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DM13" t="n">
-        <v>33</v>
+        <v>32.25</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.72</v>
+        <v>0.62</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="DP13" t="n">
-        <v>9.859999999999999</v>
+        <v>10.12</v>
       </c>
       <c r="DQ13" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.28</v>
+        <v>7</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>55.57</v>
+        <v>54.25</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DX13" t="n">
-        <v>14</v>
+        <v>15.12</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.57</v>
+        <v>9.5</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.43</v>
+        <v>5.62</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.57</v>
+        <v>22.75</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="EC13" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="14">
@@ -6211,13 +6211,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
         <v>0.25</v>
@@ -6304,46 +6304,46 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AI14" t="n">
-        <v>89.67</v>
+        <v>89.75</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.33</v>
+        <v>3.5</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="AM14" t="n">
         <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>54</v>
+        <v>49.25</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AP14" t="n">
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9</v>
+        <v>6.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.33</v>
+        <v>5.25</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AU14" t="n">
         <v>1</v>
@@ -6358,73 +6358,73 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>44.33</v>
+        <v>44.75</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.33</v>
+        <v>6.25</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="BD14" t="n">
-        <v>13</v>
+        <v>9.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.98</v>
+        <v>0.92</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.710000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="BO14" t="n">
         <v>1</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.57</v>
+        <v>4.62</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.14</v>
+        <v>3.75</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BT14" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BU14" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BV14" t="n">
         <v>0</v>
@@ -6433,7 +6433,7 @@
         <v>0</v>
       </c>
       <c r="BX14" t="n">
-        <v>28.57</v>
+        <v>37.5</v>
       </c>
       <c r="BY14" t="n">
         <v>3.47</v>
@@ -6442,22 +6442,22 @@
         <v>3.63</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.07</v>
+        <v>3.46</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.39</v>
+        <v>3.83</v>
       </c>
       <c r="CE14" t="n">
         <v>1.47</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CG14" t="n">
         <v>2.46</v>
@@ -6466,25 +6466,25 @@
         <v>1.28</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CN14" t="n">
         <v>1.66</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CP14" t="n">
         <v>2.21</v>
@@ -6493,85 +6493,85 @@
         <v>4.17</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CU14" t="n">
         <v>1.32</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="DB14" t="n">
         <v>1.43</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="DD14" t="n">
-        <v>4.51</v>
+        <v>4.5</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF14" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.14</v>
+        <v>1.88</v>
       </c>
       <c r="DH14" t="n">
-        <v>100.72</v>
+        <v>99.38</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.71</v>
+        <v>4.12</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.29</v>
+        <v>4</v>
       </c>
       <c r="DL14" t="n">
         <v>0</v>
       </c>
       <c r="DM14" t="n">
-        <v>52.43</v>
+        <v>50.25</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="DP14" t="n">
-        <v>10.43</v>
+        <v>9</v>
       </c>
       <c r="DQ14" t="n">
-        <v>2.57</v>
+        <v>2.12</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.71</v>
+        <v>5.75</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6583,28 +6583,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48</v>
+        <v>47.75</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="DX14" t="n">
-        <v>7</v>
+        <v>6.88</v>
       </c>
       <c r="DY14" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="EA14" t="n">
-        <v>14.71</v>
+        <v>12.75</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -6614,10 +6614,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
         <v>3</v>
@@ -6626,49 +6626,49 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="G15" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>89.25</v>
+        <v>92.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="K15" t="n">
-        <v>6.75</v>
+        <v>6.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>62.5</v>
+        <v>61.6</v>
       </c>
       <c r="N15" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="O15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>11.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="R15" t="n">
-        <v>6.75</v>
+        <v>5.2</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -6680,28 +6680,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>49.25</v>
+        <v>50.2</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>15.25</v>
+        <v>14.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="AC15" t="n">
-        <v>29.25</v>
+        <v>23.2</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AF15" t="n">
         <v>0.67</v>
@@ -6785,70 +6785,70 @@
         <v>4</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.86</v>
+        <v>10.25</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.29</v>
+        <v>4.38</v>
       </c>
       <c r="BQ15" t="n">
-        <v>6.57</v>
+        <v>5.88</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BT15" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BV15" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BX15" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.29</v>
+        <v>2.18</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="CC15" t="n">
         <v>3.94</v>
@@ -6857,120 +6857,124 @@
         <v>4.17</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="CJ15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CK15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CL15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="CM15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CN15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CO15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CP15" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="CQ15" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CS15" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="CT15" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="CU15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CV15" t="n">
         <v>1.74</v>
-      </c>
-      <c r="CK15" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="CL15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CM15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="CN15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="CO15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="CP15" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="CQ15" t="n">
-        <v>4</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CS15" t="inlineStr"/>
-      <c r="CT15" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="CU15" t="inlineStr"/>
-      <c r="CV15" t="n">
-        <v>1.75</v>
       </c>
       <c r="CW15" t="n">
         <v>2.1</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.07</v>
+        <v>2.02</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="DD15" t="n">
-        <v>4.97</v>
+        <v>4.89</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DF15" t="n">
         <v>2</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.57</v>
+        <v>3.25</v>
       </c>
       <c r="DH15" t="n">
-        <v>91.14</v>
+        <v>92.75</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="DK15" t="n">
-        <v>6.57</v>
+        <v>6.25</v>
       </c>
       <c r="DL15" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="DM15" t="n">
-        <v>59.71</v>
+        <v>59.5</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="DO15" t="n">
         <v>3</v>
       </c>
       <c r="DP15" t="n">
-        <v>13</v>
+        <v>11.25</v>
       </c>
       <c r="DQ15" t="n">
-        <v>2.86</v>
+        <v>2.38</v>
       </c>
       <c r="DR15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6982,28 +6986,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.57</v>
+        <v>46.63</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>13.43</v>
+        <v>13.12</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.289999999999999</v>
+        <v>8</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.14</v>
+        <v>5.12</v>
       </c>
       <c r="EA15" t="n">
-        <v>25.57</v>
+        <v>22.25</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="16">
@@ -7136,13 +7140,13 @@
         <v>3.2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>9.4</v>
+        <v>12.8</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="AT16" t="n">
         <v>0.8</v>
@@ -7160,25 +7164,25 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>54.4</v>
+        <v>52.8</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.4</v>
       </c>
       <c r="BA16" t="n">
-        <v>10.2</v>
+        <v>10.8</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BC16" t="n">
         <v>3.8</v>
       </c>
       <c r="BD16" t="n">
-        <v>18.4</v>
+        <v>24</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="BF16" t="n">
         <v>3.8</v>
@@ -7367,13 +7371,13 @@
         <v>2.75</v>
       </c>
       <c r="DP16" t="n">
-        <v>9.130000000000001</v>
+        <v>11.25</v>
       </c>
       <c r="DQ16" t="n">
-        <v>1.37</v>
+        <v>1.75</v>
       </c>
       <c r="DR16" t="n">
-        <v>3.13</v>
+        <v>4</v>
       </c>
       <c r="DS16" t="n">
         <v>0.12</v>
@@ -7385,25 +7389,25 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>54.37</v>
+        <v>53.37</v>
       </c>
       <c r="DW16" t="n">
         <v>0.37</v>
       </c>
       <c r="DX16" t="n">
-        <v>9.869999999999999</v>
+        <v>10.25</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.13</v>
+        <v>6.5</v>
       </c>
       <c r="DZ16" t="n">
         <v>3.75</v>
       </c>
       <c r="EA16" t="n">
-        <v>18</v>
+        <v>21.5</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="EC16" t="n">
         <v>3.88</v>
@@ -7416,13 +7420,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7506,130 +7510,130 @@
         <v>3.5</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AG17" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>95.33</v>
+        <v>101.25</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>5.33</v>
+        <v>4.25</v>
       </c>
       <c r="AL17" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AN17" t="n">
-        <v>40.67</v>
+        <v>53.25</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ17" t="n">
-        <v>7.67</v>
+        <v>5.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.67</v>
+        <v>0.25</v>
       </c>
       <c r="AS17" t="n">
-        <v>8</v>
+        <v>5.75</v>
       </c>
       <c r="AT17" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AU17" t="n">
         <v>1</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>49.33</v>
+        <v>49</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.67</v>
+        <v>9.75</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.33</v>
+        <v>6</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.33</v>
+        <v>3.75</v>
       </c>
       <c r="BD17" t="n">
-        <v>13.67</v>
+        <v>10</v>
       </c>
       <c r="BE17" t="n">
-        <v>0.95</v>
+        <v>1.27</v>
       </c>
       <c r="BF17" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.43</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="BP17" t="n">
-        <v>4</v>
+        <v>4.62</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.43</v>
+        <v>5.25</v>
       </c>
       <c r="BR17" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS17" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT17" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BU17" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7638,7 +7642,7 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
         <v>2.68</v>
@@ -7647,55 +7651,55 @@
         <v>3.16</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.83</v>
+        <v>3.62</v>
       </c>
       <c r="CD17" t="n">
-        <v>4.32</v>
+        <v>4</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="CG17" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CM17" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="CR17" t="n">
         <v>1.55</v>
@@ -7706,106 +7710,106 @@
       </c>
       <c r="CU17" t="inlineStr"/>
       <c r="CV17" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CW17" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DA17" t="n">
         <v>1.7</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="DD17" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="DE17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DF17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="DG17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DH17" t="n">
+        <v>101.38</v>
+      </c>
+      <c r="DI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ17" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="DK17" t="n">
         <v>4.88</v>
       </c>
-      <c r="DE17" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="DF17" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="DG17" t="n">
-        <v>3</v>
-      </c>
-      <c r="DH17" t="n">
-        <v>98.86</v>
-      </c>
-      <c r="DI17" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ17" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="DK17" t="n">
-        <v>5</v>
-      </c>
       <c r="DL17" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DM17" t="n">
-        <v>57.43</v>
+        <v>61.62</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DO17" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="DP17" t="n">
-        <v>6.72</v>
+        <v>5.75</v>
       </c>
       <c r="DQ17" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="DR17" t="n">
-        <v>5.71</v>
+        <v>4.88</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>48.28</v>
+        <v>48.25</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DX17" t="n">
-        <v>9.859999999999999</v>
+        <v>10.62</v>
       </c>
       <c r="DY17" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.86</v>
+        <v>4.38</v>
       </c>
       <c r="EA17" t="n">
-        <v>12.72</v>
+        <v>11</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="EC17" t="n">
-        <v>3.71</v>
+        <v>3.38</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1421,13 +1421,13 @@
         <v>2.2</v>
       </c>
       <c r="P2" t="n">
-        <v>10.6</v>
+        <v>14</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S2" t="n">
         <v>1.4</v>
@@ -1445,25 +1445,25 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>57.4</v>
+        <v>56.4</v>
       </c>
       <c r="Y2" t="n">
         <v>0.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.2</v>
+        <v>11</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>12.2</v>
+        <v>16.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AE2" t="n">
         <v>4.2</v>
@@ -1729,13 +1729,13 @@
         <v>2.12</v>
       </c>
       <c r="DP2" t="n">
-        <v>7.38</v>
+        <v>9.5</v>
       </c>
       <c r="DQ2" t="n">
-        <v>1.12</v>
+        <v>1.62</v>
       </c>
       <c r="DR2" t="n">
-        <v>4.63</v>
+        <v>6.13</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
@@ -1747,25 +1747,25 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>54</v>
+        <v>53.37</v>
       </c>
       <c r="DW2" t="n">
         <v>0.25</v>
       </c>
       <c r="DX2" t="n">
-        <v>9.25</v>
+        <v>9.75</v>
       </c>
       <c r="DY2" t="n">
-        <v>4.75</v>
+        <v>5.38</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.5</v>
+        <v>4.38</v>
       </c>
       <c r="EA2" t="n">
-        <v>9.25</v>
+        <v>11.87</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="EC2" t="n">
         <v>3.25</v>
@@ -2584,13 +2584,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" t="n">
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
         <v>0.2</v>
@@ -2626,13 +2626,13 @@
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>10.8</v>
+        <v>12.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="S5" t="n">
         <v>0.8</v>
@@ -2650,25 +2650,25 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>40</v>
+        <v>39.8</v>
       </c>
       <c r="Y5" t="n">
         <v>0.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>18.2</v>
+        <v>23.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AE5" t="n">
         <v>3.6</v>
@@ -2677,127 +2677,127 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>94.75</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>48.25</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>42.25</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BM5" t="n">
         <v>0.33</v>
       </c>
-      <c r="AI5" t="n">
-        <v>98.33</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>46.67</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>16.33</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>39.33</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0.38</v>
-      </c>
       <c r="BN5" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.88</v>
+        <v>5.33</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BT5" t="n">
-        <v>25</v>
+        <v>33.33</v>
       </c>
       <c r="BU5" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV5" t="n">
         <v>0</v>
@@ -2806,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BY5" t="n">
         <v>2.96</v>
@@ -2818,25 +2818,25 @@
         <v>3.06</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="CC5" t="n">
-        <v>5.63</v>
+        <v>5.07</v>
       </c>
       <c r="CD5" t="n">
-        <v>7.25</v>
+        <v>6.44</v>
       </c>
       <c r="CE5" t="n">
         <v>1.54</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.51</v>
+        <v>3.52</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CI5" t="n">
         <v>1.65</v>
@@ -2845,22 +2845,22 @@
         <v>2.11</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CO5" t="n">
         <v>1.51</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CQ5" t="n">
         <v>4.88</v>
@@ -2884,10 +2884,10 @@
         <v>2.32</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.01</v>
@@ -2899,82 +2899,82 @@
         <v>1.52</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="DD5" t="n">
-        <v>5.2</v>
+        <v>5.22</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="DG5" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="DH5" t="n">
-        <v>93.62</v>
+        <v>92.56</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ5" t="n">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="DK5" t="n">
-        <v>2.62</v>
+        <v>3.22</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM5" t="n">
-        <v>50.13</v>
+        <v>50.44</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.87</v>
+        <v>12.44</v>
       </c>
       <c r="DQ5" t="n">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.25</v>
+        <v>6.56</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>39.75</v>
+        <v>40.89</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="DX5" t="n">
-        <v>10.62</v>
+        <v>11.11</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.25</v>
+        <v>7.67</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.37</v>
+        <v>3.44</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.62</v>
+        <v>20.22</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="EC5" t="n">
         <v>4</v>
@@ -3110,13 +3110,13 @@
         <v>2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.4</v>
+        <v>11</v>
       </c>
       <c r="AR6" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.8</v>
+        <v>7.6</v>
       </c>
       <c r="AT6" t="n">
         <v>1.4</v>
@@ -3134,7 +3134,7 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>42.6</v>
+        <v>47</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -3149,7 +3149,7 @@
         <v>3.4</v>
       </c>
       <c r="BD6" t="n">
-        <v>13</v>
+        <v>16.8</v>
       </c>
       <c r="BE6" t="n">
         <v>1.22</v>
@@ -3341,13 +3341,13 @@
         <v>2</v>
       </c>
       <c r="DP6" t="n">
-        <v>8.869999999999999</v>
+        <v>11.12</v>
       </c>
       <c r="DQ6" t="n">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.5</v>
+        <v>8.25</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3359,7 +3359,7 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>45.25</v>
+        <v>48</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
@@ -3374,7 +3374,7 @@
         <v>3.13</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.62</v>
+        <v>21</v>
       </c>
       <c r="EB6" t="n">
         <v>1.23</v>
@@ -4722,13 +4722,13 @@
         <v>1.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10.75</v>
+        <v>16</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>8.5</v>
+        <v>12.25</v>
       </c>
       <c r="AT10" t="n">
         <v>2.25</v>
@@ -4746,25 +4746,25 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>46.75</v>
+        <v>47</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.25</v>
       </c>
       <c r="BA10" t="n">
-        <v>8</v>
+        <v>9.25</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="BC10" t="n">
         <v>2.75</v>
       </c>
       <c r="BD10" t="n">
-        <v>17.5</v>
+        <v>24.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="BF10" t="n">
         <v>4.25</v>
@@ -4953,13 +4953,13 @@
         <v>2.62</v>
       </c>
       <c r="DP10" t="n">
-        <v>8.75</v>
+        <v>11.38</v>
       </c>
       <c r="DQ10" t="n">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.12</v>
+        <v>8</v>
       </c>
       <c r="DS10" t="n">
         <v>0.12</v>
@@ -4971,25 +4971,25 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.38</v>
+        <v>50.5</v>
       </c>
       <c r="DW10" t="n">
         <v>0.12</v>
       </c>
       <c r="DX10" t="n">
-        <v>9.880000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.38</v>
+        <v>6</v>
       </c>
       <c r="DZ10" t="n">
         <v>4.5</v>
       </c>
       <c r="EA10" t="n">
-        <v>17.75</v>
+        <v>21.25</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="EC10" t="n">
         <v>3.62</v>
@@ -5405,13 +5405,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5447,13 +5447,13 @@
         <v>2.75</v>
       </c>
       <c r="P12" t="n">
-        <v>7.25</v>
+        <v>9.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.5</v>
+        <v>2.75</v>
       </c>
       <c r="R12" t="n">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="S12" t="n">
         <v>0.5</v>
@@ -5471,163 +5471,163 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>63.5</v>
+        <v>58</v>
       </c>
       <c r="Y12" t="n">
         <v>0.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>12</v>
+        <v>13.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.25</v>
+        <v>9</v>
       </c>
       <c r="AB12" t="n">
         <v>4.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>14.25</v>
+        <v>21.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="AE12" t="n">
         <v>2.25</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="AI12" t="n">
-        <v>104</v>
+        <v>98.8</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AL12" t="n">
-        <v>6.25</v>
+        <v>5</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AN12" t="n">
-        <v>49</v>
+        <v>46.4</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.5</v>
+        <v>11.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>58.5</v>
+        <v>55</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>11.5</v>
+        <v>10.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD12" t="n">
-        <v>26.75</v>
+        <v>21.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="BF12" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.38</v>
+        <v>2.67</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.38</v>
+        <v>0.67</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.88</v>
+        <v>4.78</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT12" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BU12" t="n">
-        <v>12.5</v>
+        <v>22.22</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BY12" t="n">
         <v>1.76</v>
@@ -5636,55 +5636,55 @@
         <v>1.73</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.69</v>
+        <v>3.62</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.88</v>
+        <v>3.82</v>
       </c>
       <c r="CC12" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="CD12" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="CE12" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="CF12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CG12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CH12" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CK12" t="n">
         <v>0.88</v>
       </c>
-      <c r="CF12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="CG12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CH12" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="CI12" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="CJ12" t="n">
+      <c r="CL12" t="n">
         <v>1.24</v>
       </c>
-      <c r="CK12" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="CL12" t="n">
-        <v>1.39</v>
-      </c>
       <c r="CM12" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.83</v>
+        <v>0.74</v>
       </c>
       <c r="CP12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="CQ12" t="n">
         <v>2.02</v>
-      </c>
-      <c r="CQ12" t="n">
-        <v>2.28</v>
       </c>
       <c r="CR12" t="n">
         <v>1.46</v>
@@ -5726,79 +5726,79 @@
         <v>3.78</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.12</v>
+        <v>2.78</v>
       </c>
       <c r="DH12" t="n">
-        <v>110.88</v>
+        <v>107.22</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.88</v>
+        <v>5.22</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DM12" t="n">
-        <v>52.5</v>
+        <v>50.67</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.88</v>
+        <v>10.56</v>
       </c>
       <c r="DQ12" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.12</v>
+        <v>5.89</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>61</v>
+        <v>56.33</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX12" t="n">
-        <v>11.75</v>
+        <v>12</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.12</v>
+        <v>7.33</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.62</v>
+        <v>4.67</v>
       </c>
       <c r="EA12" t="n">
-        <v>20.5</v>
+        <v>21.33</v>
       </c>
       <c r="EB12" t="n">
         <v>1.45</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -5808,94 +5808,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
         <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F13" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="G13" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="H13" t="n">
-        <v>114.25</v>
+        <v>119.6</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="K13" t="n">
-        <v>6.25</v>
+        <v>5.8</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M13" t="n">
-        <v>36.5</v>
+        <v>46.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="O13" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P13" t="n">
-        <v>9.75</v>
+        <v>7.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="T13" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="V13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>56.75</v>
+        <v>57.4</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.25</v>
+        <v>12</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="AB13" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AC13" t="n">
-        <v>21.75</v>
+        <v>17.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF13" t="n">
         <v>0.25</v>
@@ -5979,49 +5979,49 @@
         <v>2</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BH13" t="n">
-        <v>9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.75</v>
+        <v>4.78</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT13" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BU13" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6030,19 +6030,19 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.94</v>
+        <v>3.86</v>
       </c>
       <c r="CC13" t="n">
         <v>1.88</v>
@@ -6051,13 +6051,13 @@
         <v>2.03</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="CH13" t="n">
         <v>1.33</v>
@@ -6066,28 +6066,28 @@
         <v>1.66</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CK13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CN13" t="n">
         <v>1.67</v>
       </c>
-      <c r="CL13" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="CM13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="CN13" t="n">
-        <v>1.66</v>
-      </c>
       <c r="CO13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP13" t="n">
         <v>2.17</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="CR13" t="n">
         <v>1.45</v>
@@ -6108,16 +6108,16 @@
         <v>2.27</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DB13" t="n">
         <v>1.39</v>
@@ -6126,82 +6126,82 @@
         <v>2.21</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="DG13" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="DH13" t="n">
-        <v>107</v>
+        <v>110.78</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.88</v>
+        <v>5.67</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DM13" t="n">
-        <v>32.25</v>
+        <v>38.11</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.12</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DQ13" t="n">
-        <v>3.75</v>
+        <v>3.22</v>
       </c>
       <c r="DR13" t="n">
-        <v>7</v>
+        <v>6.11</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>54.25</v>
+        <v>54.89</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DX13" t="n">
-        <v>15.12</v>
+        <v>14.22</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.5</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.62</v>
+        <v>5.44</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.75</v>
+        <v>20.11</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="14">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6704,28 +6704,28 @@
         <v>2.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AG15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AH15" t="n">
         <v>3</v>
       </c>
-      <c r="AH15" t="n">
-        <v>3.67</v>
-      </c>
       <c r="AI15" t="n">
-        <v>93.67</v>
+        <v>94.25</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>4</v>
+        <v>4.25</v>
       </c>
       <c r="AL15" t="n">
-        <v>6.33</v>
+        <v>5.75</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AN15" t="n">
         <v>56</v>
@@ -6734,109 +6734,109 @@
         <v>1</v>
       </c>
       <c r="AP15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BG15" t="n">
         <v>2.67</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>15.33</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>40.67</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>20.67</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>2.62</v>
-      </c>
       <c r="BH15" t="n">
-        <v>10.25</v>
+        <v>10</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.38</v>
+        <v>4.44</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BT15" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BU15" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BV15" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW15" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX15" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BY15" t="n">
         <v>2.18</v>
@@ -6845,55 +6845,55 @@
         <v>2.27</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CC15" t="n">
-        <v>3.94</v>
+        <v>4.49</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.17</v>
+        <v>4.86</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="CF15" t="n">
         <v>2.91</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM15" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="CQ15" t="n">
-        <v>4.03</v>
+        <v>4.02</v>
       </c>
       <c r="CR15" t="n">
         <v>1.5</v>
@@ -6914,67 +6914,67 @@
         <v>2.1</v>
       </c>
       <c r="CX15" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="DD15" t="n">
-        <v>4.89</v>
+        <v>4.77</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF15" t="n">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="DG15" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="DH15" t="n">
-        <v>92.75</v>
+        <v>93.11</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="DK15" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DM15" t="n">
-        <v>59.5</v>
+        <v>59.11</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DO15" t="n">
         <v>3</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.25</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="DQ15" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="DR15" t="n">
-        <v>6</v>
+        <v>5.22</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6986,28 +6986,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>46.63</v>
+        <v>45.89</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>13.12</v>
+        <v>12.33</v>
       </c>
       <c r="DY15" t="n">
-        <v>8</v>
+        <v>7.56</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.12</v>
+        <v>4.78</v>
       </c>
       <c r="EA15" t="n">
-        <v>22.25</v>
+        <v>19.67</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="16">
@@ -7017,94 +7017,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
         <v>5</v>
       </c>
       <c r="E16" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="F16" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>115</v>
+        <v>121.25</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>4.67</v>
+        <v>4.25</v>
       </c>
       <c r="K16" t="n">
-        <v>3.67</v>
+        <v>4.5</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M16" t="n">
-        <v>55</v>
+        <v>63.75</v>
       </c>
       <c r="N16" t="n">
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>8.67</v>
+        <v>6.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.33</v>
+        <v>0.75</v>
       </c>
       <c r="R16" t="n">
-        <v>3.67</v>
+        <v>2.5</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T16" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>54.33</v>
+        <v>55.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>9.33</v>
+        <v>9.75</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.67</v>
+        <v>5.5</v>
       </c>
       <c r="AB16" t="n">
-        <v>3.67</v>
+        <v>4.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>17.33</v>
+        <v>12.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AE16" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7188,70 +7188,70 @@
         <v>3.8</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="BH16" t="n">
-        <v>7.75</v>
+        <v>7.67</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.25</v>
+        <v>2.56</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.5</v>
+        <v>0.78</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN16" t="n">
         <v>1</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="BR16" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS16" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BT16" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BU16" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BV16" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BY16" t="n">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.1</v>
+        <v>2.41</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CC16" t="n">
         <v>2.9</v>
@@ -7260,49 +7260,49 @@
         <v>3.04</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="CF16" t="n">
-        <v>3.05</v>
+        <v>2.71</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="CL16" t="n">
-        <v>2.17</v>
+        <v>1.93</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.14</v>
+        <v>1.9</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.72</v>
+        <v>1.53</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="CP16" t="n">
         <v>2.14</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.81</v>
+        <v>3.39</v>
       </c>
       <c r="CR16" t="n">
         <v>1.41</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CT16" t="n">
         <v>2.9</v>
@@ -7338,79 +7338,79 @@
         <v>3.88</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="DH16" t="n">
-        <v>100.38</v>
+        <v>104.78</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.38</v>
+        <v>4.67</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="DM16" t="n">
-        <v>47.88</v>
+        <v>52.56</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.25</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="DQ16" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="DR16" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>54</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DX16" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="DY16" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="DZ16" t="n">
         <v>4</v>
       </c>
-      <c r="DS16" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DT16" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV16" t="n">
-        <v>53.37</v>
-      </c>
-      <c r="DW16" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="DX16" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="DY16" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="DZ16" t="n">
-        <v>3.75</v>
-      </c>
       <c r="EA16" t="n">
-        <v>21.5</v>
+        <v>19</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="EC16" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="17">
@@ -7420,10 +7420,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" t="n">
         <v>4</v>
@@ -7432,82 +7432,82 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="H17" t="n">
-        <v>101.5</v>
+        <v>96.2</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="K17" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="L17" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M17" t="n">
-        <v>70</v>
+        <v>66.8</v>
       </c>
       <c r="N17" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="O17" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="P17" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.25</v>
+        <v>0.8</v>
       </c>
       <c r="R17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="T17" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>47.5</v>
+        <v>47.8</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>11.5</v>
+        <v>10.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AC17" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AE17" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="AF17" t="n">
         <v>0.25</v>
@@ -7543,13 +7543,13 @@
         <v>1.75</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.5</v>
+        <v>8.75</v>
       </c>
       <c r="AR17" t="n">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.75</v>
+        <v>8</v>
       </c>
       <c r="AT17" t="n">
         <v>1.25</v>
@@ -7567,73 +7567,73 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>49</v>
+        <v>50.25</v>
       </c>
       <c r="AZ17" t="n">
         <v>0.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>9.75</v>
+        <v>11.25</v>
       </c>
       <c r="BB17" t="n">
-        <v>6</v>
+        <v>8.25</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="BD17" t="n">
-        <v>10</v>
+        <v>14.25</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="BF17" t="n">
         <v>3.25</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.880000000000001</v>
+        <v>10.44</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BN17" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.62</v>
+        <v>4.78</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.25</v>
+        <v>5.67</v>
       </c>
       <c r="BR17" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS17" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT17" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BU17" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV17" t="n">
         <v>0</v>
@@ -7642,16 +7642,16 @@
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.16</v>
+        <v>2.95</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CB17" t="n">
         <v>3.1</v>
@@ -7663,43 +7663,43 @@
         <v>4</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.97</v>
+        <v>3.03</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="CM17" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="CN17" t="n">
         <v>1.48</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.1</v>
+        <v>4.19</v>
       </c>
       <c r="CR17" t="n">
         <v>1.55</v>
@@ -7716,100 +7716,100 @@
         <v>2.05</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="DA17" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="DB17" t="n">
         <v>1.48</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.94</v>
+        <v>4.99</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF17" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.75</v>
+        <v>3.11</v>
       </c>
       <c r="DH17" t="n">
-        <v>101.38</v>
+        <v>98.44</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.88</v>
+        <v>3.67</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.88</v>
+        <v>5.11</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DM17" t="n">
-        <v>61.62</v>
+        <v>60.78</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="DP17" t="n">
-        <v>5.75</v>
+        <v>6.44</v>
       </c>
       <c r="DQ17" t="n">
-        <v>0.75</v>
+        <v>1.22</v>
       </c>
       <c r="DR17" t="n">
-        <v>4.88</v>
+        <v>5.22</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>48.25</v>
+        <v>48.89</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DX17" t="n">
-        <v>10.62</v>
+        <v>10.78</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.25</v>
+        <v>6.78</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.38</v>
+        <v>4</v>
       </c>
       <c r="EA17" t="n">
-        <v>11</v>
+        <v>11.56</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="EC17" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
         <v>0.2</v>
@@ -1469,49 +1469,49 @@
         <v>4.2</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AG2" t="n">
         <v>1</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.67</v>
+        <v>2.25</v>
       </c>
       <c r="AI2" t="n">
-        <v>94.67</v>
+        <v>94.5</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN2" t="n">
-        <v>48.67</v>
+        <v>50.5</v>
       </c>
       <c r="AO2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AS2" t="n">
         <v>1</v>
       </c>
-      <c r="AP2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AT2" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="AU2" t="n">
         <v>1</v>
@@ -1526,73 +1526,73 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>48.33</v>
+        <v>50</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.67</v>
+        <v>10</v>
       </c>
       <c r="BB2" t="n">
-        <v>4</v>
+        <v>5.75</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.67</v>
+        <v>4.25</v>
       </c>
       <c r="BD2" t="n">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.12</v>
+        <v>10.11</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.38</v>
+        <v>4.67</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.75</v>
+        <v>5.44</v>
       </c>
       <c r="BR2" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS2" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BT2" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BU2" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BV2" t="n">
         <v>0</v>
@@ -1601,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BY2" t="n">
         <v>3.18</v>
@@ -1610,25 +1610,25 @@
         <v>3.24</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CB2" t="n">
         <v>3.14</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.99</v>
+        <v>3.17</v>
       </c>
       <c r="CE2" t="n">
         <v>1.51</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CH2" t="n">
         <v>1.25</v>
@@ -1637,13 +1637,13 @@
         <v>1.72</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="CM2" t="n">
         <v>2.15</v>
@@ -1658,7 +1658,7 @@
         <v>2.48</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.58</v>
+        <v>4.64</v>
       </c>
       <c r="CR2" t="n">
         <v>1.54</v>
@@ -1672,7 +1672,7 @@
         <v>1.7</v>
       </c>
       <c r="CW2" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CX2" t="n">
         <v>1.64</v>
@@ -1687,55 +1687,55 @@
         <v>1.74</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="DC2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DF2" t="n">
         <v>2.56</v>
       </c>
-      <c r="DD2" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>2.75</v>
-      </c>
       <c r="DG2" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="DH2" t="n">
-        <v>96.63</v>
+        <v>96.33</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.62</v>
+        <v>3.33</v>
       </c>
       <c r="DK2" t="n">
-        <v>5</v>
+        <v>4.89</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DM2" t="n">
-        <v>48</v>
+        <v>48.89</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="DP2" t="n">
-        <v>9.5</v>
+        <v>8.33</v>
       </c>
       <c r="DQ2" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="DR2" t="n">
-        <v>6.13</v>
+        <v>5.33</v>
       </c>
       <c r="DS2" t="n">
         <v>0</v>
@@ -1747,28 +1747,28 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>53.37</v>
+        <v>53.56</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DX2" t="n">
-        <v>9.75</v>
+        <v>10.56</v>
       </c>
       <c r="DY2" t="n">
-        <v>5.38</v>
+        <v>6</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.38</v>
+        <v>4.56</v>
       </c>
       <c r="EA2" t="n">
-        <v>11.87</v>
+        <v>10.44</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="EC2" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -1778,13 +1778,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1871,49 +1871,49 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>115</v>
+        <v>109.25</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>44.67</v>
+        <v>48.75</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.33</v>
+        <v>-0.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.67</v>
+        <v>2.5</v>
       </c>
       <c r="AT3" t="n">
         <v>1</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1925,70 +1925,70 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>47.67</v>
+        <v>47.75</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="BC3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG3" t="n">
         <v>1.67</v>
       </c>
-      <c r="BD3" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>1.5</v>
-      </c>
       <c r="BH3" t="n">
-        <v>8.25</v>
+        <v>7.78</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="BN3" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.5</v>
+        <v>4.11</v>
       </c>
       <c r="BR3" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS3" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BT3" t="n">
-        <v>12.5</v>
+        <v>22.22</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
@@ -2000,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>25</v>
+        <v>33.33</v>
       </c>
       <c r="BY3" t="n">
         <v>3.53</v>
@@ -2009,85 +2009,85 @@
         <v>4.43</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CB3" t="n">
         <v>3.2</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.76</v>
+        <v>2.9</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="CI3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CM3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CN3" t="n">
         <v>1.48</v>
       </c>
-      <c r="CJ3" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="CK3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="CL3" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="CM3" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="CN3" t="n">
-        <v>1.45</v>
-      </c>
       <c r="CO3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.88</v>
+        <v>3.99</v>
       </c>
       <c r="CR3" t="n">
         <v>1.51</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CT3" t="n">
         <v>2.55</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="CV3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CW3" t="n">
         <v>2.09</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DB3" t="n">
         <v>1.48</v>
@@ -2096,7 +2096,7 @@
         <v>2.54</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.95</v>
+        <v>4.94</v>
       </c>
       <c r="DE3" t="n">
         <v>0</v>
@@ -2105,40 +2105,40 @@
         <v>2</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="DH3" t="n">
-        <v>94.75</v>
+        <v>94.44</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.87</v>
+        <v>2.78</v>
       </c>
       <c r="DK3" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>36.38</v>
+        <v>39.11</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DP3" t="n">
-        <v>6.75</v>
+        <v>5.89</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.38</v>
+        <v>0.22</v>
       </c>
       <c r="DR3" t="n">
-        <v>5.88</v>
+        <v>5.11</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2150,28 +2150,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>48.25</v>
+        <v>48.22</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX3" t="n">
-        <v>6.62</v>
+        <v>6.67</v>
       </c>
       <c r="DY3" t="n">
-        <v>3.62</v>
+        <v>3.44</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="EA3" t="n">
-        <v>15</v>
+        <v>13.22</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="4">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
@@ -2193,82 +2193,82 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="G4" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="H4" t="n">
-        <v>90</v>
+        <v>84.5</v>
       </c>
       <c r="I4" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>5.33</v>
+        <v>5.25</v>
       </c>
       <c r="L4" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="M4" t="n">
-        <v>56.33</v>
+        <v>50.75</v>
       </c>
       <c r="N4" t="n">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="O4" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="P4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.67</v>
+        <v>0.25</v>
       </c>
       <c r="R4" t="n">
-        <v>10.33</v>
+        <v>7.5</v>
       </c>
       <c r="S4" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>39</v>
+        <v>39.25</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.33</v>
+        <v>4.25</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.67</v>
+        <v>4.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>16</v>
+        <v>11.75</v>
       </c>
       <c r="AD4" t="n">
         <v>1.24</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AF4" t="n">
         <v>0.4</v>
@@ -2352,70 +2352,70 @@
         <v>1.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.75</v>
+        <v>10</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.5</v>
+        <v>4.89</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5</v>
+        <v>4.89</v>
       </c>
       <c r="BR4" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS4" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BU4" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BV4" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW4" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BY4" t="n">
-        <v>3.66</v>
+        <v>3.49</v>
       </c>
       <c r="BZ4" t="n">
-        <v>4.04</v>
+        <v>3.92</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CC4" t="n">
         <v>3.76</v>
@@ -2430,22 +2430,22 @@
         <v>3.14</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CI4" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CK4" t="n">
         <v>1.66</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CM4" t="n">
         <v>2.07</v>
@@ -2454,31 +2454,31 @@
         <v>1.69</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CV4" t="n">
         <v>1.72</v>
       </c>
       <c r="CW4" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CX4" t="n">
         <v>1.69</v>
@@ -2496,85 +2496,85 @@
         <v>1.45</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.62</v>
+        <v>4.6</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.37</v>
+        <v>2.11</v>
       </c>
       <c r="DH4" t="n">
-        <v>88.75</v>
+        <v>86.44</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.88</v>
+        <v>2.33</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.37</v>
+        <v>4.44</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DM4" t="n">
-        <v>52.25</v>
+        <v>50.22</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="DO4" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="DP4" t="n">
-        <v>8.380000000000001</v>
+        <v>7.33</v>
       </c>
       <c r="DQ4" t="n">
-        <v>1.38</v>
+        <v>1.11</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.75</v>
+        <v>7.67</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>37.75</v>
+        <v>38</v>
       </c>
       <c r="DW4" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.62</v>
+        <v>10.33</v>
       </c>
       <c r="DY4" t="n">
-        <v>6.62</v>
+        <v>6</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.25</v>
+        <v>15.22</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.88</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="5">
@@ -2707,13 +2707,13 @@
         <v>3.25</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.75</v>
+        <v>9.25</v>
       </c>
       <c r="AT5" t="n">
         <v>2.5</v>
@@ -2731,25 +2731,25 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>42.25</v>
+        <v>42.5</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.75</v>
       </c>
       <c r="BA5" t="n">
-        <v>11.5</v>
+        <v>12.75</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.25</v>
+        <v>10.75</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="BD5" t="n">
-        <v>16.25</v>
+        <v>24</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="BF5" t="n">
         <v>4.5</v>
@@ -2818,13 +2818,13 @@
         <v>3.06</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CC5" t="n">
         <v>5.07</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.44</v>
+        <v>6.41</v>
       </c>
       <c r="CE5" t="n">
         <v>1.54</v>
@@ -2938,13 +2938,13 @@
         <v>2</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.44</v>
+        <v>13.78</v>
       </c>
       <c r="DQ5" t="n">
-        <v>3.22</v>
+        <v>3.78</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.56</v>
+        <v>7.22</v>
       </c>
       <c r="DS5" t="n">
         <v>0.11</v>
@@ -2956,25 +2956,25 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>40.89</v>
+        <v>41</v>
       </c>
       <c r="DW5" t="n">
         <v>0.44</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.11</v>
+        <v>11.67</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.67</v>
+        <v>8.33</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.44</v>
+        <v>3.33</v>
       </c>
       <c r="EA5" t="n">
-        <v>20.22</v>
+        <v>23.67</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="EC5" t="n">
         <v>4</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -2999,82 +2999,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>97.75</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M6" t="n">
+        <v>58</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P6" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AB6" t="n">
         <v>3</v>
       </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>100</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="M6" t="n">
-        <v>61.67</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2</v>
-      </c>
-      <c r="P6" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="R6" t="n">
-        <v>9.33</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>49.67</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.67</v>
-      </c>
       <c r="AC6" t="n">
-        <v>28</v>
+        <v>20.75</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3158,49 +3158,49 @@
         <v>3.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.38</v>
+        <v>9.33</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL6" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BP6" t="n">
-        <v>5.12</v>
+        <v>4.67</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.38</v>
+        <v>4.78</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BU6" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3209,19 +3209,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.95</v>
+        <v>2.89</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.29</v>
+        <v>3.23</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="CC6" t="n">
         <v>3.88</v>
@@ -3230,13 +3230,13 @@
         <v>4.42</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CG6" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CH6" t="n">
         <v>1.29</v>
@@ -3248,25 +3248,25 @@
         <v>1.97</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CL6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="CM6" t="n">
         <v>2.15</v>
       </c>
-      <c r="CM6" t="n">
-        <v>2.17</v>
-      </c>
       <c r="CN6" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CO6" t="n">
         <v>1.41</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.41</v>
+        <v>4.42</v>
       </c>
       <c r="CR6" t="n">
         <v>1.49</v>
@@ -3287,67 +3287,67 @@
         <v>2.06</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DB6" t="n">
         <v>1.43</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.46</v>
+        <v>4.48</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="DH6" t="n">
-        <v>103</v>
+        <v>101.67</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM6" t="n">
-        <v>55.63</v>
+        <v>54.67</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="DO6" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.12</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DQ6" t="n">
-        <v>1.88</v>
+        <v>1.56</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.25</v>
+        <v>7.22</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3365,22 +3365,22 @@
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>9.5</v>
+        <v>9.44</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.38</v>
+        <v>6.22</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.13</v>
+        <v>3.22</v>
       </c>
       <c r="EA6" t="n">
-        <v>21</v>
+        <v>18.56</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="7">
@@ -3390,13 +3390,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" t="n">
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3480,16 +3480,16 @@
         <v>2.25</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AI7" t="n">
-        <v>91.75</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
@@ -3498,34 +3498,34 @@
         <v>2</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AN7" t="n">
-        <v>51.25</v>
+        <v>50.8</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AP7" t="n">
         <v>1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.25</v>
+        <v>0.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3537,82 +3537,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>54.25</v>
+        <v>53.8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="BD7" t="n">
-        <v>17.75</v>
+        <v>14</v>
       </c>
       <c r="BE7" t="n">
         <v>0.98</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.88</v>
+        <v>7.11</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="BO7" t="n">
         <v>1</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.38</v>
+        <v>4</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.5</v>
+        <v>3.11</v>
       </c>
       <c r="BR7" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS7" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BU7" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BV7" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BY7" t="n">
         <v>2.29</v>
@@ -3624,52 +3624,52 @@
         <v>3.04</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.69</v>
+        <v>3.48</v>
       </c>
       <c r="CE7" t="n">
         <v>1.51</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="CO7" t="n">
         <v>1.47</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.49</v>
+        <v>4.5</v>
       </c>
       <c r="CR7" t="n">
         <v>1.53</v>
@@ -3690,67 +3690,67 @@
         <v>2.1</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.87</v>
+        <v>4.84</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DG7" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DH7" t="n">
-        <v>102.5</v>
+        <v>102.78</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DM7" t="n">
-        <v>57.12</v>
+        <v>56.22</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="DP7" t="n">
-        <v>7.5</v>
+        <v>6.56</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.62</v>
+        <v>0.44</v>
       </c>
       <c r="DR7" t="n">
-        <v>4.88</v>
+        <v>4.22</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3762,28 +3762,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>55.75</v>
+        <v>55.33</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.380000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="DY7" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.88</v>
+        <v>3.67</v>
       </c>
       <c r="EA7" t="n">
-        <v>14.88</v>
+        <v>13.11</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="8">
@@ -3793,31 +3793,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
         <v>5</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F8" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="H8" t="n">
-        <v>118.67</v>
+        <v>110</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="K8" t="n">
         <v>6</v>
@@ -3826,25 +3826,25 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>64.33</v>
+        <v>62.25</v>
       </c>
       <c r="N8" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="O8" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>4.67</v>
+        <v>3.25</v>
       </c>
       <c r="S8" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
@@ -3859,28 +3859,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>58</v>
+        <v>54.75</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.33</v>
+        <v>8.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.67</v>
+        <v>4</v>
       </c>
       <c r="AC8" t="n">
-        <v>15.67</v>
+        <v>11.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AF8" t="n">
         <v>0.2</v>
@@ -3964,46 +3964,46 @@
         <v>2.8</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.619999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.12</v>
+        <v>4.44</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.5</v>
+        <v>5.22</v>
       </c>
       <c r="BR8" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BS8" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BT8" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -4015,19 +4015,19 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.57</v>
+        <v>2.48</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="CA8" t="n">
         <v>3.04</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CC8" t="n">
         <v>2.82</v>
@@ -4039,40 +4039,40 @@
         <v>1.47</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="CM8" t="n">
         <v>2.08</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.23</v>
+        <v>4.33</v>
       </c>
       <c r="CR8" t="n">
         <v>1.47</v>
@@ -4087,10 +4087,10 @@
         <v>1.34</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CW8" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CX8" t="n">
         <v>1.68</v>
@@ -4105,55 +4105,55 @@
         <v>1.68</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.42</v>
+        <v>4.46</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="DH8" t="n">
-        <v>108.88</v>
+        <v>106.11</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM8" t="n">
-        <v>55.87</v>
+        <v>55.89</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.87</v>
+        <v>0.78</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="DP8" t="n">
-        <v>7.12</v>
+        <v>6.22</v>
       </c>
       <c r="DQ8" t="n">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="DR8" t="n">
-        <v>5.88</v>
+        <v>5.11</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4165,28 +4165,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.25</v>
+        <v>50.56</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.75</v>
+        <v>10.44</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.62</v>
+        <v>7.44</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.13</v>
+        <v>3</v>
       </c>
       <c r="EA8" t="n">
-        <v>13.88</v>
+        <v>12.22</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="9">
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4286,139 +4286,139 @@
         <v>1.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="AH9" t="n">
         <v>4</v>
       </c>
       <c r="AI9" t="n">
-        <v>100</v>
+        <v>100.2</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="AL9" t="n">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="AN9" t="n">
-        <v>46</v>
+        <v>51.4</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16</v>
+        <v>12.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>10.25</v>
+        <v>8</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>49.5</v>
+        <v>51.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>13.75</v>
+        <v>12.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>9.25</v>
+        <v>8.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>24.5</v>
+        <v>19.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.5</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BL9" t="n">
         <v>1</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.12</v>
+        <v>5.44</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="BR9" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS9" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BU9" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BV9" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW9" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BY9" t="n">
         <v>2.26</v>
@@ -4427,16 +4427,16 @@
         <v>2.13</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.08</v>
+        <v>3.69</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="CE9" t="n">
         <v>1.45</v>
@@ -4445,10 +4445,10 @@
         <v>3.2</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI9" t="n">
         <v>1.78</v>
@@ -4460,7 +4460,7 @@
         <v>1.64</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CM9" t="n">
         <v>2.11</v>
@@ -4478,13 +4478,13 @@
         <v>4.04</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="CU9" t="n">
         <v>1.34</v>
@@ -4511,85 +4511,85 @@
         <v>1.41</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.38</v>
+        <v>1.89</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="DH9" t="n">
-        <v>96.38</v>
+        <v>96.89</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.12</v>
+        <v>2.67</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="DM9" t="n">
-        <v>46.5</v>
+        <v>49.44</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DO9" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DP9" t="n">
-        <v>13.25</v>
+        <v>11.67</v>
       </c>
       <c r="DQ9" t="n">
-        <v>1.38</v>
+        <v>1.11</v>
       </c>
       <c r="DR9" t="n">
-        <v>10.38</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>54</v>
+        <v>54.67</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.75</v>
+        <v>13.22</v>
       </c>
       <c r="DY9" t="n">
-        <v>9</v>
+        <v>8.56</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="EA9" t="n">
-        <v>23.12</v>
+        <v>20.44</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="10">
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -4611,49 +4611,49 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="G10" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>108.5</v>
+        <v>104.6</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>7.25</v>
+        <v>6.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M10" t="n">
-        <v>72.75</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="O10" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>6.75</v>
+        <v>5.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.25</v>
+        <v>0.8</v>
       </c>
       <c r="R10" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="T10" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -4665,28 +4665,28 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>54</v>
+        <v>53.6</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>11.75</v>
+        <v>11.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="AC10" t="n">
-        <v>18</v>
+        <v>14.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AE10" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4770,70 +4770,70 @@
         <v>4.25</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.880000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.88</v>
+        <v>4.67</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5</v>
+        <v>4.56</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BT10" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BU10" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BV10" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.52</v>
+        <v>3.27</v>
       </c>
       <c r="BZ10" t="n">
-        <v>4.33</v>
+        <v>3.93</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.51</v>
+        <v>3.47</v>
       </c>
       <c r="CC10" t="n">
         <v>4.44</v>
@@ -4848,7 +4848,7 @@
         <v>3.26</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CH10" t="n">
         <v>1.28</v>
@@ -4857,46 +4857,46 @@
         <v>1.72</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CK10" t="n">
         <v>1.55</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.01</v>
+        <v>2.04</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.27</v>
+        <v>4.34</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CS10" t="n">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="CV10" t="n">
         <v>1.7</v>
       </c>
       <c r="CW10" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CX10" t="n">
         <v>1.62</v>
@@ -4914,85 +4914,85 @@
         <v>1.44</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="DD10" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="DH10" t="n">
-        <v>106.75</v>
+        <v>104.78</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.75</v>
+        <v>3.89</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.5</v>
+        <v>5.33</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DM10" t="n">
-        <v>59.38</v>
+        <v>60.22</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="DP10" t="n">
-        <v>11.38</v>
+        <v>10</v>
       </c>
       <c r="DQ10" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="DR10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.5</v>
+        <v>50.67</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.5</v>
+        <v>10.33</v>
       </c>
       <c r="DY10" t="n">
-        <v>6</v>
+        <v>5.78</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="EA10" t="n">
-        <v>21.25</v>
+        <v>18.78</v>
       </c>
       <c r="EB10" t="n">
         <v>1.41</v>
       </c>
       <c r="EC10" t="n">
-        <v>3.62</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="11">
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E11" t="n">
         <v>0.25</v>
@@ -5092,52 +5092,52 @@
         <v>1.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AI11" t="n">
-        <v>97.5</v>
+        <v>97.2</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AN11" t="n">
-        <v>51.5</v>
+        <v>57</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AP11" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>8.75</v>
+        <v>6.8</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.25</v>
+        <v>3.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.25</v>
+        <v>7.2</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5149,82 +5149,82 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>50.75</v>
+        <v>50.2</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.25</v>
+        <v>6.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.5</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BN11" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5</v>
+        <v>5.44</v>
       </c>
       <c r="BR11" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS11" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BT11" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BU11" t="n">
-        <v>12.5</v>
+        <v>22.22</v>
       </c>
       <c r="BV11" t="n">
-        <v>12.5</v>
+        <v>22.22</v>
       </c>
       <c r="BW11" t="n">
-        <v>12.5</v>
+        <v>22.22</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BY11" t="n">
         <v>2.03</v>
@@ -5236,61 +5236,61 @@
         <v>3.11</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="CD11" t="n">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK11" t="n">
         <v>1.65</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CO11" t="n">
         <v>1.4</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.22</v>
+        <v>4.18</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CU11" t="n">
         <v>1.33</v>
@@ -5299,103 +5299,103 @@
         <v>1.8</v>
       </c>
       <c r="CW11" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DB11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>93.56</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>52.33</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>51.89</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>21.78</v>
+      </c>
+      <c r="EB11" t="n">
         <v>1.43</v>
       </c>
-      <c r="DC11" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="DD11" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="DE11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DF11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="DG11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DH11" t="n">
-        <v>93.25</v>
-      </c>
-      <c r="DI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ11" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="DK11" t="n">
-        <v>5</v>
-      </c>
-      <c r="DL11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="DM11" t="n">
-        <v>49</v>
-      </c>
-      <c r="DN11" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="DO11" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="DP11" t="n">
-        <v>10.12</v>
-      </c>
-      <c r="DQ11" t="n">
-        <v>4</v>
-      </c>
-      <c r="DR11" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="DS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV11" t="n">
-        <v>52.38</v>
-      </c>
-      <c r="DW11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DX11" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="DY11" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="DZ11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="EA11" t="n">
-        <v>24.62</v>
-      </c>
-      <c r="EB11" t="n">
-        <v>1.42</v>
-      </c>
       <c r="EC11" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="12">
@@ -5528,13 +5528,13 @@
         <v>2.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11.4</v>
+        <v>13.8</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="AT12" t="n">
         <v>1.6</v>
@@ -5552,25 +5552,25 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>55</v>
+        <v>52.8</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.6</v>
+        <v>11</v>
       </c>
       <c r="BB12" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BD12" t="n">
-        <v>21.2</v>
+        <v>25.4</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="BF12" t="n">
         <v>1.8</v>
@@ -5759,13 +5759,13 @@
         <v>2.44</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.56</v>
+        <v>11.89</v>
       </c>
       <c r="DQ12" t="n">
-        <v>2.67</v>
+        <v>3.22</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.89</v>
+        <v>7.44</v>
       </c>
       <c r="DS12" t="n">
         <v>0.11</v>
@@ -5777,25 +5777,25 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>56.33</v>
+        <v>55.11</v>
       </c>
       <c r="DW12" t="n">
         <v>0.11</v>
       </c>
       <c r="DX12" t="n">
-        <v>12</v>
+        <v>12.22</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.33</v>
+        <v>7.67</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.67</v>
+        <v>4.56</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.33</v>
+        <v>23.67</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="EC12" t="n">
         <v>2</v>
@@ -5850,13 +5850,13 @@
         <v>2.6</v>
       </c>
       <c r="P13" t="n">
-        <v>7.6</v>
+        <v>10.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="R13" t="n">
-        <v>5</v>
+        <v>7.4</v>
       </c>
       <c r="S13" t="n">
         <v>1.2</v>
@@ -5874,25 +5874,25 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>57.4</v>
+        <v>58</v>
       </c>
       <c r="Y13" t="n">
         <v>0.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>12</v>
+        <v>13.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB13" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>17.2</v>
+        <v>21.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AE13" t="n">
         <v>1.8</v>
@@ -6036,13 +6036,13 @@
         <v>1.53</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CA13" t="n">
         <v>3.67</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="CC13" t="n">
         <v>1.88</v>
@@ -6114,7 +6114,7 @@
         <v>2.08</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DA13" t="n">
         <v>1.71</v>
@@ -6126,7 +6126,7 @@
         <v>2.21</v>
       </c>
       <c r="DD13" t="n">
-        <v>4</v>
+        <v>4.01</v>
       </c>
       <c r="DE13" t="n">
         <v>0.33</v>
@@ -6162,13 +6162,13 @@
         <v>2.67</v>
       </c>
       <c r="DP13" t="n">
-        <v>8.890000000000001</v>
+        <v>10.33</v>
       </c>
       <c r="DQ13" t="n">
-        <v>3.22</v>
+        <v>3.67</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.11</v>
+        <v>7.44</v>
       </c>
       <c r="DS13" t="n">
         <v>0.11</v>
@@ -6180,25 +6180,25 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>54.89</v>
+        <v>55.22</v>
       </c>
       <c r="DW13" t="n">
         <v>0.33</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.22</v>
+        <v>15.22</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.779999999999999</v>
+        <v>10</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.44</v>
+        <v>5.22</v>
       </c>
       <c r="EA13" t="n">
-        <v>20.11</v>
+        <v>22.33</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="EC13" t="n">
         <v>1.89</v>
@@ -6211,61 +6211,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
         <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F14" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="H14" t="n">
-        <v>109</v>
+        <v>105.8</v>
       </c>
       <c r="I14" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J14" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="K14" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M14" t="n">
-        <v>51.25</v>
+        <v>59.8</v>
       </c>
       <c r="N14" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="O14" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="P14" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="R14" t="n">
-        <v>6.25</v>
+        <v>4.8</v>
       </c>
       <c r="S14" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6277,28 +6277,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>50.75</v>
+        <v>51</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>16</v>
+        <v>12.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="AE14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6382,70 +6382,70 @@
         <v>2.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.380000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.25</v>
+        <v>2.67</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BO14" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.62</v>
+        <v>4.44</v>
       </c>
       <c r="BQ14" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BT14" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BU14" t="n">
-        <v>25</v>
+        <v>33.33</v>
       </c>
       <c r="BV14" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="BX14" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="CC14" t="n">
         <v>3.46</v>
@@ -6454,124 +6454,124 @@
         <v>3.83</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK14" t="n">
         <v>1.64</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CO14" t="n">
         <v>1.4</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.34</v>
+        <v>3.31</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="CU14" t="n">
         <v>1.32</v>
       </c>
       <c r="CV14" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CW14" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB14" t="n">
         <v>1.43</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="DD14" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF14" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="DG14" t="n">
-        <v>1.88</v>
+        <v>2.11</v>
       </c>
       <c r="DH14" t="n">
-        <v>99.38</v>
+        <v>98.67</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ14" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="DK14" t="n">
-        <v>4</v>
+        <v>4.22</v>
       </c>
       <c r="DL14" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DM14" t="n">
-        <v>50.25</v>
+        <v>55.11</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DP14" t="n">
-        <v>9</v>
+        <v>7.89</v>
       </c>
       <c r="DQ14" t="n">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6583,25 +6583,25 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>47.75</v>
+        <v>48.22</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DX14" t="n">
-        <v>6.88</v>
+        <v>7.44</v>
       </c>
       <c r="DY14" t="n">
-        <v>4.5</v>
+        <v>4.89</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="EA14" t="n">
-        <v>12.75</v>
+        <v>11.22</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.98</v>
+        <v>1.06</v>
       </c>
       <c r="EC14" t="n">
         <v>3</v>
@@ -6737,13 +6737,13 @@
         <v>2.75</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.25</v>
+        <v>15.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>1</v>
+        <v>2.25</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.25</v>
+        <v>8</v>
       </c>
       <c r="AT15" t="n">
         <v>0.75</v>
@@ -6761,25 +6761,25 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>40.5</v>
+        <v>39.75</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.75</v>
+        <v>11.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.5</v>
+        <v>7.25</v>
       </c>
       <c r="BC15" t="n">
         <v>4.25</v>
       </c>
       <c r="BD15" t="n">
-        <v>15.25</v>
+        <v>20</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
       <c r="BF15" t="n">
         <v>4.25</v>
@@ -6848,13 +6848,13 @@
         <v>3.17</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CC15" t="n">
         <v>4.49</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.86</v>
+        <v>4.62</v>
       </c>
       <c r="CE15" t="n">
         <v>1.34</v>
@@ -6920,7 +6920,7 @@
         <v>2.01</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DA15" t="n">
         <v>1.77</v>
@@ -6932,7 +6932,7 @@
         <v>2.48</v>
       </c>
       <c r="DD15" t="n">
-        <v>4.77</v>
+        <v>4.78</v>
       </c>
       <c r="DE15" t="n">
         <v>0.22</v>
@@ -6968,13 +6968,13 @@
         <v>3</v>
       </c>
       <c r="DP15" t="n">
-        <v>9.890000000000001</v>
+        <v>11.78</v>
       </c>
       <c r="DQ15" t="n">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="DR15" t="n">
-        <v>5.22</v>
+        <v>6.44</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6986,25 +6986,25 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.89</v>
+        <v>45.56</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.33</v>
+        <v>13.11</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.56</v>
+        <v>8.33</v>
       </c>
       <c r="DZ15" t="n">
         <v>4.78</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.67</v>
+        <v>21.78</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="EC15" t="n">
         <v>3.44</v>
@@ -7059,13 +7059,13 @@
         <v>2.5</v>
       </c>
       <c r="P16" t="n">
-        <v>6.25</v>
+        <v>10</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="S16" t="n">
         <v>1.5</v>
@@ -7083,25 +7083,25 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>55.5</v>
+        <v>58.25</v>
       </c>
       <c r="Y16" t="n">
         <v>0.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>9.75</v>
+        <v>11.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>12.75</v>
+        <v>21.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="AE16" t="n">
         <v>3.75</v>
@@ -7371,13 +7371,13 @@
         <v>2.89</v>
       </c>
       <c r="DP16" t="n">
-        <v>9.890000000000001</v>
+        <v>11.56</v>
       </c>
       <c r="DQ16" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="DR16" t="n">
-        <v>3.44</v>
+        <v>4.33</v>
       </c>
       <c r="DS16" t="n">
         <v>0.22</v>
@@ -7389,25 +7389,25 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>54</v>
+        <v>55.22</v>
       </c>
       <c r="DW16" t="n">
         <v>0.33</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.33</v>
+        <v>11</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.33</v>
+        <v>6.89</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="EA16" t="n">
-        <v>19</v>
+        <v>22.89</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="EC16" t="n">
         <v>3.78</v>
@@ -7462,13 +7462,13 @@
         <v>2.2</v>
       </c>
       <c r="P17" t="n">
-        <v>4.6</v>
+        <v>8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="R17" t="n">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="S17" t="n">
         <v>1.2</v>
@@ -7486,25 +7486,25 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>47.8</v>
+        <v>47.6</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>10.4</v>
+        <v>11.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.4</v>
+        <v>14.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AE17" t="n">
         <v>3.2</v>
@@ -7648,13 +7648,13 @@
         <v>2.54</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="CA17" t="n">
         <v>3.08</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CC17" t="n">
         <v>3.62</v>
@@ -7731,10 +7731,10 @@
         <v>1.48</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.99</v>
+        <v>5</v>
       </c>
       <c r="DE17" t="n">
         <v>0.11</v>
@@ -7770,13 +7770,13 @@
         <v>2</v>
       </c>
       <c r="DP17" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="DQ17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="DR17" t="n">
         <v>6.44</v>
-      </c>
-      <c r="DQ17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="DR17" t="n">
-        <v>5.22</v>
       </c>
       <c r="DS17" t="n">
         <v>0.22</v>
@@ -7788,25 +7788,25 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>48.89</v>
+        <v>48.78</v>
       </c>
       <c r="DW17" t="n">
         <v>0.22</v>
       </c>
       <c r="DX17" t="n">
-        <v>10.78</v>
+        <v>11.33</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.78</v>
+        <v>7.11</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4</v>
+        <v>4.22</v>
       </c>
       <c r="EA17" t="n">
-        <v>11.56</v>
+        <v>14.33</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="EC17" t="n">
         <v>3.22</v>

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
@@ -1901,13 +1901,13 @@
         <v>0.25</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.5</v>
+        <v>1</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.5</v>
+        <v>5.75</v>
       </c>
       <c r="AT3" t="n">
         <v>1</v>
@@ -1931,19 +1931,19 @@
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.5</v>
+        <v>6.75</v>
       </c>
       <c r="BB3" t="n">
-        <v>3</v>
+        <v>4.25</v>
       </c>
       <c r="BC3" t="n">
         <v>2.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>6.5</v>
+        <v>9.75</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.89</v>
+        <v>0.97</v>
       </c>
       <c r="BF3" t="n">
         <v>2.25</v>
@@ -2132,13 +2132,13 @@
         <v>0.67</v>
       </c>
       <c r="DP3" t="n">
-        <v>5.89</v>
+        <v>7</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.22</v>
+        <v>0.89</v>
       </c>
       <c r="DR3" t="n">
-        <v>5.11</v>
+        <v>6.56</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2156,19 +2156,19 @@
         <v>0.11</v>
       </c>
       <c r="DX3" t="n">
-        <v>6.67</v>
+        <v>7.22</v>
       </c>
       <c r="DY3" t="n">
-        <v>3.44</v>
+        <v>4</v>
       </c>
       <c r="DZ3" t="n">
         <v>3.22</v>
       </c>
       <c r="EA3" t="n">
-        <v>13.22</v>
+        <v>14.67</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.98</v>
       </c>
       <c r="EC3" t="n">
         <v>2.56</v>
@@ -3029,13 +3029,13 @@
         <v>1.5</v>
       </c>
       <c r="P6" t="n">
-        <v>8.25</v>
+        <v>12.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>6.75</v>
+        <v>8.75</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -3059,19 +3059,19 @@
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.5</v>
+        <v>10.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.75</v>
+        <v>28</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AE6" t="n">
         <v>3.25</v>
@@ -3341,13 +3341,13 @@
         <v>1.78</v>
       </c>
       <c r="DP6" t="n">
-        <v>9.779999999999999</v>
+        <v>11.67</v>
       </c>
       <c r="DQ6" t="n">
-        <v>1.56</v>
+        <v>1.89</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.22</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3365,19 +3365,19 @@
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>9.44</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.22</v>
+        <v>6.67</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.22</v>
+        <v>3.11</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.56</v>
+        <v>21.78</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="EC6" t="n">
         <v>3.22</v>
@@ -3513,13 +3513,13 @@
         <v>1</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8.199999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.8</v>
+        <v>1.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
         <v>1.8</v>
@@ -3546,16 +3546,16 @@
         <v>7</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="BF7" t="n">
         <v>1.4</v>
@@ -3744,13 +3744,13 @@
         <v>1.67</v>
       </c>
       <c r="DP7" t="n">
-        <v>6.56</v>
+        <v>7.67</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.44</v>
+        <v>1</v>
       </c>
       <c r="DR7" t="n">
-        <v>4.22</v>
+        <v>5.33</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3771,13 +3771,13 @@
         <v>8.33</v>
       </c>
       <c r="DY7" t="n">
-        <v>4.67</v>
+        <v>4.78</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.67</v>
+        <v>3.56</v>
       </c>
       <c r="EA7" t="n">
-        <v>13.11</v>
+        <v>17</v>
       </c>
       <c r="EB7" t="n">
         <v>1.19</v>
@@ -4641,13 +4641,13 @@
         <v>3.6</v>
       </c>
       <c r="P10" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="R10" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="S10" t="n">
         <v>1.2</v>
@@ -4671,19 +4671,19 @@
         <v>0.2</v>
       </c>
       <c r="Z10" t="n">
-        <v>11.2</v>
+        <v>12</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AB10" t="n">
         <v>6</v>
       </c>
       <c r="AC10" t="n">
-        <v>14.2</v>
+        <v>18.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="AE10" t="n">
         <v>3.2</v>
@@ -4953,13 +4953,13 @@
         <v>2.67</v>
       </c>
       <c r="DP10" t="n">
-        <v>10</v>
+        <v>12.22</v>
       </c>
       <c r="DQ10" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="DR10" t="n">
-        <v>7</v>
+        <v>7.89</v>
       </c>
       <c r="DS10" t="n">
         <v>0.11</v>
@@ -4977,19 +4977,19 @@
         <v>0.22</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.33</v>
+        <v>10.78</v>
       </c>
       <c r="DY10" t="n">
-        <v>5.78</v>
+        <v>6.22</v>
       </c>
       <c r="DZ10" t="n">
         <v>4.56</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.78</v>
+        <v>21.33</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="EC10" t="n">
         <v>3.67</v>
@@ -5874,7 +5874,7 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>58</v>
+        <v>58.2</v>
       </c>
       <c r="Y13" t="n">
         <v>0.4</v>
@@ -6180,7 +6180,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>55.22</v>
+        <v>55.33</v>
       </c>
       <c r="DW13" t="n">
         <v>0.33</v>
@@ -6761,7 +6761,7 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>39.75</v>
+        <v>39.5</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
@@ -6986,7 +6986,7 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.56</v>
+        <v>45.44</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8</v>
+        <v>3.17</v>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="H2" t="n">
-        <v>97.8</v>
+        <v>97.17</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4</v>
+        <v>4.17</v>
       </c>
       <c r="K2" t="n">
-        <v>5.2</v>
+        <v>5.33</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M2" t="n">
-        <v>47.6</v>
+        <v>46.67</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="P2" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="R2" t="n">
-        <v>8.800000000000001</v>
+        <v>7.17</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>56.4</v>
+        <v>54.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>11</v>
+        <v>10.17</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.2</v>
+        <v>5.67</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>16.4</v>
+        <v>13.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>4.2</v>
+        <v>3.83</v>
       </c>
       <c r="AF2" t="n">
         <v>0.25</v>
@@ -1550,49 +1550,49 @@
         <v>1.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.11</v>
+        <v>10.1</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="BN2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.44</v>
+        <v>5.4</v>
       </c>
       <c r="BR2" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS2" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BT2" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BU2" t="n">
-        <v>22.22</v>
+        <v>30</v>
       </c>
       <c r="BV2" t="n">
         <v>0</v>
@@ -1601,16 +1601,16 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.18</v>
+        <v>3.01</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.24</v>
+        <v>3.06</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CB2" t="n">
         <v>3.14</v>
@@ -1628,22 +1628,22 @@
         <v>3.39</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CH2" t="n">
         <v>1.25</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CK2" t="n">
         <v>1.64</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="CM2" t="n">
         <v>2.15</v>
@@ -1652,20 +1652,20 @@
         <v>1.7</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.64</v>
+        <v>4.7</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CS2" t="inlineStr"/>
       <c r="CT2" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CU2" t="inlineStr"/>
       <c r="CV2" t="n">
@@ -1678,10 +1678,10 @@
         <v>1.64</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DA2" t="n">
         <v>1.74</v>
@@ -1690,85 +1690,85 @@
         <v>1.49</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.95</v>
+        <v>4.93</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="DH2" t="n">
-        <v>96.33</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.89</v>
+        <v>5</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM2" t="n">
-        <v>48.89</v>
+        <v>48.2</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DP2" t="n">
-        <v>8.33</v>
+        <v>7.4</v>
       </c>
       <c r="DQ2" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.33</v>
+        <v>4.7</v>
       </c>
       <c r="DS2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>53.56</v>
+        <v>52.7</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="DX2" t="n">
-        <v>10.56</v>
+        <v>10.1</v>
       </c>
       <c r="DY2" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.56</v>
+        <v>4.4</v>
       </c>
       <c r="EA2" t="n">
-        <v>10.44</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="EC2" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="3">
@@ -1778,61 +1778,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
         <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="H3" t="n">
-        <v>82.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>31.4</v>
+        <v>34.17</v>
       </c>
       <c r="N3" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>9</v>
+        <v>7.33</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="R3" t="n">
-        <v>7.2</v>
+        <v>5.83</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2</v>
+        <v>0.83</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1844,28 +1844,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>48.6</v>
+        <v>48.33</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z3" t="n">
-        <v>7.6</v>
+        <v>8.83</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.8</v>
+        <v>4.83</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.6</v>
+        <v>15.33</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.98</v>
+        <v>1.15</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1949,70 +1949,70 @@
         <v>2.25</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="BH3" t="n">
-        <v>7.78</v>
+        <v>8</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.67</v>
+        <v>4</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="BR3" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS3" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BT3" t="n">
-        <v>22.22</v>
+        <v>30</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BV3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.53</v>
+        <v>3.34</v>
       </c>
       <c r="BZ3" t="n">
-        <v>4.43</v>
+        <v>4.14</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CC3" t="n">
         <v>2.7</v>
@@ -2021,43 +2021,43 @@
         <v>2.9</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CN3" t="n">
         <v>1.48</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP3" t="n">
         <v>2.37</v>
       </c>
       <c r="CQ3" t="n">
-        <v>3.99</v>
+        <v>4.01</v>
       </c>
       <c r="CR3" t="n">
         <v>1.51</v>
@@ -2066,7 +2066,7 @@
         <v>3.24</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CU3" t="n">
         <v>1.32</v>
@@ -2078,16 +2078,16 @@
         <v>2.09</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="DB3" t="n">
         <v>1.48</v>
@@ -2096,49 +2096,49 @@
         <v>2.54</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.94</v>
+        <v>4.95</v>
       </c>
       <c r="DE3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="DF3" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="DH3" t="n">
-        <v>94.44</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="DK3" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>39.11</v>
+        <v>40</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DP3" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.89</v>
+        <v>0.7</v>
       </c>
       <c r="DR3" t="n">
-        <v>6.56</v>
+        <v>5.8</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2150,28 +2150,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>48.22</v>
+        <v>48.1</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX3" t="n">
-        <v>7.22</v>
+        <v>8</v>
       </c>
       <c r="DY3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.22</v>
+        <v>3.9</v>
       </c>
       <c r="EA3" t="n">
-        <v>14.67</v>
+        <v>13.1</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.98</v>
+        <v>1.08</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="4">
@@ -2181,13 +2181,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2271,139 +2271,139 @@
         <v>2.75</v>
       </c>
       <c r="AF4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>87.17</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>48.5</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>38</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ4" t="n">
         <v>0.4</v>
       </c>
-      <c r="AG4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>88</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="AO4" t="n">
+      <c r="BK4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BL4" t="n">
         <v>0.6</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="BM4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BN4" t="n">
         <v>1.4</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>37</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BH4" t="n">
+      <c r="BO4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>90</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>60</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>60</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>20</v>
+      </c>
+      <c r="BV4" t="n">
         <v>10</v>
       </c>
-      <c r="BI4" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>88.89</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>22.22</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>11.11</v>
-      </c>
       <c r="BW4" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX4" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
         <v>3.49</v>
@@ -2412,67 +2412,67 @@
         <v>3.92</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.27</v>
+        <v>3.36</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.24</v>
+        <v>3.38</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.76</v>
+        <v>4.29</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.04</v>
+        <v>4.66</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI4" t="n">
         <v>1.7</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL4" t="n">
         <v>2.2</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.38</v>
+        <v>4.24</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.22</v>
+        <v>3.15</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="CV4" t="n">
         <v>1.72</v>
@@ -2481,100 +2481,100 @@
         <v>2.14</v>
       </c>
       <c r="CX4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DA4" t="n">
         <v>1.69</v>
       </c>
-      <c r="CY4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="CZ4" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="DA4" t="n">
-        <v>1.68</v>
-      </c>
       <c r="DB4" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.6</v>
+        <v>4.46</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DH4" t="n">
-        <v>86.44</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.44</v>
+        <v>4</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DM4" t="n">
-        <v>50.22</v>
+        <v>49.4</v>
       </c>
       <c r="DN4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="DP4" t="n">
-        <v>7.33</v>
+        <v>6.5</v>
       </c>
       <c r="DQ4" t="n">
-        <v>1.11</v>
+        <v>0.9</v>
       </c>
       <c r="DR4" t="n">
-        <v>7.67</v>
+        <v>6.8</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>38</v>
+        <v>38.5</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX4" t="n">
-        <v>10.33</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="DY4" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="EA4" t="n">
-        <v>15.22</v>
+        <v>13.6</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="5">
@@ -2987,13 +2987,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3080,49 +3080,49 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AI6" t="n">
-        <v>104.8</v>
+        <v>107</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.2</v>
+        <v>3.33</v>
       </c>
       <c r="AL6" t="n">
-        <v>5</v>
+        <v>4.83</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.6</v>
+        <v>6.17</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3134,73 +3134,73 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>47</v>
+        <v>48.33</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH6" t="n">
         <v>9.4</v>
       </c>
-      <c r="BB6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>9.33</v>
-      </c>
       <c r="BI6" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="BL6" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BT6" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BU6" t="n">
-        <v>22.22</v>
+        <v>30</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3209,7 +3209,7 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BY6" t="n">
         <v>2.89</v>
@@ -3218,31 +3218,31 @@
         <v>3.23</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.88</v>
+        <v>3.86</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.42</v>
+        <v>4.3</v>
       </c>
       <c r="CE6" t="n">
         <v>1.48</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CG6" t="n">
         <v>2.43</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.97</v>
@@ -3251,7 +3251,7 @@
         <v>1.65</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CM6" t="n">
         <v>2.15</v>
@@ -3260,13 +3260,13 @@
         <v>1.7</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.42</v>
+        <v>4.5</v>
       </c>
       <c r="CR6" t="n">
         <v>1.49</v>
@@ -3275,7 +3275,7 @@
         <v>3.19</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="CU6" t="n">
         <v>1.34</v>
@@ -3296,58 +3296,58 @@
         <v>2.16</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DB6" t="n">
         <v>1.43</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.48</v>
+        <v>4.51</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="DH6" t="n">
-        <v>101.67</v>
+        <v>103.3</v>
       </c>
       <c r="DI6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="DK6" t="n">
         <v>4</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DM6" t="n">
-        <v>54.67</v>
+        <v>55</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.67</v>
+        <v>10.4</v>
       </c>
       <c r="DQ6" t="n">
-        <v>1.89</v>
+        <v>1.6</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.109999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3359,28 +3359,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>48</v>
+        <v>48.7</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>9.779999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.67</v>
+        <v>6.2</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.11</v>
+        <v>3.4</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.78</v>
+        <v>19.5</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="7">
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
         <v>5</v>
@@ -3402,49 +3402,49 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="n">
-        <v>113.25</v>
+        <v>109.4</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="L7" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="M7" t="n">
-        <v>63</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="O7" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="P7" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="R7" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="S7" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3456,28 +3456,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>57.25</v>
+        <v>56</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.25</v>
+        <v>5.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AF7" t="n">
         <v>0.2</v>
@@ -3561,70 +3561,70 @@
         <v>1.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.11</v>
+        <v>7.5</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="BO7" t="n">
         <v>1</v>
       </c>
       <c r="BP7" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.11</v>
+        <v>3.6</v>
       </c>
       <c r="BR7" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS7" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT7" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BU7" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BV7" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CC7" t="n">
         <v>3.2</v>
@@ -3639,7 +3639,7 @@
         <v>3.27</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CH7" t="n">
         <v>1.27</v>
@@ -3648,28 +3648,28 @@
         <v>1.69</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CK7" t="n">
         <v>1.62</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="CM7" t="n">
         <v>2.16</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CO7" t="n">
         <v>1.47</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="CR7" t="n">
         <v>1.53</v>
@@ -3678,7 +3678,7 @@
         <v>3.36</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CU7" t="n">
         <v>1.31</v>
@@ -3690,67 +3690,67 @@
         <v>2.1</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DB7" t="n">
         <v>1.47</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.84</v>
+        <v>4.81</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="DH7" t="n">
-        <v>102.78</v>
+        <v>101.9</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.44</v>
+        <v>4</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DM7" t="n">
-        <v>56.22</v>
+        <v>58.7</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="DP7" t="n">
-        <v>7.67</v>
+        <v>6.8</v>
       </c>
       <c r="DQ7" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="DR7" t="n">
-        <v>5.33</v>
+        <v>4.7</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
@@ -3762,28 +3762,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>55.33</v>
+        <v>54.9</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.33</v>
+        <v>8.4</v>
       </c>
       <c r="DY7" t="n">
-        <v>4.78</v>
+        <v>4.6</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="EA7" t="n">
-        <v>17</v>
+        <v>15.2</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4692,136 +4692,136 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AI10" t="n">
-        <v>105</v>
+        <v>103.2</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AN10" t="n">
-        <v>46</v>
+        <v>48.2</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>16</v>
+        <v>12.6</v>
       </c>
       <c r="AR10" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>12.25</v>
+        <v>9.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AU10" t="n">
         <v>1</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="BD10" t="n">
-        <v>24.5</v>
+        <v>19.4</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.25</v>
+        <v>4.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.220000000000001</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.67</v>
+        <v>4.8</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.56</v>
+        <v>4.5</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BT10" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BU10" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BV10" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BY10" t="n">
         <v>3.27</v>
@@ -4836,19 +4836,19 @@
         <v>3.47</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.44</v>
+        <v>4.37</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.94</v>
+        <v>4.82</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.26</v>
+        <v>3.22</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="CH10" t="n">
         <v>1.28</v>
@@ -4857,28 +4857,28 @@
         <v>1.72</v>
       </c>
       <c r="CJ10" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK10" t="n">
         <v>1.55</v>
       </c>
       <c r="CL10" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.34</v>
+        <v>4.27</v>
       </c>
       <c r="CR10" t="n">
         <v>1.49</v>
@@ -4899,100 +4899,100 @@
         <v>2.15</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CY10" t="n">
         <v>2</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DB10" t="n">
         <v>1.44</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="DD10" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="DG10" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="DH10" t="n">
-        <v>104.78</v>
+        <v>103.9</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DJ10" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.33</v>
+        <v>5.4</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="DM10" t="n">
-        <v>60.22</v>
+        <v>59.9</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="DP10" t="n">
-        <v>12.22</v>
+        <v>10.9</v>
       </c>
       <c r="DQ10" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.89</v>
+        <v>7</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>50.67</v>
+        <v>51.8</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.78</v>
+        <v>10.4</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.22</v>
+        <v>6.1</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.56</v>
+        <v>4.3</v>
       </c>
       <c r="EA10" t="n">
-        <v>21.33</v>
+        <v>19.1</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="EC10" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="11">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
         <v>5</v>
@@ -5417,49 +5417,49 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="H12" t="n">
-        <v>117.75</v>
+        <v>122.2</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J12" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="K12" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="M12" t="n">
-        <v>56</v>
+        <v>65.8</v>
       </c>
       <c r="N12" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="P12" t="n">
-        <v>9.5</v>
+        <v>7.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5471,28 +5471,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>58</v>
+        <v>57.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.75</v>
+        <v>13</v>
       </c>
       <c r="AA12" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>21.5</v>
+        <v>17</v>
       </c>
       <c r="AD12" t="n">
         <v>1.61</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AF12" t="n">
         <v>0.2</v>
@@ -5576,70 +5576,70 @@
         <v>1.8</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.78</v>
+        <v>4.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.22</v>
+        <v>4</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>77.78</v>
+        <v>70</v>
       </c>
       <c r="BT12" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BU12" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV12" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.62</v>
+        <v>3.68</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="CC12" t="n">
         <v>1.76</v>
@@ -5648,55 +5648,55 @@
         <v>1.76</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="CF12" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="CG12" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.96</v>
+        <v>1.03</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="CN12" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.74</v>
+        <v>0.79</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.2</v>
+        <v>3.11</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.72</v>
+        <v>2.81</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="CV12" t="n">
         <v>1.75</v>
@@ -5708,94 +5708,94 @@
         <v>1.56</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.78</v>
+        <v>3.68</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="DH12" t="n">
-        <v>107.22</v>
+        <v>110.5</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.22</v>
+        <v>5.1</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="DM12" t="n">
-        <v>50.67</v>
+        <v>56.1</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="DP12" t="n">
-        <v>11.89</v>
+        <v>10.6</v>
       </c>
       <c r="DQ12" t="n">
-        <v>3.22</v>
+        <v>2.8</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.44</v>
+        <v>6.6</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>55.11</v>
+        <v>55.3</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.22</v>
+        <v>12</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.67</v>
+        <v>7.6</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.56</v>
+        <v>4.4</v>
       </c>
       <c r="EA12" t="n">
-        <v>23.67</v>
+        <v>21.2</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="EC12" t="n">
         <v>2</v>
@@ -5808,13 +5808,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
         <v>0.4</v>
@@ -5898,130 +5898,130 @@
         <v>1.8</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AH13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>16.6</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BG13" t="n">
         <v>2.5</v>
       </c>
-      <c r="AI13" t="n">
-        <v>99.75</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO13" t="n">
+      <c r="BH13" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ13" t="n">
         <v>0.5</v>
       </c>
-      <c r="AP13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AT13" t="n">
+      <c r="BK13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BM13" t="n">
         <v>0.5</v>
       </c>
-      <c r="AU13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>51.75</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>17</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>23.75</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>8.890000000000001</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>0.5600000000000001</v>
-      </c>
       <c r="BN13" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.78</v>
+        <v>4.4</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT13" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV13" t="n">
         <v>0</v>
@@ -6030,7 +6030,7 @@
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>66.67</v>
+        <v>60</v>
       </c>
       <c r="BY13" t="n">
         <v>1.53</v>
@@ -6039,64 +6039,64 @@
         <v>1.57</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="CC13" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.03</v>
+        <v>1.92</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CH13" t="n">
         <v>1.33</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CJ13" t="n">
         <v>2.14</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CO13" t="n">
         <v>1.37</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.89</v>
+        <v>3.86</v>
       </c>
       <c r="CR13" t="n">
         <v>1.45</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CU13" t="n">
         <v>1.35</v>
@@ -6108,16 +6108,16 @@
         <v>2.27</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DB13" t="n">
         <v>1.39</v>
@@ -6129,79 +6129,79 @@
         <v>4.01</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="DH13" t="n">
-        <v>110.78</v>
+        <v>112.4</v>
       </c>
       <c r="DI13" t="n">
         <v>0</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.67</v>
+        <v>5.4</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM13" t="n">
-        <v>38.11</v>
+        <v>43.1</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.33</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DQ13" t="n">
-        <v>3.67</v>
+        <v>3.2</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.44</v>
+        <v>6.6</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>55.33</v>
+        <v>55.8</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DX13" t="n">
-        <v>15.22</v>
+        <v>15.2</v>
       </c>
       <c r="DY13" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.22</v>
+        <v>5.5</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.33</v>
+        <v>20</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="EC13" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6211,61 +6211,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14" t="n">
         <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6</v>
+        <v>2.17</v>
       </c>
       <c r="G14" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="H14" t="n">
-        <v>105.8</v>
+        <v>103.5</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J14" t="n">
-        <v>4.4</v>
+        <v>3.83</v>
       </c>
       <c r="K14" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="M14" t="n">
-        <v>59.8</v>
+        <v>57.33</v>
       </c>
       <c r="N14" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="O14" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>9</v>
+        <v>7.33</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.6</v>
+        <v>1.17</v>
       </c>
       <c r="R14" t="n">
-        <v>4.8</v>
+        <v>3.83</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6277,28 +6277,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>51</v>
+        <v>49.17</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>8.4</v>
+        <v>7.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.6</v>
+        <v>4.83</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>12.6</v>
+        <v>10.33</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.17</v>
+        <v>1.06</v>
       </c>
       <c r="AE14" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6382,70 +6382,70 @@
         <v>2.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.779999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.44</v>
+        <v>4.1</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BT14" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BU14" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BV14" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW14" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX14" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.48</v>
+        <v>3.9</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.65</v>
+        <v>4.28</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.28</v>
+        <v>3.36</v>
       </c>
       <c r="CC14" t="n">
         <v>3.46</v>
@@ -6457,28 +6457,28 @@
         <v>1.46</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.11</v>
+        <v>3.09</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CH14" t="n">
         <v>1.29</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="CK14" t="n">
         <v>1.64</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CN14" t="n">
         <v>1.68</v>
@@ -6487,19 +6487,19 @@
         <v>1.4</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.14</v>
+        <v>4.08</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CU14" t="n">
         <v>1.32</v>
@@ -6511,67 +6511,67 @@
         <v>2.05</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DA14" t="n">
         <v>1.75</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="DC14" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="DD14" t="n">
-        <v>4.44</v>
+        <v>4.4</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF14" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DH14" t="n">
-        <v>98.67</v>
+        <v>98</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ14" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.22</v>
+        <v>3.9</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DM14" t="n">
-        <v>55.11</v>
+        <v>54.1</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="DP14" t="n">
-        <v>7.89</v>
+        <v>7</v>
       </c>
       <c r="DQ14" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="DR14" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6583,28 +6583,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48.22</v>
+        <v>47.4</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DX14" t="n">
-        <v>7.44</v>
+        <v>6.9</v>
       </c>
       <c r="DY14" t="n">
-        <v>4.89</v>
+        <v>4.5</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="EA14" t="n">
-        <v>11.22</v>
+        <v>10</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="EC14" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="15">
@@ -6614,10 +6614,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
         <v>4</v>
@@ -6626,49 +6626,49 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G15" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="H15" t="n">
+        <v>90.67</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="J15" t="n">
         <v>3</v>
       </c>
-      <c r="H15" t="n">
-        <v>92.2</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.8</v>
-      </c>
       <c r="K15" t="n">
-        <v>6.2</v>
+        <v>5.83</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0.83</v>
       </c>
       <c r="M15" t="n">
-        <v>61.6</v>
+        <v>60</v>
       </c>
       <c r="N15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="P15" t="n">
-        <v>8.800000000000001</v>
+        <v>7.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.8</v>
+        <v>2.17</v>
       </c>
       <c r="R15" t="n">
-        <v>5.2</v>
+        <v>4.17</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -6680,28 +6680,28 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>50.2</v>
+        <v>48.17</v>
       </c>
       <c r="Y15" t="n">
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>14.4</v>
+        <v>13.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>9.199999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.2</v>
+        <v>5.17</v>
       </c>
       <c r="AC15" t="n">
-        <v>23.2</v>
+        <v>19.17</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AF15" t="n">
         <v>0.5</v>
@@ -6785,70 +6785,70 @@
         <v>4.25</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="BH15" t="n">
         <v>10</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.44</v>
+        <v>4.6</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.56</v>
+        <v>5.4</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BT15" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BV15" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW15" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX15" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="CC15" t="n">
         <v>4.49</v>
@@ -6857,43 +6857,43 @@
         <v>4.62</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF15" t="n">
         <v>2.91</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CM15" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CQ15" t="n">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="CR15" t="n">
         <v>1.5</v>
@@ -6920,61 +6920,61 @@
         <v>2.01</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="DD15" t="n">
-        <v>4.78</v>
+        <v>4.7</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DG15" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="DH15" t="n">
-        <v>93.11</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
       <c r="DK15" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="DM15" t="n">
-        <v>59.11</v>
+        <v>58.4</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="DO15" t="n">
         <v>3</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.78</v>
+        <v>10.5</v>
       </c>
       <c r="DQ15" t="n">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.44</v>
+        <v>5.7</v>
       </c>
       <c r="DS15" t="n">
         <v>0</v>
@@ -6986,28 +6986,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>45.44</v>
+        <v>44.7</v>
       </c>
       <c r="DW15" t="n">
         <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>13.11</v>
+        <v>12.6</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.33</v>
+        <v>7.8</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.78</v>
+        <v>19.5</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.44</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="16">
@@ -7017,13 +7017,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
         <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
         <v>0.5</v>
@@ -7110,136 +7110,136 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.6</v>
+        <v>2.33</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AI16" t="n">
-        <v>91.59999999999999</v>
+        <v>92.67</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN16" t="n">
-        <v>43.6</v>
+        <v>48.67</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12.8</v>
+        <v>10.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.2</v>
+        <v>3.33</v>
       </c>
       <c r="AT16" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>52.17</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>19.83</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ16" t="n">
         <v>0.8</v>
       </c>
-      <c r="AU16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="AZ16" t="n">
+      <c r="BK16" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BL16" t="n">
         <v>0.4</v>
       </c>
-      <c r="BA16" t="n">
-        <v>10.8</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0.44</v>
-      </c>
       <c r="BM16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="BN16" t="n">
         <v>1</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.67</v>
+        <v>3.6</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="BR16" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS16" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BT16" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BU16" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BV16" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BY16" t="n">
         <v>2.2</v>
@@ -7248,64 +7248,64 @@
         <v>2.41</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.34</v>
+        <v>3.31</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.71</v>
+        <v>2.76</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="CL16" t="n">
         <v>1.93</v>
       </c>
       <c r="CM16" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.39</v>
+        <v>3.48</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="CS16" t="n">
         <v>3.06</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="CU16" t="n">
         <v>1.37</v>
@@ -7317,100 +7317,100 @@
         <v>1.94</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DB16" t="n">
         <v>1.37</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.88</v>
+        <v>3.96</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="DH16" t="n">
-        <v>104.78</v>
+        <v>104.1</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.67</v>
+        <v>4.4</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DM16" t="n">
-        <v>52.56</v>
+        <v>54.7</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.89</v>
+        <v>2.6</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.56</v>
+        <v>10.3</v>
       </c>
       <c r="DQ16" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="DR16" t="n">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>55.22</v>
+        <v>54.6</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DX16" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="DY16" t="n">
-        <v>6.89</v>
+        <v>7.5</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.11</v>
+        <v>3.9</v>
       </c>
       <c r="EA16" t="n">
-        <v>22.89</v>
+        <v>20.5</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="EC16" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="17">
@@ -7420,13 +7420,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7510,139 +7510,139 @@
         <v>3.2</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AI17" t="n">
-        <v>101.25</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AN17" t="n">
-        <v>53.25</v>
+        <v>56.6</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.75</v>
+        <v>2.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>8.75</v>
+        <v>6.8</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AU17" t="n">
         <v>1</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>50.25</v>
+        <v>50.8</v>
       </c>
       <c r="AZ17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>11.2</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BM17" t="n">
         <v>0.5</v>
       </c>
-      <c r="BA17" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>3</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>14.25</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>10.44</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>0.44</v>
-      </c>
       <c r="BN17" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.78</v>
+        <v>5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.67</v>
+        <v>5.4</v>
       </c>
       <c r="BR17" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS17" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT17" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BU17" t="n">
-        <v>11.11</v>
+        <v>20</v>
       </c>
       <c r="BV17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BY17" t="n">
         <v>2.54</v>
@@ -7657,46 +7657,46 @@
         <v>3.08</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.62</v>
+        <v>3.46</v>
       </c>
       <c r="CD17" t="n">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.03</v>
+        <v>3.08</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.09</v>
+        <v>2.14</v>
       </c>
       <c r="CM17" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CN17" t="n">
         <v>1.48</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CQ17" t="n">
         <v>4.19</v>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="CS17" t="inlineStr"/>
       <c r="CT17" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CU17" t="inlineStr"/>
       <c r="CV17" t="n">
@@ -7716,100 +7716,100 @@
         <v>2.05</v>
       </c>
       <c r="CX17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="CY17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="CZ17" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="DA17" t="n">
         <v>1.67</v>
-      </c>
-      <c r="CY17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CZ17" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="DA17" t="n">
-        <v>1.69</v>
       </c>
       <c r="DB17" t="n">
         <v>1.48</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="DD17" t="n">
-        <v>5</v>
+        <v>4.99</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.11</v>
+        <v>2.8</v>
       </c>
       <c r="DH17" t="n">
-        <v>98.44</v>
+        <v>96.3</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.67</v>
+        <v>3.9</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.11</v>
+        <v>5.2</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="DM17" t="n">
-        <v>60.78</v>
+        <v>61.7</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="DO17" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="DP17" t="n">
-        <v>8.33</v>
+        <v>7.4</v>
       </c>
       <c r="DQ17" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.44</v>
+        <v>5.7</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>48.78</v>
+        <v>49.2</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.33</v>
+        <v>11.7</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.11</v>
+        <v>7.4</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.22</v>
+        <v>4.3</v>
       </c>
       <c r="EA17" t="n">
-        <v>14.33</v>
+        <v>12.8</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="EC17" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -2304,13 +2304,13 @@
         <v>1.17</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7.5</v>
+        <v>9.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.33</v>
+        <v>8.83</v>
       </c>
       <c r="AT4" t="n">
         <v>0.83</v>
@@ -2328,25 +2328,25 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>38</v>
+        <v>36.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.33</v>
+        <v>10.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.5</v>
+        <v>6.67</v>
       </c>
       <c r="BC4" t="n">
         <v>3.83</v>
       </c>
       <c r="BD4" t="n">
-        <v>14.83</v>
+        <v>17.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BF4" t="n">
         <v>2</v>
@@ -2535,13 +2535,13 @@
         <v>2.1</v>
       </c>
       <c r="DP4" t="n">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="DR4" t="n">
-        <v>6.8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DS4" t="n">
         <v>0.2</v>
@@ -2553,25 +2553,25 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>38.5</v>
+        <v>37.6</v>
       </c>
       <c r="DW4" t="n">
         <v>0.1</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DY4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="DZ4" t="n">
         <v>4.1</v>
       </c>
       <c r="EA4" t="n">
-        <v>13.6</v>
+        <v>15.2</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="EC4" t="n">
         <v>2.3</v>
@@ -2584,61 +2584,61 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="H5" t="n">
-        <v>90.8</v>
+        <v>90.67</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="M5" t="n">
-        <v>52.2</v>
+        <v>52.17</v>
       </c>
       <c r="N5" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>12.8</v>
+        <v>10.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="R5" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8</v>
+        <v>0.67</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2650,28 +2650,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>39.8</v>
+        <v>40.33</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.8</v>
+        <v>9.83</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.4</v>
+        <v>5.67</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.4</v>
+        <v>4.17</v>
       </c>
       <c r="AC5" t="n">
-        <v>23.4</v>
+        <v>19.33</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.37</v>
+        <v>1.29</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2755,49 +2755,49 @@
         <v>4.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.890000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="BI5" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.33</v>
+        <v>5.4</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BT5" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BU5" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BV5" t="n">
         <v>0</v>
@@ -2806,16 +2806,16 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>33.33</v>
+        <v>30</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CB5" t="n">
         <v>3.28</v>
@@ -2830,25 +2830,25 @@
         <v>1.54</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CM5" t="n">
         <v>2.02</v>
@@ -2860,10 +2860,10 @@
         <v>1.51</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="CQ5" t="n">
-        <v>4.88</v>
+        <v>4.86</v>
       </c>
       <c r="CR5" t="n">
         <v>1.55</v>
@@ -2872,7 +2872,7 @@
         <v>3.11</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CU5" t="n">
         <v>1.36</v>
@@ -2887,7 +2887,7 @@
         <v>1.77</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.01</v>
@@ -2905,76 +2905,76 @@
         <v>5.22</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="DH5" t="n">
-        <v>92.56</v>
+        <v>92.3</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ5" t="n">
-        <v>4.56</v>
+        <v>4.5</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="DM5" t="n">
-        <v>50.44</v>
+        <v>50.6</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="DO5" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DP5" t="n">
-        <v>13.78</v>
+        <v>12.3</v>
       </c>
       <c r="DQ5" t="n">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.22</v>
+        <v>6.4</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.67</v>
+        <v>11</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.33</v>
+        <v>7.7</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="EA5" t="n">
-        <v>23.67</v>
+        <v>21.2</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="EC5" t="n">
         <v>4</v>
@@ -3793,13 +3793,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8" t="n">
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="n">
         <v>0.25</v>
@@ -3883,16 +3883,16 @@
         <v>2.25</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AI8" t="n">
-        <v>103</v>
+        <v>104.67</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
@@ -3901,34 +3901,34 @@
         <v>3</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.6</v>
+        <v>4.17</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>50.8</v>
+        <v>51.67</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AP8" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.4</v>
+        <v>6.83</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.6</v>
+        <v>0.33</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.6</v>
+        <v>5.33</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3940,70 +3940,70 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>47.2</v>
+        <v>48.83</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.2</v>
+        <v>2.33</v>
       </c>
       <c r="BD8" t="n">
-        <v>12.8</v>
+        <v>10.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.67</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BO8" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.44</v>
+        <v>4.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.22</v>
+        <v>5.3</v>
       </c>
       <c r="BR8" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BS8" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BT8" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -4015,7 +4015,7 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BY8" t="n">
         <v>2.48</v>
@@ -4024,40 +4024,40 @@
         <v>2.54</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.04</v>
+        <v>2.92</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CH8" t="n">
         <v>1.28</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="CM8" t="n">
         <v>2.08</v>
@@ -4066,22 +4066,22 @@
         <v>1.65</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.33</v>
+        <v>4.36</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="CS8" t="n">
         <v>3.28</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="CU8" t="n">
         <v>1.34</v>
@@ -4093,67 +4093,67 @@
         <v>2.02</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DA8" t="n">
         <v>1.68</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.46</v>
+        <v>4.54</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="DG8" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DH8" t="n">
-        <v>106.11</v>
+        <v>106.8</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.67</v>
+        <v>4.9</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="DM8" t="n">
-        <v>55.89</v>
+        <v>55.9</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="DP8" t="n">
-        <v>6.22</v>
+        <v>5.5</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.78</v>
+        <v>0.6</v>
       </c>
       <c r="DR8" t="n">
-        <v>5.11</v>
+        <v>4.5</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4165,28 +4165,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>50.56</v>
+        <v>51.2</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX8" t="n">
-        <v>10.44</v>
+        <v>10</v>
       </c>
       <c r="DY8" t="n">
-        <v>7.44</v>
+        <v>7</v>
       </c>
       <c r="DZ8" t="n">
         <v>3</v>
       </c>
       <c r="EA8" t="n">
-        <v>12.22</v>
+        <v>10.9</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="9">
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4286,139 +4286,139 @@
         <v>1.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.8</v>
+        <v>3.33</v>
       </c>
       <c r="AH9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>98.33</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>50.33</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BC9" t="n">
         <v>4</v>
       </c>
-      <c r="AI9" t="n">
-        <v>100.2</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AM9" t="n">
+      <c r="BD9" t="n">
+        <v>16</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ9" t="n">
         <v>0.6</v>
       </c>
-      <c r="AN9" t="n">
-        <v>51.4</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC9" t="n">
+      <c r="BK9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BQ9" t="n">
         <v>4.4</v>
       </c>
-      <c r="BD9" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>4.44</v>
-      </c>
       <c r="BR9" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS9" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BT9" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV9" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW9" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX9" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
         <v>2.26</v>
@@ -4433,19 +4433,19 @@
         <v>3.3</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.69</v>
+        <v>3.58</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CH9" t="n">
         <v>1.3</v>
@@ -4457,13 +4457,13 @@
         <v>1.91</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CN9" t="n">
         <v>1.68</v>
@@ -4472,19 +4472,19 @@
         <v>1.38</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CQ9" t="n">
-        <v>4.04</v>
+        <v>3.97</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.23</v>
+        <v>3.19</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="CU9" t="n">
         <v>1.34</v>
@@ -4508,88 +4508,88 @@
         <v>1.67</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.33</v>
+        <v>4.26</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.89</v>
+        <v>2.3</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="DH9" t="n">
-        <v>96.89</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.67</v>
+        <v>3.2</v>
       </c>
       <c r="DK9" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DM9" t="n">
-        <v>49.44</v>
+        <v>47.8</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.67</v>
+        <v>10.4</v>
       </c>
       <c r="DQ9" t="n">
-        <v>1.11</v>
+        <v>0.9</v>
       </c>
       <c r="DR9" t="n">
-        <v>9.109999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>54.67</v>
+        <v>53.6</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="DX9" t="n">
-        <v>13.22</v>
+        <v>12.4</v>
       </c>
       <c r="DY9" t="n">
-        <v>8.56</v>
+        <v>8</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.67</v>
+        <v>4.4</v>
       </c>
       <c r="EA9" t="n">
-        <v>20.44</v>
+        <v>18.3</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -5002,61 +5002,61 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
         <v>5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F11" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="G11" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H11" t="n">
-        <v>89</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="K11" t="n">
-        <v>6.25</v>
+        <v>6.2</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>46.5</v>
+        <v>50.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="P11" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
-        <v>9.25</v>
+        <v>7.2</v>
       </c>
       <c r="S11" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -5068,28 +5068,28 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>54</v>
+        <v>54.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.5</v>
+        <v>12.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.25</v>
+        <v>4.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>25.25</v>
+        <v>20</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AF11" t="n">
         <v>0.4</v>
@@ -5173,70 +5173,70 @@
         <v>1.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.779999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.44</v>
+        <v>5.3</v>
       </c>
       <c r="BR11" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS11" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BT11" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BU11" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV11" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BW11" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BX11" t="n">
-        <v>55.56</v>
+        <v>50</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CC11" t="n">
         <v>2.19</v>
@@ -5248,49 +5248,49 @@
         <v>1.44</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.21</v>
+        <v>3.18</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CH11" t="n">
         <v>1.29</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CO11" t="n">
         <v>1.4</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.29</v>
+        <v>2.26</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.18</v>
+        <v>4.1</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.28</v>
+        <v>3.24</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CU11" t="n">
         <v>1.33</v>
@@ -5314,55 +5314,55 @@
         <v>1.72</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.37</v>
+        <v>4.3</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DH11" t="n">
-        <v>93.56</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.11</v>
+        <v>5.2</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="DM11" t="n">
-        <v>52.33</v>
+        <v>53.6</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DP11" t="n">
-        <v>8.890000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="DQ11" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.109999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="DS11" t="n">
         <v>0</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>51.89</v>
+        <v>52.3</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.67</v>
+        <v>11.5</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.22</v>
+        <v>7.3</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.44</v>
+        <v>4.2</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.78</v>
+        <v>19.5</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="12">
@@ -5447,13 +5447,13 @@
         <v>2.6</v>
       </c>
       <c r="P12" t="n">
-        <v>7.4</v>
+        <v>10.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>3.6</v>
       </c>
       <c r="R12" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="S12" t="n">
         <v>0.6</v>
@@ -5471,25 +5471,25 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>57.8</v>
+        <v>59.6</v>
       </c>
       <c r="Y12" t="n">
         <v>0.2</v>
       </c>
       <c r="Z12" t="n">
-        <v>13</v>
+        <v>15.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.6</v>
+        <v>10.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>17</v>
+        <v>23.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AE12" t="n">
         <v>2.2</v>
@@ -5759,13 +5759,13 @@
         <v>2.4</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.6</v>
+        <v>12.3</v>
       </c>
       <c r="DQ12" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="DS12" t="n">
         <v>0.1</v>
@@ -5777,25 +5777,25 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>55.3</v>
+        <v>56.2</v>
       </c>
       <c r="DW12" t="n">
         <v>0.1</v>
       </c>
       <c r="DX12" t="n">
-        <v>12</v>
+        <v>13.2</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="EA12" t="n">
-        <v>21.2</v>
+        <v>24.3</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="EC12" t="n">
         <v>2</v>
@@ -5931,13 +5931,13 @@
         <v>2.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>8.199999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AT13" t="n">
         <v>0.4</v>
@@ -5964,16 +5964,16 @@
         <v>16.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="BD13" t="n">
-        <v>18.8</v>
+        <v>22.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="BF13" t="n">
         <v>2.2</v>
@@ -6162,13 +6162,13 @@
         <v>2.4</v>
       </c>
       <c r="DP13" t="n">
-        <v>9.199999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="DQ13" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="DR13" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="DS13" t="n">
         <v>0.1</v>
@@ -6189,13 +6189,13 @@
         <v>15.2</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="EA13" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="EB13" t="n">
         <v>1.66</v>
@@ -6253,13 +6253,13 @@
         <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>7.33</v>
+        <v>9.33</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="R14" t="n">
-        <v>3.83</v>
+        <v>6.17</v>
       </c>
       <c r="S14" t="n">
         <v>2</v>
@@ -6283,19 +6283,19 @@
         <v>0.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.33</v>
+        <v>8</v>
       </c>
       <c r="AA14" t="n">
-        <v>4.83</v>
+        <v>5.17</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="AC14" t="n">
-        <v>10.33</v>
+        <v>13.67</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -6565,13 +6565,13 @@
         <v>2</v>
       </c>
       <c r="DP14" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DQ14" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="DR14" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6589,19 +6589,19 @@
         <v>0.5</v>
       </c>
       <c r="DX14" t="n">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="DY14" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="EA14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="EB14" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="EC14" t="n">
         <v>2.8</v>

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
@@ -1421,13 +1421,13 @@
         <v>2.17</v>
       </c>
       <c r="P2" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="R2" t="n">
-        <v>7.17</v>
+        <v>9.17</v>
       </c>
       <c r="S2" t="n">
         <v>1.5</v>
@@ -1445,25 +1445,25 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>54.5</v>
+        <v>53.83</v>
       </c>
       <c r="Y2" t="n">
         <v>0.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.17</v>
+        <v>10.67</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.67</v>
+        <v>6.17</v>
       </c>
       <c r="AB2" t="n">
         <v>4.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE2" t="n">
         <v>3.83</v>
@@ -1729,13 +1729,13 @@
         <v>2.2</v>
       </c>
       <c r="DP2" t="n">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DQ2" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="DR2" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="DS2" t="n">
         <v>0.2</v>
@@ -1747,25 +1747,25 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>52.7</v>
+        <v>52.3</v>
       </c>
       <c r="DW2" t="n">
         <v>0.3</v>
       </c>
       <c r="DX2" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="DY2" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="DZ2" t="n">
         <v>4.4</v>
       </c>
       <c r="EA2" t="n">
-        <v>9.300000000000001</v>
+        <v>11.7</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="EC2" t="n">
         <v>2.9</v>
@@ -3110,13 +3110,13 @@
         <v>2.17</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9</v>
+        <v>11.33</v>
       </c>
       <c r="AR6" t="n">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.17</v>
+        <v>6.83</v>
       </c>
       <c r="AT6" t="n">
         <v>1.5</v>
@@ -3134,25 +3134,25 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>48.33</v>
+        <v>49</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.17</v>
+        <v>10.83</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.33</v>
+        <v>6.67</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.83</v>
+        <v>4.17</v>
       </c>
       <c r="BD6" t="n">
-        <v>13.83</v>
+        <v>17.33</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="BF6" t="n">
         <v>3.33</v>
@@ -3341,13 +3341,13 @@
         <v>1.9</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="DQ6" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3359,25 +3359,25 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>48.7</v>
+        <v>49.1</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>9.6</v>
+        <v>10.6</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.5</v>
+        <v>21.6</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="EC6" t="n">
         <v>3.3</v>

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" t="n">
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
         <v>0.17</v>
@@ -1469,49 +1469,49 @@
         <v>3.83</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AI2" t="n">
-        <v>94.5</v>
+        <v>76.2</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="AN2" t="n">
-        <v>50.5</v>
+        <v>41</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.25</v>
+        <v>2.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.25</v>
+        <v>0.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AU2" t="n">
         <v>1</v>
@@ -1526,73 +1526,73 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.75</v>
+        <v>5.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="BD2" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.1</v>
+        <v>10.36</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.7</v>
+        <v>4.73</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.4</v>
+        <v>5.64</v>
       </c>
       <c r="BR2" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS2" t="n">
-        <v>70</v>
+        <v>63.64</v>
       </c>
       <c r="BT2" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BU2" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BV2" t="n">
         <v>0</v>
@@ -1601,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BY2" t="n">
         <v>3.01</v>
@@ -1616,16 +1616,16 @@
         <v>3.14</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.17</v>
+        <v>3.06</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="CG2" t="n">
         <v>2.39</v>
@@ -1637,37 +1637,41 @@
         <v>1.71</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CK2" t="n">
         <v>1.64</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CN2" t="n">
         <v>1.7</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.7</v>
+        <v>4.66</v>
       </c>
       <c r="CR2" t="n">
         <v>1.53</v>
       </c>
-      <c r="CS2" t="inlineStr"/>
+      <c r="CS2" t="n">
+        <v>3.32</v>
+      </c>
       <c r="CT2" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="CU2" t="inlineStr"/>
+        <v>2.48</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>1.3</v>
+      </c>
       <c r="CV2" t="n">
         <v>1.7</v>
       </c>
@@ -1687,88 +1691,88 @@
         <v>1.74</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.93</v>
+        <v>4.88</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="DH2" t="n">
-        <v>96.09999999999999</v>
+        <v>87.64</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.3</v>
+        <v>3.09</v>
       </c>
       <c r="DK2" t="n">
         <v>5</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.2</v>
+        <v>0.37</v>
       </c>
       <c r="DM2" t="n">
-        <v>48.2</v>
+        <v>44.09</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.2</v>
+        <v>2.37</v>
       </c>
       <c r="DP2" t="n">
-        <v>8.300000000000001</v>
+        <v>7.45</v>
       </c>
       <c r="DQ2" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.9</v>
+        <v>5.27</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>52.3</v>
+        <v>52.54</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DX2" t="n">
-        <v>10.4</v>
+        <v>9.82</v>
       </c>
       <c r="DY2" t="n">
-        <v>6</v>
+        <v>5.73</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.4</v>
+        <v>4.09</v>
       </c>
       <c r="EA2" t="n">
-        <v>11.7</v>
+        <v>10.55</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="3">
@@ -1778,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
         <v>0.17</v>
@@ -1871,49 +1875,49 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AI3" t="n">
-        <v>109.25</v>
+        <v>103.4</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="AN3" t="n">
-        <v>48.75</v>
+        <v>48.8</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.75</v>
+        <v>4.4</v>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1925,82 +1929,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>47.75</v>
+        <v>45.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.75</v>
+        <v>5.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.25</v>
+        <v>3.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>9.75</v>
+        <v>7.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.97</v>
+        <v>0.89</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="BG3" t="n">
         <v>2</v>
       </c>
       <c r="BH3" t="n">
-        <v>8</v>
+        <v>7.73</v>
       </c>
       <c r="BI3" t="n">
         <v>2</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BP3" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BR3" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS3" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BT3" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BU3" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BV3" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BY3" t="n">
         <v>3.34</v>
@@ -2012,52 +2016,52 @@
         <v>3.06</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.9</v>
+        <v>3.17</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CP3" t="n">
         <v>2.37</v>
       </c>
       <c r="CQ3" t="n">
-        <v>4.01</v>
+        <v>4.04</v>
       </c>
       <c r="CR3" t="n">
         <v>1.51</v>
@@ -2093,52 +2097,52 @@
         <v>1.48</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.95</v>
+        <v>4.93</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="DH3" t="n">
-        <v>92.90000000000001</v>
+        <v>91.73</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="DK3" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="DL3" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="DM3" t="n">
-        <v>40</v>
+        <v>40.82</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="DP3" t="n">
-        <v>6.2</v>
+        <v>5.54</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="DR3" t="n">
-        <v>5.8</v>
+        <v>5.18</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2150,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>48.1</v>
+        <v>47.09</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="DX3" t="n">
-        <v>8</v>
+        <v>7.45</v>
       </c>
       <c r="DY3" t="n">
-        <v>4.1</v>
+        <v>3.82</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.9</v>
+        <v>3.63</v>
       </c>
       <c r="EA3" t="n">
-        <v>13.1</v>
+        <v>11.82</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.5</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="4">
@@ -2584,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
         <v>0.17</v>
@@ -2677,127 +2681,127 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AH5" t="n">
         <v>1</v>
       </c>
       <c r="AI5" t="n">
-        <v>94.75</v>
+        <v>92</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AL5" t="n">
-        <v>4.25</v>
+        <v>4.4</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AN5" t="n">
-        <v>48.25</v>
+        <v>49.6</v>
       </c>
       <c r="AO5" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15</v>
+        <v>11.8</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.25</v>
+        <v>7.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>42.5</v>
+        <v>44.8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BA5" t="n">
-        <v>12.75</v>
+        <v>13.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>10.75</v>
+        <v>11.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BH5" t="n">
-        <v>9.1</v>
+        <v>9.09</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.4</v>
+        <v>5.09</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BT5" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BU5" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BV5" t="n">
         <v>0</v>
@@ -2806,7 +2810,7 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>30</v>
+        <v>36.36</v>
       </c>
       <c r="BY5" t="n">
         <v>2.98</v>
@@ -2815,28 +2819,28 @@
         <v>3.38</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="CC5" t="n">
-        <v>5.07</v>
+        <v>4.68</v>
       </c>
       <c r="CD5" t="n">
-        <v>6.41</v>
+        <v>5.92</v>
       </c>
       <c r="CE5" t="n">
         <v>1.54</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.5</v>
+        <v>3.51</v>
       </c>
       <c r="CG5" t="n">
         <v>2.31</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CI5" t="n">
         <v>1.64</v>
@@ -2845,7 +2849,7 @@
         <v>2.1</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CL5" t="n">
         <v>2.32</v>
@@ -2854,13 +2858,13 @@
         <v>2.02</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CO5" t="n">
         <v>1.51</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CQ5" t="n">
         <v>4.86</v>
@@ -2887,7 +2891,7 @@
         <v>1.77</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.01</v>
@@ -2902,79 +2906,79 @@
         <v>2.63</v>
       </c>
       <c r="DD5" t="n">
-        <v>5.22</v>
+        <v>5.23</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="DH5" t="n">
-        <v>92.3</v>
+        <v>91.27</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="DM5" t="n">
-        <v>50.6</v>
+        <v>51</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.3</v>
+        <v>11.09</v>
       </c>
       <c r="DQ5" t="n">
-        <v>3.3</v>
+        <v>2.91</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.4</v>
+        <v>5.73</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>41.2</v>
+        <v>42.36</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DX5" t="n">
-        <v>11</v>
+        <v>11.54</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.7</v>
+        <v>8.18</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.3</v>
+        <v>3.37</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.2</v>
+        <v>19.18</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="EC5" t="n">
         <v>4</v>
@@ -2987,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>6</v>
@@ -2999,49 +3003,49 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="H6" t="n">
-        <v>97.75</v>
+        <v>93.8</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J6" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="M6" t="n">
-        <v>58</v>
+        <v>56.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="O6" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="P6" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="R6" t="n">
-        <v>8.75</v>
+        <v>6.8</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3053,28 +3057,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>49.25</v>
+        <v>48.6</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>10.25</v>
+        <v>10.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>28</v>
+        <v>22.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3158,49 +3162,49 @@
         <v>3.33</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.4</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BL6" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="BO6" t="n">
         <v>1</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.7</v>
+        <v>4.91</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.8</v>
+        <v>4.55</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BT6" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BU6" t="n">
-        <v>30</v>
+        <v>27.27</v>
       </c>
       <c r="BV6" t="n">
         <v>0</v>
@@ -3209,19 +3213,19 @@
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.89</v>
+        <v>2.76</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.23</v>
+        <v>3.02</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.24</v>
+        <v>3.21</v>
       </c>
       <c r="CC6" t="n">
         <v>3.86</v>
@@ -3230,10 +3234,10 @@
         <v>4.3</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.18</v>
+        <v>3.22</v>
       </c>
       <c r="CG6" t="n">
         <v>2.43</v>
@@ -3242,40 +3246,40 @@
         <v>1.28</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="CO6" t="n">
         <v>1.42</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.5</v>
+        <v>4.54</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CS6" t="n">
         <v>3.19</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="CU6" t="n">
         <v>1.34</v>
@@ -3287,67 +3291,67 @@
         <v>2.06</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.51</v>
+        <v>4.59</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="DH6" t="n">
-        <v>103.3</v>
+        <v>101</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="DK6" t="n">
         <v>4</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="DM6" t="n">
-        <v>55</v>
+        <v>54.73</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="DP6" t="n">
-        <v>11.8</v>
+        <v>10.63</v>
       </c>
       <c r="DQ6" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="DR6" t="n">
-        <v>7.6</v>
+        <v>6.82</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3359,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.1</v>
+        <v>48.82</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.6</v>
+        <v>10.54</v>
       </c>
       <c r="DY6" t="n">
         <v>7</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.6</v>
+        <v>19.54</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="7">
@@ -3793,61 +3797,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="G8" t="n">
-        <v>2.25</v>
+        <v>1.6</v>
       </c>
       <c r="H8" t="n">
-        <v>110</v>
+        <v>111.2</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="M8" t="n">
-        <v>62.25</v>
+        <v>67.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="O8" t="n">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="P8" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="R8" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3859,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>54.75</v>
+        <v>56.4</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AF8" t="n">
         <v>0.17</v>
@@ -3964,46 +3968,46 @@
         <v>2.83</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.3</v>
+        <v>4.73</v>
       </c>
       <c r="BR8" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>40</v>
+        <v>45.45</v>
       </c>
       <c r="BT8" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -4015,19 +4019,19 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CC8" t="n">
         <v>2.72</v>
@@ -4042,13 +4046,13 @@
         <v>3.2</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CH8" t="n">
         <v>1.28</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.96</v>
@@ -4057,13 +4061,13 @@
         <v>1.66</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CO8" t="n">
         <v>1.41</v>
@@ -4072,7 +4076,7 @@
         <v>2.32</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.36</v>
+        <v>4.35</v>
       </c>
       <c r="CR8" t="n">
         <v>1.49</v>
@@ -4099,61 +4103,61 @@
         <v>2.13</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DB8" t="n">
         <v>1.44</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.54</v>
+        <v>4.56</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DG8" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="DH8" t="n">
-        <v>106.8</v>
+        <v>107.64</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.9</v>
+        <v>4.73</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="DM8" t="n">
-        <v>55.9</v>
+        <v>59</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.9</v>
+        <v>2.54</v>
       </c>
       <c r="DP8" t="n">
-        <v>5.5</v>
+        <v>4.91</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="DR8" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
@@ -4165,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>51.2</v>
+        <v>52.27</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX8" t="n">
-        <v>10</v>
+        <v>10.09</v>
       </c>
       <c r="DY8" t="n">
-        <v>7</v>
+        <v>6.82</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3</v>
+        <v>3.27</v>
       </c>
       <c r="EA8" t="n">
-        <v>10.9</v>
+        <v>9.82</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="9">
@@ -4196,10 +4200,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
         <v>6</v>
@@ -4208,82 +4212,82 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.75</v>
+        <v>1.2</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="H9" t="n">
-        <v>92.75</v>
+        <v>95</v>
       </c>
       <c r="I9" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>47</v>
+        <v>49.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="P9" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="R9" t="n">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>58.5</v>
+        <v>56.4</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.75</v>
+        <v>13</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.75</v>
+        <v>7.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>21.75</v>
+        <v>17.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
         <v>0.17</v>
@@ -4367,70 +4371,70 @@
         <v>4</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.5</v>
+        <v>9.27</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.2</v>
+        <v>5.09</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.4</v>
+        <v>4.27</v>
       </c>
       <c r="BR9" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS9" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BU9" t="n">
-        <v>20</v>
+        <v>27.27</v>
       </c>
       <c r="BV9" t="n">
-        <v>10</v>
+        <v>18.18</v>
       </c>
       <c r="BW9" t="n">
-        <v>10</v>
+        <v>18.18</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BY9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BZ9" t="n">
         <v>2.26</v>
       </c>
-      <c r="BZ9" t="n">
-        <v>2.13</v>
-      </c>
       <c r="CA9" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CC9" t="n">
         <v>3.58</v>
@@ -4442,13 +4446,13 @@
         <v>1.44</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="CG9" t="n">
         <v>2.56</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI9" t="n">
         <v>1.78</v>
@@ -4460,31 +4464,31 @@
         <v>1.63</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CO9" t="n">
         <v>1.38</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.97</v>
+        <v>3.96</v>
       </c>
       <c r="CR9" t="n">
         <v>1.45</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CU9" t="n">
         <v>1.34</v>
@@ -4496,16 +4500,16 @@
         <v>2.02</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="DB9" t="n">
         <v>1.4</v>
@@ -4514,82 +4518,82 @@
         <v>2.28</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="DH9" t="n">
-        <v>96.09999999999999</v>
+        <v>96.81999999999999</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DM9" t="n">
-        <v>47.8</v>
+        <v>48.73</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="DP9" t="n">
-        <v>10.4</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.9</v>
+        <v>0.73</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.1</v>
+        <v>7.27</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.3</v>
+        <v>0.37</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>53.6</v>
+        <v>53.09</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.4</v>
+        <v>12.18</v>
       </c>
       <c r="DY9" t="n">
-        <v>8</v>
+        <v>7.64</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.4</v>
+        <v>4.55</v>
       </c>
       <c r="EA9" t="n">
-        <v>18.3</v>
+        <v>16.55</v>
       </c>
       <c r="EB9" t="n">
         <v>1.44</v>
       </c>
       <c r="EC9" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="10">
@@ -5405,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5495,139 +5499,139 @@
         <v>2.2</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.2</v>
+        <v>1.83</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="AI12" t="n">
-        <v>98.8</v>
+        <v>100.67</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>5</v>
+        <v>4.83</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN12" t="n">
-        <v>46.4</v>
+        <v>49.67</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13.8</v>
+        <v>11.33</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.6</v>
+        <v>2.83</v>
       </c>
       <c r="AS12" t="n">
-        <v>7.8</v>
+        <v>6.33</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>52.8</v>
+        <v>52.67</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="BA12" t="n">
         <v>11</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>25.4</v>
+        <v>21</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.5</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.5</v>
+        <v>2.82</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.5</v>
+        <v>4.45</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>70</v>
+        <v>72.73</v>
       </c>
       <c r="BT12" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BU12" t="n">
-        <v>20</v>
+        <v>27.27</v>
       </c>
       <c r="BV12" t="n">
-        <v>10</v>
+        <v>18.18</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>9.09</v>
       </c>
       <c r="BX12" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BY12" t="n">
         <v>1.68</v>
@@ -5636,67 +5640,67 @@
         <v>1.66</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.68</v>
+        <v>3.63</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.9</v>
+        <v>3.84</v>
       </c>
       <c r="CC12" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="CD12" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.84</v>
+        <v>0.89</v>
       </c>
       <c r="CF12" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="CG12" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.79</v>
+        <v>0.83</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="CT12" t="n">
         <v>2.81</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CV12" t="n">
         <v>1.75</v>
@@ -5705,100 +5709,100 @@
         <v>2.09</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CY12" t="n">
         <v>1.94</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="DA12" t="n">
         <v>1.83</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.2</v>
+        <v>1.54</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="DH12" t="n">
-        <v>110.5</v>
+        <v>110.46</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DM12" t="n">
-        <v>56.1</v>
+        <v>57</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="DP12" t="n">
-        <v>12.3</v>
+        <v>11.09</v>
       </c>
       <c r="DQ12" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="DR12" t="n">
-        <v>7.4</v>
+        <v>6.63</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>56.2</v>
+        <v>55.82</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.2</v>
+        <v>13</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.4</v>
+        <v>8.18</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.8</v>
+        <v>4.82</v>
       </c>
       <c r="EA12" t="n">
-        <v>24.3</v>
+        <v>22</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="EC12" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="13">
@@ -7017,94 +7021,94 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" t="n">
         <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="F16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="G16" t="n">
         <v>3</v>
       </c>
-      <c r="G16" t="n">
-        <v>2</v>
-      </c>
       <c r="H16" t="n">
-        <v>121.25</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M16" t="n">
-        <v>63.75</v>
+        <v>52.2</v>
       </c>
       <c r="N16" t="n">
         <v>1</v>
       </c>
       <c r="O16" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="P16" t="n">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="Q16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD16" t="n">
         <v>1.25</v>
       </c>
-      <c r="R16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>58.25</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AE16" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -7188,70 +7192,70 @@
         <v>3.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="BH16" t="n">
-        <v>8</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="BN16" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="BP16" t="n">
-        <v>3.6</v>
+        <v>3.73</v>
       </c>
       <c r="BQ16" t="n">
-        <v>4.4</v>
+        <v>4.73</v>
       </c>
       <c r="BR16" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS16" t="n">
-        <v>60</v>
+        <v>54.55</v>
       </c>
       <c r="BT16" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BU16" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BV16" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>50</v>
+        <v>45.45</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.41</v>
+        <v>2.51</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CC16" t="n">
         <v>2.85</v>
@@ -7260,55 +7264,55 @@
         <v>3</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CH16" t="n">
         <v>1.2</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CL16" t="n">
         <v>1.93</v>
       </c>
       <c r="CM16" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.48</v>
+        <v>3.54</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CV16" t="n">
         <v>1.87</v>
@@ -7320,7 +7324,7 @@
         <v>1.64</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.19</v>
@@ -7329,88 +7333,88 @@
         <v>1.73</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="DD16" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="DG16" t="n">
-        <v>1.8</v>
+        <v>2.27</v>
       </c>
       <c r="DH16" t="n">
-        <v>104.1</v>
+        <v>95.37</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.4</v>
+        <v>4.73</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DM16" t="n">
-        <v>54.7</v>
+        <v>50.27</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.3</v>
+        <v>9.27</v>
       </c>
       <c r="DQ16" t="n">
-        <v>1.4</v>
+        <v>1.18</v>
       </c>
       <c r="DR16" t="n">
-        <v>3.8</v>
+        <v>3.36</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>54.6</v>
+        <v>53.73</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="DX16" t="n">
-        <v>11.4</v>
+        <v>10.73</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.5</v>
+        <v>7.18</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.5</v>
+        <v>18.54</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="EC16" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="17">

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -706,667 +694,667 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>total_games</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>home_games</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>away_games</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>home_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>home_avg_2h_cards</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>home_avg_2h_corners</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>home_avg_attacks</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>home_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>home_avg_cards_num</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>home_avg_corners</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>home_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>home_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>home_avg_fh_cards</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>home_avg_fh_corners</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>home_avg_fouls</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>home_avg_freekicks</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>home_avg_goalkicks</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>home_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>home_avg_goals_scored</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>home_avg_penalties_won</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>home_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>home_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>home_avg_possession</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>home_avg_red_cards</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>home_avg_shots</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>home_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>home_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>home_avg_throwins</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>home_avg_xg</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>home_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>away_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>away_avg_2h_cards</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>away_avg_2h_corners</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>away_avg_attacks</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>away_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>away_avg_cards_num</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>away_avg_corners</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>away_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>away_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>away_avg_fh_cards</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>away_avg_fh_corners</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>away_avg_fouls</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>away_avg_freekicks</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>away_avg_goalkicks</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>away_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>away_avg_goals_scored</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>away_avg_penalties_won</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>away_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>away_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>away_avg_possession</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>away_avg_red_cards</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>away_avg_shots</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>away_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>away_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>away_avg_throwins</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>away_avg_xg</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>away_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>totalGoalCount</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>totalCornerCount</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>overallGoalCount</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ht_goals_team_a</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>ht_goals_team_b</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>goals_2hg_team_a</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>goals_2hg_team_b</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>GoalCount_2hg</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>HTGoalCount</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>corner_fh_count</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>corner_2h_count</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>over05</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>over15</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>over25</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>over35</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>over45</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>over55</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>btts</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>avg_odds_ft_1</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_1_odd</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>avg_odds_ft_x</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_x_odd</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>avg_odds_ft_2</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_2_odd</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over05</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over15</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under05</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under15</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>avg_odds_btts_no</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>avg_odds_btts_yes</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_85</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_95</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_85</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_95</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over15</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over25</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over35</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over05_odd</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over15_odd</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under05_odd</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under15_odd</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_no_odd</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>avg_pinnacle_btts_yes_odd</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_85_odd</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_95_odd</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_85_odd</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_95_odd</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over15_odd</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over25_odd</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over35_odd</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>total_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>total_avg_2h_cards</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>total_avg_2h_corners</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>total_avg_attacks</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>total_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>total_avg_cards_num</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>total_avg_corners</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>total_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>total_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>total_avg_fh_cards</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>total_avg_fh_corners</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>total_avg_fouls</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>total_avg_freekicks</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>total_avg_goalkicks</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>total_avg_penalties_won</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>total_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>total_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>total_avg_possession</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>total_avg_red_cards</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>total_avg_shots</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>total_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>total_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>total_avg_throwins</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>total_avg_xg</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>total_avg_yellow_cards</t>
         </is>
@@ -1379,142 +1367,142 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="F2" t="n">
-        <v>3.17</v>
+        <v>2.44</v>
       </c>
       <c r="G2" t="n">
-        <v>3.17</v>
+        <v>2.78</v>
       </c>
       <c r="H2" t="n">
-        <v>97.17</v>
+        <v>99.78</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>4.17</v>
+        <v>3.33</v>
       </c>
       <c r="K2" t="n">
-        <v>5.33</v>
+        <v>4.78</v>
       </c>
       <c r="L2" t="n">
-        <v>0.17</v>
+        <v>0.33</v>
       </c>
       <c r="M2" t="n">
-        <v>46.67</v>
+        <v>47.44</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="O2" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>13</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.83</v>
+        <v>1.22</v>
       </c>
       <c r="R2" t="n">
-        <v>9.17</v>
+        <v>6.67</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="V2" t="n">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>53.83</v>
+        <v>55.33</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="Z2" t="n">
         <v>10.67</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.17</v>
+        <v>6.11</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="AC2" t="n">
-        <v>17.5</v>
+        <v>12.67</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE2" t="n">
-        <v>3.83</v>
+        <v>3.11</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AH2" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>80.14</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
         <v>2</v>
       </c>
-      <c r="AI2" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AL2" t="n">
-        <v>4.6</v>
+        <v>4.71</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="AN2" t="n">
-        <v>41</v>
+        <v>44.14</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.6</v>
+        <v>2.14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.8</v>
+        <v>5.43</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.2</v>
+        <v>2.29</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.6</v>
+        <v>4.71</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="AU2" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1526,151 +1514,151 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>51</v>
+        <v>51.71</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.800000000000001</v>
+        <v>10.71</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.2</v>
+        <v>6.43</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.6</v>
+        <v>4.29</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.2</v>
+        <v>10.43</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.4</v>
+        <v>1.71</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.36</v>
+        <v>9.75</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.64</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.45</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.73</v>
+        <v>4.44</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.64</v>
+        <v>5.31</v>
       </c>
       <c r="BR2" t="n">
-        <v>90.91</v>
+        <v>87.5</v>
       </c>
       <c r="BS2" t="n">
-        <v>63.64</v>
+        <v>62.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>54.55</v>
+        <v>56.25</v>
       </c>
       <c r="BU2" t="n">
-        <v>27.27</v>
+        <v>31.25</v>
       </c>
       <c r="BV2" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BX2" t="n">
-        <v>54.55</v>
+        <v>56.25</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.01</v>
+        <v>2.77</v>
       </c>
       <c r="BZ2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="CA2" t="n">
         <v>3.06</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>3.04</v>
       </c>
       <c r="CB2" t="n">
         <v>3.14</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.97</v>
+        <v>3.05</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.06</v>
+        <v>3.17</v>
       </c>
       <c r="CE2" t="n">
         <v>1.5</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.37</v>
+        <v>3.32</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.23</v>
+        <v>2.16</v>
       </c>
       <c r="CM2" t="n">
         <v>2.17</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.66</v>
+        <v>4.59</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="CV2" t="n">
         <v>1.7</v>
@@ -1682,97 +1670,97 @@
         <v>1.64</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.19</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.53</v>
+        <v>2.46</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.88</v>
+        <v>4.7</v>
       </c>
       <c r="DE2" t="n">
         <v>0.18</v>
       </c>
       <c r="DF2" t="n">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="DH2" t="n">
-        <v>87.64</v>
+        <v>91.19</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.09</v>
+        <v>2.75</v>
       </c>
       <c r="DK2" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.37</v>
+        <v>0.44</v>
       </c>
       <c r="DM2" t="n">
-        <v>44.09</v>
+        <v>46</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.37</v>
+        <v>2.06</v>
       </c>
       <c r="DP2" t="n">
-        <v>7.45</v>
+        <v>7.56</v>
       </c>
       <c r="DQ2" t="n">
-        <v>1.09</v>
+        <v>1.69</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.27</v>
+        <v>5.81</v>
       </c>
       <c r="DS2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>53.75</v>
+      </c>
+      <c r="DW2" t="n">
         <v>0.18</v>
       </c>
-      <c r="DT2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>52.54</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0.27</v>
-      </c>
       <c r="DX2" t="n">
-        <v>9.82</v>
+        <v>10.69</v>
       </c>
       <c r="DY2" t="n">
-        <v>5.73</v>
+        <v>6.25</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.09</v>
+        <v>4.44</v>
       </c>
       <c r="EA2" t="n">
-        <v>10.55</v>
+        <v>11.69</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.73</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="3">
@@ -1782,61 +1770,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E3" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="G3" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="H3" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="K3" t="n">
-        <v>3.17</v>
+        <v>3.56</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="M3" t="n">
-        <v>34.17</v>
+        <v>43.44</v>
       </c>
       <c r="N3" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="O3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P3" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="S3" t="n">
         <v>1</v>
       </c>
-      <c r="P3" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R3" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.17</v>
-      </c>
       <c r="T3" t="n">
-        <v>0.83</v>
+        <v>1.33</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,220 +1836,220 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>48.33</v>
+        <v>50.78</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.83</v>
+        <v>10.78</v>
       </c>
       <c r="AA3" t="n">
-        <v>4</v>
+        <v>5.89</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.83</v>
+        <v>4.89</v>
       </c>
       <c r="AC3" t="n">
-        <v>15.33</v>
+        <v>17.33</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.67</v>
+        <v>2.44</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.6</v>
+        <v>1.29</v>
       </c>
       <c r="AI3" t="n">
-        <v>103.4</v>
+        <v>101.71</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="AK3" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.4</v>
+        <v>2.43</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>48.8</v>
+        <v>51.14</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8</v>
+        <v>0.57</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>0.43</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.4</v>
+        <v>7.43</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AS3" t="n">
-        <v>4.4</v>
+        <v>7.57</v>
       </c>
       <c r="AT3" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>48.57</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>43.75</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CH3" t="n">
         <v>1.2</v>
       </c>
-      <c r="AU3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>7.73</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BP3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BQ3" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BR3" t="n">
-        <v>90.91</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>63.64</v>
-      </c>
-      <c r="BT3" t="n">
-        <v>27.27</v>
-      </c>
-      <c r="BU3" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="BV3" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="BW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX3" t="n">
-        <v>36.36</v>
-      </c>
-      <c r="BY3" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="BZ3" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="CA3" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="CC3" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="CD3" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="CE3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="CF3" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="CG3" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="CH3" t="n">
-        <v>1.15</v>
-      </c>
       <c r="CI3" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="CQ3" t="n">
-        <v>4.04</v>
+        <v>4.03</v>
       </c>
       <c r="CR3" t="n">
         <v>1.51</v>
@@ -2082,67 +2070,67 @@
         <v>2.09</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.53</v>
+        <v>2.43</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.93</v>
+        <v>4.66</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.09</v>
+        <v>1.94</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.46</v>
+        <v>1.81</v>
       </c>
       <c r="DH3" t="n">
-        <v>91.73</v>
+        <v>93.44</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="DK3" t="n">
-        <v>2.37</v>
+        <v>3.07</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0.09</v>
+        <v>0.25</v>
       </c>
       <c r="DM3" t="n">
-        <v>40.82</v>
+        <v>46.81</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.55</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DP3" t="n">
-        <v>5.54</v>
+        <v>8.07</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.55</v>
+        <v>0.88</v>
       </c>
       <c r="DR3" t="n">
-        <v>5.18</v>
+        <v>7.31</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2154,28 +2142,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>47.09</v>
+        <v>49.81</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="DX3" t="n">
-        <v>7.45</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DY3" t="n">
-        <v>3.82</v>
+        <v>5.56</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.63</v>
+        <v>3.81</v>
       </c>
       <c r="EA3" t="n">
-        <v>11.82</v>
+        <v>15.81</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.73</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="4">
@@ -2185,298 +2173,298 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="G4" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="H4" t="n">
-        <v>84.5</v>
+        <v>84.38</v>
       </c>
       <c r="I4" t="n">
         <v>0.25</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>3.62</v>
       </c>
       <c r="K4" t="n">
-        <v>5.25</v>
+        <v>3.75</v>
       </c>
       <c r="L4" t="n">
-        <v>0.75</v>
+        <v>0.62</v>
       </c>
       <c r="M4" t="n">
-        <v>50.75</v>
+        <v>48.12</v>
       </c>
       <c r="N4" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="O4" t="n">
-        <v>3.5</v>
+        <v>2.38</v>
       </c>
       <c r="P4" t="n">
-        <v>5</v>
+        <v>5.38</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.25</v>
+        <v>1.12</v>
       </c>
       <c r="R4" t="n">
-        <v>7.5</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="T4" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="U4" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="V4" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>39.25</v>
+        <v>39.38</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.75</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>4.25</v>
       </c>
       <c r="AB4" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>88.88</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>51.62</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>36.62</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="BC4" t="n">
         <v>4.5</v>
       </c>
-      <c r="AC4" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>87.17</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>8.83</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>3.83</v>
-      </c>
       <c r="BD4" t="n">
-        <v>17.5</v>
+        <v>16.75</v>
       </c>
       <c r="BE4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>75</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="CE4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="CH4" t="n">
         <v>1.29</v>
       </c>
-      <c r="BF4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>90</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>60</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>60</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>20</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BW4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BX4" t="n">
-        <v>50</v>
-      </c>
-      <c r="BY4" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="BZ4" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="CA4" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="CB4" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="CC4" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="CD4" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="CE4" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="CF4" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="CG4" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="CH4" t="n">
-        <v>1.3</v>
-      </c>
       <c r="CI4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CL4" t="n">
         <v>2.2</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CN4" t="n">
         <v>1.7</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.24</v>
+        <v>4.33</v>
       </c>
       <c r="CR4" t="n">
         <v>1.49</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CV4" t="n">
         <v>1.72</v>
@@ -2488,13 +2476,13 @@
         <v>1.67</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.14</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DB4" t="n">
         <v>1.43</v>
@@ -2503,82 +2491,82 @@
         <v>2.37</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.46</v>
+        <v>4.45</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="DF4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>86.63</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>49.87</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>38</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>5.44</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="EB4" t="n">
         <v>1.3</v>
       </c>
-      <c r="DG4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="DH4" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="DI4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="DJ4" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="DK4" t="n">
-        <v>4</v>
-      </c>
-      <c r="DL4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="DM4" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="DN4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="DO4" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="DP4" t="n">
-        <v>7.7</v>
-      </c>
-      <c r="DQ4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="DR4" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="DS4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DT4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV4" t="n">
-        <v>37.6</v>
-      </c>
-      <c r="DW4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="DX4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="DY4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="DZ4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="EA4" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="EB4" t="n">
-        <v>1.27</v>
-      </c>
       <c r="EC4" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="5">
@@ -2588,298 +2576,298 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="F5" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="G5" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="H5" t="n">
-        <v>90.67</v>
+        <v>87.38</v>
       </c>
       <c r="I5" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="J5" t="n">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="M5" t="n">
-        <v>52.17</v>
+        <v>48.62</v>
       </c>
       <c r="N5" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="O5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="P5" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R5" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>88.38</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>49.75</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>7.38</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>45</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>21.62</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BO5" t="n">
         <v>1</v>
       </c>
-      <c r="P5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="R5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>40.33</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>5.67</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>19.33</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>92</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>19</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>0.73</v>
-      </c>
       <c r="BP5" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.09</v>
+        <v>4.69</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>54.55</v>
+        <v>62.5</v>
       </c>
       <c r="BT5" t="n">
-        <v>27.27</v>
+        <v>37.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>9.09</v>
+        <v>25</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>36.36</v>
+        <v>43.75</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.98</v>
+        <v>3.09</v>
       </c>
       <c r="BZ5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CF5" t="n">
         <v>3.38</v>
       </c>
-      <c r="CA5" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="CC5" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="CD5" t="n">
-        <v>5.92</v>
-      </c>
-      <c r="CE5" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="CF5" t="n">
-        <v>3.51</v>
-      </c>
       <c r="CG5" t="n">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="CK5" t="n">
         <v>1.69</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="CP5" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="CQ5" t="n">
-        <v>4.86</v>
+        <v>4.65</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="CS5" t="n">
-        <v>3.11</v>
+        <v>2.92</v>
       </c>
       <c r="CT5" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="CV5" t="n">
         <v>1.63</v>
@@ -2891,97 +2879,97 @@
         <v>1.77</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.63</v>
+        <v>2.54</v>
       </c>
       <c r="DD5" t="n">
-        <v>5.23</v>
+        <v>4.97</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="DG5" t="n">
         <v>1.37</v>
       </c>
       <c r="DH5" t="n">
-        <v>91.27</v>
+        <v>87.88</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="DJ5" t="n">
-        <v>4.45</v>
+        <v>4.19</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.46</v>
+        <v>3.06</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.45</v>
+        <v>0.32</v>
       </c>
       <c r="DM5" t="n">
-        <v>51</v>
+        <v>49.18</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.09</v>
+        <v>1.63</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.09</v>
+        <v>12.69</v>
       </c>
       <c r="DQ5" t="n">
-        <v>2.91</v>
+        <v>3.44</v>
       </c>
       <c r="DR5" t="n">
-        <v>5.73</v>
+        <v>6.63</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>42.36</v>
+        <v>42.75</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.37</v>
+        <v>0.31</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.54</v>
+        <v>11.44</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.18</v>
+        <v>7.94</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.37</v>
+        <v>3.5</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.18</v>
+        <v>20.5</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="EC5" t="n">
-        <v>4</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="6">
@@ -2991,61 +2979,61 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="H6" t="n">
-        <v>93.8</v>
+        <v>104.14</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4</v>
+        <v>0.29</v>
       </c>
       <c r="M6" t="n">
-        <v>56.8</v>
+        <v>55.43</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="O6" t="n">
-        <v>1.8</v>
+        <v>1.29</v>
       </c>
       <c r="P6" t="n">
-        <v>9.800000000000001</v>
+        <v>10.29</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.8</v>
+        <v>2.71</v>
       </c>
       <c r="R6" t="n">
-        <v>6.8</v>
+        <v>7.57</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="T6" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3057,76 +3045,76 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>48.6</v>
+        <v>49.57</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>10.2</v>
+        <v>9.43</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.4</v>
+        <v>6.71</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="AC6" t="n">
-        <v>22.2</v>
+        <v>21.86</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE6" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
       </c>
       <c r="AG6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH6" t="n">
         <v>2.33</v>
       </c>
-      <c r="AH6" t="n">
-        <v>2.67</v>
-      </c>
       <c r="AI6" t="n">
-        <v>107</v>
+        <v>101.56</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.33</v>
+        <v>3.11</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.83</v>
+        <v>4.11</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AN6" t="n">
-        <v>53</v>
+        <v>51.78</v>
       </c>
       <c r="AO6" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.17</v>
+        <v>1.78</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11.33</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.83</v>
+        <v>6.44</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AU6" t="n">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,115 +3126,115 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>49</v>
+        <v>49.67</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.83</v>
+        <v>10.11</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.67</v>
+        <v>6.56</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.17</v>
+        <v>3.56</v>
       </c>
       <c r="BD6" t="n">
-        <v>17.33</v>
+        <v>16.67</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.33</v>
+        <v>3.11</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="BH6" t="n">
-        <v>9.359999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.55</v>
+        <v>0.44</v>
       </c>
       <c r="BL6" t="n">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.45</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="BO6" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.91</v>
+        <v>4.31</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.55</v>
+        <v>4.06</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>72.73</v>
+        <v>56.25</v>
       </c>
       <c r="BT6" t="n">
-        <v>45.45</v>
+        <v>37.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>45.45</v>
+        <v>37.5</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.76</v>
+        <v>3.08</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.02</v>
+        <v>3.29</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CB6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CF6" t="n">
         <v>3.21</v>
       </c>
-      <c r="CC6" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="CD6" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="CE6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CF6" t="n">
-        <v>3.22</v>
-      </c>
       <c r="CG6" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="CH6" t="n">
         <v>1.28</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.98</v>
@@ -3255,31 +3243,31 @@
         <v>1.66</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.19</v>
+        <v>2.28</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CO6" t="n">
         <v>1.42</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.54</v>
+        <v>4.45</v>
       </c>
       <c r="CR6" t="n">
         <v>1.5</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CU6" t="n">
         <v>1.34</v>
@@ -3291,67 +3279,67 @@
         <v>2.06</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CY6" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="CZ6" t="n">
         <v>2.11</v>
       </c>
-      <c r="CZ6" t="n">
-        <v>2.14</v>
-      </c>
       <c r="DA6" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="DB6" t="n">
         <v>1.44</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.59</v>
+        <v>4.56</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.27</v>
+        <v>1.94</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="DH6" t="n">
-        <v>101</v>
+        <v>102.69</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3.18</v>
+        <v>2.93</v>
       </c>
       <c r="DK6" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="DM6" t="n">
-        <v>54.73</v>
+        <v>53.38</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="DO6" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.63</v>
+        <v>10.13</v>
       </c>
       <c r="DQ6" t="n">
-        <v>1.73</v>
+        <v>2.19</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.82</v>
+        <v>6.93</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3363,28 +3351,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>48.82</v>
+        <v>49.63</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>10.54</v>
+        <v>9.81</v>
       </c>
       <c r="DY6" t="n">
-        <v>7</v>
+        <v>6.63</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.55</v>
+        <v>3.19</v>
       </c>
       <c r="EA6" t="n">
-        <v>19.54</v>
+        <v>18.94</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="EC6" t="n">
-        <v>3.18</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="7">
@@ -3394,61 +3382,61 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2</v>
+        <v>2.57</v>
       </c>
       <c r="H7" t="n">
-        <v>109.4</v>
+        <v>105.29</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="K7" t="n">
-        <v>5.8</v>
+        <v>4.86</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6</v>
+        <v>0.43</v>
       </c>
       <c r="M7" t="n">
-        <v>66.59999999999999</v>
+        <v>63.14</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="O7" t="n">
-        <v>2.6</v>
+        <v>2.29</v>
       </c>
       <c r="P7" t="n">
-        <v>3.4</v>
+        <v>5.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2</v>
+        <v>0.14</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4</v>
+        <v>4.71</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8</v>
+        <v>1.43</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3460,187 +3448,187 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>56</v>
+        <v>53.43</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.800000000000001</v>
+        <v>11.29</v>
       </c>
       <c r="AA7" t="n">
-        <v>4.4</v>
+        <v>5.86</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.4</v>
+        <v>5.43</v>
       </c>
       <c r="AC7" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AI7" t="n">
-        <v>94.40000000000001</v>
+        <v>86.33</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>47</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="AT7" t="n">
         <v>2</v>
       </c>
-      <c r="AL7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AU7" t="n">
-        <v>0.6</v>
+        <v>0.89</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>53.8</v>
+        <v>52.67</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="BA7" t="n">
-        <v>7</v>
+        <v>7.78</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.8</v>
+        <v>5.33</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="BD7" t="n">
-        <v>21</v>
+        <v>17.11</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.97</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="BH7" t="n">
         <v>7.5</v>
       </c>
       <c r="BI7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>81.25</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>50</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BZ7" t="n">
         <v>2.5</v>
       </c>
-      <c r="BJ7" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BN7" t="n">
+      <c r="CA7" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="CC7" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="CD7" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="CE7" t="n">
         <v>1.5</v>
       </c>
-      <c r="BO7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>90</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>80</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>40</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>30</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>50</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="CC7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="CD7" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="CE7" t="n">
-        <v>1.51</v>
-      </c>
       <c r="CF7" t="n">
-        <v>3.27</v>
+        <v>3.23</v>
       </c>
       <c r="CG7" t="n">
         <v>2.4</v>
@@ -3649,43 +3637,43 @@
         <v>1.27</v>
       </c>
       <c r="CI7" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CN7" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.48</v>
+        <v>4.41</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.49</v>
+        <v>2.53</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="CV7" t="n">
         <v>1.75</v>
@@ -3694,100 +3682,100 @@
         <v>2.1</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.81</v>
+        <v>4.69</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="DH7" t="n">
-        <v>101.9</v>
+        <v>94.62</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="DK7" t="n">
-        <v>4</v>
+        <v>3.44</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.4</v>
+        <v>0.31</v>
       </c>
       <c r="DM7" t="n">
-        <v>58.7</v>
+        <v>54.06</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="DP7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.8</v>
+        <v>0.62</v>
       </c>
       <c r="DR7" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.9</v>
+        <v>53</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DX7" t="n">
-        <v>8.4</v>
+        <v>9.32</v>
       </c>
       <c r="DY7" t="n">
-        <v>4.6</v>
+        <v>5.56</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="EA7" t="n">
-        <v>15.2</v>
+        <v>15.31</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="EC7" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="8">
@@ -3797,61 +3785,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8</v>
+        <v>2.14</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6</v>
+        <v>2.14</v>
       </c>
       <c r="H8" t="n">
-        <v>111.2</v>
+        <v>106.86</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>5.4</v>
+        <v>5.57</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="M8" t="n">
-        <v>67.8</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="O8" t="n">
-        <v>2.8</v>
+        <v>2.71</v>
       </c>
       <c r="P8" t="n">
-        <v>2.6</v>
+        <v>5.86</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6</v>
+        <v>2.43</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4</v>
+        <v>5.57</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4</v>
+        <v>0.57</v>
       </c>
       <c r="T8" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3863,151 +3851,151 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>56.4</v>
+        <v>56.57</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.2</v>
+        <v>14.71</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.8</v>
+        <v>10.29</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.4</v>
+        <v>4.43</v>
       </c>
       <c r="AC8" t="n">
-        <v>9</v>
+        <v>16.14</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.2</v>
+        <v>2.71</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.83</v>
+        <v>2.67</v>
       </c>
       <c r="AI8" t="n">
-        <v>104.67</v>
+        <v>102.89</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.17</v>
+        <v>4.67</v>
       </c>
       <c r="AM8" t="n">
         <v>0.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>51.67</v>
+        <v>55.67</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>6.83</v>
+        <v>8</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.33</v>
+        <v>1.22</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.33</v>
+        <v>7.33</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="AU8" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>52</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BL8" t="n">
         <v>0.5</v>
       </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>48.83</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0.45</v>
-      </c>
       <c r="BM8" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP8" t="n">
-        <v>4</v>
+        <v>3.69</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.73</v>
+        <v>5.44</v>
       </c>
       <c r="BR8" t="n">
-        <v>81.81999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS8" t="n">
-        <v>45.45</v>
+        <v>56.25</v>
       </c>
       <c r="BT8" t="n">
-        <v>18.18</v>
+        <v>25</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -4019,25 +4007,25 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>36.36</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.72</v>
+        <v>3.01</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.92</v>
+        <v>3.28</v>
       </c>
       <c r="CE8" t="n">
         <v>1.48</v>
@@ -4046,7 +4034,7 @@
         <v>3.2</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CH8" t="n">
         <v>1.28</v>
@@ -4061,22 +4049,22 @@
         <v>1.66</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CO8" t="n">
         <v>1.41</v>
       </c>
       <c r="CP8" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="CR8" t="n">
         <v>1.49</v>
@@ -4085,10 +4073,10 @@
         <v>3.28</v>
       </c>
       <c r="CT8" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CV8" t="n">
         <v>1.8</v>
@@ -4097,100 +4085,100 @@
         <v>2.02</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CY8" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DB8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>104.63</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>60.94</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>7.06</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>54</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>11.88</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="EB8" t="n">
         <v>1.44</v>
       </c>
-      <c r="DC8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="DD8" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="DE8" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DF8" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="DG8" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="DH8" t="n">
-        <v>107.64</v>
-      </c>
-      <c r="DI8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ8" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="DK8" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="DL8" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="DM8" t="n">
-        <v>59</v>
-      </c>
-      <c r="DN8" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="DO8" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="DP8" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="DQ8" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="DR8" t="n">
-        <v>4</v>
-      </c>
-      <c r="DS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV8" t="n">
-        <v>52.27</v>
-      </c>
-      <c r="DW8" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DX8" t="n">
-        <v>10.09</v>
-      </c>
-      <c r="DY8" t="n">
-        <v>6.82</v>
-      </c>
-      <c r="DZ8" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="EA8" t="n">
-        <v>9.82</v>
-      </c>
-      <c r="EB8" t="n">
-        <v>1.3</v>
-      </c>
       <c r="EC8" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="9">
@@ -4200,295 +4188,295 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2</v>
+        <v>1.75</v>
       </c>
       <c r="G9" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="H9" t="n">
-        <v>95</v>
+        <v>93.62</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="K9" t="n">
-        <v>3.2</v>
+        <v>3.62</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M9" t="n">
-        <v>49.2</v>
+        <v>52.25</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="O9" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="P9" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="R9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6</v>
+        <v>0.88</v>
       </c>
       <c r="T9" t="n">
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6</v>
+        <v>0.38</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.38</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>56.4</v>
+        <v>54.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="Z9" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.8</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.2</v>
+        <v>5.12</v>
       </c>
       <c r="AC9" t="n">
-        <v>17.2</v>
+        <v>18.62</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.33</v>
+        <v>3.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.5</v>
+        <v>4.12</v>
       </c>
       <c r="AI9" t="n">
-        <v>98.33</v>
+        <v>99.75</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>4.33</v>
+        <v>4.12</v>
       </c>
       <c r="AL9" t="n">
-        <v>5.5</v>
+        <v>6.38</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.5</v>
+        <v>0.88</v>
       </c>
       <c r="AN9" t="n">
-        <v>48.33</v>
+        <v>50.75</v>
       </c>
       <c r="AO9" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AP9" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.33</v>
+        <v>11.25</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>50.33</v>
+        <v>51.88</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="BA9" t="n">
-        <v>11.5</v>
+        <v>11.38</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.5</v>
+        <v>7.38</v>
       </c>
       <c r="BC9" t="n">
         <v>4</v>
       </c>
       <c r="BD9" t="n">
-        <v>16</v>
+        <v>16.88</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="BF9" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.27</v>
+        <v>9.06</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.82</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL9" t="n">
-        <v>1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.09</v>
+        <v>4.62</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.27</v>
+        <v>4.5</v>
       </c>
       <c r="BR9" t="n">
-        <v>90.91</v>
+        <v>93.75</v>
       </c>
       <c r="BS9" t="n">
-        <v>72.73</v>
+        <v>75</v>
       </c>
       <c r="BT9" t="n">
-        <v>54.55</v>
+        <v>56.25</v>
       </c>
       <c r="BU9" t="n">
-        <v>27.27</v>
+        <v>25</v>
       </c>
       <c r="BV9" t="n">
-        <v>18.18</v>
+        <v>12.5</v>
       </c>
       <c r="BW9" t="n">
-        <v>18.18</v>
+        <v>12.5</v>
       </c>
       <c r="BX9" t="n">
-        <v>54.55</v>
+        <v>62.5</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="CA9" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="CD9" t="n">
         <v>3.24</v>
       </c>
-      <c r="CB9" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="CC9" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>3.48</v>
-      </c>
       <c r="CE9" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.56</v>
+        <v>2.53</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CI9" t="n">
         <v>1.78</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CK9" t="n">
         <v>1.63</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="CM9" t="n">
         <v>2.13</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.96</v>
+        <v>3.98</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CS9" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CT9" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="CU9" t="n">
         <v>1.34</v>
@@ -4500,100 +4488,100 @@
         <v>2.02</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DB9" t="n">
         <v>1.4</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="DH9" t="n">
-        <v>96.81999999999999</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.27</v>
+        <v>3.37</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="DM9" t="n">
-        <v>48.73</v>
+        <v>51.5</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.91</v>
+        <v>2.25</v>
       </c>
       <c r="DP9" t="n">
-        <v>9.359999999999999</v>
+        <v>10.88</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.73</v>
+        <v>1.12</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.27</v>
+        <v>7.68</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>53.09</v>
+        <v>53.19</v>
       </c>
       <c r="DW9" t="n">
         <v>0.18</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.18</v>
+        <v>12.44</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.64</v>
+        <v>7.88</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.55</v>
+        <v>4.56</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.55</v>
+        <v>17.75</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.09</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="10">
@@ -4603,148 +4591,148 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6</v>
+        <v>1.89</v>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>2.22</v>
       </c>
       <c r="H10" t="n">
-        <v>104.6</v>
+        <v>104</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8</v>
+        <v>0.44</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="K10" t="n">
-        <v>6.6</v>
+        <v>4.89</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8</v>
+        <v>0.44</v>
       </c>
       <c r="M10" t="n">
-        <v>71.59999999999999</v>
+        <v>64.67</v>
       </c>
       <c r="N10" t="n">
-        <v>1.8</v>
+        <v>1.22</v>
       </c>
       <c r="O10" t="n">
-        <v>3.6</v>
+        <v>2.67</v>
       </c>
       <c r="P10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="R10" t="n">
-        <v>4.4</v>
+        <v>5.56</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2</v>
+        <v>0.89</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>53.6</v>
+        <v>54.33</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>12</v>
+        <v>12.33</v>
       </c>
       <c r="AA10" t="n">
-        <v>6</v>
+        <v>6.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>6</v>
+        <v>5.89</v>
       </c>
       <c r="AC10" t="n">
-        <v>18.8</v>
+        <v>17.22</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AE10" t="n">
-        <v>3.2</v>
+        <v>2.89</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="AI10" t="n">
-        <v>103.2</v>
+        <v>105.43</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="AK10" t="n">
-        <v>4.4</v>
+        <v>4.71</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.6</v>
+        <v>0.43</v>
       </c>
       <c r="AN10" t="n">
-        <v>48.2</v>
+        <v>51.14</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="AQ10" t="n">
-        <v>12.6</v>
+        <v>12.29</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.6</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AT10" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AU10" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
@@ -4753,148 +4741,148 @@
         <v>50</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.2</v>
+        <v>0.29</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.4</v>
+        <v>20.14</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.2</v>
+        <v>4.29</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.300000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BK10" t="n">
         <v>0.5</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.8</v>
+        <v>3.88</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.5</v>
+        <v>4.38</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>60</v>
+        <v>68.75</v>
       </c>
       <c r="BT10" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU10" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="BV10" t="n">
-        <v>10</v>
+        <v>6.25</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY10" t="n">
-        <v>3.27</v>
+        <v>2.86</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.93</v>
+        <v>3.23</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="CB10" t="n">
         <v>3.47</v>
       </c>
       <c r="CC10" t="n">
-        <v>4.37</v>
+        <v>4.65</v>
       </c>
       <c r="CD10" t="n">
-        <v>4.82</v>
+        <v>5.02</v>
       </c>
       <c r="CE10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="CR10" t="n">
         <v>1.46</v>
       </c>
-      <c r="CF10" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="CG10" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="CH10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="CI10" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CJ10" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="CK10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CL10" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="CM10" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="CN10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="CO10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="CP10" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="CQ10" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>1.49</v>
-      </c>
       <c r="CS10" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="CT10" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CV10" t="n">
         <v>1.7</v>
@@ -4906,97 +4894,97 @@
         <v>1.63</v>
       </c>
       <c r="CY10" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="DC10" t="n">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="DD10" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>104.63</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="DK10" t="n">
         <v>4.5</v>
       </c>
-      <c r="DE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DF10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="DG10" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="DH10" t="n">
-        <v>103.9</v>
-      </c>
-      <c r="DI10" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DJ10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="DK10" t="n">
-        <v>5.4</v>
-      </c>
       <c r="DL10" t="n">
-        <v>0.7</v>
+        <v>0.44</v>
       </c>
       <c r="DM10" t="n">
-        <v>59.9</v>
+        <v>58.75</v>
       </c>
       <c r="DN10" t="n">
-        <v>1.7</v>
+        <v>1.43</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.7</v>
+        <v>2.32</v>
       </c>
       <c r="DP10" t="n">
-        <v>10.9</v>
+        <v>10.5</v>
       </c>
       <c r="DQ10" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="DR10" t="n">
-        <v>7</v>
+        <v>7.38</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>51.8</v>
+        <v>52.44</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DX10" t="n">
-        <v>10.4</v>
+        <v>11.75</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.1</v>
+        <v>6.68</v>
       </c>
       <c r="DZ10" t="n">
-        <v>4.3</v>
+        <v>5.06</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.1</v>
+        <v>18.5</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="EC10" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="11">
@@ -5006,142 +4994,142 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="G11" t="n">
-        <v>3.4</v>
+        <v>2.57</v>
       </c>
       <c r="H11" t="n">
-        <v>89.59999999999999</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>6.2</v>
+        <v>4.71</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="M11" t="n">
-        <v>50.2</v>
+        <v>50</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="O11" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="P11" t="n">
-        <v>9</v>
+        <v>11.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.8</v>
+        <v>3.14</v>
       </c>
       <c r="R11" t="n">
-        <v>7.2</v>
+        <v>7.29</v>
       </c>
       <c r="S11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>53.57</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.4</v>
       </c>
-      <c r="T11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>12.8</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>20</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AE11" t="n">
-        <v>1.6</v>
+        <v>1.86</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AI11" t="n">
-        <v>97.2</v>
+        <v>102.22</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.8</v>
+        <v>2.33</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.2</v>
+        <v>3.56</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="AN11" t="n">
-        <v>57</v>
+        <v>55.56</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.6</v>
+        <v>1.22</v>
       </c>
       <c r="AP11" t="n">
-        <v>2</v>
+        <v>1.56</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.8</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AR11" t="n">
-        <v>3.2</v>
+        <v>2.67</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.2</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
@@ -5153,151 +5141,151 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>50.2</v>
+        <v>49.22</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.2</v>
+        <v>10.78</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.4</v>
+        <v>6.78</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BD11" t="n">
-        <v>19</v>
+        <v>19.22</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.8</v>
+        <v>2.22</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BH11" t="n">
-        <v>9.5</v>
+        <v>8.31</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.9</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM11" t="n">
         <v>0.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="BO11" t="n">
         <v>1.5</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.1</v>
+        <v>3.38</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.3</v>
+        <v>4.88</v>
       </c>
       <c r="BR11" t="n">
-        <v>90</v>
+        <v>93.75</v>
       </c>
       <c r="BS11" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BT11" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BU11" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV11" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="BW11" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="BX11" t="n">
         <v>50</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.13</v>
+        <v>2.27</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.12</v>
+        <v>3.14</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.19</v>
+        <v>2.7</v>
       </c>
       <c r="CD11" t="n">
-        <v>2.31</v>
+        <v>2.89</v>
       </c>
       <c r="CE11" t="n">
         <v>1.44</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CL11" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CN11" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.1</v>
+        <v>4.07</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CS11" t="n">
         <v>3.24</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CV11" t="n">
         <v>1.8</v>
@@ -5306,100 +5294,100 @@
         <v>2.02</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CY11" t="n">
         <v>2.07</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.3</v>
+        <v>4.22</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="DH11" t="n">
-        <v>93.40000000000001</v>
+        <v>95.25</v>
       </c>
       <c r="DI11" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.3</v>
+        <v>2.62</v>
       </c>
       <c r="DK11" t="n">
-        <v>5.2</v>
+        <v>4.06</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="DM11" t="n">
-        <v>53.6</v>
+        <v>53.13</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="DP11" t="n">
-        <v>7.9</v>
+        <v>9.81</v>
       </c>
       <c r="DQ11" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.2</v>
+        <v>7.81</v>
       </c>
       <c r="DS11" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>52.3</v>
+        <v>51.12</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.5</v>
+        <v>11.25</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.3</v>
+        <v>7.19</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.2</v>
+        <v>4.06</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.5</v>
+        <v>19.25</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="EC11" t="n">
-        <v>1.7</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="12">
@@ -5409,298 +5397,298 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" t="n">
+        <v>9</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="H12" t="n">
+        <v>112.29</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M12" t="n">
+        <v>59.57</v>
+      </c>
+      <c r="N12" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="P12" t="n">
         <v>11</v>
       </c>
-      <c r="C12" t="n">
-        <v>5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>6</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H12" t="n">
-        <v>122.2</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M12" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P12" t="n">
-        <v>10.8</v>
-      </c>
       <c r="Q12" t="n">
-        <v>3.6</v>
+        <v>2.57</v>
       </c>
       <c r="R12" t="n">
-        <v>7</v>
+        <v>5.57</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>59.6</v>
+        <v>58.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.2</v>
+        <v>0.29</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.4</v>
+        <v>15.14</v>
       </c>
       <c r="AA12" t="n">
-        <v>10.2</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.2</v>
+        <v>5.43</v>
       </c>
       <c r="AC12" t="n">
-        <v>23.2</v>
+        <v>19</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.67</v>
+        <v>3.11</v>
       </c>
       <c r="AI12" t="n">
-        <v>100.67</v>
+        <v>104.11</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.83</v>
+        <v>5.33</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.17</v>
+        <v>0.22</v>
       </c>
       <c r="AN12" t="n">
+        <v>52.78</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
         <v>49.67</v>
       </c>
-      <c r="AO12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>6.33</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>52.67</v>
-      </c>
       <c r="AZ12" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="BA12" t="n">
-        <v>11</v>
+        <v>10.78</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.5</v>
+        <v>6.22</v>
       </c>
       <c r="BC12" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BP12" t="n">
         <v>4.5</v>
       </c>
-      <c r="BD12" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>8.359999999999999</v>
-      </c>
-      <c r="BI12" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="BJ12" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BK12" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="BL12" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="BM12" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="BN12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="BO12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BP12" t="n">
-        <v>4.45</v>
-      </c>
       <c r="BQ12" t="n">
-        <v>3.91</v>
+        <v>4</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>72.73</v>
+        <v>81.25</v>
       </c>
       <c r="BT12" t="n">
-        <v>54.55</v>
+        <v>68.75</v>
       </c>
       <c r="BU12" t="n">
-        <v>27.27</v>
+        <v>37.5</v>
       </c>
       <c r="BV12" t="n">
-        <v>18.18</v>
+        <v>18.75</v>
       </c>
       <c r="BW12" t="n">
-        <v>9.09</v>
+        <v>6.25</v>
       </c>
       <c r="BX12" t="n">
-        <v>54.55</v>
+        <v>62.5</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CA12" t="n">
         <v>3.63</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.84</v>
+        <v>3.73</v>
       </c>
       <c r="CC12" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="CD12" t="n">
-        <v>1.91</v>
+        <v>2.07</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.89</v>
+        <v>0.96</v>
       </c>
       <c r="CF12" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="CG12" t="n">
-        <v>1.73</v>
+        <v>1.89</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.85</v>
+        <v>0.92</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="CK12" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.42</v>
+        <v>1.51</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.27</v>
+        <v>2.43</v>
       </c>
       <c r="CR12" t="n">
         <v>1.43</v>
       </c>
       <c r="CS12" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CT12" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CV12" t="n">
         <v>1.75</v>
@@ -5712,97 +5700,97 @@
         <v>1.57</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.75</v>
+        <v>3.71</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.64</v>
+        <v>2.93</v>
       </c>
       <c r="DH12" t="n">
-        <v>110.46</v>
+        <v>107.69</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.27</v>
+        <v>0.19</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="DK12" t="n">
-        <v>5</v>
+        <v>5.56</v>
       </c>
       <c r="DL12" t="n">
         <v>0.37</v>
       </c>
       <c r="DM12" t="n">
-        <v>57</v>
+        <v>55.75</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.37</v>
+        <v>2.62</v>
       </c>
       <c r="DP12" t="n">
-        <v>11.09</v>
+        <v>10.68</v>
       </c>
       <c r="DQ12" t="n">
-        <v>3.18</v>
+        <v>2.5</v>
       </c>
       <c r="DR12" t="n">
-        <v>6.63</v>
+        <v>5.75</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.18</v>
+        <v>0.37</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.18</v>
+        <v>0.37</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>55.82</v>
+        <v>53.38</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="DX12" t="n">
-        <v>13</v>
+        <v>12.69</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.18</v>
+        <v>7.75</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.82</v>
+        <v>4.94</v>
       </c>
       <c r="EA12" t="n">
-        <v>22</v>
+        <v>18.44</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="13">
@@ -5812,142 +5800,142 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6</v>
+        <v>2.44</v>
       </c>
       <c r="G13" t="n">
-        <v>3.2</v>
+        <v>2.89</v>
       </c>
       <c r="H13" t="n">
-        <v>119.6</v>
+        <v>120.33</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="J13" t="n">
-        <v>2.4</v>
+        <v>3.56</v>
       </c>
       <c r="K13" t="n">
-        <v>5.8</v>
+        <v>5.11</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="M13" t="n">
-        <v>46.2</v>
+        <v>59.89</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>2.6</v>
+        <v>2.22</v>
       </c>
       <c r="P13" t="n">
-        <v>10.2</v>
+        <v>11.78</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.2</v>
+        <v>3.78</v>
       </c>
       <c r="R13" t="n">
-        <v>7.4</v>
+        <v>8.33</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="T13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>54</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>20.78</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AG13" t="n">
         <v>2</v>
       </c>
-      <c r="U13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AH13" t="n">
-        <v>2.6</v>
+        <v>2.29</v>
       </c>
       <c r="AI13" t="n">
-        <v>105.2</v>
+        <v>106</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.4</v>
+        <v>2.57</v>
       </c>
       <c r="AL13" t="n">
-        <v>5</v>
+        <v>4.71</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.2</v>
+        <v>0.29</v>
       </c>
       <c r="AN13" t="n">
-        <v>40</v>
+        <v>45.14</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.2</v>
+        <v>2.29</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.4</v>
+        <v>10.86</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.6</v>
+        <v>2.57</v>
       </c>
       <c r="AS13" t="n">
-        <v>7</v>
+        <v>7.43</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.4</v>
+        <v>0.71</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5959,148 +5947,148 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>53.4</v>
+        <v>54</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="BA13" t="n">
-        <v>16.6</v>
+        <v>16</v>
       </c>
       <c r="BB13" t="n">
-        <v>11.4</v>
+        <v>10.86</v>
       </c>
       <c r="BC13" t="n">
-        <v>5.2</v>
+        <v>5.14</v>
       </c>
       <c r="BD13" t="n">
-        <v>22.8</v>
+        <v>25.71</v>
       </c>
       <c r="BE13" t="n">
         <v>1.7</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="BH13" t="n">
-        <v>8.4</v>
+        <v>8.06</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.4</v>
+        <v>3.94</v>
       </c>
       <c r="BQ13" t="n">
-        <v>3.9</v>
+        <v>4.06</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT13" t="n">
         <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BV13" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.9</v>
+        <v>3.82</v>
       </c>
       <c r="CC13" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="CD13" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="CE13" t="n">
         <v>1.44</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CG13" t="n">
         <v>2.59</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CJ13" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CM13" t="n">
         <v>2.09</v>
       </c>
       <c r="CN13" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.86</v>
+        <v>3.87</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CS13" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CT13" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="CU13" t="n">
         <v>1.35</v>
@@ -6112,100 +6100,100 @@
         <v>2.27</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.07</v>
+        <v>2.09</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="DH13" t="n">
-        <v>112.4</v>
+        <v>114.06</v>
       </c>
       <c r="DI13" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.4</v>
+        <v>3.13</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.4</v>
+        <v>4.94</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.1</v>
+        <v>53.44</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.6</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.3</v>
+        <v>11.38</v>
       </c>
       <c r="DQ13" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.2</v>
+        <v>7.94</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>55.8</v>
+        <v>54</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="DX13" t="n">
-        <v>15.2</v>
+        <v>15.19</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.4</v>
+        <v>5.87</v>
       </c>
       <c r="EA13" t="n">
-        <v>22</v>
+        <v>22.94</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="EC13" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="14">
@@ -6215,298 +6203,298 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="F14" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="G14" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>103.5</v>
+        <v>98.38</v>
       </c>
       <c r="I14" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="J14" t="n">
-        <v>3.83</v>
+        <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="L14" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="M14" t="n">
-        <v>57.33</v>
+        <v>56.88</v>
       </c>
       <c r="N14" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="O14" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="P14" t="n">
-        <v>9.33</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="R14" t="n">
-        <v>6.17</v>
+        <v>5.88</v>
       </c>
       <c r="S14" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T14" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>49.17</v>
+        <v>50</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="Z14" t="n">
-        <v>8</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="AA14" t="n">
-        <v>5.17</v>
+        <v>6.88</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AC14" t="n">
-        <v>13.67</v>
+        <v>12.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>98.12</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>50.25</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>43.12</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="BC14" t="n">
         <v>3</v>
       </c>
-      <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>89.75</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>49.25</v>
-      </c>
-      <c r="AO14" t="n">
+      <c r="BD14" t="n">
+        <v>14.12</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BJ14" t="n">
         <v>0.75</v>
       </c>
-      <c r="AP14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AU14" t="n">
+      <c r="BK14" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BN14" t="n">
         <v>1</v>
       </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>44.75</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BO14" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.1</v>
+        <v>3.88</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.2</v>
+        <v>4.38</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>70</v>
+        <v>62.5</v>
       </c>
       <c r="BT14" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU14" t="n">
-        <v>30</v>
+        <v>18.75</v>
       </c>
       <c r="BV14" t="n">
-        <v>10</v>
+        <v>6.25</v>
       </c>
       <c r="BW14" t="n">
-        <v>10</v>
+        <v>6.25</v>
       </c>
       <c r="BX14" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.9</v>
+        <v>3.58</v>
       </c>
       <c r="BZ14" t="n">
-        <v>4.28</v>
+        <v>3.92</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.36</v>
+        <v>3.32</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.46</v>
+        <v>3.69</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.83</v>
+        <v>3.99</v>
       </c>
       <c r="CE14" t="n">
         <v>1.46</v>
       </c>
       <c r="CF14" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CG14" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CH14" t="n">
         <v>1.29</v>
       </c>
       <c r="CI14" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="CJ14" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CP14" t="n">
         <v>2.18</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.08</v>
+        <v>4.12</v>
       </c>
       <c r="CR14" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CV14" t="n">
         <v>1.78</v>
@@ -6515,100 +6503,100 @@
         <v>2.05</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="DA14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="DC14" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="DD14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="DE14" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DF14" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="DG14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DH14" t="n">
+        <v>98.25</v>
+      </c>
+      <c r="DI14" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="DJ14" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="DK14" t="n">
+        <v>4</v>
+      </c>
+      <c r="DL14" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="DM14" t="n">
+        <v>53.56</v>
+      </c>
+      <c r="DN14" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="DO14" t="n">
         <v>1.75</v>
       </c>
-      <c r="DB14" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="DC14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="DD14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="DE14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="DF14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="DG14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="DH14" t="n">
-        <v>98</v>
-      </c>
-      <c r="DI14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="DJ14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="DK14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="DL14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="DM14" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="DN14" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="DO14" t="n">
-        <v>2</v>
-      </c>
       <c r="DP14" t="n">
-        <v>8.199999999999999</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="DQ14" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.8</v>
+        <v>6.19</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DT14" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>47.4</v>
+        <v>46.56</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.5</v>
+        <v>0.32</v>
       </c>
       <c r="DX14" t="n">
-        <v>7.3</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DY14" t="n">
-        <v>4.7</v>
+        <v>5.38</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="EA14" t="n">
-        <v>12</v>
+        <v>13.25</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="15">
@@ -6618,142 +6606,142 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="G15" t="n">
         <v>2.67</v>
       </c>
       <c r="H15" t="n">
-        <v>90.67</v>
+        <v>86.11</v>
       </c>
       <c r="I15" t="n">
-        <v>0.17</v>
+        <v>0.11</v>
       </c>
       <c r="J15" t="n">
         <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>5.83</v>
+        <v>5.89</v>
       </c>
       <c r="L15" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="M15" t="n">
-        <v>60</v>
+        <v>62.33</v>
       </c>
       <c r="N15" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="O15" t="n">
-        <v>3.17</v>
+        <v>3.22</v>
       </c>
       <c r="P15" t="n">
-        <v>7.17</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.17</v>
+        <v>2.67</v>
       </c>
       <c r="R15" t="n">
-        <v>4.17</v>
+        <v>4.89</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="T15" t="n">
-        <v>1.83</v>
+        <v>1.56</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>48.17</v>
+        <v>46.11</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="Z15" t="n">
-        <v>13.33</v>
+        <v>12.44</v>
       </c>
       <c r="AA15" t="n">
-        <v>8.17</v>
+        <v>7.67</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.17</v>
+        <v>4.78</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.17</v>
+        <v>21.33</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="AE15" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.5</v>
+        <v>0.29</v>
       </c>
       <c r="AG15" t="n">
-        <v>3.25</v>
+        <v>2.14</v>
       </c>
       <c r="AH15" t="n">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="AI15" t="n">
-        <v>94.25</v>
+        <v>106.14</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>4.25</v>
+        <v>3.14</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="AN15" t="n">
-        <v>56</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="AO15" t="n">
         <v>1</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="AQ15" t="n">
-        <v>15.5</v>
+        <v>12.43</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.25</v>
+        <v>2.57</v>
       </c>
       <c r="AS15" t="n">
-        <v>8</v>
+        <v>5.71</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6765,151 +6753,151 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>39.5</v>
+        <v>48.14</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>11.5</v>
+        <v>12.86</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.25</v>
+        <v>9</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.25</v>
+        <v>3.86</v>
       </c>
       <c r="BD15" t="n">
-        <v>20</v>
+        <v>20.29</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.25</v>
+        <v>3.14</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="BH15" t="n">
-        <v>10</v>
+        <v>9.25</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.7</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.7</v>
+        <v>0.62</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.6</v>
+        <v>4.44</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.4</v>
+        <v>4.81</v>
       </c>
       <c r="BR15" t="n">
         <v>100</v>
       </c>
       <c r="BS15" t="n">
-        <v>70</v>
+        <v>68.75</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="BU15" t="n">
-        <v>30</v>
+        <v>18.75</v>
       </c>
       <c r="BV15" t="n">
-        <v>10</v>
+        <v>6.25</v>
       </c>
       <c r="BW15" t="n">
-        <v>10</v>
+        <v>6.25</v>
       </c>
       <c r="BX15" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY15" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BZ15" t="n">
         <v>2.12</v>
       </c>
-      <c r="BZ15" t="n">
-        <v>2.2</v>
-      </c>
       <c r="CA15" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="CC15" t="n">
-        <v>4.49</v>
+        <v>3.47</v>
       </c>
       <c r="CD15" t="n">
-        <v>4.62</v>
+        <v>3.52</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.91</v>
+        <v>3.02</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="CM15" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.55</v>
+        <v>1.63</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CQ15" t="n">
-        <v>3.99</v>
+        <v>4.13</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CS15" t="n">
-        <v>3.38</v>
+        <v>3.32</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CU15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CV15" t="n">
         <v>1.74</v>
@@ -6921,13 +6909,13 @@
         <v>1.61</v>
       </c>
       <c r="CY15" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CZ15" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DB15" t="n">
         <v>1.46</v>
@@ -6936,82 +6924,82 @@
         <v>2.45</v>
       </c>
       <c r="DD15" t="n">
-        <v>4.7</v>
+        <v>4.71</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="DH15" t="n">
-        <v>92.09999999999999</v>
+        <v>94.87</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.5</v>
+        <v>3.06</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="DM15" t="n">
-        <v>58.4</v>
+        <v>64.06</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="DO15" t="n">
         <v>3</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.5</v>
+        <v>10.94</v>
       </c>
       <c r="DQ15" t="n">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="DR15" t="n">
-        <v>5.7</v>
+        <v>5.25</v>
       </c>
       <c r="DS15" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DT15" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>44.7</v>
+        <v>47</v>
       </c>
       <c r="DW15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.6</v>
+        <v>12.62</v>
       </c>
       <c r="DY15" t="n">
-        <v>7.8</v>
+        <v>8.25</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.8</v>
+        <v>4.38</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.5</v>
+        <v>20.88</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="EC15" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="16">
@@ -7021,298 +7009,298 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H16" t="n">
+        <v>110.62</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M16" t="n">
+        <v>53.88</v>
+      </c>
+      <c r="N16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P16" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="R16" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>54.12</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AE16" t="n">
         <v>3</v>
       </c>
-      <c r="H16" t="n">
-        <v>98.59999999999999</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4</v>
-      </c>
-      <c r="K16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="M16" t="n">
-        <v>52.2</v>
-      </c>
-      <c r="N16" t="n">
-        <v>1</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="P16" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="R16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>55.6</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AF16" t="n">
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.67</v>
+        <v>2.12</v>
       </c>
       <c r="AI16" t="n">
-        <v>92.67</v>
+        <v>88.88</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="AN16" t="n">
-        <v>48.67</v>
+        <v>49.25</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.5</v>
+        <v>1.12</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.5</v>
+        <v>11.62</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.33</v>
+        <v>4.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.83</v>
+        <v>0.88</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>52.17</v>
+        <v>54.25</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.5</v>
+        <v>12.88</v>
       </c>
       <c r="BB16" t="n">
-        <v>8</v>
+        <v>8.75</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.5</v>
+        <v>4.12</v>
       </c>
       <c r="BD16" t="n">
-        <v>19.83</v>
+        <v>20.38</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="BF16" t="n">
         <v>3.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="BH16" t="n">
-        <v>8.449999999999999</v>
+        <v>9</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.73</v>
+        <v>0.88</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.73</v>
+        <v>0.62</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.36</v>
+        <v>0.44</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.91</v>
+        <v>1.06</v>
       </c>
       <c r="BO16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>93.75</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>50</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>31.25</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="BY16" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BZ16" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="CA16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="CB16" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="CC16" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CF16" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="CG16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CH16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="CI16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CJ16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CK16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CL16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CM16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CN16" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CO16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CP16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="CQ16" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="CR16" t="n">
         <v>1.45</v>
       </c>
-      <c r="BP16" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>90.91</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>54.55</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>45.45</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>36.36</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>45.45</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BZ16" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="CA16" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="CB16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="CC16" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="CD16" t="n">
-        <v>3</v>
-      </c>
-      <c r="CE16" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="CF16" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="CG16" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="CH16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="CI16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CJ16" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="CK16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="CL16" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="CM16" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="CN16" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="CO16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="CP16" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="CQ16" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>1.44</v>
-      </c>
       <c r="CS16" t="n">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="CT16" t="n">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CV16" t="n">
         <v>1.87</v>
@@ -7321,100 +7309,100 @@
         <v>1.94</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DD16" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="DH16" t="n">
-        <v>95.37</v>
+        <v>99.75</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>4</v>
+        <v>3.81</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.73</v>
+        <v>4.81</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
       <c r="DM16" t="n">
-        <v>50.27</v>
+        <v>51.56</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="DP16" t="n">
-        <v>9.27</v>
+        <v>10.31</v>
       </c>
       <c r="DQ16" t="n">
-        <v>1.18</v>
+        <v>1.75</v>
       </c>
       <c r="DR16" t="n">
-        <v>3.36</v>
+        <v>4.94</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>53.73</v>
+        <v>54.18</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
       <c r="DX16" t="n">
-        <v>10.73</v>
+        <v>12.5</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.18</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DZ16" t="n">
-        <v>3.55</v>
+        <v>4.37</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.54</v>
+        <v>19.69</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="EC16" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="17">
@@ -7424,223 +7412,223 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="G17" t="n">
-        <v>4.4</v>
+        <v>3.38</v>
       </c>
       <c r="H17" t="n">
-        <v>96.2</v>
+        <v>89.12</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="K17" t="n">
-        <v>6.6</v>
+        <v>5.25</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="M17" t="n">
-        <v>66.8</v>
+        <v>54.25</v>
       </c>
       <c r="N17" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="O17" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="P17" t="n">
-        <v>8</v>
+        <v>10.62</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R17" t="n">
-        <v>5.2</v>
+        <v>7.75</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>47.6</v>
+        <v>44.38</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="Z17" t="n">
-        <v>11.4</v>
+        <v>10.75</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.2</v>
+        <v>6.12</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.2</v>
+        <v>4.62</v>
       </c>
       <c r="AC17" t="n">
-        <v>14.4</v>
+        <v>16.88</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.2</v>
+        <v>1.88</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>96.40000000000001</v>
+        <v>104.38</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>4.6</v>
+        <v>3.88</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.8</v>
+        <v>3.88</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="AN17" t="n">
-        <v>56.6</v>
+        <v>65.75</v>
       </c>
       <c r="AO17" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AQ17" t="n">
-        <v>6.8</v>
+        <v>8.25</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.2</v>
+        <v>2.25</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.2</v>
+        <v>5.25</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AU17" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>50.8</v>
+        <v>50</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.6</v>
+        <v>0.38</v>
       </c>
       <c r="BA17" t="n">
-        <v>12</v>
+        <v>11.62</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.6</v>
+        <v>8.25</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.4</v>
+        <v>3.38</v>
       </c>
       <c r="BD17" t="n">
-        <v>11.2</v>
+        <v>13.12</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.6</v>
+        <v>2.31</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.4</v>
+        <v>9.25</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.6</v>
+        <v>2.31</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.7</v>
+        <v>0.62</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.6</v>
+        <v>0.44</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BM17" t="n">
         <v>0.5</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.3</v>
+        <v>1.06</v>
       </c>
       <c r="BP17" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.4</v>
+        <v>4.75</v>
       </c>
       <c r="BR17" t="n">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="BS17" t="n">
-        <v>80</v>
+        <v>68.75</v>
       </c>
       <c r="BT17" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU17" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="BV17" t="n">
-        <v>10</v>
+        <v>6.25</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
@@ -7649,70 +7637,74 @@
         <v>50</v>
       </c>
       <c r="BY17" t="n">
-        <v>2.54</v>
+        <v>3.01</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2.97</v>
+        <v>3.41</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.08</v>
+        <v>3.13</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.08</v>
+        <v>3.19</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.46</v>
+        <v>3.34</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.78</v>
+        <v>3.62</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.09</v>
+        <v>2.23</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="CI17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="CK17" t="n">
         <v>1.55</v>
       </c>
-      <c r="CJ17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="CK17" t="n">
-        <v>1.5</v>
-      </c>
       <c r="CL17" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="CM17" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.19</v>
+        <v>4.16</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CS17" t="inlineStr"/>
+        <v>1.52</v>
+      </c>
+      <c r="CS17" t="n">
+        <v>3.24</v>
+      </c>
       <c r="CT17" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="CU17" t="inlineStr"/>
+        <v>2.52</v>
+      </c>
+      <c r="CU17" t="n">
+        <v>1.34</v>
+      </c>
       <c r="CV17" t="n">
         <v>1.77</v>
       </c>
@@ -7720,100 +7712,100 @@
         <v>2.05</v>
       </c>
       <c r="CX17" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="DA17" t="n">
         <v>1.67</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.55</v>
+        <v>2.44</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.99</v>
+        <v>4.7</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="DH17" t="n">
-        <v>96.3</v>
+        <v>96.75</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.2</v>
+        <v>4.56</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="DM17" t="n">
-        <v>61.7</v>
+        <v>60</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.4</v>
+        <v>2.13</v>
       </c>
       <c r="DP17" t="n">
-        <v>7.4</v>
+        <v>9.43</v>
       </c>
       <c r="DQ17" t="n">
-        <v>1.4</v>
+        <v>1.94</v>
       </c>
       <c r="DR17" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>49.2</v>
+        <v>47.19</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.7</v>
+        <v>11.18</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.4</v>
+        <v>7.18</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="EA17" t="n">
-        <v>12.8</v>
+        <v>15</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="EC17" t="n">
-        <v>3.4</v>
+        <v>3.12</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
@@ -1367,13 +1367,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>0.22</v>
@@ -1457,53 +1457,53 @@
         <v>3.11</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.86</v>
+        <v>1.38</v>
       </c>
       <c r="AH2" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AI2" t="n">
-        <v>80.14</v>
+        <v>78.75</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="AL2" t="n">
-        <v>4.71</v>
+        <v>4.12</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AN2" t="n">
-        <v>44.14</v>
+        <v>42.25</v>
       </c>
       <c r="AO2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AU2" t="n">
         <v>1</v>
       </c>
-      <c r="AP2" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>5.43</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AV2" t="n">
         <v>0</v>
       </c>
@@ -1514,82 +1514,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>51.71</v>
+        <v>49.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="BA2" t="n">
-        <v>10.71</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.43</v>
+        <v>5.75</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.29</v>
+        <v>3.88</v>
       </c>
       <c r="BD2" t="n">
-        <v>10.43</v>
+        <v>9</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.71</v>
+        <v>2.25</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.75</v>
+        <v>9.94</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.44</v>
+        <v>4.59</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.31</v>
+        <v>5.35</v>
       </c>
       <c r="BR2" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BT2" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU2" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV2" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX2" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BY2" t="n">
         <v>2.77</v>
@@ -1598,55 +1598,55 @@
         <v>2.87</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="CH2" t="n">
         <v>1.26</v>
       </c>
       <c r="CI2" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CL2" t="n">
         <v>2.16</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CN2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.41</v>
+        <v>2.38</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.59</v>
+        <v>4.51</v>
       </c>
       <c r="CR2" t="n">
         <v>1.51</v>
@@ -1667,100 +1667,100 @@
         <v>2.16</v>
       </c>
       <c r="CX2" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CY2" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.7</v>
+        <v>4.64</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.69</v>
+        <v>2.53</v>
       </c>
       <c r="DH2" t="n">
-        <v>91.19</v>
+        <v>89.88</v>
       </c>
       <c r="DI2" t="n">
         <v>0</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.75</v>
+        <v>3.06</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.75</v>
+        <v>4.47</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DM2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="DP2" t="n">
-        <v>7.56</v>
+        <v>7.06</v>
       </c>
       <c r="DQ2" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.81</v>
+        <v>5.41</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>53.75</v>
+        <v>52.59</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DX2" t="n">
-        <v>10.69</v>
+        <v>10.18</v>
       </c>
       <c r="DY2" t="n">
-        <v>6.25</v>
+        <v>5.94</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.44</v>
+        <v>4.24</v>
       </c>
       <c r="EA2" t="n">
-        <v>11.69</v>
+        <v>10.94</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="3">
@@ -1770,13 +1770,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>0.11</v>
@@ -1863,49 +1863,49 @@
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AI3" t="n">
-        <v>101.71</v>
+        <v>101.12</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="AL3" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>51.14</v>
+        <v>51.12</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.43</v>
+        <v>0.62</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.43</v>
+        <v>7.62</v>
       </c>
       <c r="AR3" t="n">
         <v>1</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.57</v>
+        <v>8.25</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
@@ -1917,82 +1917,82 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>48.57</v>
+        <v>49.25</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.57</v>
+        <v>7.62</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.14</v>
+        <v>5.38</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="BD3" t="n">
-        <v>13.86</v>
+        <v>14.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.31</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.94</v>
+        <v>3.82</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.88</v>
+        <v>3.82</v>
       </c>
       <c r="BR3" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS3" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT3" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU3" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV3" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BY3" t="n">
         <v>2.94</v>
@@ -2007,37 +2007,37 @@
         <v>3.26</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.87</v>
+        <v>3.8</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CF3" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.87</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL3" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CN3" t="n">
         <v>1.53</v>
@@ -2046,10 +2046,10 @@
         <v>1.33</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CQ3" t="n">
-        <v>4.03</v>
+        <v>4.05</v>
       </c>
       <c r="CR3" t="n">
         <v>1.51</v>
@@ -2058,10 +2058,10 @@
         <v>3.24</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CV3" t="n">
         <v>1.74</v>
@@ -2070,67 +2070,67 @@
         <v>2.09</v>
       </c>
       <c r="CX3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CY3" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.66</v>
+        <v>4.62</v>
       </c>
       <c r="DE3" t="n">
         <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DH3" t="n">
-        <v>93.44</v>
+        <v>93.64</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.07</v>
+        <v>3.12</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM3" t="n">
-        <v>46.81</v>
+        <v>47.05</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="DP3" t="n">
-        <v>8.07</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DQ3" t="n">
         <v>0.88</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.31</v>
+        <v>7.65</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2142,28 +2142,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>49.81</v>
+        <v>50.06</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="DX3" t="n">
-        <v>9.380000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.56</v>
+        <v>5.65</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.81</v>
+        <v>3.65</v>
       </c>
       <c r="EA3" t="n">
-        <v>15.81</v>
+        <v>16</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="4">
@@ -2173,13 +2173,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2263,139 +2263,139 @@
         <v>3</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>88.22</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>53</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>38.56</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>8.18</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BL4" t="n">
         <v>1.12</v>
       </c>
-      <c r="AH4" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>88.88</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>51.62</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>9.25</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>36.62</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>11.12</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>16.75</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1.19</v>
-      </c>
       <c r="BM4" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="BQ4" t="n">
         <v>4.06</v>
       </c>
       <c r="BR4" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS4" t="n">
-        <v>75</v>
+        <v>70.59</v>
       </c>
       <c r="BT4" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU4" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV4" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW4" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX4" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY4" t="n">
         <v>3.18</v>
@@ -2404,25 +2404,25 @@
         <v>3.49</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CC4" t="n">
-        <v>4.03</v>
+        <v>3.85</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.29</v>
+        <v>4.12</v>
       </c>
       <c r="CE4" t="n">
         <v>1.47</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CH4" t="n">
         <v>1.29</v>
@@ -2431,37 +2431,37 @@
         <v>1.71</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CQ4" t="n">
         <v>4.33</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CS4" t="n">
         <v>3.18</v>
       </c>
       <c r="CT4" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CU4" t="n">
         <v>1.35</v>
@@ -2473,100 +2473,100 @@
         <v>2.14</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.09</v>
+        <v>2.11</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.45</v>
+        <v>4.49</v>
       </c>
       <c r="DE4" t="n">
         <v>0.12</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="DH4" t="n">
-        <v>86.63</v>
+        <v>86.41</v>
       </c>
       <c r="DI4" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.44</v>
+        <v>3.47</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DM4" t="n">
-        <v>49.87</v>
+        <v>50.7</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="DO4" t="n">
         <v>1.82</v>
       </c>
       <c r="DP4" t="n">
-        <v>7.63</v>
+        <v>7.12</v>
       </c>
       <c r="DQ4" t="n">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.68</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>38</v>
+        <v>38.95</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.869999999999999</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="DY4" t="n">
-        <v>5.44</v>
+        <v>5.35</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.44</v>
+        <v>4.18</v>
       </c>
       <c r="EA4" t="n">
-        <v>15.57</v>
+        <v>14.59</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="5">
@@ -2576,94 +2576,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F5" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="G5" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="H5" t="n">
-        <v>87.38</v>
+        <v>86.89</v>
       </c>
       <c r="I5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="L5" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M5" t="n">
-        <v>48.62</v>
+        <v>50</v>
       </c>
       <c r="N5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="P5" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R5" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>41.11</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>17.11</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.25</v>
       </c>
-      <c r="O5" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="P5" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R5" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>19.38</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AE5" t="n">
-        <v>3.38</v>
+        <v>3.44</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -2747,70 +2747,70 @@
         <v>4.25</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="BH5" t="n">
         <v>8.880000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="BO5" t="n">
         <v>1</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.12</v>
+        <v>4.18</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.69</v>
+        <v>4.65</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BT5" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BU5" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV5" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BY5" t="n">
-        <v>3.09</v>
+        <v>3.02</v>
       </c>
       <c r="BZ5" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CC5" t="n">
         <v>4.74</v>
@@ -2825,7 +2825,7 @@
         <v>3.38</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CH5" t="n">
         <v>1.26</v>
@@ -2834,19 +2834,19 @@
         <v>1.66</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CO5" t="n">
         <v>1.47</v>
@@ -2855,7 +2855,7 @@
         <v>2.46</v>
       </c>
       <c r="CQ5" t="n">
-        <v>4.65</v>
+        <v>4.63</v>
       </c>
       <c r="CR5" t="n">
         <v>1.53</v>
@@ -2876,67 +2876,67 @@
         <v>2.32</v>
       </c>
       <c r="CX5" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="CY5" t="n">
         <v>2.22</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DB5" t="n">
         <v>1.49</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="DD5" t="n">
-        <v>4.97</v>
+        <v>4.99</v>
       </c>
       <c r="DE5" t="n">
         <v>0.06</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.68</v>
+        <v>2.59</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="DH5" t="n">
-        <v>87.88</v>
+        <v>87.59</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ5" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.06</v>
+        <v>3.18</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM5" t="n">
-        <v>49.18</v>
+        <v>49.88</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="DP5" t="n">
-        <v>12.69</v>
+        <v>11.89</v>
       </c>
       <c r="DQ5" t="n">
-        <v>3.44</v>
+        <v>3.17</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.63</v>
+        <v>6.18</v>
       </c>
       <c r="DS5" t="n">
         <v>0.06</v>
@@ -2948,22 +2948,22 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>42.75</v>
+        <v>42.94</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.44</v>
+        <v>11.12</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.94</v>
+        <v>7.53</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.5</v>
+        <v>3.59</v>
       </c>
       <c r="EA5" t="n">
-        <v>20.5</v>
+        <v>19.23</v>
       </c>
       <c r="EB5" t="n">
         <v>1.32</v>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
@@ -2991,49 +2991,49 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="G6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="H6" t="n">
-        <v>104.14</v>
+        <v>102.25</v>
       </c>
       <c r="I6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J6" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="K6" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>55.43</v>
+        <v>54.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O6" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="P6" t="n">
-        <v>10.29</v>
+        <v>9.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="R6" t="n">
-        <v>7.57</v>
+        <v>7.5</v>
       </c>
       <c r="S6" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="T6" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3045,28 +3045,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>49.57</v>
+        <v>49.12</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.43</v>
+        <v>9.25</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.71</v>
+        <v>6.38</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.86</v>
+        <v>20.62</v>
       </c>
       <c r="AD6" t="n">
         <v>1.19</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3150,67 +3150,67 @@
         <v>3.11</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.31</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.88</v>
+        <v>0.82</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.31</v>
+        <v>4.18</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BT6" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BU6" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV6" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.29</v>
+        <v>3.16</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CB6" t="n">
         <v>3.2</v>
@@ -3225,7 +3225,7 @@
         <v>1.48</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CG6" t="n">
         <v>2.45</v>
@@ -3237,37 +3237,37 @@
         <v>1.72</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CN6" t="n">
         <v>1.67</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CQ6" t="n">
         <v>4.45</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CS6" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CT6" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="CU6" t="n">
         <v>1.34</v>
@@ -3279,67 +3279,67 @@
         <v>2.06</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DB6" t="n">
         <v>1.44</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.56</v>
+        <v>4.54</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="DG6" t="n">
         <v>1.94</v>
       </c>
-      <c r="DG6" t="n">
-        <v>2</v>
-      </c>
       <c r="DH6" t="n">
-        <v>102.69</v>
+        <v>101.88</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.93</v>
+        <v>2.82</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DM6" t="n">
-        <v>53.38</v>
+        <v>53.06</v>
       </c>
       <c r="DN6" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="DP6" t="n">
-        <v>10.13</v>
+        <v>9.65</v>
       </c>
       <c r="DQ6" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.93</v>
+        <v>6.94</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3351,28 +3351,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.63</v>
+        <v>49.41</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>9.81</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.63</v>
+        <v>6.48</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.19</v>
+        <v>3.24</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.94</v>
+        <v>18.53</v>
       </c>
       <c r="EB6" t="n">
         <v>1.23</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.93</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="7">
@@ -3785,61 +3785,61 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
       </c>
       <c r="E8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F8" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G8" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>106.86</v>
+        <v>105.38</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="K8" t="n">
-        <v>5.57</v>
+        <v>5.12</v>
       </c>
       <c r="L8" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M8" t="n">
-        <v>67.70999999999999</v>
+        <v>66.12</v>
       </c>
       <c r="N8" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O8" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="P8" t="n">
-        <v>5.86</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.43</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>5.57</v>
+        <v>4.75</v>
       </c>
       <c r="S8" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="T8" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3851,28 +3851,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>56.57</v>
+        <v>56</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z8" t="n">
-        <v>14.71</v>
+        <v>14.38</v>
       </c>
       <c r="AA8" t="n">
-        <v>10.29</v>
+        <v>10</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
       <c r="AC8" t="n">
-        <v>16.14</v>
+        <v>14</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AF8" t="n">
         <v>0.11</v>
@@ -3956,46 +3956,46 @@
         <v>2.44</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.619999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="BI8" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.69</v>
+        <v>3.59</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.44</v>
+        <v>5.29</v>
       </c>
       <c r="BR8" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BT8" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -4007,19 +4007,19 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.35</v>
+        <v>2.47</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CC8" t="n">
         <v>3.01</v>
@@ -4031,7 +4031,7 @@
         <v>1.48</v>
       </c>
       <c r="CF8" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CG8" t="n">
         <v>2.44</v>
@@ -4040,19 +4040,19 @@
         <v>1.28</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.96</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CN8" t="n">
         <v>1.65</v>
@@ -4064,7 +4064,7 @@
         <v>2.28</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="CR8" t="n">
         <v>1.49</v>
@@ -4103,49 +4103,49 @@
         <v>2.37</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.5</v>
+        <v>4.49</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="DH8" t="n">
-        <v>104.63</v>
+        <v>104.06</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="DK8" t="n">
-        <v>5.06</v>
+        <v>4.88</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DM8" t="n">
-        <v>60.94</v>
+        <v>60.59</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="DP8" t="n">
-        <v>7.06</v>
+        <v>6.59</v>
       </c>
       <c r="DQ8" t="n">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.56</v>
+        <v>6.12</v>
       </c>
       <c r="DS8" t="n">
         <v>0.06</v>
@@ -4157,28 +4157,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>54</v>
+        <v>53.88</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.88</v>
+        <v>11.89</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.380000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
       <c r="EA8" t="n">
-        <v>14.94</v>
+        <v>14</v>
       </c>
       <c r="EB8" t="n">
         <v>1.44</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="9">
@@ -4188,13 +4188,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>0.25</v>
@@ -4278,139 +4278,139 @@
         <v>2.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="AI9" t="n">
-        <v>99.75</v>
+        <v>100.67</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="AL9" t="n">
-        <v>6.38</v>
+        <v>6.33</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AN9" t="n">
-        <v>50.75</v>
+        <v>52.44</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AP9" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AQ9" t="n">
-        <v>11.25</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.75</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.75</v>
+        <v>5.89</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>51.88</v>
+        <v>51.78</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA9" t="n">
-        <v>11.38</v>
+        <v>10.89</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.38</v>
+        <v>6.89</v>
       </c>
       <c r="BC9" t="n">
         <v>4</v>
       </c>
       <c r="BD9" t="n">
-        <v>16.88</v>
+        <v>14.89</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.06</v>
+        <v>9.18</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.62</v>
+        <v>4.71</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="BR9" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS9" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT9" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU9" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV9" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW9" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX9" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY9" t="n">
         <v>2.25</v>
@@ -4425,16 +4425,16 @@
         <v>3.3</v>
       </c>
       <c r="CC9" t="n">
-        <v>3.22</v>
+        <v>3.12</v>
       </c>
       <c r="CD9" t="n">
-        <v>3.24</v>
+        <v>3.15</v>
       </c>
       <c r="CE9" t="n">
         <v>1.45</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="CG9" t="n">
         <v>2.53</v>
@@ -4443,31 +4443,31 @@
         <v>1.3</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="CK9" t="n">
         <v>1.63</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CM9" t="n">
         <v>2.13</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CO9" t="n">
         <v>1.37</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.98</v>
+        <v>3.96</v>
       </c>
       <c r="CR9" t="n">
         <v>1.46</v>
@@ -4494,7 +4494,7 @@
         <v>2.09</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="DA9" t="n">
         <v>1.7</v>
@@ -4512,76 +4512,76 @@
         <v>0.18</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="DH9" t="n">
-        <v>96.68000000000001</v>
+        <v>97.34999999999999</v>
       </c>
       <c r="DI9" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.37</v>
+        <v>3.35</v>
       </c>
       <c r="DK9" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DM9" t="n">
-        <v>51.5</v>
+        <v>52.35</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="DP9" t="n">
-        <v>10.88</v>
+        <v>10.18</v>
       </c>
       <c r="DQ9" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.68</v>
+        <v>7.17</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>53.19</v>
+        <v>53.06</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.44</v>
+        <v>12.12</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.88</v>
+        <v>7.59</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.56</v>
+        <v>4.53</v>
       </c>
       <c r="EA9" t="n">
-        <v>17.75</v>
+        <v>16.65</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="10">
@@ -4994,94 +4994,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F11" t="n">
-        <v>1.71</v>
+        <v>2.12</v>
       </c>
       <c r="G11" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="H11" t="n">
-        <v>86.29000000000001</v>
+        <v>87.88</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="K11" t="n">
-        <v>4.71</v>
+        <v>4.5</v>
       </c>
       <c r="L11" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="M11" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N11" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="P11" t="n">
-        <v>11.14</v>
+        <v>12</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="R11" t="n">
-        <v>7.29</v>
+        <v>7.88</v>
       </c>
       <c r="S11" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="T11" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="U11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V11" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>53.57</v>
+        <v>52.75</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>11.86</v>
+        <v>11.62</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.71</v>
+        <v>7.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.14</v>
+        <v>3.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.29</v>
+        <v>20.75</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.86</v>
+        <v>2.38</v>
       </c>
       <c r="AF11" t="n">
         <v>0.44</v>
@@ -5165,70 +5165,70 @@
         <v>2.22</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.31</v>
+        <v>8.41</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.56</v>
+        <v>2.41</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.38</v>
+        <v>3.47</v>
       </c>
       <c r="BQ11" t="n">
         <v>4.88</v>
       </c>
       <c r="BR11" t="n">
-        <v>93.75</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>75</v>
+        <v>70.59</v>
       </c>
       <c r="BT11" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BU11" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV11" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW11" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX11" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CC11" t="n">
         <v>2.7</v>
@@ -5237,19 +5237,19 @@
         <v>2.89</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CF11" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.94</v>
@@ -5267,22 +5267,22 @@
         <v>1.72</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.21</v>
+        <v>2.24</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.07</v>
+        <v>4.23</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="CS11" t="n">
         <v>3.24</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="CU11" t="n">
         <v>1.34</v>
@@ -5306,88 +5306,88 @@
         <v>1.71</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.22</v>
+        <v>4.31</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.37</v>
+        <v>1.59</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="DH11" t="n">
-        <v>95.25</v>
+        <v>95.47</v>
       </c>
       <c r="DI11" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DM11" t="n">
-        <v>53.13</v>
+        <v>53.41</v>
       </c>
       <c r="DN11" t="n">
         <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="DP11" t="n">
-        <v>9.81</v>
+        <v>10.3</v>
       </c>
       <c r="DQ11" t="n">
         <v>2.88</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.81</v>
+        <v>8.06</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>51.12</v>
+        <v>50.88</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.25</v>
+        <v>11.18</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.19</v>
+        <v>7.3</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.06</v>
+        <v>3.88</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.25</v>
+        <v>19.94</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="12">
@@ -5397,10 +5397,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
@@ -5409,82 +5409,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="G12" t="n">
-        <v>2.71</v>
+        <v>3.12</v>
       </c>
       <c r="H12" t="n">
-        <v>112.29</v>
+        <v>109.5</v>
       </c>
       <c r="I12" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="J12" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="K12" t="n">
-        <v>5.86</v>
+        <v>6.75</v>
       </c>
       <c r="L12" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M12" t="n">
-        <v>59.57</v>
+        <v>64.38</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="O12" t="n">
-        <v>3.14</v>
+        <v>3.62</v>
       </c>
       <c r="P12" t="n">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.57</v>
+        <v>2.12</v>
       </c>
       <c r="R12" t="n">
-        <v>5.57</v>
+        <v>4.75</v>
       </c>
       <c r="S12" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="T12" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="U12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="V12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>58.14</v>
+        <v>59.12</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="Z12" t="n">
-        <v>15.14</v>
+        <v>14.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.710000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.43</v>
+        <v>5.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AF12" t="n">
         <v>0.11</v>
@@ -5568,70 +5568,70 @@
         <v>2.22</v>
       </c>
       <c r="BG12" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.56</v>
+        <v>8.82</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>81.25</v>
+        <v>76.47</v>
       </c>
       <c r="BT12" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU12" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV12" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX12" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="BZ12" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="CC12" t="n">
         <v>1.98</v>
@@ -5640,43 +5640,43 @@
         <v>2.07</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.96</v>
+        <v>0.99</v>
       </c>
       <c r="CF12" t="n">
-        <v>1.98</v>
+        <v>2.03</v>
       </c>
       <c r="CG12" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="CH12" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="CI12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CJ12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CK12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="CL12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CM12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CN12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CO12" t="n">
         <v>0.92</v>
-      </c>
-      <c r="CI12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="CJ12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="CK12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="CL12" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="CM12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CN12" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="CO12" t="n">
-        <v>0.9</v>
       </c>
       <c r="CP12" t="n">
         <v>2.01</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.43</v>
+        <v>2.48</v>
       </c>
       <c r="CR12" t="n">
         <v>1.43</v>
@@ -5703,7 +5703,7 @@
         <v>1.95</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="DA12" t="n">
         <v>1.82</v>
@@ -5712,85 +5712,85 @@
         <v>1.34</v>
       </c>
       <c r="DC12" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="DE12" t="n">
         <v>0.06</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.69</v>
+        <v>1.77</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.93</v>
+        <v>3.11</v>
       </c>
       <c r="DH12" t="n">
-        <v>107.69</v>
+        <v>106.65</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="DK12" t="n">
-        <v>5.56</v>
+        <v>6</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM12" t="n">
-        <v>55.75</v>
+        <v>58.24</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="DP12" t="n">
-        <v>10.68</v>
+        <v>10</v>
       </c>
       <c r="DQ12" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.75</v>
+        <v>5.35</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>53.38</v>
+        <v>54.12</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.69</v>
+        <v>12.65</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.75</v>
+        <v>7.65</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.94</v>
+        <v>5</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.44</v>
+        <v>17.29</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="13">
@@ -5800,13 +5800,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
         <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
         <v>0.33</v>
@@ -5890,139 +5890,139 @@
         <v>3</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AI13" t="n">
-        <v>106</v>
+        <v>103.25</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.71</v>
+        <v>4.5</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN13" t="n">
-        <v>45.14</v>
+        <v>47.12</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AQ13" t="n">
-        <v>10.86</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.57</v>
+        <v>2.12</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.43</v>
+        <v>6.38</v>
       </c>
       <c r="AT13" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>53.25</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BK13" t="n">
         <v>0.71</v>
       </c>
-      <c r="AU13" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>54</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>16</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>10.86</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>25.71</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.75</v>
-      </c>
       <c r="BL13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.62</v>
+        <v>0.71</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.94</v>
+        <v>3.82</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BU13" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV13" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BY13" t="n">
         <v>1.59</v>
@@ -6031,25 +6031,25 @@
         <v>1.63</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.64</v>
+        <v>3.61</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.82</v>
+        <v>3.79</v>
       </c>
       <c r="CC13" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="CD13" t="n">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="CE13" t="n">
         <v>1.44</v>
       </c>
       <c r="CF13" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CH13" t="n">
         <v>1.32</v>
@@ -6064,7 +6064,7 @@
         <v>1.66</v>
       </c>
       <c r="CL13" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CM13" t="n">
         <v>2.09</v>
@@ -6076,10 +6076,10 @@
         <v>1.36</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="CR13" t="n">
         <v>1.44</v>
@@ -6112,88 +6112,88 @@
         <v>1.71</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="DC13" t="n">
         <v>2.2</v>
       </c>
       <c r="DD13" t="n">
-        <v>4</v>
+        <v>4.02</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF13" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="DH13" t="n">
-        <v>114.06</v>
+        <v>112.29</v>
       </c>
       <c r="DI13" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.94</v>
+        <v>4.82</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM13" t="n">
-        <v>53.44</v>
+        <v>53.88</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="DP13" t="n">
-        <v>11.38</v>
+        <v>10.65</v>
       </c>
       <c r="DQ13" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.94</v>
+        <v>7.41</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>54</v>
+        <v>53.65</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DX13" t="n">
-        <v>15.19</v>
+        <v>14.65</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.31</v>
+        <v>8.94</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.87</v>
+        <v>5.71</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.94</v>
+        <v>21.53</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.75</v>
+        <v>2.82</v>
       </c>
     </row>
     <row r="14">
@@ -6203,94 +6203,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F14" t="n">
-        <v>2.12</v>
+        <v>2.56</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="H14" t="n">
-        <v>98.38</v>
+        <v>97.78</v>
       </c>
       <c r="I14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5</v>
+        <v>3.89</v>
       </c>
       <c r="K14" t="n">
-        <v>4.25</v>
+        <v>4.11</v>
       </c>
       <c r="L14" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="M14" t="n">
-        <v>56.88</v>
+        <v>56.44</v>
       </c>
       <c r="N14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="O14" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="P14" t="n">
-        <v>9.380000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.25</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>5.88</v>
+        <v>5.11</v>
       </c>
       <c r="S14" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="T14" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="U14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>50</v>
+        <v>48.78</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="Z14" t="n">
-        <v>9.880000000000001</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.88</v>
+        <v>6.11</v>
       </c>
       <c r="AB14" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AC14" t="n">
-        <v>12.38</v>
+        <v>10.89</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.88</v>
+        <v>3.22</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -6374,70 +6374,70 @@
         <v>2.88</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.25</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BN14" t="n">
         <v>1</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="BP14" t="n">
         <v>3.88</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BU14" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV14" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW14" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX14" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BY14" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="BZ14" t="n">
-        <v>3.92</v>
+        <v>3.79</v>
       </c>
       <c r="CA14" t="n">
         <v>3.25</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CC14" t="n">
         <v>3.69</v>
@@ -6446,7 +6446,7 @@
         <v>3.99</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CF14" t="n">
         <v>3.1</v>
@@ -6461,7 +6461,7 @@
         <v>1.76</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CK14" t="n">
         <v>1.63</v>
@@ -6482,7 +6482,7 @@
         <v>2.18</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="CR14" t="n">
         <v>1.48</v>
@@ -6491,7 +6491,7 @@
         <v>3.29</v>
       </c>
       <c r="CT14" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CU14" t="n">
         <v>1.33</v>
@@ -6503,16 +6503,16 @@
         <v>2.05</v>
       </c>
       <c r="CX14" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CY14" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="DA14" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB14" t="n">
         <v>1.41</v>
@@ -6521,49 +6521,49 @@
         <v>2.31</v>
       </c>
       <c r="DD14" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="DE14" t="n">
         <v>0.12</v>
       </c>
       <c r="DF14" t="n">
-        <v>2.31</v>
+        <v>2.53</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="DH14" t="n">
-        <v>98.25</v>
+        <v>97.94</v>
       </c>
       <c r="DI14" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.44</v>
+        <v>3.65</v>
       </c>
       <c r="DK14" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DM14" t="n">
-        <v>53.56</v>
+        <v>53.53</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DP14" t="n">
-        <v>9.130000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DQ14" t="n">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="DR14" t="n">
-        <v>6.19</v>
+        <v>5.76</v>
       </c>
       <c r="DS14" t="n">
         <v>0.06</v>
@@ -6575,28 +6575,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>46.56</v>
+        <v>46.12</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="DX14" t="n">
-        <v>8.380000000000001</v>
+        <v>7.94</v>
       </c>
       <c r="DY14" t="n">
-        <v>5.38</v>
+        <v>5.06</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="EA14" t="n">
-        <v>13.25</v>
+        <v>12.41</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="15">
@@ -6606,13 +6606,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="n">
         <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6696,52 +6696,52 @@
         <v>2.67</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AI15" t="n">
-        <v>106.14</v>
+        <v>106.75</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="AL15" t="n">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AN15" t="n">
-        <v>66.29000000000001</v>
+        <v>67.38</v>
       </c>
       <c r="AO15" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.71</v>
+        <v>3</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12.43</v>
+        <v>13.12</v>
       </c>
       <c r="AR15" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.71</v>
+        <v>5.88</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6753,82 +6753,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>48.14</v>
+        <v>48.75</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>12.86</v>
+        <v>12.75</v>
       </c>
       <c r="BB15" t="n">
         <v>9</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="BD15" t="n">
-        <v>20.29</v>
+        <v>21</v>
       </c>
       <c r="BE15" t="n">
         <v>1.56</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.25</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.44</v>
+        <v>4.47</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="BR15" t="n">
-        <v>100</v>
+        <v>94.12</v>
       </c>
       <c r="BS15" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BU15" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BV15" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW15" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX15" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BY15" t="n">
         <v>2.13</v>
@@ -6837,22 +6837,22 @@
         <v>2.12</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CC15" t="n">
-        <v>3.47</v>
+        <v>3.34</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.52</v>
+        <v>3.42</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="CG15" t="n">
         <v>2.3</v>
@@ -6867,34 +6867,34 @@
         <v>1.88</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CN15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP15" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CQ15" t="n">
-        <v>4.13</v>
+        <v>4.29</v>
       </c>
       <c r="CR15" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CS15" t="n">
         <v>3.32</v>
       </c>
       <c r="CT15" t="n">
-        <v>2.55</v>
+        <v>2.51</v>
       </c>
       <c r="CU15" t="n">
         <v>1.33</v>
@@ -6918,25 +6918,25 @@
         <v>1.77</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="DC15" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="DD15" t="n">
-        <v>4.71</v>
+        <v>4.78</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DH15" t="n">
-        <v>94.87</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="DI15" t="n">
         <v>0.06</v>
@@ -6945,28 +6945,28 @@
         <v>3.06</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.5</v>
+        <v>5.59</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DM15" t="n">
-        <v>64.06</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="DO15" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="DP15" t="n">
-        <v>10.94</v>
+        <v>11.35</v>
       </c>
       <c r="DQ15" t="n">
-        <v>2.63</v>
+        <v>2.71</v>
       </c>
       <c r="DR15" t="n">
-        <v>5.25</v>
+        <v>5.36</v>
       </c>
       <c r="DS15" t="n">
         <v>0.06</v>
@@ -6978,22 +6978,22 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47</v>
+        <v>47.35</v>
       </c>
       <c r="DW15" t="n">
         <v>0.12</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.62</v>
+        <v>12.59</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.25</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.38</v>
+        <v>4.3</v>
       </c>
       <c r="EA15" t="n">
-        <v>20.88</v>
+        <v>21.17</v>
       </c>
       <c r="EB15" t="n">
         <v>1.57</v>
@@ -7009,13 +7009,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
         <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
         <v>0.25</v>
@@ -7102,109 +7102,109 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.12</v>
+        <v>2.33</v>
       </c>
       <c r="AI16" t="n">
-        <v>88.88</v>
+        <v>91</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>4.12</v>
+        <v>3.89</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.75</v>
+        <v>4.89</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AN16" t="n">
-        <v>49.25</v>
+        <v>52.22</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11.62</v>
+        <v>10.22</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AS16" t="n">
-        <v>4.5</v>
+        <v>3.89</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>54.25</v>
+        <v>55</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BA16" t="n">
-        <v>12.88</v>
+        <v>12.11</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.75</v>
+        <v>8</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="BD16" t="n">
-        <v>20.38</v>
+        <v>18</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.5</v>
+        <v>3.33</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="BH16" t="n">
         <v>9</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="BJ16" t="n">
         <v>0.88</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BN16" t="n">
         <v>1.06</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BP16" t="n">
         <v>4</v>
@@ -7213,25 +7213,25 @@
         <v>5</v>
       </c>
       <c r="BR16" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS16" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT16" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU16" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV16" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY16" t="n">
         <v>2.2</v>
@@ -7240,61 +7240,61 @@
         <v>2.39</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="CG16" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="CM16" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="CP16" t="n">
         <v>2.16</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="CR16" t="n">
         <v>1.45</v>
       </c>
       <c r="CS16" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="CT16" t="n">
         <v>2.73</v>
@@ -7309,22 +7309,22 @@
         <v>1.94</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CY16" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DA16" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="DB16" t="n">
         <v>1.39</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DD16" t="n">
         <v>4.06</v>
@@ -7333,76 +7333,76 @@
         <v>0.12</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
       <c r="DH16" t="n">
-        <v>99.75</v>
+        <v>100.23</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.81</v>
+        <v>3.71</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.81</v>
+        <v>4.89</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DM16" t="n">
-        <v>51.56</v>
+        <v>53</v>
       </c>
       <c r="DN16" t="n">
         <v>1.18</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="DP16" t="n">
-        <v>10.31</v>
+        <v>9.65</v>
       </c>
       <c r="DQ16" t="n">
-        <v>1.75</v>
+        <v>1.59</v>
       </c>
       <c r="DR16" t="n">
-        <v>4.94</v>
+        <v>4.59</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>54.18</v>
+        <v>54.59</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.32</v>
+        <v>0.29</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.5</v>
+        <v>12.11</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.119999999999999</v>
+        <v>7.76</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.37</v>
+        <v>4.35</v>
       </c>
       <c r="EA16" t="n">
-        <v>19.69</v>
+        <v>18.47</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="EC16" t="n">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="17">
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
         <v>8</v>
@@ -7424,82 +7424,82 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="G17" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="H17" t="n">
-        <v>89.12</v>
+        <v>90.78</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="K17" t="n">
-        <v>5.25</v>
+        <v>5.22</v>
       </c>
       <c r="L17" t="n">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="M17" t="n">
-        <v>54.25</v>
+        <v>55.56</v>
       </c>
       <c r="N17" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="O17" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="P17" t="n">
-        <v>10.62</v>
+        <v>9.33</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="R17" t="n">
-        <v>7.75</v>
+        <v>6.78</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="U17" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="V17" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>44.38</v>
+        <v>44.89</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z17" t="n">
-        <v>10.75</v>
+        <v>10.33</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.12</v>
+        <v>6</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.62</v>
+        <v>4.33</v>
       </c>
       <c r="AC17" t="n">
-        <v>16.88</v>
+        <v>14.89</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE17" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AF17" t="n">
         <v>0.12</v>
@@ -7583,70 +7583,70 @@
         <v>3.25</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.25</v>
+        <v>9.35</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.5</v>
+        <v>4.59</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="BR17" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT17" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU17" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BV17" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW17" t="n">
         <v>0</v>
       </c>
       <c r="BX17" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY17" t="n">
         <v>3.01</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.41</v>
+        <v>3.35</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CC17" t="n">
         <v>3.34</v>
@@ -7658,28 +7658,28 @@
         <v>1.4</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.84</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CM17" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CN17" t="n">
         <v>1.57</v>
@@ -7688,10 +7688,10 @@
         <v>1.34</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.16</v>
+        <v>4.14</v>
       </c>
       <c r="CR17" t="n">
         <v>1.52</v>
@@ -7700,7 +7700,7 @@
         <v>3.24</v>
       </c>
       <c r="CT17" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CU17" t="n">
         <v>1.34</v>
@@ -7715,10 +7715,10 @@
         <v>1.7</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DA17" t="n">
         <v>1.67</v>
@@ -7727,85 +7727,85 @@
         <v>1.45</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.7</v>
+        <v>4.67</v>
       </c>
       <c r="DE17" t="n">
         <v>0.06</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.44</v>
+        <v>2.41</v>
       </c>
       <c r="DH17" t="n">
-        <v>96.75</v>
+        <v>97.18000000000001</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.5</v>
+        <v>3.36</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.56</v>
+        <v>4.59</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.37</v>
+        <v>0.47</v>
       </c>
       <c r="DM17" t="n">
-        <v>60</v>
+        <v>60.36</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="DP17" t="n">
-        <v>9.43</v>
+        <v>8.82</v>
       </c>
       <c r="DQ17" t="n">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.5</v>
+        <v>6.06</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>47.19</v>
+        <v>47.29</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DX17" t="n">
-        <v>11.18</v>
+        <v>10.94</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.18</v>
+        <v>7.06</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="EA17" t="n">
-        <v>15</v>
+        <v>14.06</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="EC17" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
@@ -1367,94 +1367,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>8</v>
       </c>
       <c r="E2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F2" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="G2" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H2" t="n">
-        <v>99.78</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J2" t="n">
-        <v>3.33</v>
+        <v>3.7</v>
       </c>
       <c r="K2" t="n">
-        <v>4.78</v>
+        <v>4.7</v>
       </c>
       <c r="L2" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M2" t="n">
-        <v>47.44</v>
+        <v>46.4</v>
       </c>
       <c r="N2" t="n">
-        <v>0.89</v>
+        <v>1.1</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="P2" t="n">
-        <v>9.220000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.22</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>6.67</v>
+        <v>5.9</v>
       </c>
       <c r="S2" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="U2" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="V2" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>55.33</v>
+        <v>53.3</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.67</v>
+        <v>10.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>6.11</v>
+        <v>5.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.56</v>
+        <v>4.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>12.67</v>
+        <v>11.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE2" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="AF2" t="n">
         <v>0.12</v>
@@ -1538,64 +1538,64 @@
         <v>2.25</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="BH2" t="n">
-        <v>9.94</v>
+        <v>10.22</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.59</v>
+        <v>4.67</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.35</v>
+        <v>5.56</v>
       </c>
       <c r="BR2" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS2" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BT2" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU2" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV2" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW2" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX2" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CA2" t="n">
         <v>3.08</v>
@@ -1613,25 +1613,25 @@
         <v>1.49</v>
       </c>
       <c r="CF2" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CG2" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CI2" t="n">
         <v>1.75</v>
       </c>
       <c r="CJ2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CK2" t="n">
         <v>1.61</v>
       </c>
       <c r="CL2" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CM2" t="n">
         <v>2.18</v>
@@ -1643,19 +1643,19 @@
         <v>1.43</v>
       </c>
       <c r="CP2" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CQ2" t="n">
-        <v>4.51</v>
+        <v>4.49</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CS2" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CT2" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CU2" t="n">
         <v>1.32</v>
@@ -1673,94 +1673,94 @@
         <v>2.02</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DB2" t="n">
         <v>1.45</v>
       </c>
       <c r="DC2" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DD2" t="n">
-        <v>4.64</v>
+        <v>4.6</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DG2" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="DH2" t="n">
-        <v>89.88</v>
+        <v>88.94</v>
       </c>
       <c r="DI2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>3.06</v>
+        <v>3.28</v>
       </c>
       <c r="DK2" t="n">
-        <v>4.47</v>
+        <v>4.44</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM2" t="n">
-        <v>45</v>
+        <v>44.56</v>
       </c>
       <c r="DN2" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="DO2" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="DP2" t="n">
-        <v>7.06</v>
+        <v>6.61</v>
       </c>
       <c r="DQ2" t="n">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="DR2" t="n">
-        <v>5.41</v>
+        <v>5.06</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>52.59</v>
+        <v>51.61</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="DX2" t="n">
-        <v>10.18</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="DY2" t="n">
-        <v>5.94</v>
+        <v>5.72</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.24</v>
+        <v>4.17</v>
       </c>
       <c r="EA2" t="n">
-        <v>10.94</v>
+        <v>10.28</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="3">
@@ -1770,61 +1770,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
       </c>
       <c r="E3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="G3" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="H3" t="n">
-        <v>87</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="J3" t="n">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="K3" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="L3" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M3" t="n">
-        <v>43.44</v>
+        <v>43.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>8.56</v>
+        <v>7.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.78</v>
+        <v>0.6</v>
       </c>
       <c r="R3" t="n">
-        <v>7.11</v>
+        <v>6.3</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1836,28 +1836,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>50.78</v>
+        <v>49.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.78</v>
+        <v>10.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.89</v>
+        <v>5.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.89</v>
+        <v>4.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>17.33</v>
+        <v>15.5</v>
       </c>
       <c r="AD3" t="n">
         <v>1.34</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -1917,16 +1917,16 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>49.25</v>
+        <v>48.88</v>
       </c>
       <c r="AZ3" t="n">
         <v>0.25</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.62</v>
+        <v>7.75</v>
       </c>
       <c r="BB3" t="n">
-        <v>5.38</v>
+        <v>5.5</v>
       </c>
       <c r="BC3" t="n">
         <v>2.25</v>
@@ -1935,73 +1935,73 @@
         <v>14.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
         <v>2.62</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="BH3" t="n">
-        <v>8.119999999999999</v>
+        <v>8.06</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="BR3" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS3" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BT3" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BU3" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV3" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="BZ3" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CB3" t="n">
         <v>3.26</v>
@@ -2019,13 +2019,13 @@
         <v>3.03</v>
       </c>
       <c r="CG3" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CH3" t="n">
         <v>1.21</v>
       </c>
       <c r="CI3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.87</v>
@@ -2037,28 +2037,28 @@
         <v>2.17</v>
       </c>
       <c r="CM3" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="CN3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CO3" t="n">
         <v>1.33</v>
       </c>
       <c r="CP3" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CQ3" t="n">
-        <v>4.05</v>
+        <v>4.08</v>
       </c>
       <c r="CR3" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CS3" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CT3" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CU3" t="n">
         <v>1.33</v>
@@ -2085,52 +2085,52 @@
         <v>1.44</v>
       </c>
       <c r="DC3" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DD3" t="n">
-        <v>4.62</v>
+        <v>4.58</v>
       </c>
       <c r="DE3" t="n">
         <v>0.06</v>
       </c>
       <c r="DF3" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DG3" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DH3" t="n">
-        <v>93.64</v>
+        <v>91.94</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DJ3" t="n">
-        <v>2.83</v>
+        <v>2.94</v>
       </c>
       <c r="DK3" t="n">
-        <v>3.12</v>
+        <v>3.05</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM3" t="n">
-        <v>47.05</v>
+        <v>46.89</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="DO3" t="n">
         <v>1</v>
       </c>
       <c r="DP3" t="n">
-        <v>8.119999999999999</v>
+        <v>7.61</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.65</v>
+        <v>7.17</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2142,28 +2142,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>50.06</v>
+        <v>49.45</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX3" t="n">
-        <v>9.289999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.65</v>
+        <v>5.67</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.65</v>
+        <v>3.72</v>
       </c>
       <c r="EA3" t="n">
-        <v>16</v>
+        <v>15.06</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="EC3" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="4">
@@ -2173,13 +2173,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
         <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2263,139 +2263,139 @@
         <v>3</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AI4" t="n">
-        <v>88.22</v>
+        <v>90</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AN4" t="n">
-        <v>53</v>
+        <v>51.3</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.67</v>
+        <v>8.9</v>
       </c>
       <c r="AR4" t="n">
         <v>2</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.109999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>38.56</v>
+        <v>38.9</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.33</v>
+        <v>10</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.33</v>
+        <v>6.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>14.78</v>
+        <v>14.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="BF4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BN4" t="n">
         <v>1.67</v>
       </c>
-      <c r="BG4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>8.18</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>1.71</v>
-      </c>
       <c r="BO4" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BP4" t="n">
-        <v>4</v>
+        <v>4.17</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.06</v>
+        <v>3.94</v>
       </c>
       <c r="BR4" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS4" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BU4" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV4" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW4" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX4" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY4" t="n">
         <v>3.18</v>
@@ -2404,25 +2404,25 @@
         <v>3.49</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.22</v>
+        <v>3.27</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.85</v>
+        <v>4.12</v>
       </c>
       <c r="CD4" t="n">
-        <v>4.12</v>
+        <v>4.38</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CH4" t="n">
         <v>1.29</v>
@@ -2431,28 +2431,28 @@
         <v>1.71</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CK4" t="n">
         <v>1.67</v>
       </c>
       <c r="CL4" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CP4" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="CQ4" t="n">
-        <v>4.33</v>
+        <v>4.28</v>
       </c>
       <c r="CR4" t="n">
         <v>1.5</v>
@@ -2473,7 +2473,7 @@
         <v>2.14</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CY4" t="n">
         <v>2.11</v>
@@ -2485,88 +2485,88 @@
         <v>1.69</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="DC4" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="DD4" t="n">
-        <v>4.49</v>
+        <v>4.44</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="DH4" t="n">
-        <v>86.41</v>
+        <v>87.5</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ4" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="DK4" t="n">
-        <v>3.47</v>
+        <v>3.39</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.29</v>
+        <v>0.39</v>
       </c>
       <c r="DM4" t="n">
-        <v>50.7</v>
+        <v>49.89</v>
       </c>
       <c r="DN4" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="DO4" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="DP4" t="n">
-        <v>7.12</v>
+        <v>7.34</v>
       </c>
       <c r="DQ4" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.109999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>38.95</v>
+        <v>39.11</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.529999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="DY4" t="n">
-        <v>5.35</v>
+        <v>5.33</v>
       </c>
       <c r="DZ4" t="n">
-        <v>4.18</v>
+        <v>4.06</v>
       </c>
       <c r="EA4" t="n">
-        <v>14.59</v>
+        <v>14.45</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="5">
@@ -2576,13 +2576,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0.11</v>
@@ -2618,13 +2618,13 @@
         <v>1.11</v>
       </c>
       <c r="P5" t="n">
-        <v>10.56</v>
+        <v>12.56</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.44</v>
+        <v>2.89</v>
       </c>
       <c r="R5" t="n">
-        <v>5.11</v>
+        <v>6.11</v>
       </c>
       <c r="S5" t="n">
         <v>0.67</v>
@@ -2642,25 +2642,25 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>41.11</v>
+        <v>41.22</v>
       </c>
       <c r="Y5" t="n">
         <v>0.11</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.44</v>
+        <v>10.44</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.33</v>
+        <v>6.33</v>
       </c>
       <c r="AB5" t="n">
         <v>4.11</v>
       </c>
       <c r="AC5" t="n">
-        <v>17.11</v>
+        <v>18.78</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AE5" t="n">
         <v>3.44</v>
@@ -2669,136 +2669,136 @@
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AI5" t="n">
-        <v>88.38</v>
+        <v>90.11</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK5" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="AL5" t="n">
-        <v>3.62</v>
+        <v>3.33</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>49.75</v>
+        <v>48.89</v>
       </c>
       <c r="AO5" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13.38</v>
+        <v>12.67</v>
       </c>
       <c r="AR5" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.38</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>45</v>
+        <v>44.11</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BA5" t="n">
-        <v>13</v>
+        <v>12.56</v>
       </c>
       <c r="BB5" t="n">
-        <v>10</v>
+        <v>9.67</v>
       </c>
       <c r="BC5" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="BD5" t="n">
-        <v>21.62</v>
+        <v>22</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.25</v>
+        <v>4.11</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BH5" t="n">
-        <v>8.880000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="BO5" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.65</v>
+        <v>4.56</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BT5" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU5" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV5" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BY5" t="n">
         <v>3.02</v>
@@ -2807,25 +2807,25 @@
         <v>3.42</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CC5" t="n">
-        <v>4.74</v>
+        <v>4.57</v>
       </c>
       <c r="CD5" t="n">
-        <v>5.75</v>
+        <v>5.57</v>
       </c>
       <c r="CE5" t="n">
         <v>1.52</v>
       </c>
       <c r="CF5" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CH5" t="n">
         <v>1.26</v>
@@ -2834,19 +2834,19 @@
         <v>1.66</v>
       </c>
       <c r="CJ5" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CL5" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="CM5" t="n">
         <v>2.01</v>
       </c>
       <c r="CN5" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CO5" t="n">
         <v>1.47</v>
@@ -2855,7 +2855,7 @@
         <v>2.46</v>
       </c>
       <c r="CQ5" t="n">
-        <v>4.63</v>
+        <v>4.65</v>
       </c>
       <c r="CR5" t="n">
         <v>1.53</v>
@@ -2882,7 +2882,7 @@
         <v>2.22</v>
       </c>
       <c r="CZ5" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="DA5" t="n">
         <v>1.62</v>
@@ -2891,52 +2891,52 @@
         <v>1.49</v>
       </c>
       <c r="DC5" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="DD5" t="n">
-        <v>4.99</v>
+        <v>4.98</v>
       </c>
       <c r="DE5" t="n">
         <v>0.06</v>
       </c>
       <c r="DF5" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="DG5" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="DH5" t="n">
-        <v>87.59</v>
+        <v>88.5</v>
       </c>
       <c r="DI5" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ5" t="n">
-        <v>4.18</v>
+        <v>4.22</v>
       </c>
       <c r="DK5" t="n">
-        <v>3.18</v>
+        <v>3.06</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM5" t="n">
-        <v>49.88</v>
+        <v>49.44</v>
       </c>
       <c r="DN5" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.71</v>
+        <v>1.61</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.89</v>
+        <v>12.62</v>
       </c>
       <c r="DQ5" t="n">
-        <v>3.17</v>
+        <v>3.39</v>
       </c>
       <c r="DR5" t="n">
-        <v>6.18</v>
+        <v>7.11</v>
       </c>
       <c r="DS5" t="n">
         <v>0.06</v>
@@ -2948,28 +2948,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>42.94</v>
+        <v>42.66</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="DX5" t="n">
-        <v>11.12</v>
+        <v>11.5</v>
       </c>
       <c r="DY5" t="n">
-        <v>7.53</v>
+        <v>8</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.59</v>
+        <v>3.5</v>
       </c>
       <c r="EA5" t="n">
-        <v>19.23</v>
+        <v>20.39</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="EC5" t="n">
-        <v>3.82</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="6">
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
@@ -2991,49 +2991,49 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="H6" t="n">
-        <v>102.25</v>
+        <v>104.56</v>
       </c>
       <c r="I6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="L6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M6" t="n">
-        <v>54.5</v>
+        <v>56.44</v>
       </c>
       <c r="N6" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="O6" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="P6" t="n">
-        <v>9.25</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="R6" t="n">
-        <v>7.5</v>
+        <v>7.78</v>
       </c>
       <c r="S6" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -3045,28 +3045,28 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>49.12</v>
+        <v>51</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.25</v>
+        <v>10.22</v>
       </c>
       <c r="AA6" t="n">
-        <v>6.38</v>
+        <v>7.11</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.62</v>
+        <v>21.78</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3150,67 +3150,67 @@
         <v>3.11</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="BH6" t="n">
-        <v>8.119999999999999</v>
+        <v>8</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.18</v>
+        <v>4.11</v>
       </c>
       <c r="BQ6" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BT6" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BU6" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV6" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.98</v>
+        <v>2.87</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.16</v>
+        <v>3.04</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="CB6" t="n">
         <v>3.2</v>
@@ -3225,7 +3225,7 @@
         <v>1.48</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CG6" t="n">
         <v>2.45</v>
@@ -3234,7 +3234,7 @@
         <v>1.28</v>
       </c>
       <c r="CI6" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.97</v>
@@ -3243,22 +3243,22 @@
         <v>1.67</v>
       </c>
       <c r="CL6" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="CN6" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CP6" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CQ6" t="n">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
       <c r="CR6" t="n">
         <v>1.49</v>
@@ -3282,10 +3282,10 @@
         <v>1.71</v>
       </c>
       <c r="CY6" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="DA6" t="n">
         <v>1.67</v>
@@ -3294,52 +3294,52 @@
         <v>1.44</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DD6" t="n">
-        <v>4.54</v>
+        <v>4.56</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="DG6" t="n">
         <v>1.94</v>
       </c>
       <c r="DH6" t="n">
-        <v>101.88</v>
+        <v>103.06</v>
       </c>
       <c r="DI6" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="DK6" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DM6" t="n">
-        <v>53.06</v>
+        <v>54.11</v>
       </c>
       <c r="DN6" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="DP6" t="n">
-        <v>9.65</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="DQ6" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="DR6" t="n">
-        <v>6.94</v>
+        <v>7.11</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
@@ -3351,28 +3351,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>49.41</v>
+        <v>50.34</v>
       </c>
       <c r="DW6" t="n">
         <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>9.710000000000001</v>
+        <v>10.16</v>
       </c>
       <c r="DY6" t="n">
-        <v>6.48</v>
+        <v>6.84</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.24</v>
+        <v>3.34</v>
       </c>
       <c r="EA6" t="n">
-        <v>18.53</v>
+        <v>19.23</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="7">
@@ -3382,10 +3382,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>9</v>
@@ -3397,46 +3397,46 @@
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="H7" t="n">
-        <v>105.29</v>
+        <v>105.62</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="K7" t="n">
-        <v>4.86</v>
+        <v>4.62</v>
       </c>
       <c r="L7" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M7" t="n">
-        <v>63.14</v>
+        <v>61.62</v>
       </c>
       <c r="N7" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O7" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="P7" t="n">
-        <v>5.71</v>
+        <v>4.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.14</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>4.71</v>
+        <v>4</v>
       </c>
       <c r="S7" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -3448,28 +3448,28 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>53.43</v>
+        <v>52.88</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>11.29</v>
+        <v>10.62</v>
       </c>
       <c r="AA7" t="n">
-        <v>5.86</v>
+        <v>5.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.43</v>
+        <v>5.12</v>
       </c>
       <c r="AC7" t="n">
-        <v>13</v>
+        <v>11.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AF7" t="n">
         <v>0.22</v>
@@ -3553,67 +3553,67 @@
         <v>1.67</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="BH7" t="n">
-        <v>7.5</v>
+        <v>7.65</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="BO7" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BP7" t="n">
-        <v>3.69</v>
+        <v>3.88</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.81</v>
+        <v>3.76</v>
       </c>
       <c r="BR7" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS7" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU7" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV7" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY7" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="CB7" t="n">
         <v>3.11</v>
@@ -3625,13 +3625,13 @@
         <v>3.71</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CF7" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CG7" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CH7" t="n">
         <v>1.27</v>
@@ -3640,16 +3640,16 @@
         <v>1.72</v>
       </c>
       <c r="CJ7" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CK7" t="n">
         <v>1.6</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CN7" t="n">
         <v>1.71</v>
@@ -3658,19 +3658,19 @@
         <v>1.44</v>
       </c>
       <c r="CP7" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.41</v>
+        <v>4.4</v>
       </c>
       <c r="CR7" t="n">
         <v>1.52</v>
       </c>
       <c r="CS7" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CT7" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CU7" t="n">
         <v>1.34</v>
@@ -3685,10 +3685,10 @@
         <v>1.64</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DA7" t="n">
         <v>1.72</v>
@@ -3697,52 +3697,52 @@
         <v>1.45</v>
       </c>
       <c r="DC7" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="DD7" t="n">
-        <v>4.69</v>
+        <v>4.67</v>
       </c>
       <c r="DE7" t="n">
         <v>0.12</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="DH7" t="n">
-        <v>94.62</v>
+        <v>95.41</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM7" t="n">
-        <v>54.06</v>
+        <v>53.88</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DP7" t="n">
-        <v>7</v>
+        <v>6.53</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.62</v>
+        <v>0.53</v>
       </c>
       <c r="DR7" t="n">
-        <v>5</v>
+        <v>4.65</v>
       </c>
       <c r="DS7" t="n">
         <v>0.06</v>
@@ -3754,25 +3754,25 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>53</v>
+        <v>52.77</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DX7" t="n">
-        <v>9.32</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.56</v>
+        <v>5.41</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="EA7" t="n">
-        <v>15.31</v>
+        <v>14.35</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="EC7" t="n">
         <v>2.12</v>
@@ -3785,13 +3785,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>0.12</v>
@@ -3827,13 +3827,13 @@
         <v>2.5</v>
       </c>
       <c r="P8" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="R8" t="n">
-        <v>4.75</v>
+        <v>6</v>
       </c>
       <c r="S8" t="n">
         <v>0.75</v>
@@ -3851,151 +3851,151 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>56</v>
+        <v>56.5</v>
       </c>
       <c r="Y8" t="n">
         <v>0.12</v>
       </c>
       <c r="Z8" t="n">
-        <v>14.38</v>
+        <v>14.75</v>
       </c>
       <c r="AA8" t="n">
-        <v>10</v>
+        <v>10.38</v>
       </c>
       <c r="AB8" t="n">
         <v>4.38</v>
       </c>
       <c r="AC8" t="n">
-        <v>14</v>
+        <v>16.75</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AE8" t="n">
         <v>2.62</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AI8" t="n">
-        <v>102.89</v>
+        <v>102.7</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.67</v>
+        <v>4.3</v>
       </c>
       <c r="AM8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK8" t="n">
         <v>0.33</v>
       </c>
-      <c r="AN8" t="n">
-        <v>55.67</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>7.33</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>52</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>14</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>9.35</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.35</v>
-      </c>
       <c r="BL8" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.59</v>
+        <v>3.78</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.29</v>
+        <v>5.22</v>
       </c>
       <c r="BR8" t="n">
-        <v>88.23999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS8" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BT8" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -4007,7 +4007,7 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BY8" t="n">
         <v>2.38</v>
@@ -4016,19 +4016,19 @@
         <v>2.47</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.01</v>
+        <v>3.06</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CF8" t="n">
         <v>3.18</v>
@@ -4040,22 +4040,22 @@
         <v>1.28</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.96</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CL8" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CN8" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CO8" t="n">
         <v>1.41</v>
@@ -4064,7 +4064,7 @@
         <v>2.28</v>
       </c>
       <c r="CQ8" t="n">
-        <v>4.32</v>
+        <v>4.33</v>
       </c>
       <c r="CR8" t="n">
         <v>1.49</v>
@@ -4088,64 +4088,64 @@
         <v>1.68</v>
       </c>
       <c r="CY8" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="CZ8" t="n">
         <v>2.12</v>
       </c>
-      <c r="CZ8" t="n">
-        <v>2.11</v>
-      </c>
       <c r="DA8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="DC8" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DD8" t="n">
-        <v>4.49</v>
+        <v>4.51</v>
       </c>
       <c r="DE8" t="n">
         <v>0.11</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="DH8" t="n">
-        <v>104.06</v>
+        <v>103.89</v>
       </c>
       <c r="DI8" t="n">
         <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.77</v>
+        <v>2.67</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.88</v>
+        <v>4.66</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM8" t="n">
-        <v>60.59</v>
+        <v>60.61</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="DO8" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="DP8" t="n">
-        <v>6.59</v>
+        <v>7.11</v>
       </c>
       <c r="DQ8" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="DR8" t="n">
-        <v>6.12</v>
+        <v>7.33</v>
       </c>
       <c r="DS8" t="n">
         <v>0.06</v>
@@ -4157,28 +4157,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>53.88</v>
+        <v>54.22</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX8" t="n">
-        <v>11.89</v>
+        <v>11.78</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.35</v>
+        <v>8.34</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.53</v>
+        <v>3.45</v>
       </c>
       <c r="EA8" t="n">
-        <v>14</v>
+        <v>15.67</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="9">
@@ -4188,94 +4188,94 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
         <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F9" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="G9" t="n">
-        <v>1.38</v>
+        <v>1.67</v>
       </c>
       <c r="H9" t="n">
-        <v>93.62</v>
+        <v>92.33</v>
       </c>
       <c r="I9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J9" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="K9" t="n">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M9" t="n">
-        <v>52.25</v>
+        <v>53.78</v>
       </c>
       <c r="N9" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="O9" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="P9" t="n">
-        <v>10.5</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="R9" t="n">
-        <v>8.619999999999999</v>
+        <v>7.56</v>
       </c>
       <c r="S9" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="T9" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="U9" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V9" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>54.5</v>
+        <v>54.11</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.380000000000001</v>
+        <v>8</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="AC9" t="n">
-        <v>18.62</v>
+        <v>16.44</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AF9" t="n">
         <v>0.11</v>
@@ -4359,70 +4359,70 @@
         <v>3.78</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="BH9" t="n">
-        <v>9.18</v>
+        <v>9.44</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.76</v>
+        <v>0.89</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.71</v>
+        <v>4.72</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.53</v>
+        <v>4.78</v>
       </c>
       <c r="BR9" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS9" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT9" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU9" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV9" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW9" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX9" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="BZ9" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="CA9" t="n">
         <v>3.23</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CC9" t="n">
         <v>3.12</v>
@@ -4431,46 +4431,46 @@
         <v>3.15</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF9" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="CG9" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CL9" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CO9" t="n">
         <v>1.37</v>
       </c>
       <c r="CP9" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CQ9" t="n">
-        <v>3.96</v>
+        <v>3.93</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CS9" t="n">
         <v>3.19</v>
@@ -4488,100 +4488,100 @@
         <v>2.02</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="DC9" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="DD9" t="n">
-        <v>4.23</v>
+        <v>4.18</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.77</v>
+        <v>2.84</v>
       </c>
       <c r="DH9" t="n">
-        <v>97.34999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ9" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="DK9" t="n">
-        <v>5.05</v>
+        <v>5.16</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM9" t="n">
-        <v>52.35</v>
+        <v>53.11</v>
       </c>
       <c r="DN9" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="DQ9" t="n">
         <v>0.89</v>
       </c>
-      <c r="DO9" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="DP9" t="n">
-        <v>10.18</v>
-      </c>
-      <c r="DQ9" t="n">
-        <v>1</v>
-      </c>
       <c r="DR9" t="n">
-        <v>7.17</v>
+        <v>6.72</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>53.06</v>
+        <v>52.94</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.12</v>
+        <v>11.94</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.59</v>
+        <v>7.44</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.53</v>
+        <v>4.5</v>
       </c>
       <c r="EA9" t="n">
-        <v>16.65</v>
+        <v>15.66</v>
       </c>
       <c r="EB9" t="n">
         <v>1.46</v>
       </c>
       <c r="EC9" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="10">
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>7</v>
@@ -4603,82 +4603,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>104</v>
+        <v>103.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>4.89</v>
+        <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M10" t="n">
-        <v>64.67</v>
+        <v>63.3</v>
       </c>
       <c r="N10" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="O10" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="P10" t="n">
-        <v>9.109999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.11</v>
+        <v>0.9</v>
       </c>
       <c r="R10" t="n">
-        <v>5.56</v>
+        <v>4.9</v>
       </c>
       <c r="S10" t="n">
-        <v>0.89</v>
+        <v>1.3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="U10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>54.33</v>
+        <v>54</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>12.33</v>
+        <v>11.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.44</v>
+        <v>5.8</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.89</v>
+        <v>5.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>17.22</v>
+        <v>15.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4762,70 +4762,70 @@
         <v>4.29</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.56</v>
+        <v>2.82</v>
       </c>
       <c r="BH10" t="n">
-        <v>8.25</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.56</v>
+        <v>2.82</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BP10" t="n">
-        <v>3.88</v>
+        <v>3.76</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.38</v>
+        <v>4.35</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT10" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU10" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BV10" t="n">
-        <v>6.25</v>
+        <v>11.76</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="BX10" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="BZ10" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="CC10" t="n">
         <v>4.65</v>
@@ -4834,22 +4834,22 @@
         <v>5.02</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CF10" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CG10" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CH10" t="n">
         <v>1.3</v>
       </c>
       <c r="CI10" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="CK10" t="n">
         <v>1.59</v>
@@ -4858,19 +4858,19 @@
         <v>2.08</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CN10" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CO10" t="n">
         <v>1.38</v>
       </c>
       <c r="CP10" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CQ10" t="n">
-        <v>4.15</v>
+        <v>4.14</v>
       </c>
       <c r="CR10" t="n">
         <v>1.46</v>
@@ -4891,16 +4891,16 @@
         <v>2.15</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CY10" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="DA10" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="DB10" t="n">
         <v>1.41</v>
@@ -4909,49 +4909,49 @@
         <v>2.29</v>
       </c>
       <c r="DD10" t="n">
-        <v>4.29</v>
+        <v>4.27</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="DG10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>104.12</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>4</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>58.29</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DO10" t="n">
         <v>2.18</v>
       </c>
-      <c r="DH10" t="n">
-        <v>104.63</v>
-      </c>
-      <c r="DI10" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="DJ10" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="DK10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="DL10" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="DM10" t="n">
-        <v>58.75</v>
-      </c>
-      <c r="DN10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="DO10" t="n">
-        <v>2.32</v>
-      </c>
       <c r="DP10" t="n">
-        <v>10.5</v>
+        <v>9.83</v>
       </c>
       <c r="DQ10" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="DR10" t="n">
-        <v>7.38</v>
+        <v>6.88</v>
       </c>
       <c r="DS10" t="n">
         <v>0.12</v>
@@ -4963,28 +4963,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>52.44</v>
+        <v>52.35</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="DX10" t="n">
-        <v>11.75</v>
+        <v>11.18</v>
       </c>
       <c r="DY10" t="n">
-        <v>6.68</v>
+        <v>6.29</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.06</v>
+        <v>4.88</v>
       </c>
       <c r="EA10" t="n">
-        <v>18.5</v>
+        <v>17.35</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="EC10" t="n">
-        <v>3.5</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="11">
@@ -4994,13 +4994,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>0.12</v>
@@ -5084,139 +5084,139 @@
         <v>2.38</v>
       </c>
       <c r="AF11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>56.6</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BM11" t="n">
         <v>0.44</v>
       </c>
-      <c r="AG11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>102.22</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>55.56</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>8.779999999999999</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>49.22</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>10.78</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>6.78</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>19.22</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>8.41</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>0.47</v>
-      </c>
       <c r="BN11" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BP11" t="n">
-        <v>3.47</v>
+        <v>3.44</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.88</v>
+        <v>4.83</v>
       </c>
       <c r="BR11" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS11" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BT11" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BU11" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV11" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW11" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX11" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BY11" t="n">
         <v>2.3</v>
@@ -5225,16 +5225,16 @@
         <v>2.35</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CB11" t="n">
         <v>3.27</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="CD11" t="n">
-        <v>2.89</v>
+        <v>2.82</v>
       </c>
       <c r="CE11" t="n">
         <v>1.45</v>
@@ -5243,13 +5243,13 @@
         <v>3.17</v>
       </c>
       <c r="CG11" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CH11" t="n">
         <v>1.29</v>
       </c>
       <c r="CI11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.94</v>
@@ -5270,19 +5270,19 @@
         <v>1.39</v>
       </c>
       <c r="CP11" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CQ11" t="n">
-        <v>4.23</v>
+        <v>4.25</v>
       </c>
       <c r="CR11" t="n">
         <v>1.48</v>
       </c>
       <c r="CS11" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CT11" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CU11" t="n">
         <v>1.34</v>
@@ -5297,10 +5297,10 @@
         <v>1.66</v>
       </c>
       <c r="CY11" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DA11" t="n">
         <v>1.71</v>
@@ -5309,85 +5309,85 @@
         <v>1.41</v>
       </c>
       <c r="DC11" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="DD11" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.59</v>
+        <v>1.78</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="DH11" t="n">
-        <v>95.47</v>
+        <v>95</v>
       </c>
       <c r="DI11" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="DK11" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM11" t="n">
-        <v>53.41</v>
+        <v>54.11</v>
       </c>
       <c r="DN11" t="n">
         <v>1</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="DP11" t="n">
-        <v>10.3</v>
+        <v>9.67</v>
       </c>
       <c r="DQ11" t="n">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.06</v>
+        <v>7.56</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>50.88</v>
+        <v>51.28</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.18</v>
+        <v>11.11</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.3</v>
+        <v>7.11</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="EA11" t="n">
-        <v>19.94</v>
+        <v>18.78</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12">
@@ -5397,13 +5397,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
         <v>8</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5487,139 +5487,139 @@
         <v>2.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="AI12" t="n">
-        <v>104.11</v>
+        <v>101.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>5.33</v>
+        <v>5.5</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>52.78</v>
+        <v>52.9</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10.44</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.89</v>
+        <v>5.2</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>49.67</v>
+        <v>49.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA12" t="n">
-        <v>10.78</v>
+        <v>11.3</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.22</v>
+        <v>6.8</v>
       </c>
       <c r="BC12" t="n">
-        <v>4.56</v>
+        <v>4.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>18</v>
+        <v>16.1</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="BG12" t="n">
         <v>3</v>
       </c>
       <c r="BH12" t="n">
-        <v>8.82</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BI12" t="n">
         <v>3</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.76</v>
+        <v>0.89</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.65</v>
+        <v>4.67</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.12</v>
+        <v>4.39</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT12" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BU12" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV12" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX12" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY12" t="n">
         <v>1.66</v>
@@ -5628,55 +5628,55 @@
         <v>1.7</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="CC12" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="CD12" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="CE12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CF12" t="n">
         <v>2.07</v>
       </c>
-      <c r="CE12" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="CF12" t="n">
-        <v>2.03</v>
-      </c>
       <c r="CG12" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.95</v>
+        <v>0.97</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="CP12" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="CR12" t="n">
         <v>1.43</v>
@@ -5715,82 +5715,82 @@
         <v>2.08</v>
       </c>
       <c r="DD12" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="DE12" t="n">
         <v>0.06</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DG12" t="n">
-        <v>3.11</v>
+        <v>3.22</v>
       </c>
       <c r="DH12" t="n">
-        <v>106.65</v>
+        <v>104.94</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DK12" t="n">
-        <v>6</v>
+        <v>6.06</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.35</v>
+        <v>0.39</v>
       </c>
       <c r="DM12" t="n">
-        <v>58.24</v>
+        <v>58</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DO12" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="DP12" t="n">
-        <v>10</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="DQ12" t="n">
-        <v>2.29</v>
+        <v>2.11</v>
       </c>
       <c r="DR12" t="n">
-        <v>5.35</v>
+        <v>5</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>54.12</v>
+        <v>53.83</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.65</v>
+        <v>12.83</v>
       </c>
       <c r="DY12" t="n">
-        <v>7.65</v>
+        <v>7.89</v>
       </c>
       <c r="DZ12" t="n">
-        <v>5</v>
+        <v>4.94</v>
       </c>
       <c r="EA12" t="n">
-        <v>17.29</v>
+        <v>16.28</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="13">
@@ -5800,91 +5800,91 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F13" t="n">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="G13" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="H13" t="n">
-        <v>120.33</v>
+        <v>125</v>
       </c>
       <c r="I13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>5.11</v>
+        <v>5.2</v>
       </c>
       <c r="L13" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="M13" t="n">
-        <v>59.89</v>
+        <v>63.6</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="P13" t="n">
-        <v>11.78</v>
+        <v>10.5</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="R13" t="n">
-        <v>8.33</v>
+        <v>7.4</v>
       </c>
       <c r="S13" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T13" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>54</v>
+        <v>54.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.44</v>
+        <v>0.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>14.56</v>
+        <v>13.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.109999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>6.44</v>
+        <v>6.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>20.78</v>
+        <v>18.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AE13" t="n">
         <v>3</v>
@@ -5923,13 +5923,13 @@
         <v>2.12</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9.380000000000001</v>
+        <v>10.88</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.38</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AT13" t="n">
         <v>0.62</v>
@@ -5947,94 +5947,94 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>53.25</v>
+        <v>52.75</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.12</v>
       </c>
       <c r="BA13" t="n">
-        <v>14.75</v>
+        <v>15.5</v>
       </c>
       <c r="BB13" t="n">
-        <v>9.880000000000001</v>
+        <v>10.62</v>
       </c>
       <c r="BC13" t="n">
         <v>4.88</v>
       </c>
       <c r="BD13" t="n">
-        <v>22.38</v>
+        <v>25.75</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="BF13" t="n">
         <v>2.62</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>7.88</v>
+        <v>7.94</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BP13" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BT13" t="n">
-        <v>47.06</v>
+        <v>44.44</v>
       </c>
       <c r="BU13" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV13" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY13" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="BZ13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.61</v>
+        <v>3.64</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="CC13" t="n">
         <v>1.79</v>
@@ -6049,37 +6049,37 @@
         <v>3.01</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CI13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CK13" t="n">
         <v>1.67</v>
       </c>
-      <c r="CJ13" t="n">
+      <c r="CL13" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="CM13" t="n">
         <v>2.08</v>
       </c>
-      <c r="CK13" t="n">
+      <c r="CN13" t="n">
         <v>1.66</v>
-      </c>
-      <c r="CL13" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="CM13" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="CN13" t="n">
-        <v>1.67</v>
       </c>
       <c r="CO13" t="n">
         <v>1.36</v>
       </c>
       <c r="CP13" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.89</v>
+        <v>3.86</v>
       </c>
       <c r="CR13" t="n">
         <v>1.44</v>
@@ -6100,67 +6100,67 @@
         <v>2.27</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CY13" t="n">
         <v>2.09</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DB13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="DC13" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DD13" t="n">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF13" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="DH13" t="n">
-        <v>112.29</v>
+        <v>115.33</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.18</v>
+        <v>3.44</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.82</v>
+        <v>4.89</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DM13" t="n">
-        <v>53.88</v>
+        <v>56.28</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.17</v>
+        <v>2.28</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.65</v>
+        <v>10.67</v>
       </c>
       <c r="DQ13" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.41</v>
+        <v>7.72</v>
       </c>
       <c r="DS13" t="n">
         <v>0.11</v>
@@ -6172,28 +6172,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.65</v>
+        <v>53.61</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.29</v>
+        <v>0.44</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.65</v>
+        <v>14.56</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.94</v>
+        <v>9</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.71</v>
+        <v>5.56</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.53</v>
+        <v>21.78</v>
       </c>
       <c r="EB13" t="n">
         <v>1.72</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="14">
@@ -6203,13 +6203,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
         <v>0.22</v>
@@ -6296,49 +6296,49 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AI14" t="n">
-        <v>98.12</v>
+        <v>100.22</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="AL14" t="n">
-        <v>3.75</v>
+        <v>4.11</v>
       </c>
       <c r="AM14" t="n">
         <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>50.25</v>
+        <v>52.56</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.25</v>
+        <v>1.67</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.880000000000001</v>
+        <v>7.78</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.5</v>
+        <v>5.67</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6350,82 +6350,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>43.12</v>
+        <v>44</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.88</v>
+        <v>7.33</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="BC14" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="BD14" t="n">
-        <v>14.12</v>
+        <v>12.44</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="BH14" t="n">
-        <v>8.289999999999999</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="BI14" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="BN14" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BP14" t="n">
-        <v>3.88</v>
+        <v>4.06</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.41</v>
+        <v>4.33</v>
       </c>
       <c r="BR14" t="n">
         <v>100</v>
       </c>
       <c r="BS14" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT14" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BU14" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV14" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX14" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY14" t="n">
         <v>3.57</v>
@@ -6437,13 +6437,13 @@
         <v>3.25</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CC14" t="n">
         <v>3.69</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.99</v>
+        <v>4.03</v>
       </c>
       <c r="CE14" t="n">
         <v>1.45</v>
@@ -6467,28 +6467,28 @@
         <v>1.63</v>
       </c>
       <c r="CL14" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="CN14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CO14" t="n">
         <v>1.39</v>
       </c>
       <c r="CP14" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CQ14" t="n">
-        <v>4.11</v>
+        <v>4.12</v>
       </c>
       <c r="CR14" t="n">
         <v>1.48</v>
       </c>
       <c r="CS14" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CT14" t="n">
         <v>2.63</v>
@@ -6509,7 +6509,7 @@
         <v>2.04</v>
       </c>
       <c r="CZ14" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DA14" t="n">
         <v>1.75</v>
@@ -6524,46 +6524,46 @@
         <v>4.29</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF14" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="DH14" t="n">
-        <v>97.94</v>
+        <v>99</v>
       </c>
       <c r="DI14" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ14" t="n">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="DK14" t="n">
-        <v>3.94</v>
+        <v>4.11</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DM14" t="n">
-        <v>53.53</v>
+        <v>54.5</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DO14" t="n">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="DP14" t="n">
-        <v>8.529999999999999</v>
+        <v>8</v>
       </c>
       <c r="DQ14" t="n">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="DR14" t="n">
-        <v>5.76</v>
+        <v>5.39</v>
       </c>
       <c r="DS14" t="n">
         <v>0.06</v>
@@ -6575,28 +6575,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>46.12</v>
+        <v>46.39</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DX14" t="n">
-        <v>7.94</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DY14" t="n">
         <v>5.06</v>
       </c>
       <c r="DZ14" t="n">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="EA14" t="n">
-        <v>12.41</v>
+        <v>11.66</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="EC14" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -6606,10 +6606,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
         <v>8</v>
@@ -6618,82 +6618,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="G15" t="n">
-        <v>2.67</v>
+        <v>2.8</v>
       </c>
       <c r="H15" t="n">
-        <v>86.11</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="K15" t="n">
-        <v>5.89</v>
+        <v>6.3</v>
       </c>
       <c r="L15" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>62.33</v>
+        <v>65.5</v>
       </c>
       <c r="N15" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="O15" t="n">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="P15" t="n">
-        <v>9.779999999999999</v>
+        <v>10</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="R15" t="n">
-        <v>4.89</v>
+        <v>5</v>
       </c>
       <c r="S15" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="T15" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="U15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>46.11</v>
+        <v>45.9</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z15" t="n">
-        <v>12.44</v>
+        <v>13.6</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.67</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.78</v>
+        <v>4.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>21.33</v>
+        <v>22.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="AF15" t="n">
         <v>0.25</v>
@@ -6777,70 +6777,70 @@
         <v>3.12</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="BH15" t="n">
-        <v>9.289999999999999</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.47</v>
+        <v>4.61</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.82</v>
+        <v>4.78</v>
       </c>
       <c r="BR15" t="n">
-        <v>94.12</v>
+        <v>88.89</v>
       </c>
       <c r="BS15" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BT15" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU15" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV15" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW15" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX15" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="BZ15" t="n">
         <v>2.12</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="CC15" t="n">
         <v>3.34</v>
@@ -6849,31 +6849,31 @@
         <v>3.42</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CF15" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CG15" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CH15" t="n">
         <v>1.19</v>
       </c>
       <c r="CI15" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CN15" t="n">
         <v>1.64</v>
@@ -6885,7 +6885,7 @@
         <v>2.35</v>
       </c>
       <c r="CQ15" t="n">
-        <v>4.29</v>
+        <v>4.3</v>
       </c>
       <c r="CR15" t="n">
         <v>1.52</v>
@@ -6915,7 +6915,7 @@
         <v>2.23</v>
       </c>
       <c r="DA15" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DB15" t="n">
         <v>1.47</v>
@@ -6924,49 +6924,49 @@
         <v>2.48</v>
       </c>
       <c r="DD15" t="n">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="DH15" t="n">
-        <v>95.81999999999999</v>
+        <v>97.11</v>
       </c>
       <c r="DI15" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.06</v>
+        <v>2.89</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.59</v>
+        <v>5.83</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="DM15" t="n">
-        <v>64.70999999999999</v>
+        <v>66.34</v>
       </c>
       <c r="DN15" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="DO15" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.35</v>
+        <v>11.39</v>
       </c>
       <c r="DQ15" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="DR15" t="n">
-        <v>5.36</v>
+        <v>5.39</v>
       </c>
       <c r="DS15" t="n">
         <v>0.06</v>
@@ -6978,28 +6978,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>47.35</v>
+        <v>47.17</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX15" t="n">
-        <v>12.59</v>
+        <v>13.22</v>
       </c>
       <c r="DY15" t="n">
-        <v>8.300000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.3</v>
+        <v>4.11</v>
       </c>
       <c r="EA15" t="n">
-        <v>21.17</v>
+        <v>21.78</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="16">
@@ -7009,13 +7009,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
         <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>0.25</v>
@@ -7102,136 +7102,136 @@
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AH16" t="n">
-        <v>2.33</v>
+        <v>2.7</v>
       </c>
       <c r="AI16" t="n">
-        <v>91</v>
+        <v>94.7</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>3.89</v>
+        <v>3.7</v>
       </c>
       <c r="AL16" t="n">
-        <v>4.89</v>
+        <v>5.5</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AN16" t="n">
-        <v>52.22</v>
+        <v>55.2</v>
       </c>
       <c r="AO16" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10.22</v>
+        <v>9.1</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.89</v>
+        <v>3.4</v>
       </c>
       <c r="AT16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>56</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BJ16" t="n">
         <v>0.89</v>
       </c>
-      <c r="AU16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>12.11</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC16" t="n">
+      <c r="BK16" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BP16" t="n">
         <v>4.11</v>
       </c>
-      <c r="BD16" t="n">
-        <v>18</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>9</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>4</v>
-      </c>
       <c r="BQ16" t="n">
-        <v>5</v>
+        <v>5.22</v>
       </c>
       <c r="BR16" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS16" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT16" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU16" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV16" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BY16" t="n">
         <v>2.2</v>
@@ -7246,49 +7246,49 @@
         <v>3.36</v>
       </c>
       <c r="CC16" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="CD16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="CE16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CF16" t="n">
         <v>2.74</v>
       </c>
-      <c r="CD16" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="CE16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="CF16" t="n">
-        <v>2.73</v>
-      </c>
       <c r="CG16" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CI16" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CK16" t="n">
         <v>1.42</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="CM16" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="CN16" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP16" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CQ16" t="n">
-        <v>3.4</v>
+        <v>3.44</v>
       </c>
       <c r="CR16" t="n">
         <v>1.45</v>
@@ -7309,100 +7309,100 @@
         <v>1.94</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CY16" t="n">
         <v>2.04</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DA16" t="n">
         <v>1.74</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="DC16" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DD16" t="n">
         <v>4.06</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.41</v>
+        <v>2.61</v>
       </c>
       <c r="DH16" t="n">
-        <v>100.23</v>
+        <v>101.78</v>
       </c>
       <c r="DI16" t="n">
         <v>0</v>
       </c>
       <c r="DJ16" t="n">
-        <v>3.71</v>
+        <v>3.61</v>
       </c>
       <c r="DK16" t="n">
-        <v>4.89</v>
+        <v>5.22</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM16" t="n">
-        <v>53</v>
+        <v>54.61</v>
       </c>
       <c r="DN16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.48</v>
+        <v>2.61</v>
       </c>
       <c r="DP16" t="n">
-        <v>9.65</v>
+        <v>9.06</v>
       </c>
       <c r="DQ16" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="DR16" t="n">
-        <v>4.59</v>
+        <v>4.28</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>54.59</v>
+        <v>55.16</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.11</v>
+        <v>12.05</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.76</v>
+        <v>7.67</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.35</v>
+        <v>4.39</v>
       </c>
       <c r="EA16" t="n">
-        <v>18.47</v>
+        <v>17.39</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="EC16" t="n">
-        <v>3.17</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="17">
@@ -7412,13 +7412,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
         <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7502,139 +7502,139 @@
         <v>2.78</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AI17" t="n">
-        <v>104.38</v>
+        <v>102.11</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="AL17" t="n">
-        <v>3.88</v>
+        <v>4.11</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN17" t="n">
-        <v>65.75</v>
+        <v>65.89</v>
       </c>
       <c r="AO17" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AQ17" t="n">
-        <v>8.25</v>
+        <v>7.22</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.25</v>
+        <v>4.56</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.88</v>
+        <v>1.33</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>50</v>
+        <v>49.89</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BA17" t="n">
-        <v>11.62</v>
+        <v>11.56</v>
       </c>
       <c r="BB17" t="n">
-        <v>8.25</v>
+        <v>7.56</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.38</v>
+        <v>4</v>
       </c>
       <c r="BD17" t="n">
-        <v>13.12</v>
+        <v>11.56</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="BF17" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.29</v>
+        <v>2.56</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.35</v>
+        <v>9.17</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.29</v>
+        <v>2.56</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.47</v>
+        <v>0.67</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.18</v>
+        <v>1.39</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.59</v>
+        <v>4.44</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.76</v>
+        <v>4.72</v>
       </c>
       <c r="BR17" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS17" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT17" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU17" t="n">
-        <v>11.76</v>
+        <v>16.67</v>
       </c>
       <c r="BV17" t="n">
-        <v>5.88</v>
+        <v>11.11</v>
       </c>
       <c r="BW17" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="BX17" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY17" t="n">
         <v>3.01</v>
@@ -7646,28 +7646,28 @@
         <v>3.14</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CC17" t="n">
-        <v>3.34</v>
+        <v>3.31</v>
       </c>
       <c r="CD17" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="CE17" t="n">
         <v>1.4</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CH17" t="n">
         <v>1.2</v>
       </c>
       <c r="CI17" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.84</v>
@@ -7676,22 +7676,22 @@
         <v>1.56</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CM17" t="n">
         <v>1.96</v>
       </c>
       <c r="CN17" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CO17" t="n">
         <v>1.34</v>
       </c>
       <c r="CP17" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.14</v>
+        <v>4.13</v>
       </c>
       <c r="CR17" t="n">
         <v>1.52</v>
@@ -7715,7 +7715,7 @@
         <v>1.7</v>
       </c>
       <c r="CY17" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CZ17" t="n">
         <v>2.1</v>
@@ -7724,85 +7724,85 @@
         <v>1.67</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="DC17" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DD17" t="n">
-        <v>4.67</v>
+        <v>4.63</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.41</v>
+        <v>2.5</v>
       </c>
       <c r="DH17" t="n">
-        <v>97.18000000000001</v>
+        <v>96.44</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.59</v>
+        <v>4.66</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DM17" t="n">
-        <v>60.36</v>
+        <v>60.72</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="DP17" t="n">
-        <v>8.82</v>
+        <v>8.27</v>
       </c>
       <c r="DQ17" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="DR17" t="n">
-        <v>6.06</v>
+        <v>5.67</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>47.29</v>
+        <v>47.39</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DX17" t="n">
         <v>10.94</v>
       </c>
       <c r="DY17" t="n">
-        <v>7.06</v>
+        <v>6.78</v>
       </c>
       <c r="DZ17" t="n">
-        <v>3.88</v>
+        <v>4.16</v>
       </c>
       <c r="EA17" t="n">
-        <v>14.06</v>
+        <v>13.23</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="EC17" t="n">
         <v>3</v>

--- a/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
+++ b/data/teams/leagues/Averages_Uruguay_Primera_División_2026.xlsx
@@ -1812,13 +1812,13 @@
         <v>1.3</v>
       </c>
       <c r="P3" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="R3" t="n">
-        <v>6.3</v>
+        <v>7.9</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -1836,25 +1836,25 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>49.9</v>
+        <v>51</v>
       </c>
       <c r="Y3" t="n">
         <v>0.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>10.7</v>
+        <v>11</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.8</v>
+        <v>6.1</v>
       </c>
       <c r="AB3" t="n">
         <v>4.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE3" t="n">
         <v>2.7</v>
@@ -2124,13 +2124,13 @@
         <v>1</v>
       </c>
       <c r="DP3" t="n">
-        <v>7.61</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.78</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DR3" t="n">
-        <v>7.17</v>
+        <v>8.06</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
@@ -2142,25 +2142,25 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>49.45</v>
+        <v>50.06</v>
       </c>
       <c r="DW3" t="n">
         <v>0.17</v>
       </c>
       <c r="DX3" t="n">
-        <v>9.390000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="DY3" t="n">
-        <v>5.67</v>
+        <v>5.83</v>
       </c>
       <c r="DZ3" t="n">
         <v>3.72</v>
       </c>
       <c r="EA3" t="n">
-        <v>15.06</v>
+        <v>16.44</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="EC3" t="n">
         <v>2.66</v>
@@ -2296,13 +2296,13 @@
         <v>1.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.5</v>
+        <v>10.1</v>
       </c>
       <c r="AT4" t="n">
         <v>1.4</v>
@@ -2320,25 +2320,25 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>38.9</v>
+        <v>38.6</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>10</v>
+        <v>10.3</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="BC4" t="n">
         <v>3.8</v>
       </c>
       <c r="BD4" t="n">
-        <v>14.5</v>
+        <v>16.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="BF4" t="n">
         <v>1.7</v>
@@ -2527,13 +2527,13 @@
         <v>1.89</v>
       </c>
       <c r="DP4" t="n">
-        <v>7.34</v>
+        <v>7.67</v>
       </c>
       <c r="DQ4" t="n">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.33</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DS4" t="n">
         <v>0.22</v>
@@ -2545,25 +2545,25 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>39.11</v>
+        <v>38.95</v>
       </c>
       <c r="DW4" t="n">
         <v>0.22</v>
       </c>
       <c r="DX4" t="n">
-        <v>9.390000000000001</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="DY4" t="n">
-        <v>5.33</v>
+        <v>5.5</v>
       </c>
       <c r="DZ4" t="n">
         <v>4.06</v>
       </c>
       <c r="EA4" t="n">
-        <v>14.45</v>
+        <v>15.45</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="EC4" t="n">
         <v>2.28</v>
@@ -3382,13 +3382,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3472,139 +3472,139 @@
         <v>2.62</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="AI7" t="n">
-        <v>86.33</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AL7" t="n">
-        <v>2.33</v>
+        <v>2.9</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN7" t="n">
-        <v>47</v>
+        <v>47.6</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8</v>
+        <v>7.1</v>
       </c>
       <c r="AR7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>53.4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>7.78</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BL7" t="n">
         <v>1</v>
       </c>
-      <c r="AS7" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU7" t="n">
+      <c r="BM7" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO7" t="n">
         <v>0.89</v>
       </c>
-      <c r="AV7" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>52.67</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>7.78</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>17.11</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>0.9399999999999999</v>
-      </c>
       <c r="BP7" t="n">
-        <v>3.88</v>
+        <v>3.72</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.76</v>
+        <v>4.06</v>
       </c>
       <c r="BR7" t="n">
-        <v>94.12</v>
+        <v>88.89</v>
       </c>
       <c r="BS7" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BT7" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV7" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY7" t="n">
         <v>2.36</v>
@@ -3619,10 +3619,10 @@
         <v>3.11</v>
       </c>
       <c r="CC7" t="n">
-        <v>3.34</v>
+        <v>3.27</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.71</v>
+        <v>3.67</v>
       </c>
       <c r="CE7" t="n">
         <v>1.49</v>
@@ -3646,7 +3646,7 @@
         <v>1.6</v>
       </c>
       <c r="CL7" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CM7" t="n">
         <v>2.16</v>
@@ -3661,7 +3661,7 @@
         <v>2.35</v>
       </c>
       <c r="CQ7" t="n">
-        <v>4.4</v>
+        <v>4.41</v>
       </c>
       <c r="CR7" t="n">
         <v>1.52</v>
@@ -3703,46 +3703,46 @@
         <v>4.67</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.71</v>
+        <v>2</v>
       </c>
       <c r="DH7" t="n">
-        <v>95.41</v>
+        <v>94.5</v>
       </c>
       <c r="DI7" t="n">
         <v>0</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="DK7" t="n">
-        <v>3.41</v>
+        <v>3.66</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM7" t="n">
-        <v>53.88</v>
+        <v>53.83</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="DO7" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="DP7" t="n">
-        <v>6.53</v>
+        <v>6.11</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="DR7" t="n">
-        <v>4.65</v>
+        <v>4.33</v>
       </c>
       <c r="DS7" t="n">
         <v>0.06</v>
@@ -3754,28 +3754,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>52.77</v>
+        <v>53.17</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DX7" t="n">
-        <v>9.119999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DY7" t="n">
-        <v>5.41</v>
+        <v>5.44</v>
       </c>
       <c r="DZ7" t="n">
-        <v>3.7</v>
+        <v>3.83</v>
       </c>
       <c r="EA7" t="n">
-        <v>14.35</v>
+        <v>13.5</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="8">
@@ -5117,13 +5117,13 @@
         <v>1.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7.8</v>
+        <v>9.1</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT11" t="n">
         <v>1</v>
@@ -5141,25 +5141,25 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>50.1</v>
+        <v>49</v>
       </c>
       <c r="AZ11" t="n">
         <v>0.1</v>
       </c>
       <c r="BA11" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="BC11" t="n">
         <v>4.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>17.2</v>
+        <v>19.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="BF11" t="n">
         <v>2.6</v>
@@ -5348,13 +5348,13 @@
         <v>1.67</v>
       </c>
       <c r="DP11" t="n">
-        <v>9.67</v>
+        <v>10.39</v>
       </c>
       <c r="DQ11" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="DR11" t="n">
-        <v>7.56</v>
+        <v>8.06</v>
       </c>
       <c r="DS11" t="n">
         <v>0.11</v>
@@ -5366,22 +5366,22 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>51.28</v>
+        <v>50.67</v>
       </c>
       <c r="DW11" t="n">
         <v>0.28</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.11</v>
+        <v>11.16</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.11</v>
+        <v>7.17</v>
       </c>
       <c r="DZ11" t="n">
         <v>4</v>
       </c>
       <c r="EA11" t="n">
-        <v>18.78</v>
+        <v>19.89</v>
       </c>
       <c r="EB11" t="n">
         <v>1.38</v>
@@ -5842,13 +5842,13 @@
         <v>2.4</v>
       </c>
       <c r="P13" t="n">
-        <v>10.5</v>
+        <v>11.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="S13" t="n">
         <v>1.3</v>
@@ -5866,25 +5866,25 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>54.3</v>
+        <v>54.6</v>
       </c>
       <c r="Y13" t="n">
         <v>0.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>13.8</v>
+        <v>15.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AB13" t="n">
         <v>6.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>18.6</v>
+        <v>21.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AE13" t="n">
         <v>3</v>
@@ -6154,13 +6154,13 @@
         <v>2.28</v>
       </c>
       <c r="DP13" t="n">
-        <v>10.67</v>
+        <v>11.28</v>
       </c>
       <c r="DQ13" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="DR13" t="n">
-        <v>7.72</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DS13" t="n">
         <v>0.11</v>
@@ -6172,25 +6172,25 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>53.61</v>
+        <v>53.78</v>
       </c>
       <c r="DW13" t="n">
         <v>0.44</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.56</v>
+        <v>15.39</v>
       </c>
       <c r="DY13" t="n">
-        <v>9</v>
+        <v>9.83</v>
       </c>
       <c r="DZ13" t="n">
         <v>5.56</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.78</v>
+        <v>23.44</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="EC13" t="n">
         <v>2.83</v>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -7424,82 +7424,82 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="G17" t="n">
-        <v>3.22</v>
+        <v>3.1</v>
       </c>
       <c r="H17" t="n">
-        <v>90.78</v>
+        <v>88</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="K17" t="n">
-        <v>5.22</v>
+        <v>4.9</v>
       </c>
       <c r="L17" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M17" t="n">
-        <v>55.56</v>
+        <v>53.3</v>
       </c>
       <c r="N17" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="P17" t="n">
-        <v>9.33</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.33</v>
+        <v>1.1</v>
       </c>
       <c r="R17" t="n">
-        <v>6.78</v>
+        <v>6</v>
       </c>
       <c r="S17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="T17" t="n">
         <v>1</v>
       </c>
-      <c r="T17" t="n">
-        <v>1.11</v>
-      </c>
       <c r="U17" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="V17" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>44.89</v>
+        <v>44.4</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>10.33</v>
+        <v>10.1</v>
       </c>
       <c r="AA17" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="AB17" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="AC17" t="n">
-        <v>14.89</v>
+        <v>13.3</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="AF17" t="n">
         <v>0.22</v>
@@ -7583,70 +7583,70 @@
         <v>3.22</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="BH17" t="n">
-        <v>9.17</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.44</v>
+        <v>4.26</v>
       </c>
       <c r="BQ17" t="n">
-        <v>4.72</v>
+        <v>4.95</v>
       </c>
       <c r="BR17" t="n">
-        <v>88.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>72.22</v>
+        <v>68.42</v>
       </c>
       <c r="BT17" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BU17" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV17" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW17" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX17" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BY17" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="BZ17" t="n">
-        <v>3.35</v>
+        <v>3.24</v>
       </c>
       <c r="CA17" t="n">
         <v>3.14</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CC17" t="n">
         <v>3.31</v>
@@ -7658,13 +7658,13 @@
         <v>1.4</v>
       </c>
       <c r="CF17" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CG17" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CI17" t="n">
         <v>1.66</v>
@@ -7673,25 +7673,25 @@
         <v>1.84</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CL17" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CM17" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CN17" t="n">
         <v>1.58</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CP17" t="n">
         <v>2.31</v>
       </c>
       <c r="CQ17" t="n">
-        <v>4.13</v>
+        <v>4.15</v>
       </c>
       <c r="CR17" t="n">
         <v>1.52</v>
@@ -7733,79 +7733,79 @@
         <v>4.63</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DH17" t="n">
-        <v>96.44</v>
+        <v>94.68000000000001</v>
       </c>
       <c r="DI17" t="n">
         <v>0</v>
       </c>
       <c r="DJ17" t="n">
-        <v>3.34</v>
+        <v>3.21</v>
       </c>
       <c r="DK17" t="n">
-        <v>4.66</v>
+        <v>4.53</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="DM17" t="n">
-        <v>60.72</v>
+        <v>59.26</v>
       </c>
       <c r="DN17" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.16</v>
+        <v>2.05</v>
       </c>
       <c r="DP17" t="n">
-        <v>8.27</v>
+        <v>7.79</v>
       </c>
       <c r="DQ17" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="DR17" t="n">
-        <v>5.67</v>
+        <v>5.32</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>47.39</v>
+        <v>47</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DX17" t="n">
-        <v>10.94</v>
+        <v>10.79</v>
       </c>
       <c r="DY17" t="n">
-        <v>6.78</v>
+        <v>6.79</v>
       </c>
       <c r="DZ17" t="n">
-        <v>4.16</v>
+        <v>4</v>
       </c>
       <c r="EA17" t="n">
-        <v>13.23</v>
+        <v>12.48</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="EC17" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
     </row>
   </sheetData>
